--- a/res/fonts/sortingOrder.xlsx
+++ b/res/fonts/sortingOrder.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/c43/res/fonts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D1EF37-435F-4E4A-BBCA-C26760C11D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B747BC-E483-2B44-B015-A613396B4BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="sortingOrder" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="table">sortingOrder!$A$1:$I$1071</definedName>
+    <definedName name="table">sortingOrder!$A$1:$I$1077</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2739" uniqueCount="2007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="2025">
   <si>
     <t>Code point</t>
   </si>
@@ -6157,6 +6157,60 @@
   </si>
   <si>
     <t>U+24EA</t>
+  </si>
+  <si>
+    <t>U+2610</t>
+  </si>
+  <si>
+    <t>U+2612</t>
+  </si>
+  <si>
+    <t>U+25ef</t>
+  </si>
+  <si>
+    <t>U+29bf</t>
+  </si>
+  <si>
+    <t>U+25c7</t>
+  </si>
+  <si>
+    <t>U+25c8</t>
+  </si>
+  <si>
+    <t>BALLOT BOX (empty checkbox)</t>
+  </si>
+  <si>
+    <t>BALLOT BOX WITH X (checkbox with X)</t>
+  </si>
+  <si>
+    <t>LARGE CIRCLE (large outline circle)</t>
+  </si>
+  <si>
+    <t>CIRCLED BULLET (circle with filled center dot)</t>
+  </si>
+  <si>
+    <t>BLACK CIRCLE (filled circle)</t>
+  </si>
+  <si>
+    <t>WHITE DIAMOND CONTAINING BLACK SMALL DIAMOND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CB_OFF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CB_ON  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RB_OFF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RB_ON  </t>
+  </si>
+  <si>
+    <t>DIA_OFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIA_ON </t>
   </si>
 </sst>
 </file>
@@ -6244,7 +6298,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6254,6 +6308,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6270,7 +6330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6306,6 +6366,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6439,7 +6502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K708"/>
+  <dimension ref="A1:K714"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.5" style="1" customWidth="1"/>
@@ -6493,7 +6556,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="5">
-        <f>IF(ISNA(VLOOKUP(H2,$A$2:$C$1005,3,1)),C2,VLOOKUP(H2,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H2,$A$2:$C$1011,3,1)),C2,VLOOKUP(H2,$A$2:$C$1011,3,1))</f>
         <v>1</v>
       </c>
       <c r="C2" s="1">
@@ -6529,7 +6592,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5">
-        <f>IF(ISNA(VLOOKUP(H3,$A$2:$C$1005,3,1)),C3,VLOOKUP(H3,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H3,$A$2:$C$1011,3,1)),C3,VLOOKUP(H3,$A$2:$C$1011,3,1))</f>
         <v>536</v>
       </c>
       <c r="C3" s="1">
@@ -6565,7 +6628,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="5">
-        <f>IF(ISNA(VLOOKUP(H4,$A$2:$C$1005,3,1)),C4,VLOOKUP(H4,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H4,$A$2:$C$1011,3,1)),C4,VLOOKUP(H4,$A$2:$C$1011,3,1))</f>
         <v>550</v>
       </c>
       <c r="C4" s="1">
@@ -6598,11 +6661,11 @@
         <v>18</v>
       </c>
       <c r="B5" s="5">
-        <f>IF(ISNA(VLOOKUP(H5,$A$2:$C$1005,3,1)),C5,VLOOKUP(H5,$A$2:$C$1005,3,1))</f>
-        <v>654</v>
+        <f>IF(ISNA(VLOOKUP(H5,$A$2:$C$1011,3,1)),C5,VLOOKUP(H5,$A$2:$C$1011,3,1))</f>
+        <v>660</v>
       </c>
       <c r="C5" s="1">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>19</v>
@@ -6618,8 +6681,9 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A5,3,4)))</f>
         <v>#</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>18</v>
+      <c r="H5" s="17" t="str">
+        <f>A5</f>
+        <v>U+0023</v>
       </c>
       <c r="I5" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H5,3,4)))</f>
@@ -6634,7 +6698,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="5">
-        <f>IF(ISNA(VLOOKUP(H6,$A$2:$C$1005,3,1)),C6,VLOOKUP(H6,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H6,$A$2:$C$1011,3,1)),C6,VLOOKUP(H6,$A$2:$C$1011,3,1))</f>
         <v>614</v>
       </c>
       <c r="C6" s="1">
@@ -6670,7 +6734,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="5">
-        <f>IF(ISNA(VLOOKUP(H7,$A$2:$C$1005,3,1)),C7,VLOOKUP(H7,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H7,$A$2:$C$1011,3,1)),C7,VLOOKUP(H7,$A$2:$C$1011,3,1))</f>
         <v>614</v>
       </c>
       <c r="C7" s="1">
@@ -6706,7 +6770,7 @@
         <v>29</v>
       </c>
       <c r="B8" s="5">
-        <f>IF(ISNA(VLOOKUP(H8,$A$2:$C$1005,3,1)),C8,VLOOKUP(H8,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H8,$A$2:$C$1011,3,1)),C8,VLOOKUP(H8,$A$2:$C$1011,3,1))</f>
         <v>594</v>
       </c>
       <c r="C8" s="1">
@@ -6739,7 +6803,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="5">
-        <f>IF(ISNA(VLOOKUP(H9,$A$2:$C$1005,3,1)),C9,VLOOKUP(H9,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H9,$A$2:$C$1011,3,1)),C9,VLOOKUP(H9,$A$2:$C$1011,3,1))</f>
         <v>544</v>
       </c>
       <c r="C9" s="1">
@@ -6775,7 +6839,7 @@
         <v>36</v>
       </c>
       <c r="B10" s="5">
-        <f>IF(ISNA(VLOOKUP(H10,$A$2:$C$1005,3,1)),C10,VLOOKUP(H10,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H10,$A$2:$C$1011,3,1)),C10,VLOOKUP(H10,$A$2:$C$1011,3,1))</f>
         <v>494</v>
       </c>
       <c r="C10" s="1">
@@ -6811,7 +6875,7 @@
         <v>40</v>
       </c>
       <c r="B11" s="5">
-        <f>IF(ISNA(VLOOKUP(H11,$A$2:$C$1005,3,1)),C11,VLOOKUP(H11,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H11,$A$2:$C$1011,3,1)),C11,VLOOKUP(H11,$A$2:$C$1011,3,1))</f>
         <v>494</v>
       </c>
       <c r="C11" s="1">
@@ -6847,7 +6911,7 @@
         <v>44</v>
       </c>
       <c r="B12" s="5">
-        <f>IF(ISNA(VLOOKUP(H12,$A$2:$C$1005,3,1)),C12,VLOOKUP(H12,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H12,$A$2:$C$1011,3,1)),C12,VLOOKUP(H12,$A$2:$C$1011,3,1))</f>
         <v>519</v>
       </c>
       <c r="C12" s="1">
@@ -6880,7 +6944,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="5">
-        <f>IF(ISNA(VLOOKUP(H13,$A$2:$C$1005,3,1)),C13,VLOOKUP(H13,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H13,$A$2:$C$1011,3,1)),C13,VLOOKUP(H13,$A$2:$C$1011,3,1))</f>
         <v>510</v>
       </c>
       <c r="C13" s="1">
@@ -6916,7 +6980,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="5">
-        <f>IF(ISNA(VLOOKUP(H14,$A$2:$C$1005,3,1)),C14,VLOOKUP(H14,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H14,$A$2:$C$1011,3,1)),C14,VLOOKUP(H14,$A$2:$C$1011,3,1))</f>
         <v>528</v>
       </c>
       <c r="C14" s="1">
@@ -6952,7 +7016,7 @@
         <v>55</v>
       </c>
       <c r="B15" s="5">
-        <f>IF(ISNA(VLOOKUP(H15,$A$2:$C$1005,3,1)),C15,VLOOKUP(H15,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H15,$A$2:$C$1011,3,1)),C15,VLOOKUP(H15,$A$2:$C$1011,3,1))</f>
         <v>514</v>
       </c>
       <c r="C15" s="1">
@@ -6988,7 +7052,7 @@
         <v>59</v>
       </c>
       <c r="B16" s="5">
-        <f>IF(ISNA(VLOOKUP(H16,$A$2:$C$1005,3,1)),C16,VLOOKUP(H16,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H16,$A$2:$C$1011,3,1)),C16,VLOOKUP(H16,$A$2:$C$1011,3,1))</f>
         <v>531</v>
       </c>
       <c r="C16" s="1">
@@ -7024,7 +7088,7 @@
         <v>63</v>
       </c>
       <c r="B17" s="5">
-        <f>IF(ISNA(VLOOKUP(H17,$A$2:$C$1005,3,1)),C17,VLOOKUP(H17,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H17,$A$2:$C$1011,3,1)),C17,VLOOKUP(H17,$A$2:$C$1011,3,1))</f>
         <v>525</v>
       </c>
       <c r="C17" s="1">
@@ -7060,7 +7124,7 @@
         <v>67</v>
       </c>
       <c r="B18" s="5">
-        <f>IF(ISNA(VLOOKUP(H18,$A$2:$C$1005,3,1)),C18,VLOOKUP(H18,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H18,$A$2:$C$1011,3,1)),C18,VLOOKUP(H18,$A$2:$C$1011,3,1))</f>
         <v>11</v>
       </c>
       <c r="C18" s="1">
@@ -7093,7 +7157,7 @@
         <v>70</v>
       </c>
       <c r="B19" s="5">
-        <f>IF(ISNA(VLOOKUP(H19,$A$2:$C$1005,3,1)),C19,VLOOKUP(H19,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H19,$A$2:$C$1011,3,1)),C19,VLOOKUP(H19,$A$2:$C$1011,3,1))</f>
         <v>18</v>
       </c>
       <c r="C19" s="1">
@@ -7129,7 +7193,7 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <f>IF(ISNA(VLOOKUP(H20,$A$2:$C$1005,3,1)),C20,VLOOKUP(H20,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H20,$A$2:$C$1011,3,1)),C20,VLOOKUP(H20,$A$2:$C$1011,3,1))</f>
         <v>25</v>
       </c>
       <c r="C20" s="1">
@@ -7165,7 +7229,7 @@
         <v>76</v>
       </c>
       <c r="B21" s="5">
-        <f>IF(ISNA(VLOOKUP(H21,$A$2:$C$1005,3,1)),C21,VLOOKUP(H21,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H21,$A$2:$C$1011,3,1)),C21,VLOOKUP(H21,$A$2:$C$1011,3,1))</f>
         <v>29</v>
       </c>
       <c r="C21" s="1">
@@ -7201,7 +7265,7 @@
         <v>79</v>
       </c>
       <c r="B22" s="5">
-        <f>IF(ISNA(VLOOKUP(H22,$A$2:$C$1005,3,1)),C22,VLOOKUP(H22,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H22,$A$2:$C$1011,3,1)),C22,VLOOKUP(H22,$A$2:$C$1011,3,1))</f>
         <v>34</v>
       </c>
       <c r="C22" s="1">
@@ -7234,7 +7298,7 @@
         <v>83</v>
       </c>
       <c r="B23" s="5">
-        <f>IF(ISNA(VLOOKUP(H23,$A$2:$C$1005,3,1)),C23,VLOOKUP(H23,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H23,$A$2:$C$1011,3,1)),C23,VLOOKUP(H23,$A$2:$C$1011,3,1))</f>
         <v>38</v>
       </c>
       <c r="C23" s="1">
@@ -7270,7 +7334,7 @@
         <v>86</v>
       </c>
       <c r="B24" s="5">
-        <f>IF(ISNA(VLOOKUP(H24,$A$2:$C$1005,3,1)),C24,VLOOKUP(H24,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H24,$A$2:$C$1011,3,1)),C24,VLOOKUP(H24,$A$2:$C$1011,3,1))</f>
         <v>42</v>
       </c>
       <c r="C24" s="1">
@@ -7303,7 +7367,7 @@
         <v>89</v>
       </c>
       <c r="B25" s="5">
-        <f>IF(ISNA(VLOOKUP(H25,$A$2:$C$1005,3,1)),C25,VLOOKUP(H25,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H25,$A$2:$C$1011,3,1)),C25,VLOOKUP(H25,$A$2:$C$1011,3,1))</f>
         <v>46</v>
       </c>
       <c r="C25" s="1">
@@ -7336,7 +7400,7 @@
         <v>92</v>
       </c>
       <c r="B26" s="5">
-        <f>IF(ISNA(VLOOKUP(H26,$A$2:$C$1005,3,1)),C26,VLOOKUP(H26,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H26,$A$2:$C$1011,3,1)),C26,VLOOKUP(H26,$A$2:$C$1011,3,1))</f>
         <v>50</v>
       </c>
       <c r="C26" s="1">
@@ -7369,7 +7433,7 @@
         <v>95</v>
       </c>
       <c r="B27" s="5">
-        <f>IF(ISNA(VLOOKUP(H27,$A$2:$C$1005,3,1)),C27,VLOOKUP(H27,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H27,$A$2:$C$1011,3,1)),C27,VLOOKUP(H27,$A$2:$C$1011,3,1))</f>
         <v>54</v>
       </c>
       <c r="C27" s="1">
@@ -7402,7 +7466,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="5">
-        <f>IF(ISNA(VLOOKUP(H28,$A$2:$C$1005,3,1)),C28,VLOOKUP(H28,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H28,$A$2:$C$1011,3,1)),C28,VLOOKUP(H28,$A$2:$C$1011,3,1))</f>
         <v>540</v>
       </c>
       <c r="C28" s="1">
@@ -7435,7 +7499,7 @@
         <v>101</v>
       </c>
       <c r="B29" s="5">
-        <f>IF(ISNA(VLOOKUP(H29,$A$2:$C$1005,3,1)),C29,VLOOKUP(H29,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H29,$A$2:$C$1011,3,1)),C29,VLOOKUP(H29,$A$2:$C$1011,3,1))</f>
         <v>543</v>
       </c>
       <c r="C29" s="1">
@@ -7468,7 +7532,7 @@
         <v>104</v>
       </c>
       <c r="B30" s="5">
-        <f>IF(ISNA(VLOOKUP(H30,$A$2:$C$1005,3,1)),C30,VLOOKUP(H30,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H30,$A$2:$C$1011,3,1)),C30,VLOOKUP(H30,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C30" s="1">
@@ -7501,7 +7565,7 @@
         <v>108</v>
       </c>
       <c r="B31" s="5">
-        <f>IF(ISNA(VLOOKUP(H31,$A$2:$C$1005,3,1)),C31,VLOOKUP(H31,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H31,$A$2:$C$1011,3,1)),C31,VLOOKUP(H31,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C31" s="1">
@@ -7534,7 +7598,7 @@
         <v>111</v>
       </c>
       <c r="B32" s="5">
-        <f>IF(ISNA(VLOOKUP(H32,$A$2:$C$1005,3,1)),C32,VLOOKUP(H32,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H32,$A$2:$C$1011,3,1)),C32,VLOOKUP(H32,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C32" s="1">
@@ -7567,7 +7631,7 @@
         <v>114</v>
       </c>
       <c r="B33" s="5">
-        <f>IF(ISNA(VLOOKUP(H33,$A$2:$C$1005,3,1)),C33,VLOOKUP(H33,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H33,$A$2:$C$1011,3,1)),C33,VLOOKUP(H33,$A$2:$C$1011,3,1))</f>
         <v>538</v>
       </c>
       <c r="C33" s="1">
@@ -7600,7 +7664,7 @@
         <v>117</v>
       </c>
       <c r="B34" s="5">
-        <f>IF(ISNA(VLOOKUP(H34,$A$2:$C$1005,3,1)),C34,VLOOKUP(H34,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H34,$A$2:$C$1011,3,1)),C34,VLOOKUP(H34,$A$2:$C$1011,3,1))</f>
         <v>557</v>
       </c>
       <c r="C34" s="1">
@@ -7633,7 +7697,7 @@
         <v>120</v>
       </c>
       <c r="B35" s="5">
-        <f>IF(ISNA(VLOOKUP(H35,$A$2:$C$1005,3,1)),C35,VLOOKUP(H35,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H35,$A$2:$C$1011,3,1)),C35,VLOOKUP(H35,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C35" s="1">
@@ -7666,7 +7730,7 @@
         <v>123</v>
       </c>
       <c r="B36" s="5">
-        <f>IF(ISNA(VLOOKUP(H36,$A$2:$C$1005,3,1)),C36,VLOOKUP(H36,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H36,$A$2:$C$1011,3,1)),C36,VLOOKUP(H36,$A$2:$C$1011,3,1))</f>
         <v>92</v>
       </c>
       <c r="C36" s="1">
@@ -7699,7 +7763,7 @@
         <v>126</v>
       </c>
       <c r="B37" s="5">
-        <f>IF(ISNA(VLOOKUP(H37,$A$2:$C$1005,3,1)),C37,VLOOKUP(H37,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H37,$A$2:$C$1011,3,1)),C37,VLOOKUP(H37,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C37" s="1">
@@ -7732,7 +7796,7 @@
         <v>129</v>
       </c>
       <c r="B38" s="5">
-        <f>IF(ISNA(VLOOKUP(H38,$A$2:$C$1005,3,1)),C38,VLOOKUP(H38,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H38,$A$2:$C$1011,3,1)),C38,VLOOKUP(H38,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C38" s="1">
@@ -7765,7 +7829,7 @@
         <v>132</v>
       </c>
       <c r="B39" s="5">
-        <f>IF(ISNA(VLOOKUP(H39,$A$2:$C$1005,3,1)),C39,VLOOKUP(H39,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H39,$A$2:$C$1011,3,1)),C39,VLOOKUP(H39,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C39" s="1">
@@ -7798,7 +7862,7 @@
         <v>135</v>
       </c>
       <c r="B40" s="5">
-        <f>IF(ISNA(VLOOKUP(H40,$A$2:$C$1005,3,1)),C40,VLOOKUP(H40,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H40,$A$2:$C$1011,3,1)),C40,VLOOKUP(H40,$A$2:$C$1011,3,1))</f>
         <v>152</v>
       </c>
       <c r="C40" s="1">
@@ -7831,7 +7895,7 @@
         <v>138</v>
       </c>
       <c r="B41" s="5">
-        <f>IF(ISNA(VLOOKUP(H41,$A$2:$C$1005,3,1)),C41,VLOOKUP(H41,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H41,$A$2:$C$1011,3,1)),C41,VLOOKUP(H41,$A$2:$C$1011,3,1))</f>
         <v>161</v>
       </c>
       <c r="C41" s="1">
@@ -7864,7 +7928,7 @@
         <v>141</v>
       </c>
       <c r="B42" s="5">
-        <f>IF(ISNA(VLOOKUP(H42,$A$2:$C$1005,3,1)),C42,VLOOKUP(H42,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H42,$A$2:$C$1011,3,1)),C42,VLOOKUP(H42,$A$2:$C$1011,3,1))</f>
         <v>171</v>
       </c>
       <c r="C42" s="1">
@@ -7897,7 +7961,7 @@
         <v>144</v>
       </c>
       <c r="B43" s="5">
-        <f>IF(ISNA(VLOOKUP(H43,$A$2:$C$1005,3,1)),C43,VLOOKUP(H43,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H43,$A$2:$C$1011,3,1)),C43,VLOOKUP(H43,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C43" s="1">
@@ -7930,7 +7994,7 @@
         <v>147</v>
       </c>
       <c r="B44" s="5">
-        <f>IF(ISNA(VLOOKUP(H44,$A$2:$C$1005,3,1)),C44,VLOOKUP(H44,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H44,$A$2:$C$1011,3,1)),C44,VLOOKUP(H44,$A$2:$C$1011,3,1))</f>
         <v>205</v>
       </c>
       <c r="C44" s="1">
@@ -7963,7 +8027,7 @@
         <v>150</v>
       </c>
       <c r="B45" s="5">
-        <f>IF(ISNA(VLOOKUP(H45,$A$2:$C$1005,3,1)),C45,VLOOKUP(H45,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H45,$A$2:$C$1011,3,1)),C45,VLOOKUP(H45,$A$2:$C$1011,3,1))</f>
         <v>213</v>
       </c>
       <c r="C45" s="1">
@@ -7996,7 +8060,7 @@
         <v>153</v>
       </c>
       <c r="B46" s="5">
-        <f>IF(ISNA(VLOOKUP(H46,$A$2:$C$1005,3,1)),C46,VLOOKUP(H46,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H46,$A$2:$C$1011,3,1)),C46,VLOOKUP(H46,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C46" s="1">
@@ -8029,7 +8093,7 @@
         <v>156</v>
       </c>
       <c r="B47" s="5">
-        <f>IF(ISNA(VLOOKUP(H47,$A$2:$C$1005,3,1)),C47,VLOOKUP(H47,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H47,$A$2:$C$1011,3,1)),C47,VLOOKUP(H47,$A$2:$C$1011,3,1))</f>
         <v>233</v>
       </c>
       <c r="C47" s="1">
@@ -8062,7 +8126,7 @@
         <v>159</v>
       </c>
       <c r="B48" s="5">
-        <f>IF(ISNA(VLOOKUP(H48,$A$2:$C$1005,3,1)),C48,VLOOKUP(H48,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H48,$A$2:$C$1011,3,1)),C48,VLOOKUP(H48,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C48" s="1">
@@ -8095,7 +8159,7 @@
         <v>162</v>
       </c>
       <c r="B49" s="5">
-        <f>IF(ISNA(VLOOKUP(H49,$A$2:$C$1005,3,1)),C49,VLOOKUP(H49,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H49,$A$2:$C$1011,3,1)),C49,VLOOKUP(H49,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C49" s="1">
@@ -8128,7 +8192,7 @@
         <v>165</v>
       </c>
       <c r="B50" s="5">
-        <f>IF(ISNA(VLOOKUP(H50,$A$2:$C$1005,3,1)),C50,VLOOKUP(H50,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H50,$A$2:$C$1011,3,1)),C50,VLOOKUP(H50,$A$2:$C$1011,3,1))</f>
         <v>278</v>
       </c>
       <c r="C50" s="1">
@@ -8161,7 +8225,7 @@
         <v>168</v>
       </c>
       <c r="B51" s="5">
-        <f>IF(ISNA(VLOOKUP(H51,$A$2:$C$1005,3,1)),C51,VLOOKUP(H51,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H51,$A$2:$C$1011,3,1)),C51,VLOOKUP(H51,$A$2:$C$1011,3,1))</f>
         <v>284</v>
       </c>
       <c r="C51" s="1">
@@ -8194,7 +8258,7 @@
         <v>171</v>
       </c>
       <c r="B52" s="5">
-        <f>IF(ISNA(VLOOKUP(H52,$A$2:$C$1005,3,1)),C52,VLOOKUP(H52,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H52,$A$2:$C$1011,3,1)),C52,VLOOKUP(H52,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C52" s="1">
@@ -8227,7 +8291,7 @@
         <v>174</v>
       </c>
       <c r="B53" s="5">
-        <f>IF(ISNA(VLOOKUP(H53,$A$2:$C$1005,3,1)),C53,VLOOKUP(H53,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H53,$A$2:$C$1011,3,1)),C53,VLOOKUP(H53,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C53" s="1">
@@ -8260,7 +8324,7 @@
         <v>177</v>
       </c>
       <c r="B54" s="5">
-        <f>IF(ISNA(VLOOKUP(H54,$A$2:$C$1005,3,1)),C54,VLOOKUP(H54,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H54,$A$2:$C$1011,3,1)),C54,VLOOKUP(H54,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C54" s="1">
@@ -8293,7 +8357,7 @@
         <v>180</v>
       </c>
       <c r="B55" s="5">
-        <f>IF(ISNA(VLOOKUP(H55,$A$2:$C$1005,3,1)),C55,VLOOKUP(H55,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H55,$A$2:$C$1011,3,1)),C55,VLOOKUP(H55,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C55" s="1">
@@ -8326,7 +8390,7 @@
         <v>183</v>
       </c>
       <c r="B56" s="5">
-        <f>IF(ISNA(VLOOKUP(H56,$A$2:$C$1005,3,1)),C56,VLOOKUP(H56,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H56,$A$2:$C$1011,3,1)),C56,VLOOKUP(H56,$A$2:$C$1011,3,1))</f>
         <v>356</v>
       </c>
       <c r="C56" s="1">
@@ -8359,7 +8423,7 @@
         <v>186</v>
       </c>
       <c r="B57" s="5">
-        <f>IF(ISNA(VLOOKUP(H57,$A$2:$C$1005,3,1)),C57,VLOOKUP(H57,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H57,$A$2:$C$1011,3,1)),C57,VLOOKUP(H57,$A$2:$C$1011,3,1))</f>
         <v>364</v>
       </c>
       <c r="C57" s="1">
@@ -8392,7 +8456,7 @@
         <v>189</v>
       </c>
       <c r="B58" s="5">
-        <f>IF(ISNA(VLOOKUP(H58,$A$2:$C$1005,3,1)),C58,VLOOKUP(H58,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H58,$A$2:$C$1011,3,1)),C58,VLOOKUP(H58,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C58" s="1">
@@ -8425,7 +8489,7 @@
         <v>192</v>
       </c>
       <c r="B59" s="5">
-        <f>IF(ISNA(VLOOKUP(H59,$A$2:$C$1005,3,1)),C59,VLOOKUP(H59,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H59,$A$2:$C$1011,3,1)),C59,VLOOKUP(H59,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C59" s="1">
@@ -8458,7 +8522,7 @@
         <v>195</v>
       </c>
       <c r="B60" s="5">
-        <f>IF(ISNA(VLOOKUP(H60,$A$2:$C$1005,3,1)),C60,VLOOKUP(H60,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H60,$A$2:$C$1011,3,1)),C60,VLOOKUP(H60,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C60" s="1">
@@ -8491,7 +8555,7 @@
         <v>198</v>
       </c>
       <c r="B61" s="5">
-        <f>IF(ISNA(VLOOKUP(H61,$A$2:$C$1005,3,1)),C61,VLOOKUP(H61,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H61,$A$2:$C$1011,3,1)),C61,VLOOKUP(H61,$A$2:$C$1011,3,1))</f>
         <v>496</v>
       </c>
       <c r="C61" s="1">
@@ -8524,7 +8588,7 @@
         <v>201</v>
       </c>
       <c r="B62" s="5">
-        <f>IF(ISNA(VLOOKUP(H62,$A$2:$C$1005,3,1)),C62,VLOOKUP(H62,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H62,$A$2:$C$1011,3,1)),C62,VLOOKUP(H62,$A$2:$C$1011,3,1))</f>
         <v>525</v>
       </c>
       <c r="C62" s="1">
@@ -8557,7 +8621,7 @@
         <v>204</v>
       </c>
       <c r="B63" s="5">
-        <f>IF(ISNA(VLOOKUP(H63,$A$2:$C$1005,3,1)),C63,VLOOKUP(H63,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H63,$A$2:$C$1011,3,1)),C63,VLOOKUP(H63,$A$2:$C$1011,3,1))</f>
         <v>496</v>
       </c>
       <c r="C63" s="1">
@@ -8590,7 +8654,7 @@
         <v>207</v>
       </c>
       <c r="B64" s="5">
-        <f>IF(ISNA(VLOOKUP(H64,$A$2:$C$1005,3,1)),C64,VLOOKUP(H64,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H64,$A$2:$C$1011,3,1)),C64,VLOOKUP(H64,$A$2:$C$1011,3,1))</f>
         <v>527</v>
       </c>
       <c r="C64" s="1">
@@ -8623,7 +8687,7 @@
         <v>210</v>
       </c>
       <c r="B65" s="5">
-        <f>IF(ISNA(VLOOKUP(H65,$A$2:$C$1005,3,1)),C65,VLOOKUP(H65,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H65,$A$2:$C$1011,3,1)),C65,VLOOKUP(H65,$A$2:$C$1011,3,1))</f>
         <v>558</v>
       </c>
       <c r="C65" s="1">
@@ -8656,7 +8720,7 @@
         <v>213</v>
       </c>
       <c r="B66" s="5">
-        <f>IF(ISNA(VLOOKUP(H66,$A$2:$C$1005,3,1)),C66,VLOOKUP(H66,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H66,$A$2:$C$1011,3,1)),C66,VLOOKUP(H66,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C66" s="1">
@@ -8689,7 +8753,7 @@
         <v>216</v>
       </c>
       <c r="B67" s="5">
-        <f>IF(ISNA(VLOOKUP(H67,$A$2:$C$1005,3,1)),C67,VLOOKUP(H67,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H67,$A$2:$C$1011,3,1)),C67,VLOOKUP(H67,$A$2:$C$1011,3,1))</f>
         <v>92</v>
       </c>
       <c r="C67" s="1">
@@ -8722,7 +8786,7 @@
         <v>219</v>
       </c>
       <c r="B68" s="5">
-        <f>IF(ISNA(VLOOKUP(H68,$A$2:$C$1005,3,1)),C68,VLOOKUP(H68,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H68,$A$2:$C$1011,3,1)),C68,VLOOKUP(H68,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C68" s="1">
@@ -8755,7 +8819,7 @@
         <v>222</v>
       </c>
       <c r="B69" s="5">
-        <f>IF(ISNA(VLOOKUP(H69,$A$2:$C$1005,3,1)),C69,VLOOKUP(H69,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H69,$A$2:$C$1011,3,1)),C69,VLOOKUP(H69,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C69" s="1">
@@ -8788,7 +8852,7 @@
         <v>225</v>
       </c>
       <c r="B70" s="5">
-        <f>IF(ISNA(VLOOKUP(H70,$A$2:$C$1005,3,1)),C70,VLOOKUP(H70,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H70,$A$2:$C$1011,3,1)),C70,VLOOKUP(H70,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C70" s="1">
@@ -8821,7 +8885,7 @@
         <v>228</v>
       </c>
       <c r="B71" s="5">
-        <f>IF(ISNA(VLOOKUP(H71,$A$2:$C$1005,3,1)),C71,VLOOKUP(H71,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H71,$A$2:$C$1011,3,1)),C71,VLOOKUP(H71,$A$2:$C$1011,3,1))</f>
         <v>152</v>
       </c>
       <c r="C71" s="1">
@@ -8854,7 +8918,7 @@
         <v>231</v>
       </c>
       <c r="B72" s="5">
-        <f>IF(ISNA(VLOOKUP(H72,$A$2:$C$1005,3,1)),C72,VLOOKUP(H72,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H72,$A$2:$C$1011,3,1)),C72,VLOOKUP(H72,$A$2:$C$1011,3,1))</f>
         <v>161</v>
       </c>
       <c r="C72" s="1">
@@ -8887,7 +8951,7 @@
         <v>234</v>
       </c>
       <c r="B73" s="5">
-        <f>IF(ISNA(VLOOKUP(H73,$A$2:$C$1005,3,1)),C73,VLOOKUP(H73,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H73,$A$2:$C$1011,3,1)),C73,VLOOKUP(H73,$A$2:$C$1011,3,1))</f>
         <v>171</v>
       </c>
       <c r="C73" s="1">
@@ -8920,7 +8984,7 @@
         <v>237</v>
       </c>
       <c r="B74" s="5">
-        <f>IF(ISNA(VLOOKUP(H74,$A$2:$C$1005,3,1)),C74,VLOOKUP(H74,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H74,$A$2:$C$1011,3,1)),C74,VLOOKUP(H74,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C74" s="1">
@@ -8953,7 +9017,7 @@
         <v>240</v>
       </c>
       <c r="B75" s="5">
-        <f>IF(ISNA(VLOOKUP(H75,$A$2:$C$1005,3,1)),C75,VLOOKUP(H75,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H75,$A$2:$C$1011,3,1)),C75,VLOOKUP(H75,$A$2:$C$1011,3,1))</f>
         <v>205</v>
       </c>
       <c r="C75" s="1">
@@ -8986,7 +9050,7 @@
         <v>243</v>
       </c>
       <c r="B76" s="5">
-        <f>IF(ISNA(VLOOKUP(H76,$A$2:$C$1005,3,1)),C76,VLOOKUP(H76,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H76,$A$2:$C$1011,3,1)),C76,VLOOKUP(H76,$A$2:$C$1011,3,1))</f>
         <v>213</v>
       </c>
       <c r="C76" s="1">
@@ -9019,7 +9083,7 @@
         <v>246</v>
       </c>
       <c r="B77" s="5">
-        <f>IF(ISNA(VLOOKUP(H77,$A$2:$C$1005,3,1)),C77,VLOOKUP(H77,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H77,$A$2:$C$1011,3,1)),C77,VLOOKUP(H77,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C77" s="1">
@@ -9052,7 +9116,7 @@
         <v>249</v>
       </c>
       <c r="B78" s="5">
-        <f>IF(ISNA(VLOOKUP(H78,$A$2:$C$1005,3,1)),C78,VLOOKUP(H78,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H78,$A$2:$C$1011,3,1)),C78,VLOOKUP(H78,$A$2:$C$1011,3,1))</f>
         <v>233</v>
       </c>
       <c r="C78" s="1">
@@ -9085,7 +9149,7 @@
         <v>252</v>
       </c>
       <c r="B79" s="5">
-        <f>IF(ISNA(VLOOKUP(H79,$A$2:$C$1005,3,1)),C79,VLOOKUP(H79,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H79,$A$2:$C$1011,3,1)),C79,VLOOKUP(H79,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C79" s="1">
@@ -9118,7 +9182,7 @@
         <v>255</v>
       </c>
       <c r="B80" s="5">
-        <f>IF(ISNA(VLOOKUP(H80,$A$2:$C$1005,3,1)),C80,VLOOKUP(H80,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H80,$A$2:$C$1011,3,1)),C80,VLOOKUP(H80,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C80" s="1">
@@ -9151,7 +9215,7 @@
         <v>258</v>
       </c>
       <c r="B81" s="5">
-        <f>IF(ISNA(VLOOKUP(H81,$A$2:$C$1005,3,1)),C81,VLOOKUP(H81,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H81,$A$2:$C$1011,3,1)),C81,VLOOKUP(H81,$A$2:$C$1011,3,1))</f>
         <v>278</v>
       </c>
       <c r="C81" s="1">
@@ -9184,7 +9248,7 @@
         <v>261</v>
       </c>
       <c r="B82" s="5">
-        <f>IF(ISNA(VLOOKUP(H82,$A$2:$C$1005,3,1)),C82,VLOOKUP(H82,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H82,$A$2:$C$1011,3,1)),C82,VLOOKUP(H82,$A$2:$C$1011,3,1))</f>
         <v>284</v>
       </c>
       <c r="C82" s="1">
@@ -9217,7 +9281,7 @@
         <v>264</v>
       </c>
       <c r="B83" s="5">
-        <f>IF(ISNA(VLOOKUP(H83,$A$2:$C$1005,3,1)),C83,VLOOKUP(H83,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H83,$A$2:$C$1011,3,1)),C83,VLOOKUP(H83,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C83" s="1">
@@ -9250,7 +9314,7 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <f>IF(ISNA(VLOOKUP(H84,$A$2:$C$1005,3,1)),C84,VLOOKUP(H84,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H84,$A$2:$C$1011,3,1)),C84,VLOOKUP(H84,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C84" s="1">
@@ -9283,7 +9347,7 @@
         <v>270</v>
       </c>
       <c r="B85" s="5">
-        <f>IF(ISNA(VLOOKUP(H85,$A$2:$C$1005,3,1)),C85,VLOOKUP(H85,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H85,$A$2:$C$1011,3,1)),C85,VLOOKUP(H85,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C85" s="1">
@@ -9316,7 +9380,7 @@
         <v>273</v>
       </c>
       <c r="B86" s="5">
-        <f>IF(ISNA(VLOOKUP(H86,$A$2:$C$1005,3,1)),C86,VLOOKUP(H86,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H86,$A$2:$C$1011,3,1)),C86,VLOOKUP(H86,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C86" s="1">
@@ -9349,7 +9413,7 @@
         <v>276</v>
       </c>
       <c r="B87" s="5">
-        <f>IF(ISNA(VLOOKUP(H87,$A$2:$C$1005,3,1)),C87,VLOOKUP(H87,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H87,$A$2:$C$1011,3,1)),C87,VLOOKUP(H87,$A$2:$C$1011,3,1))</f>
         <v>356</v>
       </c>
       <c r="C87" s="1">
@@ -9382,7 +9446,7 @@
         <v>279</v>
       </c>
       <c r="B88" s="5">
-        <f>IF(ISNA(VLOOKUP(H88,$A$2:$C$1005,3,1)),C88,VLOOKUP(H88,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H88,$A$2:$C$1011,3,1)),C88,VLOOKUP(H88,$A$2:$C$1011,3,1))</f>
         <v>364</v>
       </c>
       <c r="C88" s="1">
@@ -9415,7 +9479,7 @@
         <v>282</v>
       </c>
       <c r="B89" s="5">
-        <f>IF(ISNA(VLOOKUP(H89,$A$2:$C$1005,3,1)),C89,VLOOKUP(H89,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H89,$A$2:$C$1011,3,1)),C89,VLOOKUP(H89,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C89" s="1">
@@ -9448,7 +9512,7 @@
         <v>285</v>
       </c>
       <c r="B90" s="5">
-        <f>IF(ISNA(VLOOKUP(H90,$A$2:$C$1005,3,1)),C90,VLOOKUP(H90,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H90,$A$2:$C$1011,3,1)),C90,VLOOKUP(H90,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C90" s="1">
@@ -9481,7 +9545,7 @@
         <v>288</v>
       </c>
       <c r="B91" s="5">
-        <f>IF(ISNA(VLOOKUP(H91,$A$2:$C$1005,3,1)),C91,VLOOKUP(H91,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H91,$A$2:$C$1011,3,1)),C91,VLOOKUP(H91,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C91" s="1">
@@ -9514,7 +9578,7 @@
         <v>291</v>
       </c>
       <c r="B92" s="5">
-        <f>IF(ISNA(VLOOKUP(H92,$A$2:$C$1005,3,1)),C92,VLOOKUP(H92,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H92,$A$2:$C$1011,3,1)),C92,VLOOKUP(H92,$A$2:$C$1011,3,1))</f>
         <v>504</v>
       </c>
       <c r="C92" s="1">
@@ -9547,7 +9611,7 @@
         <v>294</v>
       </c>
       <c r="B93" s="5">
-        <f>IF(ISNA(VLOOKUP(H93,$A$2:$C$1005,3,1)),C93,VLOOKUP(H93,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H93,$A$2:$C$1011,3,1)),C93,VLOOKUP(H93,$A$2:$C$1011,3,1))</f>
         <v>595</v>
       </c>
       <c r="C93" s="1">
@@ -9580,7 +9644,7 @@
         <v>297</v>
       </c>
       <c r="B94" s="5">
-        <f>IF(ISNA(VLOOKUP(H94,$A$2:$C$1005,3,1)),C94,VLOOKUP(H94,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H94,$A$2:$C$1011,3,1)),C94,VLOOKUP(H94,$A$2:$C$1011,3,1))</f>
         <v>504</v>
       </c>
       <c r="C94" s="1">
@@ -9613,7 +9677,7 @@
         <v>300</v>
       </c>
       <c r="B95" s="5">
-        <f>IF(ISNA(VLOOKUP(H95,$A$2:$C$1005,3,1)),C95,VLOOKUP(H95,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H95,$A$2:$C$1011,3,1)),C95,VLOOKUP(H95,$A$2:$C$1011,3,1))</f>
         <v>560</v>
       </c>
       <c r="C95" s="1">
@@ -9646,7 +9710,7 @@
         <v>303</v>
       </c>
       <c r="B96" s="5">
-        <f>IF(ISNA(VLOOKUP(H96,$A$2:$C$1005,3,1)),C96,VLOOKUP(H96,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H96,$A$2:$C$1011,3,1)),C96,VLOOKUP(H96,$A$2:$C$1011,3,1))</f>
         <v>11</v>
       </c>
       <c r="C96" s="1">
@@ -9679,7 +9743,7 @@
         <v>306</v>
       </c>
       <c r="B97" s="5">
-        <f>IF(ISNA(VLOOKUP(H97,$A$2:$C$1005,3,1)),C97,VLOOKUP(H97,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H97,$A$2:$C$1011,3,1)),C97,VLOOKUP(H97,$A$2:$C$1011,3,1))</f>
         <v>536</v>
       </c>
       <c r="C97" s="1">
@@ -9712,7 +9776,7 @@
         <v>309</v>
       </c>
       <c r="B98" s="5">
-        <f>IF(ISNA(VLOOKUP(H98,$A$2:$C$1005,3,1)),C98,VLOOKUP(H98,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H98,$A$2:$C$1011,3,1)),C98,VLOOKUP(H98,$A$2:$C$1011,3,1))</f>
         <v>614</v>
       </c>
       <c r="C98" s="1">
@@ -9745,7 +9809,7 @@
         <v>312</v>
       </c>
       <c r="B99" s="5">
-        <f>IF(ISNA(VLOOKUP(H99,$A$2:$C$1005,3,1)),C99,VLOOKUP(H99,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H99,$A$2:$C$1011,3,1)),C99,VLOOKUP(H99,$A$2:$C$1011,3,1))</f>
         <v>614</v>
       </c>
       <c r="C99" s="1">
@@ -9778,7 +9842,7 @@
         <v>315</v>
       </c>
       <c r="B100" s="5">
-        <f>IF(ISNA(VLOOKUP(H100,$A$2:$C$1005,3,1)),C100,VLOOKUP(H100,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H100,$A$2:$C$1011,3,1)),C100,VLOOKUP(H100,$A$2:$C$1011,3,1))</f>
         <v>614</v>
       </c>
       <c r="C100" s="1">
@@ -9811,7 +9875,7 @@
         <v>318</v>
       </c>
       <c r="B101" s="5">
-        <f>IF(ISNA(VLOOKUP(H101,$A$2:$C$1005,3,1)),C101,VLOOKUP(H101,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H101,$A$2:$C$1011,3,1)),C101,VLOOKUP(H101,$A$2:$C$1011,3,1))</f>
         <v>614</v>
       </c>
       <c r="C101" s="1">
@@ -9844,7 +9908,7 @@
         <v>321</v>
       </c>
       <c r="B102" s="5">
-        <f>IF(ISNA(VLOOKUP(H102,$A$2:$C$1005,3,1)),C102,VLOOKUP(H102,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H102,$A$2:$C$1011,3,1)),C102,VLOOKUP(H102,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C102" s="1">
@@ -9877,7 +9941,7 @@
         <v>324</v>
       </c>
       <c r="B103" s="5">
-        <f>IF(ISNA(VLOOKUP(H103,$A$2:$C$1005,3,1)),C103,VLOOKUP(H103,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H103,$A$2:$C$1011,3,1)),C103,VLOOKUP(H103,$A$2:$C$1011,3,1))</f>
         <v>550</v>
       </c>
       <c r="C103" s="1">
@@ -9910,7 +9974,7 @@
         <v>327</v>
       </c>
       <c r="B104" s="5">
-        <f>IF(ISNA(VLOOKUP(H104,$A$2:$C$1005,3,1)),C104,VLOOKUP(H104,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H104,$A$2:$C$1011,3,1)),C104,VLOOKUP(H104,$A$2:$C$1011,3,1))</f>
         <v>588</v>
       </c>
       <c r="C104" s="1">
@@ -9943,7 +10007,7 @@
         <v>330</v>
       </c>
       <c r="B105" s="5">
-        <f>IF(ISNA(VLOOKUP(H105,$A$2:$C$1005,3,1)),C105,VLOOKUP(H105,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H105,$A$2:$C$1011,3,1)),C105,VLOOKUP(H105,$A$2:$C$1011,3,1))</f>
         <v>11</v>
       </c>
       <c r="C105" s="1">
@@ -9976,7 +10040,7 @@
         <v>333</v>
       </c>
       <c r="B106" s="5">
-        <f>IF(ISNA(VLOOKUP(H106,$A$2:$C$1005,3,1)),C106,VLOOKUP(H106,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H106,$A$2:$C$1011,3,1)),C106,VLOOKUP(H106,$A$2:$C$1011,3,1))</f>
         <v>510</v>
       </c>
       <c r="C106" s="1">
@@ -10009,7 +10073,7 @@
         <v>336</v>
       </c>
       <c r="B107" s="5">
-        <f>IF(ISNA(VLOOKUP(H107,$A$2:$C$1005,3,1)),C107,VLOOKUP(H107,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H107,$A$2:$C$1011,3,1)),C107,VLOOKUP(H107,$A$2:$C$1011,3,1))</f>
         <v>448</v>
       </c>
       <c r="C107" s="1">
@@ -10042,7 +10106,7 @@
         <v>340</v>
       </c>
       <c r="B108" s="5">
-        <f>IF(ISNA(VLOOKUP(H108,$A$2:$C$1005,3,1)),C108,VLOOKUP(H108,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H108,$A$2:$C$1011,3,1)),C108,VLOOKUP(H108,$A$2:$C$1011,3,1))</f>
         <v>519</v>
       </c>
       <c r="C108" s="1">
@@ -10075,7 +10139,7 @@
         <v>343</v>
       </c>
       <c r="B109" s="5">
-        <f>IF(ISNA(VLOOKUP(H109,$A$2:$C$1005,3,1)),C109,VLOOKUP(H109,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H109,$A$2:$C$1011,3,1)),C109,VLOOKUP(H109,$A$2:$C$1011,3,1))</f>
         <v>550</v>
       </c>
       <c r="C109" s="1">
@@ -10108,7 +10172,7 @@
         <v>346</v>
       </c>
       <c r="B110" s="5">
-        <f>IF(ISNA(VLOOKUP(H110,$A$2:$C$1005,3,1)),C110,VLOOKUP(H110,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H110,$A$2:$C$1011,3,1)),C110,VLOOKUP(H110,$A$2:$C$1011,3,1))</f>
         <v>18</v>
       </c>
       <c r="C110" s="1">
@@ -10141,7 +10205,7 @@
         <v>349</v>
       </c>
       <c r="B111" s="5">
-        <f>IF(ISNA(VLOOKUP(H111,$A$2:$C$1005,3,1)),C111,VLOOKUP(H111,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H111,$A$2:$C$1011,3,1)),C111,VLOOKUP(H111,$A$2:$C$1011,3,1))</f>
         <v>18</v>
       </c>
       <c r="C111" s="1">
@@ -10174,7 +10238,7 @@
         <v>352</v>
       </c>
       <c r="B112" s="5">
-        <f>IF(ISNA(VLOOKUP(H112,$A$2:$C$1005,3,1)),C112,VLOOKUP(H112,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H112,$A$2:$C$1011,3,1)),C112,VLOOKUP(H112,$A$2:$C$1011,3,1))</f>
         <v>538</v>
       </c>
       <c r="C112" s="1">
@@ -10207,7 +10271,7 @@
         <v>355</v>
       </c>
       <c r="B113" s="5">
-        <f>IF(ISNA(VLOOKUP(H113,$A$2:$C$1005,3,1)),C113,VLOOKUP(H113,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H113,$A$2:$C$1011,3,1)),C113,VLOOKUP(H113,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C113" s="1">
@@ -10240,7 +10304,7 @@
         <v>358</v>
       </c>
       <c r="B114" s="5">
-        <f>IF(ISNA(VLOOKUP(H114,$A$2:$C$1005,3,1)),C114,VLOOKUP(H114,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H114,$A$2:$C$1011,3,1)),C114,VLOOKUP(H114,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C114" s="1">
@@ -10273,7 +10337,7 @@
         <v>361</v>
       </c>
       <c r="B115" s="5">
-        <f>IF(ISNA(VLOOKUP(H115,$A$2:$C$1005,3,1)),C115,VLOOKUP(H115,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H115,$A$2:$C$1011,3,1)),C115,VLOOKUP(H115,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C115" s="1">
@@ -10306,7 +10370,7 @@
         <v>364</v>
       </c>
       <c r="B116" s="5">
-        <f>IF(ISNA(VLOOKUP(H116,$A$2:$C$1005,3,1)),C116,VLOOKUP(H116,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H116,$A$2:$C$1011,3,1)),C116,VLOOKUP(H116,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C116" s="1">
@@ -10339,7 +10403,7 @@
         <v>367</v>
       </c>
       <c r="B117" s="5">
-        <f>IF(ISNA(VLOOKUP(H117,$A$2:$C$1005,3,1)),C117,VLOOKUP(H117,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H117,$A$2:$C$1011,3,1)),C117,VLOOKUP(H117,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C117" s="1">
@@ -10372,7 +10436,7 @@
         <v>370</v>
       </c>
       <c r="B118" s="5">
-        <f>IF(ISNA(VLOOKUP(H118,$A$2:$C$1005,3,1)),C118,VLOOKUP(H118,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H118,$A$2:$C$1011,3,1)),C118,VLOOKUP(H118,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C118" s="1">
@@ -10405,7 +10469,7 @@
         <v>373</v>
       </c>
       <c r="B119" s="5">
-        <f>IF(ISNA(VLOOKUP(H119,$A$2:$C$1005,3,1)),C119,VLOOKUP(H119,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H119,$A$2:$C$1011,3,1)),C119,VLOOKUP(H119,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C119" s="1">
@@ -10438,7 +10502,7 @@
         <v>376</v>
       </c>
       <c r="B120" s="5">
-        <f>IF(ISNA(VLOOKUP(H120,$A$2:$C$1005,3,1)),C120,VLOOKUP(H120,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H120,$A$2:$C$1011,3,1)),C120,VLOOKUP(H120,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C120" s="1">
@@ -10471,7 +10535,7 @@
         <v>379</v>
       </c>
       <c r="B121" s="5">
-        <f>IF(ISNA(VLOOKUP(H121,$A$2:$C$1005,3,1)),C121,VLOOKUP(H121,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H121,$A$2:$C$1011,3,1)),C121,VLOOKUP(H121,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C121" s="1">
@@ -10504,7 +10568,7 @@
         <v>382</v>
       </c>
       <c r="B122" s="5">
-        <f>IF(ISNA(VLOOKUP(H122,$A$2:$C$1005,3,1)),C122,VLOOKUP(H122,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H122,$A$2:$C$1011,3,1)),C122,VLOOKUP(H122,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C122" s="1">
@@ -10537,7 +10601,7 @@
         <v>385</v>
       </c>
       <c r="B123" s="5">
-        <f>IF(ISNA(VLOOKUP(H123,$A$2:$C$1005,3,1)),C123,VLOOKUP(H123,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H123,$A$2:$C$1011,3,1)),C123,VLOOKUP(H123,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C123" s="1">
@@ -10570,7 +10634,7 @@
         <v>388</v>
       </c>
       <c r="B124" s="5">
-        <f>IF(ISNA(VLOOKUP(H124,$A$2:$C$1005,3,1)),C124,VLOOKUP(H124,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H124,$A$2:$C$1011,3,1)),C124,VLOOKUP(H124,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C124" s="1">
@@ -10603,7 +10667,7 @@
         <v>391</v>
       </c>
       <c r="B125" s="5">
-        <f>IF(ISNA(VLOOKUP(H125,$A$2:$C$1005,3,1)),C125,VLOOKUP(H125,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H125,$A$2:$C$1011,3,1)),C125,VLOOKUP(H125,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C125" s="1">
@@ -10636,7 +10700,7 @@
         <v>394</v>
       </c>
       <c r="B126" s="5">
-        <f>IF(ISNA(VLOOKUP(H126,$A$2:$C$1005,3,1)),C126,VLOOKUP(H126,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H126,$A$2:$C$1011,3,1)),C126,VLOOKUP(H126,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C126" s="1">
@@ -10669,7 +10733,7 @@
         <v>397</v>
       </c>
       <c r="B127" s="5">
-        <f>IF(ISNA(VLOOKUP(H127,$A$2:$C$1005,3,1)),C127,VLOOKUP(H127,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H127,$A$2:$C$1011,3,1)),C127,VLOOKUP(H127,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C127" s="1">
@@ -10702,7 +10766,7 @@
         <v>400</v>
       </c>
       <c r="B128" s="5">
-        <f>IF(ISNA(VLOOKUP(H128,$A$2:$C$1005,3,1)),C128,VLOOKUP(H128,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H128,$A$2:$C$1011,3,1)),C128,VLOOKUP(H128,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C128" s="1">
@@ -10735,7 +10799,7 @@
         <v>403</v>
       </c>
       <c r="B129" s="5">
-        <f>IF(ISNA(VLOOKUP(H129,$A$2:$C$1005,3,1)),C129,VLOOKUP(H129,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H129,$A$2:$C$1011,3,1)),C129,VLOOKUP(H129,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C129" s="1">
@@ -10768,7 +10832,7 @@
         <v>406</v>
       </c>
       <c r="B130" s="5">
-        <f>IF(ISNA(VLOOKUP(H130,$A$2:$C$1005,3,1)),C130,VLOOKUP(H130,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H130,$A$2:$C$1011,3,1)),C130,VLOOKUP(H130,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C130" s="1">
@@ -10801,7 +10865,7 @@
         <v>410</v>
       </c>
       <c r="B131" s="5">
-        <f>IF(ISNA(VLOOKUP(H131,$A$2:$C$1005,3,1)),C131,VLOOKUP(H131,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H131,$A$2:$C$1011,3,1)),C131,VLOOKUP(H131,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C131" s="1">
@@ -10834,7 +10898,7 @@
         <v>413</v>
       </c>
       <c r="B132" s="5">
-        <f>IF(ISNA(VLOOKUP(H132,$A$2:$C$1005,3,1)),C132,VLOOKUP(H132,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H132,$A$2:$C$1011,3,1)),C132,VLOOKUP(H132,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C132" s="1">
@@ -10867,7 +10931,7 @@
         <v>416</v>
       </c>
       <c r="B133" s="5">
-        <f>IF(ISNA(VLOOKUP(H133,$A$2:$C$1005,3,1)),C133,VLOOKUP(H133,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H133,$A$2:$C$1011,3,1)),C133,VLOOKUP(H133,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C133" s="1">
@@ -10900,7 +10964,7 @@
         <v>419</v>
       </c>
       <c r="B134" s="5">
-        <f>IF(ISNA(VLOOKUP(H134,$A$2:$C$1005,3,1)),C134,VLOOKUP(H134,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H134,$A$2:$C$1011,3,1)),C134,VLOOKUP(H134,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C134" s="1">
@@ -10933,7 +10997,7 @@
         <v>422</v>
       </c>
       <c r="B135" s="5">
-        <f>IF(ISNA(VLOOKUP(H135,$A$2:$C$1005,3,1)),C135,VLOOKUP(H135,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H135,$A$2:$C$1011,3,1)),C135,VLOOKUP(H135,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C135" s="1">
@@ -10966,7 +11030,7 @@
         <v>47</v>
       </c>
       <c r="B136" s="5">
-        <f>IF(ISNA(VLOOKUP(H136,$A$2:$C$1005,3,1)),C136,VLOOKUP(H136,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H136,$A$2:$C$1011,3,1)),C136,VLOOKUP(H136,$A$2:$C$1011,3,1))</f>
         <v>519</v>
       </c>
       <c r="C136" s="1">
@@ -10999,7 +11063,7 @@
         <v>427</v>
       </c>
       <c r="B137" s="5">
-        <f>IF(ISNA(VLOOKUP(H137,$A$2:$C$1005,3,1)),C137,VLOOKUP(H137,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H137,$A$2:$C$1011,3,1)),C137,VLOOKUP(H137,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C137" s="1">
@@ -11032,7 +11096,7 @@
         <v>430</v>
       </c>
       <c r="B138" s="5">
-        <f>IF(ISNA(VLOOKUP(H138,$A$2:$C$1005,3,1)),C138,VLOOKUP(H138,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H138,$A$2:$C$1011,3,1)),C138,VLOOKUP(H138,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C138" s="1">
@@ -11065,7 +11129,7 @@
         <v>433</v>
       </c>
       <c r="B139" s="5">
-        <f>IF(ISNA(VLOOKUP(H139,$A$2:$C$1005,3,1)),C139,VLOOKUP(H139,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H139,$A$2:$C$1011,3,1)),C139,VLOOKUP(H139,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C139" s="1">
@@ -11098,7 +11162,7 @@
         <v>436</v>
       </c>
       <c r="B140" s="5">
-        <f>IF(ISNA(VLOOKUP(H140,$A$2:$C$1005,3,1)),C140,VLOOKUP(H140,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H140,$A$2:$C$1011,3,1)),C140,VLOOKUP(H140,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C140" s="1">
@@ -11131,7 +11195,7 @@
         <v>439</v>
       </c>
       <c r="B141" s="5">
-        <f>IF(ISNA(VLOOKUP(H141,$A$2:$C$1005,3,1)),C141,VLOOKUP(H141,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H141,$A$2:$C$1011,3,1)),C141,VLOOKUP(H141,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C141" s="1">
@@ -11164,7 +11228,7 @@
         <v>442</v>
       </c>
       <c r="B142" s="5">
-        <f>IF(ISNA(VLOOKUP(H142,$A$2:$C$1005,3,1)),C142,VLOOKUP(H142,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H142,$A$2:$C$1011,3,1)),C142,VLOOKUP(H142,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C142" s="1">
@@ -11197,7 +11261,7 @@
         <v>445</v>
       </c>
       <c r="B143" s="5">
-        <f>IF(ISNA(VLOOKUP(H143,$A$2:$C$1005,3,1)),C143,VLOOKUP(H143,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H143,$A$2:$C$1011,3,1)),C143,VLOOKUP(H143,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C143" s="1">
@@ -11230,7 +11294,7 @@
         <v>448</v>
       </c>
       <c r="B144" s="5">
-        <f>IF(ISNA(VLOOKUP(H144,$A$2:$C$1005,3,1)),C144,VLOOKUP(H144,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H144,$A$2:$C$1011,3,1)),C144,VLOOKUP(H144,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C144" s="1">
@@ -11263,7 +11327,7 @@
         <v>451</v>
       </c>
       <c r="B145" s="5">
-        <f>IF(ISNA(VLOOKUP(H145,$A$2:$C$1005,3,1)),C145,VLOOKUP(H145,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H145,$A$2:$C$1011,3,1)),C145,VLOOKUP(H145,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C145" s="1">
@@ -11296,7 +11360,7 @@
         <v>454</v>
       </c>
       <c r="B146" s="5">
-        <f>IF(ISNA(VLOOKUP(H146,$A$2:$C$1005,3,1)),C146,VLOOKUP(H146,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H146,$A$2:$C$1011,3,1)),C146,VLOOKUP(H146,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C146" s="1">
@@ -11329,7 +11393,7 @@
         <v>457</v>
       </c>
       <c r="B147" s="5">
-        <f>IF(ISNA(VLOOKUP(H147,$A$2:$C$1005,3,1)),C147,VLOOKUP(H147,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H147,$A$2:$C$1011,3,1)),C147,VLOOKUP(H147,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C147" s="1">
@@ -11362,7 +11426,7 @@
         <v>460</v>
       </c>
       <c r="B148" s="5">
-        <f>IF(ISNA(VLOOKUP(H148,$A$2:$C$1005,3,1)),C148,VLOOKUP(H148,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H148,$A$2:$C$1011,3,1)),C148,VLOOKUP(H148,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C148" s="1">
@@ -11395,7 +11459,7 @@
         <v>463</v>
       </c>
       <c r="B149" s="5">
-        <f>IF(ISNA(VLOOKUP(H149,$A$2:$C$1005,3,1)),C149,VLOOKUP(H149,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H149,$A$2:$C$1011,3,1)),C149,VLOOKUP(H149,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C149" s="1">
@@ -11428,7 +11492,7 @@
         <v>466</v>
       </c>
       <c r="B150" s="5">
-        <f>IF(ISNA(VLOOKUP(H150,$A$2:$C$1005,3,1)),C150,VLOOKUP(H150,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H150,$A$2:$C$1011,3,1)),C150,VLOOKUP(H150,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C150" s="1">
@@ -11461,7 +11525,7 @@
         <v>469</v>
       </c>
       <c r="B151" s="5">
-        <f>IF(ISNA(VLOOKUP(H151,$A$2:$C$1005,3,1)),C151,VLOOKUP(H151,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H151,$A$2:$C$1011,3,1)),C151,VLOOKUP(H151,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C151" s="1">
@@ -11494,7 +11558,7 @@
         <v>472</v>
       </c>
       <c r="B152" s="5">
-        <f>IF(ISNA(VLOOKUP(H152,$A$2:$C$1005,3,1)),C152,VLOOKUP(H152,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H152,$A$2:$C$1011,3,1)),C152,VLOOKUP(H152,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C152" s="1">
@@ -11527,7 +11591,7 @@
         <v>475</v>
       </c>
       <c r="B153" s="5">
-        <f>IF(ISNA(VLOOKUP(H153,$A$2:$C$1005,3,1)),C153,VLOOKUP(H153,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H153,$A$2:$C$1011,3,1)),C153,VLOOKUP(H153,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C153" s="1">
@@ -11560,7 +11624,7 @@
         <v>478</v>
       </c>
       <c r="B154" s="5">
-        <f>IF(ISNA(VLOOKUP(H154,$A$2:$C$1005,3,1)),C154,VLOOKUP(H154,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H154,$A$2:$C$1011,3,1)),C154,VLOOKUP(H154,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C154" s="1">
@@ -11593,7 +11657,7 @@
         <v>481</v>
       </c>
       <c r="B155" s="5">
-        <f>IF(ISNA(VLOOKUP(H155,$A$2:$C$1005,3,1)),C155,VLOOKUP(H155,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H155,$A$2:$C$1011,3,1)),C155,VLOOKUP(H155,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C155" s="1">
@@ -11626,7 +11690,7 @@
         <v>484</v>
       </c>
       <c r="B156" s="5">
-        <f>IF(ISNA(VLOOKUP(H156,$A$2:$C$1005,3,1)),C156,VLOOKUP(H156,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H156,$A$2:$C$1011,3,1)),C156,VLOOKUP(H156,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C156" s="1">
@@ -11660,7 +11724,7 @@
         <v>487</v>
       </c>
       <c r="B157" s="5">
-        <f>IF(ISNA(VLOOKUP(H157,$A$2:$C$1005,3,1)),C157,VLOOKUP(H157,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H157,$A$2:$C$1011,3,1)),C157,VLOOKUP(H157,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C157" s="1">
@@ -11695,7 +11759,7 @@
         <v>490</v>
       </c>
       <c r="B158" s="5">
-        <f>IF(ISNA(VLOOKUP(H158,$A$2:$C$1005,3,1)),C158,VLOOKUP(H158,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H158,$A$2:$C$1011,3,1)),C158,VLOOKUP(H158,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C158" s="1">
@@ -11728,7 +11792,7 @@
         <v>493</v>
       </c>
       <c r="B159" s="5">
-        <f>IF(ISNA(VLOOKUP(H159,$A$2:$C$1005,3,1)),C159,VLOOKUP(H159,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H159,$A$2:$C$1011,3,1)),C159,VLOOKUP(H159,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C159" s="1">
@@ -11761,7 +11825,7 @@
         <v>496</v>
       </c>
       <c r="B160" s="5">
-        <f>IF(ISNA(VLOOKUP(H160,$A$2:$C$1005,3,1)),C160,VLOOKUP(H160,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H160,$A$2:$C$1011,3,1)),C160,VLOOKUP(H160,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C160" s="1">
@@ -11794,7 +11858,7 @@
         <v>499</v>
       </c>
       <c r="B161" s="5">
-        <f>IF(ISNA(VLOOKUP(H161,$A$2:$C$1005,3,1)),C161,VLOOKUP(H161,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H161,$A$2:$C$1011,3,1)),C161,VLOOKUP(H161,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C161" s="1">
@@ -11827,7 +11891,7 @@
         <v>502</v>
       </c>
       <c r="B162" s="5">
-        <f>IF(ISNA(VLOOKUP(H162,$A$2:$C$1005,3,1)),C162,VLOOKUP(H162,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H162,$A$2:$C$1011,3,1)),C162,VLOOKUP(H162,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C162" s="1">
@@ -11860,7 +11924,7 @@
         <v>505</v>
       </c>
       <c r="B163" s="5">
-        <f>IF(ISNA(VLOOKUP(H163,$A$2:$C$1005,3,1)),C163,VLOOKUP(H163,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H163,$A$2:$C$1011,3,1)),C163,VLOOKUP(H163,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C163" s="1">
@@ -11893,7 +11957,7 @@
         <v>508</v>
       </c>
       <c r="B164" s="5">
-        <f>IF(ISNA(VLOOKUP(H164,$A$2:$C$1005,3,1)),C164,VLOOKUP(H164,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H164,$A$2:$C$1011,3,1)),C164,VLOOKUP(H164,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C164" s="1">
@@ -11926,7 +11990,7 @@
         <v>511</v>
       </c>
       <c r="B165" s="5">
-        <f>IF(ISNA(VLOOKUP(H165,$A$2:$C$1005,3,1)),C165,VLOOKUP(H165,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H165,$A$2:$C$1011,3,1)),C165,VLOOKUP(H165,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C165" s="1">
@@ -11959,7 +12023,7 @@
         <v>514</v>
       </c>
       <c r="B166" s="5">
-        <f>IF(ISNA(VLOOKUP(H166,$A$2:$C$1005,3,1)),C166,VLOOKUP(H166,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H166,$A$2:$C$1011,3,1)),C166,VLOOKUP(H166,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C166" s="1">
@@ -11992,7 +12056,7 @@
         <v>517</v>
       </c>
       <c r="B167" s="5">
-        <f>IF(ISNA(VLOOKUP(H167,$A$2:$C$1005,3,1)),C167,VLOOKUP(H167,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H167,$A$2:$C$1011,3,1)),C167,VLOOKUP(H167,$A$2:$C$1011,3,1))</f>
         <v>540</v>
       </c>
       <c r="C167" s="1">
@@ -12025,7 +12089,7 @@
         <v>520</v>
       </c>
       <c r="B168" s="5">
-        <f>IF(ISNA(VLOOKUP(H168,$A$2:$C$1005,3,1)),C168,VLOOKUP(H168,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H168,$A$2:$C$1011,3,1)),C168,VLOOKUP(H168,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C168" s="1">
@@ -12058,7 +12122,7 @@
         <v>523</v>
       </c>
       <c r="B169" s="5">
-        <f>IF(ISNA(VLOOKUP(H169,$A$2:$C$1005,3,1)),C169,VLOOKUP(H169,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H169,$A$2:$C$1011,3,1)),C169,VLOOKUP(H169,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C169" s="1">
@@ -12091,7 +12155,7 @@
         <v>526</v>
       </c>
       <c r="B170" s="5">
-        <f>IF(ISNA(VLOOKUP(H170,$A$2:$C$1005,3,1)),C170,VLOOKUP(H170,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H170,$A$2:$C$1011,3,1)),C170,VLOOKUP(H170,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C170" s="1">
@@ -12124,7 +12188,7 @@
         <v>529</v>
       </c>
       <c r="B171" s="5">
-        <f>IF(ISNA(VLOOKUP(H171,$A$2:$C$1005,3,1)),C171,VLOOKUP(H171,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H171,$A$2:$C$1011,3,1)),C171,VLOOKUP(H171,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C171" s="1">
@@ -12157,7 +12221,7 @@
         <v>532</v>
       </c>
       <c r="B172" s="5">
-        <f>IF(ISNA(VLOOKUP(H172,$A$2:$C$1005,3,1)),C172,VLOOKUP(H172,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H172,$A$2:$C$1011,3,1)),C172,VLOOKUP(H172,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C172" s="1">
@@ -12190,7 +12254,7 @@
         <v>535</v>
       </c>
       <c r="B173" s="5">
-        <f>IF(ISNA(VLOOKUP(H173,$A$2:$C$1005,3,1)),C173,VLOOKUP(H173,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H173,$A$2:$C$1011,3,1)),C173,VLOOKUP(H173,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C173" s="1">
@@ -12223,7 +12287,7 @@
         <v>538</v>
       </c>
       <c r="B174" s="5">
-        <f>IF(ISNA(VLOOKUP(H174,$A$2:$C$1005,3,1)),C174,VLOOKUP(H174,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H174,$A$2:$C$1011,3,1)),C174,VLOOKUP(H174,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C174" s="1">
@@ -12256,7 +12320,7 @@
         <v>541</v>
       </c>
       <c r="B175" s="5">
-        <f>IF(ISNA(VLOOKUP(H175,$A$2:$C$1005,3,1)),C175,VLOOKUP(H175,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H175,$A$2:$C$1011,3,1)),C175,VLOOKUP(H175,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C175" s="1">
@@ -12289,7 +12353,7 @@
         <v>544</v>
       </c>
       <c r="B176" s="5">
-        <f>IF(ISNA(VLOOKUP(H176,$A$2:$C$1005,3,1)),C176,VLOOKUP(H176,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H176,$A$2:$C$1011,3,1)),C176,VLOOKUP(H176,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C176" s="1">
@@ -12322,7 +12386,7 @@
         <v>547</v>
       </c>
       <c r="B177" s="5">
-        <f>IF(ISNA(VLOOKUP(H177,$A$2:$C$1005,3,1)),C177,VLOOKUP(H177,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H177,$A$2:$C$1011,3,1)),C177,VLOOKUP(H177,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C177" s="1">
@@ -12355,7 +12419,7 @@
         <v>550</v>
       </c>
       <c r="B178" s="5">
-        <f>IF(ISNA(VLOOKUP(H178,$A$2:$C$1005,3,1)),C178,VLOOKUP(H178,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H178,$A$2:$C$1011,3,1)),C178,VLOOKUP(H178,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C178" s="1">
@@ -12388,7 +12452,7 @@
         <v>553</v>
       </c>
       <c r="B179" s="5">
-        <f>IF(ISNA(VLOOKUP(H179,$A$2:$C$1005,3,1)),C179,VLOOKUP(H179,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H179,$A$2:$C$1011,3,1)),C179,VLOOKUP(H179,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C179" s="1">
@@ -12421,7 +12485,7 @@
         <v>556</v>
       </c>
       <c r="B180" s="5">
-        <f>IF(ISNA(VLOOKUP(H180,$A$2:$C$1005,3,1)),C180,VLOOKUP(H180,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H180,$A$2:$C$1011,3,1)),C180,VLOOKUP(H180,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C180" s="1">
@@ -12454,7 +12518,7 @@
         <v>559</v>
       </c>
       <c r="B181" s="5">
-        <f>IF(ISNA(VLOOKUP(H181,$A$2:$C$1005,3,1)),C181,VLOOKUP(H181,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H181,$A$2:$C$1011,3,1)),C181,VLOOKUP(H181,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C181" s="1">
@@ -12487,7 +12551,7 @@
         <v>562</v>
       </c>
       <c r="B182" s="5">
-        <f>IF(ISNA(VLOOKUP(H182,$A$2:$C$1005,3,1)),C182,VLOOKUP(H182,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H182,$A$2:$C$1011,3,1)),C182,VLOOKUP(H182,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C182" s="1">
@@ -12520,7 +12584,7 @@
         <v>565</v>
       </c>
       <c r="B183" s="5">
-        <f>IF(ISNA(VLOOKUP(H183,$A$2:$C$1005,3,1)),C183,VLOOKUP(H183,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H183,$A$2:$C$1011,3,1)),C183,VLOOKUP(H183,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C183" s="1">
@@ -12553,7 +12617,7 @@
         <v>568</v>
       </c>
       <c r="B184" s="5">
-        <f>IF(ISNA(VLOOKUP(H184,$A$2:$C$1005,3,1)),C184,VLOOKUP(H184,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H184,$A$2:$C$1011,3,1)),C184,VLOOKUP(H184,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C184" s="1">
@@ -12586,7 +12650,7 @@
         <v>571</v>
       </c>
       <c r="B185" s="5">
-        <f>IF(ISNA(VLOOKUP(H185,$A$2:$C$1005,3,1)),C185,VLOOKUP(H185,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H185,$A$2:$C$1011,3,1)),C185,VLOOKUP(H185,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C185" s="1">
@@ -12619,7 +12683,7 @@
         <v>574</v>
       </c>
       <c r="B186" s="5">
-        <f>IF(ISNA(VLOOKUP(H186,$A$2:$C$1005,3,1)),C186,VLOOKUP(H186,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H186,$A$2:$C$1011,3,1)),C186,VLOOKUP(H186,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C186" s="1">
@@ -12652,7 +12716,7 @@
         <v>577</v>
       </c>
       <c r="B187" s="5">
-        <f>IF(ISNA(VLOOKUP(H187,$A$2:$C$1005,3,1)),C187,VLOOKUP(H187,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H187,$A$2:$C$1011,3,1)),C187,VLOOKUP(H187,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C187" s="1">
@@ -12685,7 +12749,7 @@
         <v>580</v>
       </c>
       <c r="B188" s="5">
-        <f>IF(ISNA(VLOOKUP(H188,$A$2:$C$1005,3,1)),C188,VLOOKUP(H188,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H188,$A$2:$C$1011,3,1)),C188,VLOOKUP(H188,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C188" s="1">
@@ -12718,7 +12782,7 @@
         <v>583</v>
       </c>
       <c r="B189" s="5">
-        <f>IF(ISNA(VLOOKUP(H189,$A$2:$C$1005,3,1)),C189,VLOOKUP(H189,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H189,$A$2:$C$1011,3,1)),C189,VLOOKUP(H189,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C189" s="1">
@@ -12751,7 +12815,7 @@
         <v>586</v>
       </c>
       <c r="B190" s="5">
-        <f>IF(ISNA(VLOOKUP(H190,$A$2:$C$1005,3,1)),C190,VLOOKUP(H190,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H190,$A$2:$C$1011,3,1)),C190,VLOOKUP(H190,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C190" s="1">
@@ -12784,7 +12848,7 @@
         <v>589</v>
       </c>
       <c r="B191" s="5">
-        <f>IF(ISNA(VLOOKUP(H191,$A$2:$C$1005,3,1)),C191,VLOOKUP(H191,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H191,$A$2:$C$1011,3,1)),C191,VLOOKUP(H191,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C191" s="1">
@@ -12817,7 +12881,7 @@
         <v>592</v>
       </c>
       <c r="B192" s="5">
-        <f>IF(ISNA(VLOOKUP(H192,$A$2:$C$1005,3,1)),C192,VLOOKUP(H192,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H192,$A$2:$C$1011,3,1)),C192,VLOOKUP(H192,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C192" s="1">
@@ -12850,7 +12914,7 @@
         <v>595</v>
       </c>
       <c r="B193" s="5">
-        <f>IF(ISNA(VLOOKUP(H193,$A$2:$C$1005,3,1)),C193,VLOOKUP(H193,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H193,$A$2:$C$1011,3,1)),C193,VLOOKUP(H193,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C193" s="1">
@@ -12883,7 +12947,7 @@
         <v>598</v>
       </c>
       <c r="B194" s="5">
-        <f>IF(ISNA(VLOOKUP(H194,$A$2:$C$1005,3,1)),C194,VLOOKUP(H194,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H194,$A$2:$C$1011,3,1)),C194,VLOOKUP(H194,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C194" s="1">
@@ -12916,7 +12980,7 @@
         <v>601</v>
       </c>
       <c r="B195" s="5">
-        <f>IF(ISNA(VLOOKUP(H195,$A$2:$C$1005,3,1)),C195,VLOOKUP(H195,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H195,$A$2:$C$1011,3,1)),C195,VLOOKUP(H195,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C195" s="1">
@@ -12949,7 +13013,7 @@
         <v>604</v>
       </c>
       <c r="B196" s="5">
-        <f>IF(ISNA(VLOOKUP(H196,$A$2:$C$1005,3,1)),C196,VLOOKUP(H196,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H196,$A$2:$C$1011,3,1)),C196,VLOOKUP(H196,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C196" s="1">
@@ -12982,7 +13046,7 @@
         <v>607</v>
       </c>
       <c r="B197" s="5">
-        <f>IF(ISNA(VLOOKUP(H197,$A$2:$C$1005,3,1)),C197,VLOOKUP(H197,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H197,$A$2:$C$1011,3,1)),C197,VLOOKUP(H197,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C197" s="1">
@@ -13015,7 +13079,7 @@
         <v>610</v>
       </c>
       <c r="B198" s="5">
-        <f>IF(ISNA(VLOOKUP(H198,$A$2:$C$1005,3,1)),C198,VLOOKUP(H198,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H198,$A$2:$C$1011,3,1)),C198,VLOOKUP(H198,$A$2:$C$1011,3,1))</f>
         <v>161</v>
       </c>
       <c r="C198" s="1">
@@ -13048,7 +13112,7 @@
         <v>613</v>
       </c>
       <c r="B199" s="5">
-        <f>IF(ISNA(VLOOKUP(H199,$A$2:$C$1005,3,1)),C199,VLOOKUP(H199,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H199,$A$2:$C$1011,3,1)),C199,VLOOKUP(H199,$A$2:$C$1011,3,1))</f>
         <v>161</v>
       </c>
       <c r="C199" s="1">
@@ -13081,7 +13145,7 @@
         <v>616</v>
       </c>
       <c r="B200" s="5">
-        <f>IF(ISNA(VLOOKUP(H200,$A$2:$C$1005,3,1)),C200,VLOOKUP(H200,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H200,$A$2:$C$1011,3,1)),C200,VLOOKUP(H200,$A$2:$C$1011,3,1))</f>
         <v>171</v>
       </c>
       <c r="C200" s="1">
@@ -13114,7 +13178,7 @@
         <v>619</v>
       </c>
       <c r="B201" s="5">
-        <f>IF(ISNA(VLOOKUP(H201,$A$2:$C$1005,3,1)),C201,VLOOKUP(H201,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H201,$A$2:$C$1011,3,1)),C201,VLOOKUP(H201,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C201" s="1">
@@ -13147,7 +13211,7 @@
         <v>622</v>
       </c>
       <c r="B202" s="5">
-        <f>IF(ISNA(VLOOKUP(H202,$A$2:$C$1005,3,1)),C202,VLOOKUP(H202,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H202,$A$2:$C$1011,3,1)),C202,VLOOKUP(H202,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C202" s="1">
@@ -13180,7 +13244,7 @@
         <v>625</v>
       </c>
       <c r="B203" s="5">
-        <f>IF(ISNA(VLOOKUP(H203,$A$2:$C$1005,3,1)),C203,VLOOKUP(H203,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H203,$A$2:$C$1011,3,1)),C203,VLOOKUP(H203,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C203" s="1">
@@ -13213,7 +13277,7 @@
         <v>628</v>
       </c>
       <c r="B204" s="5">
-        <f>IF(ISNA(VLOOKUP(H204,$A$2:$C$1005,3,1)),C204,VLOOKUP(H204,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H204,$A$2:$C$1011,3,1)),C204,VLOOKUP(H204,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C204" s="1">
@@ -13246,7 +13310,7 @@
         <v>631</v>
       </c>
       <c r="B205" s="5">
-        <f>IF(ISNA(VLOOKUP(H205,$A$2:$C$1005,3,1)),C205,VLOOKUP(H205,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H205,$A$2:$C$1011,3,1)),C205,VLOOKUP(H205,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C205" s="1">
@@ -13279,7 +13343,7 @@
         <v>634</v>
       </c>
       <c r="B206" s="5">
-        <f>IF(ISNA(VLOOKUP(H206,$A$2:$C$1005,3,1)),C206,VLOOKUP(H206,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H206,$A$2:$C$1011,3,1)),C206,VLOOKUP(H206,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C206" s="1">
@@ -13312,7 +13376,7 @@
         <v>637</v>
       </c>
       <c r="B207" s="5">
-        <f>IF(ISNA(VLOOKUP(H207,$A$2:$C$1005,3,1)),C207,VLOOKUP(H207,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H207,$A$2:$C$1011,3,1)),C207,VLOOKUP(H207,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C207" s="1">
@@ -13345,7 +13409,7 @@
         <v>640</v>
       </c>
       <c r="B208" s="5">
-        <f>IF(ISNA(VLOOKUP(H208,$A$2:$C$1005,3,1)),C208,VLOOKUP(H208,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H208,$A$2:$C$1011,3,1)),C208,VLOOKUP(H208,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C208" s="1">
@@ -13380,7 +13444,7 @@
         <v>1990</v>
       </c>
       <c r="B209" s="13">
-        <f>IF(ISNA(VLOOKUP(H209,$A$2:$C$1005,3,1)),C209,VLOOKUP(H209,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H209,$A$2:$C$1011,3,1)),C209,VLOOKUP(H209,$A$2:$C$1011,3,1))</f>
         <v>205</v>
       </c>
       <c r="C209" s="1">
@@ -13416,7 +13480,7 @@
         <v>1991</v>
       </c>
       <c r="B210" s="13">
-        <f>IF(ISNA(VLOOKUP(H210,$A$2:$C$1005,3,1)),C210,VLOOKUP(H210,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H210,$A$2:$C$1011,3,1)),C210,VLOOKUP(H210,$A$2:$C$1011,3,1))</f>
         <v>213</v>
       </c>
       <c r="C210" s="1">
@@ -13453,7 +13517,7 @@
         <v>643</v>
       </c>
       <c r="B211" s="5">
-        <f>IF(ISNA(VLOOKUP(H211,$A$2:$C$1005,3,1)),C211,VLOOKUP(H211,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H211,$A$2:$C$1011,3,1)),C211,VLOOKUP(H211,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C211" s="1">
@@ -13486,7 +13550,7 @@
         <v>646</v>
       </c>
       <c r="B212" s="5">
-        <f>IF(ISNA(VLOOKUP(H212,$A$2:$C$1005,3,1)),C212,VLOOKUP(H212,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H212,$A$2:$C$1011,3,1)),C212,VLOOKUP(H212,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C212" s="1">
@@ -13519,7 +13583,7 @@
         <v>649</v>
       </c>
       <c r="B213" s="5">
-        <f>IF(ISNA(VLOOKUP(H213,$A$2:$C$1005,3,1)),C213,VLOOKUP(H213,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H213,$A$2:$C$1011,3,1)),C213,VLOOKUP(H213,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C213" s="1">
@@ -13552,7 +13616,7 @@
         <v>652</v>
       </c>
       <c r="B214" s="5">
-        <f>IF(ISNA(VLOOKUP(H214,$A$2:$C$1005,3,1)),C214,VLOOKUP(H214,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H214,$A$2:$C$1011,3,1)),C214,VLOOKUP(H214,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C214" s="1">
@@ -13585,7 +13649,7 @@
         <v>655</v>
       </c>
       <c r="B215" s="5">
-        <f>IF(ISNA(VLOOKUP(H215,$A$2:$C$1005,3,1)),C215,VLOOKUP(H215,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H215,$A$2:$C$1011,3,1)),C215,VLOOKUP(H215,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C215" s="1">
@@ -13618,7 +13682,7 @@
         <v>658</v>
       </c>
       <c r="B216" s="5">
-        <f>IF(ISNA(VLOOKUP(H216,$A$2:$C$1005,3,1)),C216,VLOOKUP(H216,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H216,$A$2:$C$1011,3,1)),C216,VLOOKUP(H216,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C216" s="1">
@@ -13651,7 +13715,7 @@
         <v>661</v>
       </c>
       <c r="B217" s="5">
-        <f>IF(ISNA(VLOOKUP(H217,$A$2:$C$1005,3,1)),C217,VLOOKUP(H217,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H217,$A$2:$C$1011,3,1)),C217,VLOOKUP(H217,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C217" s="1">
@@ -13684,7 +13748,7 @@
         <v>664</v>
       </c>
       <c r="B218" s="5">
-        <f>IF(ISNA(VLOOKUP(H218,$A$2:$C$1005,3,1)),C218,VLOOKUP(H218,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H218,$A$2:$C$1011,3,1)),C218,VLOOKUP(H218,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C218" s="1">
@@ -13717,7 +13781,7 @@
         <v>667</v>
       </c>
       <c r="B219" s="5">
-        <f>IF(ISNA(VLOOKUP(H219,$A$2:$C$1005,3,1)),C219,VLOOKUP(H219,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H219,$A$2:$C$1011,3,1)),C219,VLOOKUP(H219,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C219" s="1">
@@ -13750,7 +13814,7 @@
         <v>670</v>
       </c>
       <c r="B220" s="5">
-        <f>IF(ISNA(VLOOKUP(H220,$A$2:$C$1005,3,1)),C220,VLOOKUP(H220,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H220,$A$2:$C$1011,3,1)),C220,VLOOKUP(H220,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C220" s="1">
@@ -13783,7 +13847,7 @@
         <v>673</v>
       </c>
       <c r="B221" s="5">
-        <f>IF(ISNA(VLOOKUP(H221,$A$2:$C$1005,3,1)),C221,VLOOKUP(H221,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H221,$A$2:$C$1011,3,1)),C221,VLOOKUP(H221,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C221" s="1">
@@ -13816,7 +13880,7 @@
         <v>676</v>
       </c>
       <c r="B222" s="5">
-        <f>IF(ISNA(VLOOKUP(H222,$A$2:$C$1005,3,1)),C222,VLOOKUP(H222,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H222,$A$2:$C$1011,3,1)),C222,VLOOKUP(H222,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C222" s="1">
@@ -13849,7 +13913,7 @@
         <v>679</v>
       </c>
       <c r="B223" s="5">
-        <f>IF(ISNA(VLOOKUP(H223,$A$2:$C$1005,3,1)),C223,VLOOKUP(H223,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H223,$A$2:$C$1011,3,1)),C223,VLOOKUP(H223,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C223" s="1">
@@ -13882,7 +13946,7 @@
         <v>682</v>
       </c>
       <c r="B224" s="5">
-        <f>IF(ISNA(VLOOKUP(H224,$A$2:$C$1005,3,1)),C224,VLOOKUP(H224,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H224,$A$2:$C$1011,3,1)),C224,VLOOKUP(H224,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C224" s="1">
@@ -13915,7 +13979,7 @@
         <v>685</v>
       </c>
       <c r="B225" s="5">
-        <f>IF(ISNA(VLOOKUP(H225,$A$2:$C$1005,3,1)),C225,VLOOKUP(H225,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H225,$A$2:$C$1011,3,1)),C225,VLOOKUP(H225,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C225" s="1">
@@ -13948,7 +14012,7 @@
         <v>688</v>
       </c>
       <c r="B226" s="5">
-        <f>IF(ISNA(VLOOKUP(H226,$A$2:$C$1005,3,1)),C226,VLOOKUP(H226,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H226,$A$2:$C$1011,3,1)),C226,VLOOKUP(H226,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C226" s="1">
@@ -13981,7 +14045,7 @@
         <v>691</v>
       </c>
       <c r="B227" s="5">
-        <f>IF(ISNA(VLOOKUP(H227,$A$2:$C$1005,3,1)),C227,VLOOKUP(H227,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H227,$A$2:$C$1011,3,1)),C227,VLOOKUP(H227,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C227" s="1">
@@ -14014,7 +14078,7 @@
         <v>694</v>
       </c>
       <c r="B228" s="5">
-        <f>IF(ISNA(VLOOKUP(H228,$A$2:$C$1005,3,1)),C228,VLOOKUP(H228,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H228,$A$2:$C$1011,3,1)),C228,VLOOKUP(H228,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C228" s="1">
@@ -14047,7 +14111,7 @@
         <v>697</v>
       </c>
       <c r="B229" s="5">
-        <f>IF(ISNA(VLOOKUP(H229,$A$2:$C$1005,3,1)),C229,VLOOKUP(H229,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H229,$A$2:$C$1011,3,1)),C229,VLOOKUP(H229,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C229" s="1">
@@ -14080,7 +14144,7 @@
         <v>700</v>
       </c>
       <c r="B230" s="5">
-        <f>IF(ISNA(VLOOKUP(H230,$A$2:$C$1005,3,1)),C230,VLOOKUP(H230,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H230,$A$2:$C$1011,3,1)),C230,VLOOKUP(H230,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C230" s="1">
@@ -14113,7 +14177,7 @@
         <v>703</v>
       </c>
       <c r="B231" s="5">
-        <f>IF(ISNA(VLOOKUP(H231,$A$2:$C$1005,3,1)),C231,VLOOKUP(H231,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H231,$A$2:$C$1011,3,1)),C231,VLOOKUP(H231,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C231" s="1">
@@ -14146,7 +14210,7 @@
         <v>706</v>
       </c>
       <c r="B232" s="5">
-        <f>IF(ISNA(VLOOKUP(H232,$A$2:$C$1005,3,1)),C232,VLOOKUP(H232,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H232,$A$2:$C$1011,3,1)),C232,VLOOKUP(H232,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C232" s="1">
@@ -14179,7 +14243,7 @@
         <v>709</v>
       </c>
       <c r="B233" s="5">
-        <f>IF(ISNA(VLOOKUP(H233,$A$2:$C$1005,3,1)),C233,VLOOKUP(H233,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H233,$A$2:$C$1011,3,1)),C233,VLOOKUP(H233,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C233" s="1">
@@ -14212,7 +14276,7 @@
         <v>712</v>
       </c>
       <c r="B234" s="5">
-        <f>IF(ISNA(VLOOKUP(H234,$A$2:$C$1005,3,1)),C234,VLOOKUP(H234,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H234,$A$2:$C$1011,3,1)),C234,VLOOKUP(H234,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C234" s="1">
@@ -14245,7 +14309,7 @@
         <v>715</v>
       </c>
       <c r="B235" s="5">
-        <f>IF(ISNA(VLOOKUP(H235,$A$2:$C$1005,3,1)),C235,VLOOKUP(H235,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H235,$A$2:$C$1011,3,1)),C235,VLOOKUP(H235,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C235" s="1">
@@ -14278,7 +14342,7 @@
         <v>718</v>
       </c>
       <c r="B236" s="5">
-        <f>IF(ISNA(VLOOKUP(H236,$A$2:$C$1005,3,1)),C236,VLOOKUP(H236,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H236,$A$2:$C$1011,3,1)),C236,VLOOKUP(H236,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C236" s="1">
@@ -14311,7 +14375,7 @@
         <v>721</v>
       </c>
       <c r="B237" s="5">
-        <f>IF(ISNA(VLOOKUP(H237,$A$2:$C$1005,3,1)),C237,VLOOKUP(H237,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H237,$A$2:$C$1011,3,1)),C237,VLOOKUP(H237,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C237" s="1">
@@ -14344,7 +14408,7 @@
         <v>724</v>
       </c>
       <c r="B238" s="5">
-        <f>IF(ISNA(VLOOKUP(H238,$A$2:$C$1005,3,1)),C238,VLOOKUP(H238,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H238,$A$2:$C$1011,3,1)),C238,VLOOKUP(H238,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C238" s="1">
@@ -14377,7 +14441,7 @@
         <v>727</v>
       </c>
       <c r="B239" s="5">
-        <f>IF(ISNA(VLOOKUP(H239,$A$2:$C$1005,3,1)),C239,VLOOKUP(H239,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H239,$A$2:$C$1011,3,1)),C239,VLOOKUP(H239,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C239" s="1">
@@ -14410,7 +14474,7 @@
         <v>730</v>
       </c>
       <c r="B240" s="5">
-        <f>IF(ISNA(VLOOKUP(H240,$A$2:$C$1005,3,1)),C240,VLOOKUP(H240,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H240,$A$2:$C$1011,3,1)),C240,VLOOKUP(H240,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C240" s="1">
@@ -14443,7 +14507,7 @@
         <v>733</v>
       </c>
       <c r="B241" s="5">
-        <f>IF(ISNA(VLOOKUP(H241,$A$2:$C$1005,3,1)),C241,VLOOKUP(H241,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H241,$A$2:$C$1011,3,1)),C241,VLOOKUP(H241,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C241" s="1">
@@ -14476,7 +14540,7 @@
         <v>736</v>
       </c>
       <c r="B242" s="5">
-        <f>IF(ISNA(VLOOKUP(H242,$A$2:$C$1005,3,1)),C242,VLOOKUP(H242,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H242,$A$2:$C$1011,3,1)),C242,VLOOKUP(H242,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C242" s="1">
@@ -14509,7 +14573,7 @@
         <v>739</v>
       </c>
       <c r="B243" s="5">
-        <f>IF(ISNA(VLOOKUP(H243,$A$2:$C$1005,3,1)),C243,VLOOKUP(H243,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H243,$A$2:$C$1011,3,1)),C243,VLOOKUP(H243,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C243" s="1">
@@ -14542,7 +14606,7 @@
         <v>742</v>
       </c>
       <c r="B244" s="5">
-        <f>IF(ISNA(VLOOKUP(H244,$A$2:$C$1005,3,1)),C244,VLOOKUP(H244,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H244,$A$2:$C$1011,3,1)),C244,VLOOKUP(H244,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C244" s="1">
@@ -14575,7 +14639,7 @@
         <v>745</v>
       </c>
       <c r="B245" s="5">
-        <f>IF(ISNA(VLOOKUP(H245,$A$2:$C$1005,3,1)),C245,VLOOKUP(H245,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H245,$A$2:$C$1011,3,1)),C245,VLOOKUP(H245,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C245" s="1">
@@ -14608,7 +14672,7 @@
         <v>748</v>
       </c>
       <c r="B246" s="5">
-        <f>IF(ISNA(VLOOKUP(H246,$A$2:$C$1005,3,1)),C246,VLOOKUP(H246,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H246,$A$2:$C$1011,3,1)),C246,VLOOKUP(H246,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C246" s="1">
@@ -14641,7 +14705,7 @@
         <v>751</v>
       </c>
       <c r="B247" s="5">
-        <f>IF(ISNA(VLOOKUP(H247,$A$2:$C$1005,3,1)),C247,VLOOKUP(H247,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H247,$A$2:$C$1011,3,1)),C247,VLOOKUP(H247,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C247" s="1">
@@ -14674,7 +14738,7 @@
         <v>754</v>
       </c>
       <c r="B248" s="5">
-        <f>IF(ISNA(VLOOKUP(H248,$A$2:$C$1005,3,1)),C248,VLOOKUP(H248,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H248,$A$2:$C$1011,3,1)),C248,VLOOKUP(H248,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C248" s="1">
@@ -14707,7 +14771,7 @@
         <v>757</v>
       </c>
       <c r="B249" s="5">
-        <f>IF(ISNA(VLOOKUP(H249,$A$2:$C$1005,3,1)),C249,VLOOKUP(H249,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H249,$A$2:$C$1011,3,1)),C249,VLOOKUP(H249,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C249" s="1">
@@ -14740,7 +14804,7 @@
         <v>760</v>
       </c>
       <c r="B250" s="5">
-        <f>IF(ISNA(VLOOKUP(H250,$A$2:$C$1005,3,1)),C250,VLOOKUP(H250,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H250,$A$2:$C$1011,3,1)),C250,VLOOKUP(H250,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C250" s="1">
@@ -14773,7 +14837,7 @@
         <v>763</v>
       </c>
       <c r="B251" s="5">
-        <f>IF(ISNA(VLOOKUP(H251,$A$2:$C$1005,3,1)),C251,VLOOKUP(H251,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H251,$A$2:$C$1011,3,1)),C251,VLOOKUP(H251,$A$2:$C$1011,3,1))</f>
         <v>364</v>
       </c>
       <c r="C251" s="1">
@@ -14806,7 +14870,7 @@
         <v>766</v>
       </c>
       <c r="B252" s="5">
-        <f>IF(ISNA(VLOOKUP(H252,$A$2:$C$1005,3,1)),C252,VLOOKUP(H252,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H252,$A$2:$C$1011,3,1)),C252,VLOOKUP(H252,$A$2:$C$1011,3,1))</f>
         <v>364</v>
       </c>
       <c r="C252" s="1">
@@ -14839,7 +14903,7 @@
         <v>769</v>
       </c>
       <c r="B253" s="5">
-        <f>IF(ISNA(VLOOKUP(H253,$A$2:$C$1005,3,1)),C253,VLOOKUP(H253,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H253,$A$2:$C$1011,3,1)),C253,VLOOKUP(H253,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C253" s="1">
@@ -14872,7 +14936,7 @@
         <v>772</v>
       </c>
       <c r="B254" s="5">
-        <f>IF(ISNA(VLOOKUP(H254,$A$2:$C$1005,3,1)),C254,VLOOKUP(H254,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H254,$A$2:$C$1011,3,1)),C254,VLOOKUP(H254,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C254" s="1">
@@ -14905,7 +14969,7 @@
         <v>775</v>
       </c>
       <c r="B255" s="5">
-        <f>IF(ISNA(VLOOKUP(H255,$A$2:$C$1005,3,1)),C255,VLOOKUP(H255,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H255,$A$2:$C$1011,3,1)),C255,VLOOKUP(H255,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C255" s="1">
@@ -14938,7 +15002,7 @@
         <v>778</v>
       </c>
       <c r="B256" s="5">
-        <f>IF(ISNA(VLOOKUP(H256,$A$2:$C$1005,3,1)),C256,VLOOKUP(H256,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H256,$A$2:$C$1011,3,1)),C256,VLOOKUP(H256,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C256" s="1">
@@ -14971,7 +15035,7 @@
         <v>781</v>
       </c>
       <c r="B257" s="5">
-        <f>IF(ISNA(VLOOKUP(H257,$A$2:$C$1005,3,1)),C257,VLOOKUP(H257,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H257,$A$2:$C$1011,3,1)),C257,VLOOKUP(H257,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C257" s="1">
@@ -15004,7 +15068,7 @@
         <v>784</v>
       </c>
       <c r="B258" s="5">
-        <f>IF(ISNA(VLOOKUP(H258,$A$2:$C$1005,3,1)),C258,VLOOKUP(H258,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H258,$A$2:$C$1011,3,1)),C258,VLOOKUP(H258,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C258" s="1">
@@ -15037,7 +15101,7 @@
         <v>787</v>
       </c>
       <c r="B259" s="5">
-        <f>IF(ISNA(VLOOKUP(H259,$A$2:$C$1005,3,1)),C259,VLOOKUP(H259,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H259,$A$2:$C$1011,3,1)),C259,VLOOKUP(H259,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C259" s="1">
@@ -15070,7 +15134,7 @@
         <v>790</v>
       </c>
       <c r="B260" s="5">
-        <f>IF(ISNA(VLOOKUP(H260,$A$2:$C$1005,3,1)),C260,VLOOKUP(H260,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H260,$A$2:$C$1011,3,1)),C260,VLOOKUP(H260,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C260" s="1">
@@ -15103,7 +15167,7 @@
         <v>793</v>
       </c>
       <c r="B261" s="5">
-        <f>IF(ISNA(VLOOKUP(H261,$A$2:$C$1005,3,1)),C261,VLOOKUP(H261,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H261,$A$2:$C$1011,3,1)),C261,VLOOKUP(H261,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C261" s="1">
@@ -15136,7 +15200,7 @@
         <v>796</v>
       </c>
       <c r="B262" s="5">
-        <f>IF(ISNA(VLOOKUP(H262,$A$2:$C$1005,3,1)),C262,VLOOKUP(H262,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H262,$A$2:$C$1011,3,1)),C262,VLOOKUP(H262,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C262" s="1">
@@ -15169,7 +15233,7 @@
         <v>799</v>
       </c>
       <c r="B263" s="5">
-        <f>IF(ISNA(VLOOKUP(H263,$A$2:$C$1005,3,1)),C263,VLOOKUP(H263,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H263,$A$2:$C$1011,3,1)),C263,VLOOKUP(H263,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C263" s="1">
@@ -15202,7 +15266,7 @@
         <v>802</v>
       </c>
       <c r="B264" s="5">
-        <f>IF(ISNA(VLOOKUP(H264,$A$2:$C$1005,3,1)),C264,VLOOKUP(H264,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H264,$A$2:$C$1011,3,1)),C264,VLOOKUP(H264,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C264" s="1">
@@ -15235,7 +15299,7 @@
         <v>805</v>
       </c>
       <c r="B265" s="5">
-        <f>IF(ISNA(VLOOKUP(H265,$A$2:$C$1005,3,1)),C265,VLOOKUP(H265,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H265,$A$2:$C$1011,3,1)),C265,VLOOKUP(H265,$A$2:$C$1011,3,1))</f>
         <v>171</v>
       </c>
       <c r="C265" s="1">
@@ -15268,7 +15332,7 @@
         <v>808</v>
       </c>
       <c r="B266" s="5">
-        <f>IF(ISNA(VLOOKUP(H266,$A$2:$C$1005,3,1)),C266,VLOOKUP(H266,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H266,$A$2:$C$1011,3,1)),C266,VLOOKUP(H266,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C266" s="1">
@@ -15301,7 +15365,7 @@
         <v>811</v>
       </c>
       <c r="B267" s="5">
-        <f>IF(ISNA(VLOOKUP(H267,$A$2:$C$1005,3,1)),C267,VLOOKUP(H267,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H267,$A$2:$C$1011,3,1)),C267,VLOOKUP(H267,$A$2:$C$1011,3,1))</f>
         <v>544</v>
       </c>
       <c r="C267" s="1">
@@ -15334,7 +15398,7 @@
         <v>814</v>
       </c>
       <c r="B268" s="5">
-        <f>IF(ISNA(VLOOKUP(H268,$A$2:$C$1005,3,1)),C268,VLOOKUP(H268,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H268,$A$2:$C$1011,3,1)),C268,VLOOKUP(H268,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C268" s="1">
@@ -15367,7 +15431,7 @@
         <v>817</v>
       </c>
       <c r="B269" s="5">
-        <f>IF(ISNA(VLOOKUP(H269,$A$2:$C$1005,3,1)),C269,VLOOKUP(H269,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H269,$A$2:$C$1011,3,1)),C269,VLOOKUP(H269,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C269" s="1">
@@ -15400,7 +15464,7 @@
         <v>819</v>
       </c>
       <c r="B270" s="5">
-        <f>IF(ISNA(VLOOKUP(H270,$A$2:$C$1005,3,1)),C270,VLOOKUP(H270,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H270,$A$2:$C$1011,3,1)),C270,VLOOKUP(H270,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C270" s="1">
@@ -15433,7 +15497,7 @@
         <v>821</v>
       </c>
       <c r="B271" s="5">
-        <f>IF(ISNA(VLOOKUP(H271,$A$2:$C$1005,3,1)),C271,VLOOKUP(H271,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H271,$A$2:$C$1011,3,1)),C271,VLOOKUP(H271,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C271" s="1">
@@ -15466,7 +15530,7 @@
         <v>824</v>
       </c>
       <c r="B272" s="5">
-        <f>IF(ISNA(VLOOKUP(H272,$A$2:$C$1005,3,1)),C272,VLOOKUP(H272,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H272,$A$2:$C$1011,3,1)),C272,VLOOKUP(H272,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C272" s="1">
@@ -15499,7 +15563,7 @@
         <v>825</v>
       </c>
       <c r="B273" s="5">
-        <f>IF(ISNA(VLOOKUP(H273,$A$2:$C$1005,3,1)),C273,VLOOKUP(H273,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H273,$A$2:$C$1011,3,1)),C273,VLOOKUP(H273,$A$2:$C$1011,3,1))</f>
         <v>356</v>
       </c>
       <c r="C273" s="1">
@@ -15532,7 +15596,7 @@
         <v>827</v>
       </c>
       <c r="B274" s="5">
-        <f>IF(ISNA(VLOOKUP(H274,$A$2:$C$1005,3,1)),C274,VLOOKUP(H274,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H274,$A$2:$C$1011,3,1)),C274,VLOOKUP(H274,$A$2:$C$1011,3,1))</f>
         <v>364</v>
       </c>
       <c r="C274" s="1">
@@ -15565,7 +15629,7 @@
         <v>829</v>
       </c>
       <c r="B275" s="5">
-        <f>IF(ISNA(VLOOKUP(H275,$A$2:$C$1005,3,1)),C275,VLOOKUP(H275,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H275,$A$2:$C$1011,3,1)),C275,VLOOKUP(H275,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C275" s="1">
@@ -15598,7 +15662,7 @@
         <v>831</v>
       </c>
       <c r="B276" s="5">
-        <f>IF(ISNA(VLOOKUP(H276,$A$2:$C$1005,3,1)),C276,VLOOKUP(H276,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H276,$A$2:$C$1011,3,1)),C276,VLOOKUP(H276,$A$2:$C$1011,3,1))</f>
         <v>356</v>
       </c>
       <c r="C276" s="1">
@@ -15631,7 +15695,7 @@
         <v>833</v>
       </c>
       <c r="B277" s="5">
-        <f>IF(ISNA(VLOOKUP(H277,$A$2:$C$1005,3,1)),C277,VLOOKUP(H277,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H277,$A$2:$C$1011,3,1)),C277,VLOOKUP(H277,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C277" s="1">
@@ -15664,7 +15728,7 @@
         <v>835</v>
       </c>
       <c r="B278" s="5">
-        <f>IF(ISNA(VLOOKUP(H278,$A$2:$C$1005,3,1)),C278,VLOOKUP(H278,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H278,$A$2:$C$1011,3,1)),C278,VLOOKUP(H278,$A$2:$C$1011,3,1))</f>
         <v>438</v>
       </c>
       <c r="C278" s="1">
@@ -15697,7 +15761,7 @@
         <v>839</v>
       </c>
       <c r="B279" s="5">
-        <f>IF(ISNA(VLOOKUP(H279,$A$2:$C$1005,3,1)),C279,VLOOKUP(H279,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H279,$A$2:$C$1011,3,1)),C279,VLOOKUP(H279,$A$2:$C$1011,3,1))</f>
         <v>415</v>
       </c>
       <c r="C279" s="1">
@@ -15730,7 +15794,7 @@
         <v>842</v>
       </c>
       <c r="B280" s="5">
-        <f>IF(ISNA(VLOOKUP(H280,$A$2:$C$1005,3,1)),C280,VLOOKUP(H280,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H280,$A$2:$C$1011,3,1)),C280,VLOOKUP(H280,$A$2:$C$1011,3,1))</f>
         <v>419</v>
       </c>
       <c r="C280" s="1">
@@ -15763,7 +15827,7 @@
         <v>845</v>
       </c>
       <c r="B281" s="5">
-        <f>IF(ISNA(VLOOKUP(H281,$A$2:$C$1005,3,1)),C281,VLOOKUP(H281,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H281,$A$2:$C$1011,3,1)),C281,VLOOKUP(H281,$A$2:$C$1011,3,1))</f>
         <v>421</v>
       </c>
       <c r="C281" s="1">
@@ -15796,7 +15860,7 @@
         <v>848</v>
       </c>
       <c r="B282" s="5">
-        <f>IF(ISNA(VLOOKUP(H282,$A$2:$C$1005,3,1)),C282,VLOOKUP(H282,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H282,$A$2:$C$1011,3,1)),C282,VLOOKUP(H282,$A$2:$C$1011,3,1))</f>
         <v>423</v>
       </c>
       <c r="C282" s="1">
@@ -15829,7 +15893,7 @@
         <v>851</v>
       </c>
       <c r="B283" s="5">
-        <f>IF(ISNA(VLOOKUP(H283,$A$2:$C$1005,3,1)),C283,VLOOKUP(H283,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H283,$A$2:$C$1011,3,1)),C283,VLOOKUP(H283,$A$2:$C$1011,3,1))</f>
         <v>426</v>
       </c>
       <c r="C283" s="1">
@@ -15862,7 +15926,7 @@
         <v>854</v>
       </c>
       <c r="B284" s="5">
-        <f>IF(ISNA(VLOOKUP(H284,$A$2:$C$1005,3,1)),C284,VLOOKUP(H284,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H284,$A$2:$C$1011,3,1)),C284,VLOOKUP(H284,$A$2:$C$1011,3,1))</f>
         <v>429</v>
       </c>
       <c r="C284" s="1">
@@ -15895,7 +15959,7 @@
         <v>857</v>
       </c>
       <c r="B285" s="5">
-        <f>IF(ISNA(VLOOKUP(H285,$A$2:$C$1005,3,1)),C285,VLOOKUP(H285,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H285,$A$2:$C$1011,3,1)),C285,VLOOKUP(H285,$A$2:$C$1011,3,1))</f>
         <v>431</v>
       </c>
       <c r="C285" s="1">
@@ -15928,7 +15992,7 @@
         <v>860</v>
       </c>
       <c r="B286" s="5">
-        <f>IF(ISNA(VLOOKUP(H286,$A$2:$C$1005,3,1)),C286,VLOOKUP(H286,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H286,$A$2:$C$1011,3,1)),C286,VLOOKUP(H286,$A$2:$C$1011,3,1))</f>
         <v>434</v>
       </c>
       <c r="C286" s="1">
@@ -15961,7 +16025,7 @@
         <v>838</v>
       </c>
       <c r="B287" s="5">
-        <f>IF(ISNA(VLOOKUP(H287,$A$2:$C$1005,3,1)),C287,VLOOKUP(H287,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H287,$A$2:$C$1011,3,1)),C287,VLOOKUP(H287,$A$2:$C$1011,3,1))</f>
         <v>438</v>
       </c>
       <c r="C287" s="1">
@@ -15994,7 +16058,7 @@
         <v>865</v>
       </c>
       <c r="B288" s="5">
-        <f>IF(ISNA(VLOOKUP(H288,$A$2:$C$1005,3,1)),C288,VLOOKUP(H288,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H288,$A$2:$C$1011,3,1)),C288,VLOOKUP(H288,$A$2:$C$1011,3,1))</f>
         <v>444</v>
       </c>
       <c r="C288" s="1">
@@ -16027,7 +16091,7 @@
         <v>868</v>
       </c>
       <c r="B289" s="5">
-        <f>IF(ISNA(VLOOKUP(H289,$A$2:$C$1005,3,1)),C289,VLOOKUP(H289,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H289,$A$2:$C$1011,3,1)),C289,VLOOKUP(H289,$A$2:$C$1011,3,1))</f>
         <v>446</v>
       </c>
       <c r="C289" s="1">
@@ -16060,7 +16124,7 @@
         <v>339</v>
       </c>
       <c r="B290" s="5">
-        <f>IF(ISNA(VLOOKUP(H290,$A$2:$C$1005,3,1)),C290,VLOOKUP(H290,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H290,$A$2:$C$1011,3,1)),C290,VLOOKUP(H290,$A$2:$C$1011,3,1))</f>
         <v>448</v>
       </c>
       <c r="C290" s="1">
@@ -16093,7 +16157,7 @@
         <v>873</v>
       </c>
       <c r="B291" s="5">
-        <f>IF(ISNA(VLOOKUP(H291,$A$2:$C$1005,3,1)),C291,VLOOKUP(H291,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H291,$A$2:$C$1011,3,1)),C291,VLOOKUP(H291,$A$2:$C$1011,3,1))</f>
         <v>452</v>
       </c>
       <c r="C291" s="1">
@@ -16126,7 +16190,7 @@
         <v>876</v>
       </c>
       <c r="B292" s="5">
-        <f>IF(ISNA(VLOOKUP(H292,$A$2:$C$1005,3,1)),C292,VLOOKUP(H292,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H292,$A$2:$C$1011,3,1)),C292,VLOOKUP(H292,$A$2:$C$1011,3,1))</f>
         <v>454</v>
       </c>
       <c r="C292" s="1">
@@ -16159,7 +16223,7 @@
         <v>879</v>
       </c>
       <c r="B293" s="5">
-        <f>IF(ISNA(VLOOKUP(H293,$A$2:$C$1005,3,1)),C293,VLOOKUP(H293,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H293,$A$2:$C$1011,3,1)),C293,VLOOKUP(H293,$A$2:$C$1011,3,1))</f>
         <v>456</v>
       </c>
       <c r="C293" s="1">
@@ -16192,7 +16256,7 @@
         <v>882</v>
       </c>
       <c r="B294" s="5">
-        <f>IF(ISNA(VLOOKUP(H294,$A$2:$C$1005,3,1)),C294,VLOOKUP(H294,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H294,$A$2:$C$1011,3,1)),C294,VLOOKUP(H294,$A$2:$C$1011,3,1))</f>
         <v>459</v>
       </c>
       <c r="C294" s="1">
@@ -16225,7 +16289,7 @@
         <v>885</v>
       </c>
       <c r="B295" s="5">
-        <f>IF(ISNA(VLOOKUP(H295,$A$2:$C$1005,3,1)),C295,VLOOKUP(H295,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H295,$A$2:$C$1011,3,1)),C295,VLOOKUP(H295,$A$2:$C$1011,3,1))</f>
         <v>465</v>
       </c>
       <c r="C295" s="1">
@@ -16258,7 +16322,7 @@
         <v>888</v>
       </c>
       <c r="B296" s="5">
-        <f>IF(ISNA(VLOOKUP(H296,$A$2:$C$1005,3,1)),C296,VLOOKUP(H296,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H296,$A$2:$C$1011,3,1)),C296,VLOOKUP(H296,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C296" s="1">
@@ -16291,7 +16355,7 @@
         <v>889</v>
       </c>
       <c r="B297" s="5">
-        <f>IF(ISNA(VLOOKUP(H297,$A$2:$C$1005,3,1)),C297,VLOOKUP(H297,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H297,$A$2:$C$1011,3,1)),C297,VLOOKUP(H297,$A$2:$C$1011,3,1))</f>
         <v>467</v>
       </c>
       <c r="C297" s="1">
@@ -16324,7 +16388,7 @@
         <v>892</v>
       </c>
       <c r="B298" s="5">
-        <f>IF(ISNA(VLOOKUP(H298,$A$2:$C$1005,3,1)),C298,VLOOKUP(H298,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H298,$A$2:$C$1011,3,1)),C298,VLOOKUP(H298,$A$2:$C$1011,3,1))</f>
         <v>471</v>
       </c>
       <c r="C298" s="1">
@@ -16357,7 +16421,7 @@
         <v>895</v>
       </c>
       <c r="B299" s="5">
-        <f>IF(ISNA(VLOOKUP(H299,$A$2:$C$1005,3,1)),C299,VLOOKUP(H299,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H299,$A$2:$C$1011,3,1)),C299,VLOOKUP(H299,$A$2:$C$1011,3,1))</f>
         <v>473</v>
       </c>
       <c r="C299" s="1">
@@ -16390,7 +16454,7 @@
         <v>898</v>
       </c>
       <c r="B300" s="5">
-        <f>IF(ISNA(VLOOKUP(H300,$A$2:$C$1005,3,1)),C300,VLOOKUP(H300,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H300,$A$2:$C$1011,3,1)),C300,VLOOKUP(H300,$A$2:$C$1011,3,1))</f>
         <v>479</v>
       </c>
       <c r="C300" s="1">
@@ -16423,7 +16487,7 @@
         <v>901</v>
       </c>
       <c r="B301" s="5">
-        <f>IF(ISNA(VLOOKUP(H301,$A$2:$C$1005,3,1)),C301,VLOOKUP(H301,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H301,$A$2:$C$1011,3,1)),C301,VLOOKUP(H301,$A$2:$C$1011,3,1))</f>
         <v>481</v>
       </c>
       <c r="C301" s="1">
@@ -16456,7 +16520,7 @@
         <v>904</v>
       </c>
       <c r="B302" s="5">
-        <f>IF(ISNA(VLOOKUP(H302,$A$2:$C$1005,3,1)),C302,VLOOKUP(H302,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H302,$A$2:$C$1011,3,1)),C302,VLOOKUP(H302,$A$2:$C$1011,3,1))</f>
         <v>483</v>
       </c>
       <c r="C302" s="1">
@@ -16489,7 +16553,7 @@
         <v>907</v>
       </c>
       <c r="B303" s="5">
-        <f>IF(ISNA(VLOOKUP(H303,$A$2:$C$1005,3,1)),C303,VLOOKUP(H303,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H303,$A$2:$C$1011,3,1)),C303,VLOOKUP(H303,$A$2:$C$1011,3,1))</f>
         <v>485</v>
       </c>
       <c r="C303" s="1">
@@ -16522,7 +16586,7 @@
         <v>910</v>
       </c>
       <c r="B304" s="5">
-        <f>IF(ISNA(VLOOKUP(H304,$A$2:$C$1005,3,1)),C304,VLOOKUP(H304,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H304,$A$2:$C$1011,3,1)),C304,VLOOKUP(H304,$A$2:$C$1011,3,1))</f>
         <v>438</v>
       </c>
       <c r="C304" s="1">
@@ -16555,7 +16619,7 @@
         <v>913</v>
       </c>
       <c r="B305" s="5">
-        <f>IF(ISNA(VLOOKUP(H305,$A$2:$C$1005,3,1)),C305,VLOOKUP(H305,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H305,$A$2:$C$1011,3,1)),C305,VLOOKUP(H305,$A$2:$C$1011,3,1))</f>
         <v>473</v>
       </c>
       <c r="C305" s="1">
@@ -16588,7 +16652,7 @@
         <v>916</v>
       </c>
       <c r="B306" s="5">
-        <f>IF(ISNA(VLOOKUP(H306,$A$2:$C$1005,3,1)),C306,VLOOKUP(H306,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H306,$A$2:$C$1011,3,1)),C306,VLOOKUP(H306,$A$2:$C$1011,3,1))</f>
         <v>415</v>
       </c>
       <c r="C306" s="1">
@@ -16621,7 +16685,7 @@
         <v>919</v>
       </c>
       <c r="B307" s="5">
-        <f>IF(ISNA(VLOOKUP(H307,$A$2:$C$1005,3,1)),C307,VLOOKUP(H307,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H307,$A$2:$C$1011,3,1)),C307,VLOOKUP(H307,$A$2:$C$1011,3,1))</f>
         <v>426</v>
       </c>
       <c r="C307" s="1">
@@ -16654,7 +16718,7 @@
         <v>922</v>
       </c>
       <c r="B308" s="5">
-        <f>IF(ISNA(VLOOKUP(H308,$A$2:$C$1005,3,1)),C308,VLOOKUP(H308,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H308,$A$2:$C$1011,3,1)),C308,VLOOKUP(H308,$A$2:$C$1011,3,1))</f>
         <v>431</v>
       </c>
       <c r="C308" s="1">
@@ -16687,7 +16751,7 @@
         <v>925</v>
       </c>
       <c r="B309" s="5">
-        <f>IF(ISNA(VLOOKUP(H309,$A$2:$C$1005,3,1)),C309,VLOOKUP(H309,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H309,$A$2:$C$1011,3,1)),C309,VLOOKUP(H309,$A$2:$C$1011,3,1))</f>
         <v>438</v>
       </c>
       <c r="C309" s="1">
@@ -16720,7 +16784,7 @@
         <v>928</v>
       </c>
       <c r="B310" s="5">
-        <f>IF(ISNA(VLOOKUP(H310,$A$2:$C$1005,3,1)),C310,VLOOKUP(H310,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H310,$A$2:$C$1011,3,1)),C310,VLOOKUP(H310,$A$2:$C$1011,3,1))</f>
         <v>473</v>
       </c>
       <c r="C310" s="1">
@@ -16753,7 +16817,7 @@
         <v>931</v>
       </c>
       <c r="B311" s="5">
-        <f>IF(ISNA(VLOOKUP(H311,$A$2:$C$1005,3,1)),C311,VLOOKUP(H311,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H311,$A$2:$C$1011,3,1)),C311,VLOOKUP(H311,$A$2:$C$1011,3,1))</f>
         <v>415</v>
       </c>
       <c r="C311" s="1">
@@ -16786,7 +16850,7 @@
         <v>934</v>
       </c>
       <c r="B312" s="5">
-        <f>IF(ISNA(VLOOKUP(H312,$A$2:$C$1005,3,1)),C312,VLOOKUP(H312,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H312,$A$2:$C$1011,3,1)),C312,VLOOKUP(H312,$A$2:$C$1011,3,1))</f>
         <v>419</v>
       </c>
       <c r="C312" s="1">
@@ -16819,7 +16883,7 @@
         <v>937</v>
       </c>
       <c r="B313" s="5">
-        <f>IF(ISNA(VLOOKUP(H313,$A$2:$C$1005,3,1)),C313,VLOOKUP(H313,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H313,$A$2:$C$1011,3,1)),C313,VLOOKUP(H313,$A$2:$C$1011,3,1))</f>
         <v>421</v>
       </c>
       <c r="C313" s="1">
@@ -16852,7 +16916,7 @@
         <v>940</v>
       </c>
       <c r="B314" s="5">
-        <f>IF(ISNA(VLOOKUP(H314,$A$2:$C$1005,3,1)),C314,VLOOKUP(H314,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H314,$A$2:$C$1011,3,1)),C314,VLOOKUP(H314,$A$2:$C$1011,3,1))</f>
         <v>423</v>
       </c>
       <c r="C314" s="1">
@@ -16885,7 +16949,7 @@
         <v>943</v>
       </c>
       <c r="B315" s="5">
-        <f>IF(ISNA(VLOOKUP(H315,$A$2:$C$1005,3,1)),C315,VLOOKUP(H315,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H315,$A$2:$C$1011,3,1)),C315,VLOOKUP(H315,$A$2:$C$1011,3,1))</f>
         <v>426</v>
       </c>
       <c r="C315" s="1">
@@ -16918,7 +16982,7 @@
         <v>946</v>
       </c>
       <c r="B316" s="5">
-        <f>IF(ISNA(VLOOKUP(H316,$A$2:$C$1005,3,1)),C316,VLOOKUP(H316,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H316,$A$2:$C$1011,3,1)),C316,VLOOKUP(H316,$A$2:$C$1011,3,1))</f>
         <v>429</v>
       </c>
       <c r="C316" s="1">
@@ -16951,7 +17015,7 @@
         <v>949</v>
       </c>
       <c r="B317" s="5">
-        <f>IF(ISNA(VLOOKUP(H317,$A$2:$C$1005,3,1)),C317,VLOOKUP(H317,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H317,$A$2:$C$1011,3,1)),C317,VLOOKUP(H317,$A$2:$C$1011,3,1))</f>
         <v>431</v>
       </c>
       <c r="C317" s="1">
@@ -16984,7 +17048,7 @@
         <v>952</v>
       </c>
       <c r="B318" s="13">
-        <f>IF(ISNA(VLOOKUP(H318,$A$2:$C$1005,3,1)),C318,VLOOKUP(H318,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H318,$A$2:$C$1011,3,1)),C318,VLOOKUP(H318,$A$2:$C$1011,3,1))</f>
         <v>434</v>
       </c>
       <c r="C318" s="1">
@@ -17021,7 +17085,7 @@
         <v>954</v>
       </c>
       <c r="B319" s="5">
-        <f>IF(ISNA(VLOOKUP(H319,$A$2:$C$1005,3,1)),C319,VLOOKUP(H319,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H319,$A$2:$C$1011,3,1)),C319,VLOOKUP(H319,$A$2:$C$1011,3,1))</f>
         <v>438</v>
       </c>
       <c r="C319" s="1">
@@ -17054,7 +17118,7 @@
         <v>957</v>
       </c>
       <c r="B320" s="5">
-        <f>IF(ISNA(VLOOKUP(H320,$A$2:$C$1005,3,1)),C320,VLOOKUP(H320,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H320,$A$2:$C$1011,3,1)),C320,VLOOKUP(H320,$A$2:$C$1011,3,1))</f>
         <v>444</v>
       </c>
       <c r="C320" s="1">
@@ -17087,7 +17151,7 @@
         <v>960</v>
       </c>
       <c r="B321" s="5">
-        <f>IF(ISNA(VLOOKUP(H321,$A$2:$C$1005,3,1)),C321,VLOOKUP(H321,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H321,$A$2:$C$1011,3,1)),C321,VLOOKUP(H321,$A$2:$C$1011,3,1))</f>
         <v>446</v>
       </c>
       <c r="C321" s="1">
@@ -17120,7 +17184,7 @@
         <v>963</v>
       </c>
       <c r="B322" s="5">
-        <f>IF(ISNA(VLOOKUP(H322,$A$2:$C$1005,3,1)),C322,VLOOKUP(H322,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H322,$A$2:$C$1011,3,1)),C322,VLOOKUP(H322,$A$2:$C$1011,3,1))</f>
         <v>448</v>
       </c>
       <c r="C322" s="1">
@@ -17153,7 +17217,7 @@
         <v>965</v>
       </c>
       <c r="B323" s="5">
-        <f>IF(ISNA(VLOOKUP(H323,$A$2:$C$1005,3,1)),C323,VLOOKUP(H323,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H323,$A$2:$C$1011,3,1)),C323,VLOOKUP(H323,$A$2:$C$1011,3,1))</f>
         <v>452</v>
       </c>
       <c r="C323" s="1">
@@ -17186,7 +17250,7 @@
         <v>968</v>
       </c>
       <c r="B324" s="5">
-        <f>IF(ISNA(VLOOKUP(H324,$A$2:$C$1005,3,1)),C324,VLOOKUP(H324,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H324,$A$2:$C$1011,3,1)),C324,VLOOKUP(H324,$A$2:$C$1011,3,1))</f>
         <v>454</v>
       </c>
       <c r="C324" s="1">
@@ -17219,7 +17283,7 @@
         <v>971</v>
       </c>
       <c r="B325" s="5">
-        <f>IF(ISNA(VLOOKUP(H325,$A$2:$C$1005,3,1)),C325,VLOOKUP(H325,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H325,$A$2:$C$1011,3,1)),C325,VLOOKUP(H325,$A$2:$C$1011,3,1))</f>
         <v>456</v>
       </c>
       <c r="C325" s="1">
@@ -17252,7 +17316,7 @@
         <v>974</v>
       </c>
       <c r="B326" s="5">
-        <f>IF(ISNA(VLOOKUP(H326,$A$2:$C$1005,3,1)),C326,VLOOKUP(H326,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H326,$A$2:$C$1011,3,1)),C326,VLOOKUP(H326,$A$2:$C$1011,3,1))</f>
         <v>459</v>
       </c>
       <c r="C326" s="1">
@@ -17285,7 +17349,7 @@
         <v>977</v>
       </c>
       <c r="B327" s="5">
-        <f>IF(ISNA(VLOOKUP(H327,$A$2:$C$1005,3,1)),C327,VLOOKUP(H327,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H327,$A$2:$C$1011,3,1)),C327,VLOOKUP(H327,$A$2:$C$1011,3,1))</f>
         <v>465</v>
       </c>
       <c r="C327" s="1">
@@ -17318,7 +17382,7 @@
         <v>980</v>
       </c>
       <c r="B328" s="5">
-        <f>IF(ISNA(VLOOKUP(H328,$A$2:$C$1005,3,1)),C328,VLOOKUP(H328,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H328,$A$2:$C$1011,3,1)),C328,VLOOKUP(H328,$A$2:$C$1011,3,1))</f>
         <v>467</v>
       </c>
       <c r="C328" s="1">
@@ -17351,7 +17415,7 @@
         <v>983</v>
       </c>
       <c r="B329" s="5">
-        <f>IF(ISNA(VLOOKUP(H329,$A$2:$C$1005,3,1)),C329,VLOOKUP(H329,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H329,$A$2:$C$1011,3,1)),C329,VLOOKUP(H329,$A$2:$C$1011,3,1))</f>
         <v>467</v>
       </c>
       <c r="C329" s="1">
@@ -17384,7 +17448,7 @@
         <v>986</v>
       </c>
       <c r="B330" s="5">
-        <f>IF(ISNA(VLOOKUP(H330,$A$2:$C$1005,3,1)),C330,VLOOKUP(H330,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H330,$A$2:$C$1011,3,1)),C330,VLOOKUP(H330,$A$2:$C$1011,3,1))</f>
         <v>471</v>
       </c>
       <c r="C330" s="1">
@@ -17417,7 +17481,7 @@
         <v>989</v>
       </c>
       <c r="B331" s="5">
-        <f>IF(ISNA(VLOOKUP(H331,$A$2:$C$1005,3,1)),C331,VLOOKUP(H331,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H331,$A$2:$C$1011,3,1)),C331,VLOOKUP(H331,$A$2:$C$1011,3,1))</f>
         <v>473</v>
       </c>
       <c r="C331" s="1">
@@ -17450,7 +17514,7 @@
         <v>992</v>
       </c>
       <c r="B332" s="5">
-        <f>IF(ISNA(VLOOKUP(H332,$A$2:$C$1005,3,1)),C332,VLOOKUP(H332,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H332,$A$2:$C$1011,3,1)),C332,VLOOKUP(H332,$A$2:$C$1011,3,1))</f>
         <v>479</v>
       </c>
       <c r="C332" s="1">
@@ -17483,7 +17547,7 @@
         <v>995</v>
       </c>
       <c r="B333" s="5">
-        <f>IF(ISNA(VLOOKUP(H333,$A$2:$C$1005,3,1)),C333,VLOOKUP(H333,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H333,$A$2:$C$1011,3,1)),C333,VLOOKUP(H333,$A$2:$C$1011,3,1))</f>
         <v>481</v>
       </c>
       <c r="C333" s="1">
@@ -17516,7 +17580,7 @@
         <v>998</v>
       </c>
       <c r="B334" s="5">
-        <f>IF(ISNA(VLOOKUP(H334,$A$2:$C$1005,3,1)),C334,VLOOKUP(H334,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H334,$A$2:$C$1011,3,1)),C334,VLOOKUP(H334,$A$2:$C$1011,3,1))</f>
         <v>483</v>
       </c>
       <c r="C334" s="1">
@@ -17549,7 +17613,7 @@
         <v>1001</v>
       </c>
       <c r="B335" s="5">
-        <f>IF(ISNA(VLOOKUP(H335,$A$2:$C$1005,3,1)),C335,VLOOKUP(H335,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H335,$A$2:$C$1011,3,1)),C335,VLOOKUP(H335,$A$2:$C$1011,3,1))</f>
         <v>485</v>
       </c>
       <c r="C335" s="1">
@@ -17582,7 +17646,7 @@
         <v>1004</v>
       </c>
       <c r="B336" s="5">
-        <f>IF(ISNA(VLOOKUP(H336,$A$2:$C$1005,3,1)),C336,VLOOKUP(H336,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H336,$A$2:$C$1011,3,1)),C336,VLOOKUP(H336,$A$2:$C$1011,3,1))</f>
         <v>438</v>
       </c>
       <c r="C336" s="1">
@@ -17615,7 +17679,7 @@
         <v>1007</v>
       </c>
       <c r="B337" s="5">
-        <f>IF(ISNA(VLOOKUP(H337,$A$2:$C$1005,3,1)),C337,VLOOKUP(H337,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H337,$A$2:$C$1011,3,1)),C337,VLOOKUP(H337,$A$2:$C$1011,3,1))</f>
         <v>473</v>
       </c>
       <c r="C337" s="1">
@@ -17648,7 +17712,7 @@
         <v>1010</v>
       </c>
       <c r="B338" s="5">
-        <f>IF(ISNA(VLOOKUP(H338,$A$2:$C$1005,3,1)),C338,VLOOKUP(H338,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H338,$A$2:$C$1011,3,1)),C338,VLOOKUP(H338,$A$2:$C$1011,3,1))</f>
         <v>456</v>
       </c>
       <c r="C338" s="1">
@@ -17681,7 +17745,7 @@
         <v>1013</v>
       </c>
       <c r="B339" s="5">
-        <f>IF(ISNA(VLOOKUP(H339,$A$2:$C$1005,3,1)),C339,VLOOKUP(H339,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H339,$A$2:$C$1011,3,1)),C339,VLOOKUP(H339,$A$2:$C$1011,3,1))</f>
         <v>473</v>
       </c>
       <c r="C339" s="1">
@@ -17714,7 +17778,7 @@
         <v>1016</v>
       </c>
       <c r="B340" s="5">
-        <f>IF(ISNA(VLOOKUP(H340,$A$2:$C$1005,3,1)),C340,VLOOKUP(H340,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H340,$A$2:$C$1011,3,1)),C340,VLOOKUP(H340,$A$2:$C$1011,3,1))</f>
         <v>485</v>
       </c>
       <c r="C340" s="1">
@@ -17747,7 +17811,7 @@
         <v>1996</v>
       </c>
       <c r="B341" s="13">
-        <f>IF(ISNA(VLOOKUP(H341,$A$2:$C$1005,3,1)),C341,VLOOKUP(H341,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H341,$A$2:$C$1011,3,1)),C341,VLOOKUP(H341,$A$2:$C$1011,3,1))</f>
         <v>434</v>
       </c>
       <c r="C341" s="1">
@@ -17784,7 +17848,7 @@
         <v>2001</v>
       </c>
       <c r="B342" s="13">
-        <f>IF(ISNA(VLOOKUP(H342,$A$2:$C$1005,3,1)),C342,VLOOKUP(H342,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H342,$A$2:$C$1011,3,1)),C342,VLOOKUP(H342,$A$2:$C$1011,3,1))</f>
         <v>479</v>
       </c>
       <c r="C342" s="1">
@@ -17821,7 +17885,7 @@
         <v>1019</v>
       </c>
       <c r="B343" s="5">
-        <f>IF(ISNA(VLOOKUP(H343,$A$2:$C$1005,3,1)),C343,VLOOKUP(H343,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H343,$A$2:$C$1011,3,1)),C343,VLOOKUP(H343,$A$2:$C$1011,3,1))</f>
         <v>488</v>
       </c>
       <c r="C343" s="1">
@@ -17854,7 +17918,7 @@
         <v>1022</v>
       </c>
       <c r="B344" s="5">
-        <f>IF(ISNA(VLOOKUP(H344,$A$2:$C$1005,3,1)),C344,VLOOKUP(H344,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H344,$A$2:$C$1011,3,1)),C344,VLOOKUP(H344,$A$2:$C$1011,3,1))</f>
         <v>488</v>
       </c>
       <c r="C344" s="1">
@@ -17887,7 +17951,7 @@
         <v>1025</v>
       </c>
       <c r="B345" s="5">
-        <f>IF(ISNA(VLOOKUP(H345,$A$2:$C$1005,3,1)),C345,VLOOKUP(H345,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H345,$A$2:$C$1011,3,1)),C345,VLOOKUP(H345,$A$2:$C$1011,3,1))</f>
         <v>490</v>
       </c>
       <c r="C345" s="1">
@@ -17920,7 +17984,7 @@
         <v>1028</v>
       </c>
       <c r="B346" s="5">
-        <f>IF(ISNA(VLOOKUP(H346,$A$2:$C$1005,3,1)),C346,VLOOKUP(H346,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H346,$A$2:$C$1011,3,1)),C346,VLOOKUP(H346,$A$2:$C$1011,3,1))</f>
         <v>490</v>
       </c>
       <c r="C346" s="1">
@@ -17953,7 +18017,7 @@
         <v>1031</v>
       </c>
       <c r="B347" s="5">
-        <f>IF(ISNA(VLOOKUP(H347,$A$2:$C$1005,3,1)),C347,VLOOKUP(H347,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H347,$A$2:$C$1011,3,1)),C347,VLOOKUP(H347,$A$2:$C$1011,3,1))</f>
         <v>492</v>
       </c>
       <c r="C347" s="1">
@@ -17986,7 +18050,7 @@
         <v>1034</v>
       </c>
       <c r="B348" s="5">
-        <f>IF(ISNA(VLOOKUP(H348,$A$2:$C$1005,3,1)),C348,VLOOKUP(H348,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H348,$A$2:$C$1011,3,1)),C348,VLOOKUP(H348,$A$2:$C$1011,3,1))</f>
         <v>492</v>
       </c>
       <c r="C348" s="1">
@@ -18019,7 +18083,7 @@
         <v>1037</v>
       </c>
       <c r="B349" s="5">
-        <f>IF(ISNA(VLOOKUP(H349,$A$2:$C$1005,3,1)),C349,VLOOKUP(H349,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H349,$A$2:$C$1011,3,1)),C349,VLOOKUP(H349,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C349" s="1">
@@ -18052,7 +18116,7 @@
         <v>1040</v>
       </c>
       <c r="B350" s="5">
-        <f>IF(ISNA(VLOOKUP(H350,$A$2:$C$1005,3,1)),C350,VLOOKUP(H350,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H350,$A$2:$C$1011,3,1)),C350,VLOOKUP(H350,$A$2:$C$1011,3,1))</f>
         <v>161</v>
       </c>
       <c r="C350" s="1">
@@ -18085,7 +18149,7 @@
         <v>1043</v>
       </c>
       <c r="B351" s="5">
-        <f>IF(ISNA(VLOOKUP(H351,$A$2:$C$1005,3,1)),C351,VLOOKUP(H351,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H351,$A$2:$C$1011,3,1)),C351,VLOOKUP(H351,$A$2:$C$1011,3,1))</f>
         <v>152</v>
       </c>
       <c r="C351" s="1">
@@ -18118,7 +18182,7 @@
         <v>1046</v>
       </c>
       <c r="B352" s="5">
-        <f>IF(ISNA(VLOOKUP(H352,$A$2:$C$1005,3,1)),C352,VLOOKUP(H352,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H352,$A$2:$C$1011,3,1)),C352,VLOOKUP(H352,$A$2:$C$1011,3,1))</f>
         <v>152</v>
       </c>
       <c r="C352" s="1">
@@ -18151,7 +18215,7 @@
         <v>1049</v>
       </c>
       <c r="B353" s="5">
-        <f>IF(ISNA(VLOOKUP(H353,$A$2:$C$1005,3,1)),C353,VLOOKUP(H353,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H353,$A$2:$C$1011,3,1)),C353,VLOOKUP(H353,$A$2:$C$1011,3,1))</f>
         <v>161</v>
       </c>
       <c r="C353" s="1">
@@ -18184,7 +18248,7 @@
         <v>1051</v>
       </c>
       <c r="B354" s="5">
-        <f>IF(ISNA(VLOOKUP(H354,$A$2:$C$1005,3,1)),C354,VLOOKUP(H354,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H354,$A$2:$C$1011,3,1)),C354,VLOOKUP(H354,$A$2:$C$1011,3,1))</f>
         <v>1</v>
       </c>
       <c r="C354" s="1">
@@ -18217,7 +18281,7 @@
         <v>1054</v>
       </c>
       <c r="B355" s="5">
-        <f>IF(ISNA(VLOOKUP(H355,$A$2:$C$1005,3,1)),C355,VLOOKUP(H355,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H355,$A$2:$C$1011,3,1)),C355,VLOOKUP(H355,$A$2:$C$1011,3,1))</f>
         <v>1</v>
       </c>
       <c r="C355" s="1">
@@ -18250,7 +18314,7 @@
         <v>1057</v>
       </c>
       <c r="B356" s="5">
-        <f>IF(ISNA(VLOOKUP(H356,$A$2:$C$1005,3,1)),C356,VLOOKUP(H356,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H356,$A$2:$C$1011,3,1)),C356,VLOOKUP(H356,$A$2:$C$1011,3,1))</f>
         <v>1</v>
       </c>
       <c r="C356" s="1">
@@ -18283,7 +18347,7 @@
         <v>1060</v>
       </c>
       <c r="B357" s="5">
-        <f>IF(ISNA(VLOOKUP(H357,$A$2:$C$1005,3,1)),C357,VLOOKUP(H357,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H357,$A$2:$C$1011,3,1)),C357,VLOOKUP(H357,$A$2:$C$1011,3,1))</f>
         <v>1</v>
       </c>
       <c r="C357" s="1">
@@ -18316,7 +18380,7 @@
         <v>1063</v>
       </c>
       <c r="B358" s="5">
-        <f>IF(ISNA(VLOOKUP(H358,$A$2:$C$1005,3,1)),C358,VLOOKUP(H358,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H358,$A$2:$C$1011,3,1)),C358,VLOOKUP(H358,$A$2:$C$1011,3,1))</f>
         <v>1</v>
       </c>
       <c r="C358" s="1">
@@ -18349,7 +18413,7 @@
         <v>1066</v>
       </c>
       <c r="B359" s="5">
-        <f>IF(ISNA(VLOOKUP(H359,$A$2:$C$1005,3,1)),C359,VLOOKUP(H359,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H359,$A$2:$C$1011,3,1)),C359,VLOOKUP(H359,$A$2:$C$1011,3,1))</f>
         <v>1</v>
       </c>
       <c r="C359" s="1">
@@ -18382,7 +18446,7 @@
         <v>1069</v>
       </c>
       <c r="B360" s="5">
-        <f>IF(ISNA(VLOOKUP(H360,$A$2:$C$1005,3,1)),C360,VLOOKUP(H360,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H360,$A$2:$C$1011,3,1)),C360,VLOOKUP(H360,$A$2:$C$1011,3,1))</f>
         <v>1</v>
       </c>
       <c r="C360" s="1">
@@ -18415,7 +18479,7 @@
         <v>1072</v>
       </c>
       <c r="B361" s="5">
-        <f>IF(ISNA(VLOOKUP(H361,$A$2:$C$1005,3,1)),C361,VLOOKUP(H361,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H361,$A$2:$C$1011,3,1)),C361,VLOOKUP(H361,$A$2:$C$1011,3,1))</f>
         <v>544</v>
       </c>
       <c r="C361" s="1">
@@ -18448,7 +18512,7 @@
         <v>1075</v>
       </c>
       <c r="B362" s="5">
-        <f>IF(ISNA(VLOOKUP(H362,$A$2:$C$1005,3,1)),C362,VLOOKUP(H362,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H362,$A$2:$C$1011,3,1)),C362,VLOOKUP(H362,$A$2:$C$1011,3,1))</f>
         <v>544</v>
       </c>
       <c r="C362" s="1">
@@ -18481,7 +18545,7 @@
         <v>1078</v>
       </c>
       <c r="B363" s="5">
-        <f>IF(ISNA(VLOOKUP(H363,$A$2:$C$1005,3,1)),C363,VLOOKUP(H363,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H363,$A$2:$C$1011,3,1)),C363,VLOOKUP(H363,$A$2:$C$1011,3,1))</f>
         <v>544</v>
       </c>
       <c r="C363" s="1">
@@ -18514,7 +18578,7 @@
         <v>1081</v>
       </c>
       <c r="B364" s="5">
-        <f>IF(ISNA(VLOOKUP(H364,$A$2:$C$1005,3,1)),C364,VLOOKUP(H364,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H364,$A$2:$C$1011,3,1)),C364,VLOOKUP(H364,$A$2:$C$1011,3,1))</f>
         <v>544</v>
       </c>
       <c r="C364" s="1">
@@ -18547,7 +18611,7 @@
         <v>1084</v>
       </c>
       <c r="B365" s="5">
-        <f>IF(ISNA(VLOOKUP(H365,$A$2:$C$1005,3,1)),C365,VLOOKUP(H365,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H365,$A$2:$C$1011,3,1)),C365,VLOOKUP(H365,$A$2:$C$1011,3,1))</f>
         <v>550</v>
       </c>
       <c r="C365" s="1">
@@ -18580,7 +18644,7 @@
         <v>1087</v>
       </c>
       <c r="B366" s="5">
-        <f>IF(ISNA(VLOOKUP(H366,$A$2:$C$1005,3,1)),C366,VLOOKUP(H366,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H366,$A$2:$C$1011,3,1)),C366,VLOOKUP(H366,$A$2:$C$1011,3,1))</f>
         <v>550</v>
       </c>
       <c r="C366" s="1">
@@ -18613,7 +18677,7 @@
         <v>1090</v>
       </c>
       <c r="B367" s="5">
-        <f>IF(ISNA(VLOOKUP(H367,$A$2:$C$1005,3,1)),C367,VLOOKUP(H367,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H367,$A$2:$C$1011,3,1)),C367,VLOOKUP(H367,$A$2:$C$1011,3,1))</f>
         <v>550</v>
       </c>
       <c r="C367" s="1">
@@ -18646,7 +18710,7 @@
         <v>1093</v>
       </c>
       <c r="B368" s="5">
-        <f>IF(ISNA(VLOOKUP(H368,$A$2:$C$1005,3,1)),C368,VLOOKUP(H368,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H368,$A$2:$C$1011,3,1)),C368,VLOOKUP(H368,$A$2:$C$1011,3,1))</f>
         <v>550</v>
       </c>
       <c r="C368" s="1">
@@ -18679,7 +18743,7 @@
         <v>1096</v>
       </c>
       <c r="B369" s="5">
-        <f>IF(ISNA(VLOOKUP(H369,$A$2:$C$1005,3,1)),C369,VLOOKUP(H369,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H369,$A$2:$C$1011,3,1)),C369,VLOOKUP(H369,$A$2:$C$1011,3,1))</f>
         <v>531</v>
       </c>
       <c r="C369" s="1">
@@ -18712,7 +18776,7 @@
         <v>1099</v>
       </c>
       <c r="B370" s="5">
-        <f>IF(ISNA(VLOOKUP(H370,$A$2:$C$1005,3,1)),C370,VLOOKUP(H370,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H370,$A$2:$C$1011,3,1)),C370,VLOOKUP(H370,$A$2:$C$1011,3,1))</f>
         <v>18</v>
       </c>
       <c r="C370" s="1">
@@ -18745,7 +18809,7 @@
         <v>1102</v>
       </c>
       <c r="B371" s="5">
-        <f>IF(ISNA(VLOOKUP(H371,$A$2:$C$1005,3,1)),C371,VLOOKUP(H371,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H371,$A$2:$C$1011,3,1)),C371,VLOOKUP(H371,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C371" s="1">
@@ -18778,7 +18842,7 @@
         <v>1104</v>
       </c>
       <c r="B372" s="5">
-        <f>IF(ISNA(VLOOKUP(H372,$A$2:$C$1005,3,1)),C372,VLOOKUP(H372,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H372,$A$2:$C$1011,3,1)),C372,VLOOKUP(H372,$A$2:$C$1011,3,1))</f>
         <v>11</v>
       </c>
       <c r="C372" s="1">
@@ -18811,7 +18875,7 @@
         <v>1107</v>
       </c>
       <c r="B373" s="5">
-        <f>IF(ISNA(VLOOKUP(H373,$A$2:$C$1005,3,1)),C373,VLOOKUP(H373,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H373,$A$2:$C$1011,3,1)),C373,VLOOKUP(H373,$A$2:$C$1011,3,1))</f>
         <v>18</v>
       </c>
       <c r="C373" s="1">
@@ -18844,7 +18908,7 @@
         <v>1110</v>
       </c>
       <c r="B374" s="5">
-        <f>IF(ISNA(VLOOKUP(H374,$A$2:$C$1005,3,1)),C374,VLOOKUP(H374,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H374,$A$2:$C$1011,3,1)),C374,VLOOKUP(H374,$A$2:$C$1011,3,1))</f>
         <v>25</v>
       </c>
       <c r="C374" s="1">
@@ -18877,7 +18941,7 @@
         <v>1113</v>
       </c>
       <c r="B375" s="5">
-        <f>IF(ISNA(VLOOKUP(H375,$A$2:$C$1005,3,1)),C375,VLOOKUP(H375,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H375,$A$2:$C$1011,3,1)),C375,VLOOKUP(H375,$A$2:$C$1011,3,1))</f>
         <v>29</v>
       </c>
       <c r="C375" s="1">
@@ -18910,7 +18974,7 @@
         <v>1116</v>
       </c>
       <c r="B376" s="5">
-        <f>IF(ISNA(VLOOKUP(H376,$A$2:$C$1005,3,1)),C376,VLOOKUP(H376,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H376,$A$2:$C$1011,3,1)),C376,VLOOKUP(H376,$A$2:$C$1011,3,1))</f>
         <v>34</v>
       </c>
       <c r="C376" s="1">
@@ -18943,7 +19007,7 @@
         <v>1119</v>
       </c>
       <c r="B377" s="5">
-        <f>IF(ISNA(VLOOKUP(H377,$A$2:$C$1005,3,1)),C377,VLOOKUP(H377,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H377,$A$2:$C$1011,3,1)),C377,VLOOKUP(H377,$A$2:$C$1011,3,1))</f>
         <v>38</v>
       </c>
       <c r="C377" s="1">
@@ -18976,7 +19040,7 @@
         <v>1122</v>
       </c>
       <c r="B378" s="5">
-        <f>IF(ISNA(VLOOKUP(H378,$A$2:$C$1005,3,1)),C378,VLOOKUP(H378,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H378,$A$2:$C$1011,3,1)),C378,VLOOKUP(H378,$A$2:$C$1011,3,1))</f>
         <v>42</v>
       </c>
       <c r="C378" s="1">
@@ -19009,7 +19073,7 @@
         <v>1125</v>
       </c>
       <c r="B379" s="5">
-        <f>IF(ISNA(VLOOKUP(H379,$A$2:$C$1005,3,1)),C379,VLOOKUP(H379,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H379,$A$2:$C$1011,3,1)),C379,VLOOKUP(H379,$A$2:$C$1011,3,1))</f>
         <v>46</v>
       </c>
       <c r="C379" s="1">
@@ -19042,7 +19106,7 @@
         <v>1128</v>
       </c>
       <c r="B380" s="5">
-        <f>IF(ISNA(VLOOKUP(H380,$A$2:$C$1005,3,1)),C380,VLOOKUP(H380,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H380,$A$2:$C$1011,3,1)),C380,VLOOKUP(H380,$A$2:$C$1011,3,1))</f>
         <v>50</v>
       </c>
       <c r="C380" s="1">
@@ -19075,7 +19139,7 @@
         <v>1131</v>
       </c>
       <c r="B381" s="5">
-        <f>IF(ISNA(VLOOKUP(H381,$A$2:$C$1005,3,1)),C381,VLOOKUP(H381,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H381,$A$2:$C$1011,3,1)),C381,VLOOKUP(H381,$A$2:$C$1011,3,1))</f>
         <v>54</v>
       </c>
       <c r="C381" s="1">
@@ -19108,7 +19172,7 @@
         <v>1134</v>
       </c>
       <c r="B382" s="5">
-        <f>IF(ISNA(VLOOKUP(H382,$A$2:$C$1005,3,1)),C382,VLOOKUP(H382,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H382,$A$2:$C$1011,3,1)),C382,VLOOKUP(H382,$A$2:$C$1011,3,1))</f>
         <v>510</v>
       </c>
       <c r="C382" s="1">
@@ -19141,7 +19205,7 @@
         <v>1137</v>
       </c>
       <c r="B383" s="5">
-        <f>IF(ISNA(VLOOKUP(H383,$A$2:$C$1005,3,1)),C383,VLOOKUP(H383,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H383,$A$2:$C$1011,3,1)),C383,VLOOKUP(H383,$A$2:$C$1011,3,1))</f>
         <v>514</v>
       </c>
       <c r="C383" s="1">
@@ -19174,7 +19238,7 @@
         <v>1140</v>
       </c>
       <c r="B384" s="5">
-        <f>IF(ISNA(VLOOKUP(H384,$A$2:$C$1005,3,1)),C384,VLOOKUP(H384,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H384,$A$2:$C$1011,3,1)),C384,VLOOKUP(H384,$A$2:$C$1011,3,1))</f>
         <v>519</v>
       </c>
       <c r="C384" s="1">
@@ -19207,7 +19271,7 @@
         <v>1142</v>
       </c>
       <c r="B385" s="5">
-        <f>IF(ISNA(VLOOKUP(H385,$A$2:$C$1005,3,1)),C385,VLOOKUP(H385,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H385,$A$2:$C$1011,3,1)),C385,VLOOKUP(H385,$A$2:$C$1011,3,1))</f>
         <v>623</v>
       </c>
       <c r="C385" s="1">
@@ -19240,7 +19304,7 @@
         <v>1145</v>
       </c>
       <c r="B386" s="5">
-        <f>IF(ISNA(VLOOKUP(H386,$A$2:$C$1005,3,1)),C386,VLOOKUP(H386,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H386,$A$2:$C$1011,3,1)),C386,VLOOKUP(H386,$A$2:$C$1011,3,1))</f>
         <v>623</v>
       </c>
       <c r="C386" s="1">
@@ -19273,7 +19337,7 @@
         <v>1147</v>
       </c>
       <c r="B387" s="5">
-        <f>IF(ISNA(VLOOKUP(H387,$A$2:$C$1005,3,1)),C387,VLOOKUP(H387,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H387,$A$2:$C$1011,3,1)),C387,VLOOKUP(H387,$A$2:$C$1011,3,1))</f>
         <v>614</v>
       </c>
       <c r="C387" s="1">
@@ -19306,7 +19370,7 @@
         <v>1150</v>
       </c>
       <c r="B388" s="5">
-        <f>IF(ISNA(VLOOKUP(H388,$A$2:$C$1005,3,1)),C388,VLOOKUP(H388,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H388,$A$2:$C$1011,3,1)),C388,VLOOKUP(H388,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C388" s="1">
@@ -19339,7 +19403,7 @@
         <v>1153</v>
       </c>
       <c r="B389" s="5">
-        <f>IF(ISNA(VLOOKUP(H389,$A$2:$C$1005,3,1)),C389,VLOOKUP(H389,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H389,$A$2:$C$1011,3,1)),C389,VLOOKUP(H389,$A$2:$C$1011,3,1))</f>
         <v>171</v>
       </c>
       <c r="C389" s="1">
@@ -19372,7 +19436,7 @@
         <v>1156</v>
       </c>
       <c r="B390" s="5">
-        <f>IF(ISNA(VLOOKUP(H390,$A$2:$C$1005,3,1)),C390,VLOOKUP(H390,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H390,$A$2:$C$1011,3,1)),C390,VLOOKUP(H390,$A$2:$C$1011,3,1))</f>
         <v>171</v>
       </c>
       <c r="C390" s="1">
@@ -19405,7 +19469,7 @@
         <v>1159</v>
       </c>
       <c r="B391" s="5">
-        <f>IF(ISNA(VLOOKUP(H391,$A$2:$C$1005,3,1)),C391,VLOOKUP(H391,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H391,$A$2:$C$1011,3,1)),C391,VLOOKUP(H391,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C391" s="1">
@@ -19438,7 +19502,7 @@
         <v>1162</v>
       </c>
       <c r="B392" s="5">
-        <f>IF(ISNA(VLOOKUP(H392,$A$2:$C$1005,3,1)),C392,VLOOKUP(H392,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H392,$A$2:$C$1011,3,1)),C392,VLOOKUP(H392,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C392" s="1">
@@ -19471,7 +19535,7 @@
         <v>1165</v>
       </c>
       <c r="B393" s="5">
-        <f>IF(ISNA(VLOOKUP(H393,$A$2:$C$1005,3,1)),C393,VLOOKUP(H393,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H393,$A$2:$C$1011,3,1)),C393,VLOOKUP(H393,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C393" s="1">
@@ -19504,7 +19568,7 @@
         <v>1168</v>
       </c>
       <c r="B394" s="5">
-        <f>IF(ISNA(VLOOKUP(H394,$A$2:$C$1005,3,1)),C394,VLOOKUP(H394,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H394,$A$2:$C$1011,3,1)),C394,VLOOKUP(H394,$A$2:$C$1011,3,1))</f>
         <v>284</v>
       </c>
       <c r="C394" s="1">
@@ -19537,7 +19601,7 @@
         <v>1171</v>
       </c>
       <c r="B395" s="5">
-        <f>IF(ISNA(VLOOKUP(H395,$A$2:$C$1005,3,1)),C395,VLOOKUP(H395,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H395,$A$2:$C$1011,3,1)),C395,VLOOKUP(H395,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C395" s="1">
@@ -19570,7 +19634,7 @@
         <v>1174</v>
       </c>
       <c r="B396" s="5">
-        <f>IF(ISNA(VLOOKUP(H396,$A$2:$C$1005,3,1)),C396,VLOOKUP(H396,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H396,$A$2:$C$1011,3,1)),C396,VLOOKUP(H396,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C396" s="1">
@@ -19603,7 +19667,7 @@
         <v>1177</v>
       </c>
       <c r="B397" s="5">
-        <f>IF(ISNA(VLOOKUP(H397,$A$2:$C$1005,3,1)),C397,VLOOKUP(H397,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H397,$A$2:$C$1011,3,1)),C397,VLOOKUP(H397,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C397" s="1">
@@ -19636,7 +19700,7 @@
         <v>1180</v>
       </c>
       <c r="B398" s="5">
-        <f>IF(ISNA(VLOOKUP(H398,$A$2:$C$1005,3,1)),C398,VLOOKUP(H398,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H398,$A$2:$C$1011,3,1)),C398,VLOOKUP(H398,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C398" s="1">
@@ -19669,7 +19733,7 @@
         <v>1182</v>
       </c>
       <c r="B399" s="5">
-        <f>IF(ISNA(VLOOKUP(H399,$A$2:$C$1005,3,1)),C399,VLOOKUP(H399,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H399,$A$2:$C$1011,3,1)),C399,VLOOKUP(H399,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C399" s="1">
@@ -19702,7 +19766,7 @@
         <v>1184</v>
       </c>
       <c r="B400" s="5">
-        <f>IF(ISNA(VLOOKUP(H400,$A$2:$C$1005,3,1)),C400,VLOOKUP(H400,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H400,$A$2:$C$1011,3,1)),C400,VLOOKUP(H400,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C400" s="1">
@@ -19735,7 +19799,7 @@
         <v>1187</v>
       </c>
       <c r="B401" s="5">
-        <f>IF(ISNA(VLOOKUP(H401,$A$2:$C$1005,3,1)),C401,VLOOKUP(H401,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H401,$A$2:$C$1011,3,1)),C401,VLOOKUP(H401,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C401" s="1">
@@ -19768,7 +19832,7 @@
         <v>1190</v>
       </c>
       <c r="B402" s="5">
-        <f>IF(ISNA(VLOOKUP(H402,$A$2:$C$1005,3,1)),C402,VLOOKUP(H402,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H402,$A$2:$C$1011,3,1)),C402,VLOOKUP(H402,$A$2:$C$1011,3,1))</f>
         <v>205</v>
       </c>
       <c r="C402" s="1">
@@ -19801,7 +19865,7 @@
         <v>1193</v>
       </c>
       <c r="B403" s="5">
-        <f>IF(ISNA(VLOOKUP(H403,$A$2:$C$1005,3,1)),C403,VLOOKUP(H403,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H403,$A$2:$C$1011,3,1)),C403,VLOOKUP(H403,$A$2:$C$1011,3,1))</f>
         <v>11</v>
       </c>
       <c r="C403" s="1">
@@ -19834,7 +19898,7 @@
         <v>1196</v>
       </c>
       <c r="B404" s="5">
-        <f>IF(ISNA(VLOOKUP(H404,$A$2:$C$1005,3,1)),C404,VLOOKUP(H404,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H404,$A$2:$C$1011,3,1)),C404,VLOOKUP(H404,$A$2:$C$1011,3,1))</f>
         <v>18</v>
       </c>
       <c r="C404" s="1">
@@ -19867,7 +19931,7 @@
         <v>1199</v>
       </c>
       <c r="B405" s="5">
-        <f>IF(ISNA(VLOOKUP(H405,$A$2:$C$1005,3,1)),C405,VLOOKUP(H405,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H405,$A$2:$C$1011,3,1)),C405,VLOOKUP(H405,$A$2:$C$1011,3,1))</f>
         <v>25</v>
       </c>
       <c r="C405" s="1">
@@ -19900,7 +19964,7 @@
         <v>1202</v>
       </c>
       <c r="B406" s="5">
-        <f>IF(ISNA(VLOOKUP(H406,$A$2:$C$1005,3,1)),C406,VLOOKUP(H406,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H406,$A$2:$C$1011,3,1)),C406,VLOOKUP(H406,$A$2:$C$1011,3,1))</f>
         <v>29</v>
       </c>
       <c r="C406" s="1">
@@ -19933,7 +19997,7 @@
         <v>1205</v>
       </c>
       <c r="B407" s="5">
-        <f>IF(ISNA(VLOOKUP(H407,$A$2:$C$1005,3,1)),C407,VLOOKUP(H407,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H407,$A$2:$C$1011,3,1)),C407,VLOOKUP(H407,$A$2:$C$1011,3,1))</f>
         <v>34</v>
       </c>
       <c r="C407" s="1">
@@ -19966,7 +20030,7 @@
         <v>1208</v>
       </c>
       <c r="B408" s="5">
-        <f>IF(ISNA(VLOOKUP(H408,$A$2:$C$1005,3,1)),C408,VLOOKUP(H408,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H408,$A$2:$C$1011,3,1)),C408,VLOOKUP(H408,$A$2:$C$1011,3,1))</f>
         <v>38</v>
       </c>
       <c r="C408" s="1">
@@ -19999,7 +20063,7 @@
         <v>1211</v>
       </c>
       <c r="B409" s="5">
-        <f>IF(ISNA(VLOOKUP(H409,$A$2:$C$1005,3,1)),C409,VLOOKUP(H409,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H409,$A$2:$C$1011,3,1)),C409,VLOOKUP(H409,$A$2:$C$1011,3,1))</f>
         <v>42</v>
       </c>
       <c r="C409" s="1">
@@ -20032,7 +20096,7 @@
         <v>1214</v>
       </c>
       <c r="B410" s="5">
-        <f>IF(ISNA(VLOOKUP(H410,$A$2:$C$1005,3,1)),C410,VLOOKUP(H410,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H410,$A$2:$C$1011,3,1)),C410,VLOOKUP(H410,$A$2:$C$1011,3,1))</f>
         <v>46</v>
       </c>
       <c r="C410" s="1">
@@ -20065,7 +20129,7 @@
         <v>1217</v>
       </c>
       <c r="B411" s="5">
-        <f>IF(ISNA(VLOOKUP(H411,$A$2:$C$1005,3,1)),C411,VLOOKUP(H411,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H411,$A$2:$C$1011,3,1)),C411,VLOOKUP(H411,$A$2:$C$1011,3,1))</f>
         <v>50</v>
       </c>
       <c r="C411" s="1">
@@ -20098,7 +20162,7 @@
         <v>1220</v>
       </c>
       <c r="B412" s="5">
-        <f>IF(ISNA(VLOOKUP(H412,$A$2:$C$1005,3,1)),C412,VLOOKUP(H412,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H412,$A$2:$C$1011,3,1)),C412,VLOOKUP(H412,$A$2:$C$1011,3,1))</f>
         <v>54</v>
       </c>
       <c r="C412" s="1">
@@ -20131,7 +20195,7 @@
         <v>1223</v>
       </c>
       <c r="B413" s="5">
-        <f>IF(ISNA(VLOOKUP(H413,$A$2:$C$1005,3,1)),C413,VLOOKUP(H413,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H413,$A$2:$C$1011,3,1)),C413,VLOOKUP(H413,$A$2:$C$1011,3,1))</f>
         <v>510</v>
       </c>
       <c r="C413" s="1">
@@ -20164,7 +20228,7 @@
         <v>1226</v>
       </c>
       <c r="B414" s="5">
-        <f>IF(ISNA(VLOOKUP(H414,$A$2:$C$1005,3,1)),C414,VLOOKUP(H414,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H414,$A$2:$C$1011,3,1)),C414,VLOOKUP(H414,$A$2:$C$1011,3,1))</f>
         <v>514</v>
       </c>
       <c r="C414" s="1">
@@ -20197,7 +20261,7 @@
         <v>1229</v>
       </c>
       <c r="B415" s="5">
-        <f>IF(ISNA(VLOOKUP(H415,$A$2:$C$1005,3,1)),C415,VLOOKUP(H415,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H415,$A$2:$C$1011,3,1)),C415,VLOOKUP(H415,$A$2:$C$1011,3,1))</f>
         <v>567</v>
       </c>
       <c r="C415" s="1">
@@ -20230,7 +20294,7 @@
         <v>1232</v>
       </c>
       <c r="B416" s="5">
-        <f>IF(ISNA(VLOOKUP(H416,$A$2:$C$1005,3,1)),C416,VLOOKUP(H416,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H416,$A$2:$C$1011,3,1)),C416,VLOOKUP(H416,$A$2:$C$1011,3,1))</f>
         <v>572</v>
       </c>
       <c r="C416" s="1">
@@ -20263,7 +20327,7 @@
         <v>1235</v>
       </c>
       <c r="B417" s="5">
-        <f>IF(ISNA(VLOOKUP(H417,$A$2:$C$1005,3,1)),C417,VLOOKUP(H417,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H417,$A$2:$C$1011,3,1)),C417,VLOOKUP(H417,$A$2:$C$1011,3,1))</f>
         <v>562</v>
       </c>
       <c r="C417" s="1">
@@ -20296,7 +20360,7 @@
         <v>1238</v>
       </c>
       <c r="B418" s="5">
-        <f>IF(ISNA(VLOOKUP(H418,$A$2:$C$1005,3,1)),C418,VLOOKUP(H418,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H418,$A$2:$C$1011,3,1)),C418,VLOOKUP(H418,$A$2:$C$1011,3,1))</f>
         <v>578</v>
       </c>
       <c r="C418" s="1">
@@ -20329,7 +20393,7 @@
         <v>1241</v>
       </c>
       <c r="B419" s="5">
-        <f>IF(ISNA(VLOOKUP(H419,$A$2:$C$1005,3,1)),C419,VLOOKUP(H419,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H419,$A$2:$C$1011,3,1)),C419,VLOOKUP(H419,$A$2:$C$1011,3,1))</f>
         <v>583</v>
       </c>
       <c r="C419" s="1">
@@ -20362,7 +20426,7 @@
         <v>1245</v>
       </c>
       <c r="B420" s="5">
-        <f>IF(ISNA(VLOOKUP(H420,$A$2:$C$1005,3,1)),C420,VLOOKUP(H420,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H420,$A$2:$C$1011,3,1)),C420,VLOOKUP(H420,$A$2:$C$1011,3,1))</f>
         <v>586</v>
       </c>
       <c r="C420" s="1">
@@ -20395,7 +20459,7 @@
         <v>1248</v>
       </c>
       <c r="B421" s="5">
-        <f>IF(ISNA(VLOOKUP(H421,$A$2:$C$1005,3,1)),C421,VLOOKUP(H421,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H421,$A$2:$C$1011,3,1)),C421,VLOOKUP(H421,$A$2:$C$1011,3,1))</f>
         <v>567</v>
       </c>
       <c r="C421" s="1">
@@ -20428,7 +20492,7 @@
         <v>1251</v>
       </c>
       <c r="B422" s="5">
-        <f>IF(ISNA(VLOOKUP(H422,$A$2:$C$1005,3,1)),C422,VLOOKUP(H422,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H422,$A$2:$C$1011,3,1)),C422,VLOOKUP(H422,$A$2:$C$1011,3,1))</f>
         <v>562</v>
       </c>
       <c r="C422" s="1">
@@ -20461,7 +20525,7 @@
         <v>1244</v>
       </c>
       <c r="B423" s="5">
-        <f>IF(ISNA(VLOOKUP(H423,$A$2:$C$1005,3,1)),C423,VLOOKUP(H423,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H423,$A$2:$C$1011,3,1)),C423,VLOOKUP(H423,$A$2:$C$1011,3,1))</f>
         <v>583</v>
       </c>
       <c r="C423" s="1">
@@ -20494,7 +20558,7 @@
         <v>1255</v>
       </c>
       <c r="B424" s="5">
-        <f>IF(ISNA(VLOOKUP(H424,$A$2:$C$1005,3,1)),C424,VLOOKUP(H424,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H424,$A$2:$C$1011,3,1)),C424,VLOOKUP(H424,$A$2:$C$1011,3,1))</f>
         <v>572</v>
       </c>
       <c r="C424" s="1">
@@ -20527,7 +20591,7 @@
         <v>1258</v>
       </c>
       <c r="B425" s="5">
-        <f>IF(ISNA(VLOOKUP(H425,$A$2:$C$1005,3,1)),C425,VLOOKUP(H425,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H425,$A$2:$C$1011,3,1)),C425,VLOOKUP(H425,$A$2:$C$1011,3,1))</f>
         <v>578</v>
       </c>
       <c r="C425" s="1">
@@ -20560,7 +20624,7 @@
         <v>1261</v>
       </c>
       <c r="B426" s="5">
-        <f>IF(ISNA(VLOOKUP(H426,$A$2:$C$1005,3,1)),C426,VLOOKUP(H426,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H426,$A$2:$C$1011,3,1)),C426,VLOOKUP(H426,$A$2:$C$1011,3,1))</f>
         <v>587</v>
       </c>
       <c r="C426" s="1">
@@ -20593,7 +20657,7 @@
         <v>1264</v>
       </c>
       <c r="B427" s="5">
-        <f>IF(ISNA(VLOOKUP(H427,$A$2:$C$1005,3,1)),C427,VLOOKUP(H427,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H427,$A$2:$C$1011,3,1)),C427,VLOOKUP(H427,$A$2:$C$1011,3,1))</f>
         <v>567</v>
       </c>
       <c r="C427" s="1">
@@ -20626,7 +20690,7 @@
         <v>1267</v>
       </c>
       <c r="B428" s="5">
-        <f>IF(ISNA(VLOOKUP(H428,$A$2:$C$1005,3,1)),C428,VLOOKUP(H428,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H428,$A$2:$C$1011,3,1)),C428,VLOOKUP(H428,$A$2:$C$1011,3,1))</f>
         <v>562</v>
       </c>
       <c r="C428" s="1">
@@ -20659,7 +20723,7 @@
         <v>1270</v>
       </c>
       <c r="B429" s="5">
-        <f>IF(ISNA(VLOOKUP(H429,$A$2:$C$1005,3,1)),C429,VLOOKUP(H429,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H429,$A$2:$C$1011,3,1)),C429,VLOOKUP(H429,$A$2:$C$1011,3,1))</f>
         <v>583</v>
       </c>
       <c r="C429" s="1">
@@ -20692,7 +20756,7 @@
         <v>1273</v>
       </c>
       <c r="B430" s="5">
-        <f>IF(ISNA(VLOOKUP(H430,$A$2:$C$1005,3,1)),C430,VLOOKUP(H430,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H430,$A$2:$C$1011,3,1)),C430,VLOOKUP(H430,$A$2:$C$1011,3,1))</f>
         <v>567</v>
       </c>
       <c r="C430" s="1">
@@ -20725,7 +20789,7 @@
         <v>1274</v>
       </c>
       <c r="B431" s="5">
-        <f>IF(ISNA(VLOOKUP(H431,$A$2:$C$1005,3,1)),C431,VLOOKUP(H431,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H431,$A$2:$C$1011,3,1)),C431,VLOOKUP(H431,$A$2:$C$1011,3,1))</f>
         <v>572</v>
       </c>
       <c r="C431" s="1">
@@ -20758,7 +20822,7 @@
         <v>1275</v>
       </c>
       <c r="B432" s="5">
-        <f>IF(ISNA(VLOOKUP(H432,$A$2:$C$1005,3,1)),C432,VLOOKUP(H432,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H432,$A$2:$C$1011,3,1)),C432,VLOOKUP(H432,$A$2:$C$1011,3,1))</f>
         <v>562</v>
       </c>
       <c r="C432" s="1">
@@ -20791,7 +20855,7 @@
         <v>1276</v>
       </c>
       <c r="B433" s="5">
-        <f>IF(ISNA(VLOOKUP(H433,$A$2:$C$1005,3,1)),C433,VLOOKUP(H433,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H433,$A$2:$C$1011,3,1)),C433,VLOOKUP(H433,$A$2:$C$1011,3,1))</f>
         <v>578</v>
       </c>
       <c r="C433" s="1">
@@ -20824,7 +20888,7 @@
         <v>1277</v>
       </c>
       <c r="B434" s="5">
-        <f>IF(ISNA(VLOOKUP(H434,$A$2:$C$1005,3,1)),C434,VLOOKUP(H434,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H434,$A$2:$C$1011,3,1)),C434,VLOOKUP(H434,$A$2:$C$1011,3,1))</f>
         <v>572</v>
       </c>
       <c r="C434" s="1">
@@ -20857,7 +20921,7 @@
         <v>1280</v>
       </c>
       <c r="B435" s="5">
-        <f>IF(ISNA(VLOOKUP(H435,$A$2:$C$1005,3,1)),C435,VLOOKUP(H435,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H435,$A$2:$C$1011,3,1)),C435,VLOOKUP(H435,$A$2:$C$1011,3,1))</f>
         <v>578</v>
       </c>
       <c r="C435" s="1">
@@ -20890,7 +20954,7 @@
         <v>1283</v>
       </c>
       <c r="B436" s="5">
-        <f>IF(ISNA(VLOOKUP(H436,$A$2:$C$1005,3,1)),C436,VLOOKUP(H436,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H436,$A$2:$C$1011,3,1)),C436,VLOOKUP(H436,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C436" s="1">
@@ -20923,11 +20987,11 @@
         <v>1286</v>
       </c>
       <c r="B437" s="5">
-        <f>IF(ISNA(VLOOKUP(H437,$A$2:$C$1005,3,1)),C437,VLOOKUP(H437,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H437,$A$2:$C$1011,3,1)),C437,VLOOKUP(H437,$A$2:$C$1011,3,1))</f>
+        <v>664</v>
       </c>
       <c r="C437" s="1">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="D437" s="2" t="s">
         <v>1287</v>
@@ -20943,12 +21007,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A437,3,4)))</f>
         <v>∂</v>
       </c>
-      <c r="H437" s="1" t="s">
-        <v>1289</v>
+      <c r="H437" s="17" t="str">
+        <f>A437</f>
+        <v>U+2202</v>
       </c>
       <c r="I437" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H437,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∂</v>
       </c>
     </row>
     <row r="438" spans="1:11" s="16" customFormat="1" ht="17" customHeight="1">
@@ -20956,11 +21021,11 @@
         <v>1290</v>
       </c>
       <c r="B438" s="5">
-        <f>IF(ISNA(VLOOKUP(H438,$A$2:$C$1005,3,1)),C438,VLOOKUP(H438,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H438,$A$2:$C$1011,3,1)),C438,VLOOKUP(H438,$A$2:$C$1011,3,1))</f>
+        <v>665</v>
       </c>
       <c r="C438" s="1">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>1291</v>
@@ -20976,12 +21041,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A438,3,4)))</f>
         <v>∃</v>
       </c>
-      <c r="H438" s="1" t="s">
-        <v>1289</v>
+      <c r="H438" s="17" t="str">
+        <f>A438</f>
+        <v>U+2203</v>
       </c>
       <c r="I438" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H438,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∃</v>
       </c>
       <c r="J438" s="4"/>
       <c r="K438" s="2"/>
@@ -20991,11 +21057,11 @@
         <v>1293</v>
       </c>
       <c r="B439" s="5">
-        <f>IF(ISNA(VLOOKUP(H439,$A$2:$C$1005,3,1)),C439,VLOOKUP(H439,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H439,$A$2:$C$1011,3,1)),C439,VLOOKUP(H439,$A$2:$C$1011,3,1))</f>
+        <v>666</v>
       </c>
       <c r="C439" s="1">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="D439" s="2" t="s">
         <v>1294</v>
@@ -21011,12 +21077,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A439,3,4)))</f>
         <v>∄</v>
       </c>
-      <c r="H439" s="1" t="s">
-        <v>1289</v>
+      <c r="H439" s="17" t="str">
+        <f>A439</f>
+        <v>U+2204</v>
       </c>
       <c r="I439" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H439,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∄</v>
       </c>
     </row>
     <row r="440" spans="1:11" ht="17" customHeight="1">
@@ -21024,11 +21091,11 @@
         <v>1296</v>
       </c>
       <c r="B440" s="5">
-        <f>IF(ISNA(VLOOKUP(H440,$A$2:$C$1005,3,1)),C440,VLOOKUP(H440,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H440,$A$2:$C$1011,3,1)),C440,VLOOKUP(H440,$A$2:$C$1011,3,1))</f>
+        <v>667</v>
       </c>
       <c r="C440" s="1">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="D440" s="2" t="s">
         <v>1297</v>
@@ -21044,12 +21111,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A440,3,4)))</f>
         <v>∅</v>
       </c>
-      <c r="H440" s="1" t="s">
-        <v>1289</v>
+      <c r="H440" s="17" t="str">
+        <f>A440</f>
+        <v>U+2205</v>
       </c>
       <c r="I440" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H440,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∅</v>
       </c>
     </row>
     <row r="441" spans="1:11" ht="17" customHeight="1">
@@ -21057,11 +21125,11 @@
         <v>1299</v>
       </c>
       <c r="B441" s="5">
-        <f>IF(ISNA(VLOOKUP(H441,$A$2:$C$1005,3,1)),C441,VLOOKUP(H441,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H441,$A$2:$C$1011,3,1)),C441,VLOOKUP(H441,$A$2:$C$1011,3,1))</f>
+        <v>668</v>
       </c>
       <c r="C441" s="1">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D441" s="2" t="s">
         <v>1300</v>
@@ -21077,12 +21145,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A441,3,4)))</f>
         <v>∆</v>
       </c>
-      <c r="H441" s="1" t="s">
-        <v>1289</v>
+      <c r="H441" s="17" t="str">
+        <f>A441</f>
+        <v>U+2206</v>
       </c>
       <c r="I441" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H441,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∆</v>
       </c>
     </row>
     <row r="442" spans="1:11" ht="17" customHeight="1">
@@ -21090,11 +21159,11 @@
         <v>1302</v>
       </c>
       <c r="B442" s="5">
-        <f>IF(ISNA(VLOOKUP(H442,$A$2:$C$1005,3,1)),C442,VLOOKUP(H442,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H442,$A$2:$C$1011,3,1)),C442,VLOOKUP(H442,$A$2:$C$1011,3,1))</f>
+        <v>669</v>
       </c>
       <c r="C442" s="1">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D442" s="2" t="s">
         <v>1303</v>
@@ -21110,12 +21179,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A442,3,4)))</f>
         <v>∇</v>
       </c>
-      <c r="H442" s="1" t="s">
-        <v>1289</v>
+      <c r="H442" s="17" t="str">
+        <f>A442</f>
+        <v>U+2207</v>
       </c>
       <c r="I442" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H442,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∇</v>
       </c>
     </row>
     <row r="443" spans="1:11" ht="17" customHeight="1">
@@ -21123,11 +21193,11 @@
         <v>1305</v>
       </c>
       <c r="B443" s="5">
-        <f>IF(ISNA(VLOOKUP(H443,$A$2:$C$1005,3,1)),C443,VLOOKUP(H443,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H443,$A$2:$C$1011,3,1)),C443,VLOOKUP(H443,$A$2:$C$1011,3,1))</f>
+        <v>670</v>
       </c>
       <c r="C443" s="1">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>1306</v>
@@ -21143,12 +21213,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A443,3,4)))</f>
         <v>∈</v>
       </c>
-      <c r="H443" s="1" t="s">
-        <v>1289</v>
+      <c r="H443" s="17" t="str">
+        <f>A443</f>
+        <v>U+2208</v>
       </c>
       <c r="I443" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H443,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∈</v>
       </c>
     </row>
     <row r="444" spans="1:11" ht="17" customHeight="1">
@@ -21156,11 +21227,11 @@
         <v>1308</v>
       </c>
       <c r="B444" s="5">
-        <f>IF(ISNA(VLOOKUP(H444,$A$2:$C$1005,3,1)),C444,VLOOKUP(H444,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H444,$A$2:$C$1011,3,1)),C444,VLOOKUP(H444,$A$2:$C$1011,3,1))</f>
+        <v>671</v>
       </c>
       <c r="C444" s="1">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D444" s="2" t="s">
         <v>1309</v>
@@ -21176,12 +21247,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A444,3,4)))</f>
         <v>∉</v>
       </c>
-      <c r="H444" s="1" t="s">
-        <v>1289</v>
+      <c r="H444" s="17" t="str">
+        <f>A444</f>
+        <v>U+2209</v>
       </c>
       <c r="I444" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H444,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∉</v>
       </c>
     </row>
     <row r="445" spans="1:11" ht="17" customHeight="1">
@@ -21189,11 +21261,11 @@
         <v>1311</v>
       </c>
       <c r="B445" s="5">
-        <f>IF(ISNA(VLOOKUP(H445,$A$2:$C$1005,3,1)),C445,VLOOKUP(H445,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H445,$A$2:$C$1011,3,1)),C445,VLOOKUP(H445,$A$2:$C$1011,3,1))</f>
+        <v>672</v>
       </c>
       <c r="C445" s="1">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="D445" s="2" t="s">
         <v>1312</v>
@@ -21209,12 +21281,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A445,3,4)))</f>
         <v>∋</v>
       </c>
-      <c r="H445" s="1" t="s">
-        <v>1289</v>
+      <c r="H445" s="17" t="str">
+        <f>A445</f>
+        <v>U+220b</v>
       </c>
       <c r="I445" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H445,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∋</v>
       </c>
     </row>
     <row r="446" spans="1:11" ht="17" customHeight="1">
@@ -21222,11 +21295,11 @@
         <v>1314</v>
       </c>
       <c r="B446" s="5">
-        <f>IF(ISNA(VLOOKUP(H446,$A$2:$C$1005,3,1)),C446,VLOOKUP(H446,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H446,$A$2:$C$1011,3,1)),C446,VLOOKUP(H446,$A$2:$C$1011,3,1))</f>
+        <v>673</v>
       </c>
       <c r="C446" s="1">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="D446" s="2" t="s">
         <v>1315</v>
@@ -21242,12 +21315,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A446,3,4)))</f>
         <v>∌</v>
       </c>
-      <c r="H446" s="1" t="s">
-        <v>1289</v>
+      <c r="H446" s="17" t="str">
+        <f>A446</f>
+        <v>U+220c</v>
       </c>
       <c r="I446" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H446,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∌</v>
       </c>
     </row>
     <row r="447" spans="1:11" ht="17" customHeight="1">
@@ -21255,7 +21329,7 @@
         <v>1317</v>
       </c>
       <c r="B447" s="5">
-        <f>IF(ISNA(VLOOKUP(H447,$A$2:$C$1005,3,1)),C447,VLOOKUP(H447,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H447,$A$2:$C$1011,3,1)),C447,VLOOKUP(H447,$A$2:$C$1011,3,1))</f>
         <v>11</v>
       </c>
       <c r="C447" s="1">
@@ -21288,7 +21362,7 @@
         <v>1320</v>
       </c>
       <c r="B448" s="5">
-        <f>IF(ISNA(VLOOKUP(H448,$A$2:$C$1005,3,1)),C448,VLOOKUP(H448,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H448,$A$2:$C$1011,3,1)),C448,VLOOKUP(H448,$A$2:$C$1011,3,1))</f>
         <v>459</v>
       </c>
       <c r="C448" s="1">
@@ -21321,7 +21395,7 @@
         <v>1323</v>
       </c>
       <c r="B449" s="5">
-        <f>IF(ISNA(VLOOKUP(H449,$A$2:$C$1005,3,1)),C449,VLOOKUP(H449,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H449,$A$2:$C$1011,3,1)),C449,VLOOKUP(H449,$A$2:$C$1011,3,1))</f>
         <v>467</v>
       </c>
       <c r="C449" s="1">
@@ -21354,7 +21428,7 @@
         <v>1326</v>
       </c>
       <c r="B450" s="5">
-        <f>IF(ISNA(VLOOKUP(H450,$A$2:$C$1005,3,1)),C450,VLOOKUP(H450,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H450,$A$2:$C$1011,3,1)),C450,VLOOKUP(H450,$A$2:$C$1011,3,1))</f>
         <v>514</v>
       </c>
       <c r="C450" s="1">
@@ -21387,7 +21461,7 @@
         <v>1329</v>
       </c>
       <c r="B451" s="5">
-        <f>IF(ISNA(VLOOKUP(H451,$A$2:$C$1005,3,1)),C451,VLOOKUP(H451,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H451,$A$2:$C$1011,3,1)),C451,VLOOKUP(H451,$A$2:$C$1011,3,1))</f>
         <v>519</v>
       </c>
       <c r="C451" s="1">
@@ -21420,7 +21494,7 @@
         <v>1332</v>
       </c>
       <c r="B452" s="5">
-        <f>IF(ISNA(VLOOKUP(H452,$A$2:$C$1005,3,1)),C452,VLOOKUP(H452,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H452,$A$2:$C$1011,3,1)),C452,VLOOKUP(H452,$A$2:$C$1011,3,1))</f>
         <v>519</v>
       </c>
       <c r="C452" s="1">
@@ -21453,7 +21527,7 @@
         <v>1335</v>
       </c>
       <c r="B453" s="5">
-        <f>IF(ISNA(VLOOKUP(H453,$A$2:$C$1005,3,1)),C453,VLOOKUP(H453,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H453,$A$2:$C$1011,3,1)),C453,VLOOKUP(H453,$A$2:$C$1011,3,1))</f>
         <v>621</v>
       </c>
       <c r="C453" s="1">
@@ -21486,7 +21560,7 @@
         <v>1338</v>
       </c>
       <c r="B454" s="5">
-        <f>IF(ISNA(VLOOKUP(H454,$A$2:$C$1005,3,1)),C454,VLOOKUP(H454,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H454,$A$2:$C$1011,3,1)),C454,VLOOKUP(H454,$A$2:$C$1011,3,1))</f>
         <v>29</v>
       </c>
       <c r="C454" s="1">
@@ -21519,7 +21593,7 @@
         <v>1341</v>
       </c>
       <c r="B455" s="5">
-        <f>IF(ISNA(VLOOKUP(H455,$A$2:$C$1005,3,1)),C455,VLOOKUP(H455,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H455,$A$2:$C$1011,3,1)),C455,VLOOKUP(H455,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C455" s="1">
@@ -21552,7 +21626,7 @@
         <v>1344</v>
       </c>
       <c r="B456" s="5">
-        <f>IF(ISNA(VLOOKUP(H456,$A$2:$C$1005,3,1)),C456,VLOOKUP(H456,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H456,$A$2:$C$1011,3,1)),C456,VLOOKUP(H456,$A$2:$C$1011,3,1))</f>
         <v>621</v>
       </c>
       <c r="C456" s="1">
@@ -21585,7 +21659,7 @@
         <v>1144</v>
       </c>
       <c r="B457" s="5">
-        <f>IF(ISNA(VLOOKUP(H457,$A$2:$C$1005,3,1)),C457,VLOOKUP(H457,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H457,$A$2:$C$1011,3,1)),C457,VLOOKUP(H457,$A$2:$C$1011,3,1))</f>
         <v>623</v>
       </c>
       <c r="C457" s="1">
@@ -21618,7 +21692,7 @@
         <v>1349</v>
       </c>
       <c r="B458" s="5">
-        <f>IF(ISNA(VLOOKUP(H458,$A$2:$C$1005,3,1)),C458,VLOOKUP(H458,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H458,$A$2:$C$1011,3,1)),C458,VLOOKUP(H458,$A$2:$C$1011,3,1))</f>
         <v>635</v>
       </c>
       <c r="C458" s="1">
@@ -21651,7 +21725,7 @@
         <v>1352</v>
       </c>
       <c r="B459" s="5">
-        <f>IF(ISNA(VLOOKUP(H459,$A$2:$C$1005,3,1)),C459,VLOOKUP(H459,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H459,$A$2:$C$1011,3,1)),C459,VLOOKUP(H459,$A$2:$C$1011,3,1))</f>
         <v>637</v>
       </c>
       <c r="C459" s="1">
@@ -21684,7 +21758,7 @@
         <v>1355</v>
       </c>
       <c r="B460" s="5">
-        <f>IF(ISNA(VLOOKUP(H460,$A$2:$C$1005,3,1)),C460,VLOOKUP(H460,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H460,$A$2:$C$1011,3,1)),C460,VLOOKUP(H460,$A$2:$C$1011,3,1))</f>
         <v>637</v>
       </c>
       <c r="C460" s="1">
@@ -21717,7 +21791,7 @@
         <v>1358</v>
       </c>
       <c r="B461" s="5">
-        <f>IF(ISNA(VLOOKUP(H461,$A$2:$C$1005,3,1)),C461,VLOOKUP(H461,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H461,$A$2:$C$1011,3,1)),C461,VLOOKUP(H461,$A$2:$C$1011,3,1))</f>
         <v>637</v>
       </c>
       <c r="C461" s="1">
@@ -21750,7 +21824,7 @@
         <v>1361</v>
       </c>
       <c r="B462" s="5">
-        <f>IF(ISNA(VLOOKUP(H462,$A$2:$C$1005,3,1)),C462,VLOOKUP(H462,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H462,$A$2:$C$1011,3,1)),C462,VLOOKUP(H462,$A$2:$C$1011,3,1))</f>
         <v>595</v>
       </c>
       <c r="C462" s="1">
@@ -21783,7 +21857,7 @@
         <v>1364</v>
       </c>
       <c r="B463" s="5">
-        <f>IF(ISNA(VLOOKUP(H463,$A$2:$C$1005,3,1)),C463,VLOOKUP(H463,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H463,$A$2:$C$1011,3,1)),C463,VLOOKUP(H463,$A$2:$C$1011,3,1))</f>
         <v>595</v>
       </c>
       <c r="C463" s="1">
@@ -21816,7 +21890,7 @@
         <v>1367</v>
       </c>
       <c r="B464" s="5">
-        <f>IF(ISNA(VLOOKUP(H464,$A$2:$C$1005,3,1)),C464,VLOOKUP(H464,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H464,$A$2:$C$1011,3,1)),C464,VLOOKUP(H464,$A$2:$C$1011,3,1))</f>
         <v>595</v>
       </c>
       <c r="C464" s="1">
@@ -21849,7 +21923,7 @@
         <v>1370</v>
       </c>
       <c r="B465" s="5">
-        <f>IF(ISNA(VLOOKUP(H465,$A$2:$C$1005,3,1)),C465,VLOOKUP(H465,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H465,$A$2:$C$1011,3,1)),C465,VLOOKUP(H465,$A$2:$C$1011,3,1))</f>
         <v>595</v>
       </c>
       <c r="C465" s="1">
@@ -21882,7 +21956,7 @@
         <v>1373</v>
       </c>
       <c r="B466" s="5">
-        <f>IF(ISNA(VLOOKUP(H466,$A$2:$C$1005,3,1)),C466,VLOOKUP(H466,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H466,$A$2:$C$1011,3,1)),C466,VLOOKUP(H466,$A$2:$C$1011,3,1))</f>
         <v>588</v>
       </c>
       <c r="C466" s="1">
@@ -21915,7 +21989,7 @@
         <v>1376</v>
       </c>
       <c r="B467" s="5">
-        <f>IF(ISNA(VLOOKUP(H467,$A$2:$C$1005,3,1)),C467,VLOOKUP(H467,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H467,$A$2:$C$1011,3,1)),C467,VLOOKUP(H467,$A$2:$C$1011,3,1))</f>
         <v>588</v>
       </c>
       <c r="C467" s="1">
@@ -21948,11 +22022,11 @@
         <v>1379</v>
       </c>
       <c r="B468" s="5">
-        <f>IF(ISNA(VLOOKUP(H468,$A$2:$C$1005,3,1)),C468,VLOOKUP(H468,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H468,$A$2:$C$1011,3,1)),C468,VLOOKUP(H468,$A$2:$C$1011,3,1))</f>
+        <v>674</v>
       </c>
       <c r="C468" s="1">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="D468" s="2" t="s">
         <v>1380</v>
@@ -21968,12 +22042,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A468,3,4)))</f>
         <v>∩</v>
       </c>
-      <c r="H468" s="1" t="s">
-        <v>1289</v>
+      <c r="H468" s="17" t="str">
+        <f>A468</f>
+        <v>U+2229</v>
       </c>
       <c r="I468" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H468,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∩</v>
       </c>
     </row>
     <row r="469" spans="1:9" ht="17" customHeight="1">
@@ -21981,11 +22056,11 @@
         <v>1382</v>
       </c>
       <c r="B469" s="5">
-        <f>IF(ISNA(VLOOKUP(H469,$A$2:$C$1005,3,1)),C469,VLOOKUP(H469,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H469,$A$2:$C$1011,3,1)),C469,VLOOKUP(H469,$A$2:$C$1011,3,1))</f>
+        <v>675</v>
       </c>
       <c r="C469" s="1">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D469" s="2" t="s">
         <v>1383</v>
@@ -22001,12 +22076,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A469,3,4)))</f>
         <v>∪</v>
       </c>
-      <c r="H469" s="1" t="s">
-        <v>1289</v>
+      <c r="H469" s="17" t="str">
+        <f>A469</f>
+        <v>U+222a</v>
       </c>
       <c r="I469" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H469,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∪</v>
       </c>
     </row>
     <row r="470" spans="1:9" ht="17" customHeight="1">
@@ -22014,7 +22090,7 @@
         <v>1385</v>
       </c>
       <c r="B470" s="5">
-        <f>IF(ISNA(VLOOKUP(H470,$A$2:$C$1005,3,1)),C470,VLOOKUP(H470,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H470,$A$2:$C$1011,3,1)),C470,VLOOKUP(H470,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C470" s="1">
@@ -22047,7 +22123,7 @@
         <v>1388</v>
       </c>
       <c r="B471" s="5">
-        <f>IF(ISNA(VLOOKUP(H471,$A$2:$C$1005,3,1)),C471,VLOOKUP(H471,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H471,$A$2:$C$1011,3,1)),C471,VLOOKUP(H471,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C471" s="1">
@@ -22080,7 +22156,7 @@
         <v>1391</v>
       </c>
       <c r="B472" s="5">
-        <f>IF(ISNA(VLOOKUP(H472,$A$2:$C$1005,3,1)),C472,VLOOKUP(H472,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H472,$A$2:$C$1011,3,1)),C472,VLOOKUP(H472,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C472" s="1">
@@ -22113,7 +22189,7 @@
         <v>1394</v>
       </c>
       <c r="B473" s="5">
-        <f>IF(ISNA(VLOOKUP(H473,$A$2:$C$1005,3,1)),C473,VLOOKUP(H473,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H473,$A$2:$C$1011,3,1)),C473,VLOOKUP(H473,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C473" s="1">
@@ -22146,7 +22222,7 @@
         <v>1397</v>
       </c>
       <c r="B474" s="5">
-        <f>IF(ISNA(VLOOKUP(H474,$A$2:$C$1005,3,1)),C474,VLOOKUP(H474,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H474,$A$2:$C$1011,3,1)),C474,VLOOKUP(H474,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C474" s="1">
@@ -22179,7 +22255,7 @@
         <v>1400</v>
       </c>
       <c r="B475" s="5">
-        <f>IF(ISNA(VLOOKUP(H475,$A$2:$C$1005,3,1)),C475,VLOOKUP(H475,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H475,$A$2:$C$1011,3,1)),C475,VLOOKUP(H475,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C475" s="1">
@@ -22212,7 +22288,7 @@
         <v>1403</v>
       </c>
       <c r="B476" s="5">
-        <f>IF(ISNA(VLOOKUP(H476,$A$2:$C$1005,3,1)),C476,VLOOKUP(H476,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H476,$A$2:$C$1011,3,1)),C476,VLOOKUP(H476,$A$2:$C$1011,3,1))</f>
         <v>540</v>
       </c>
       <c r="C476" s="1">
@@ -22245,7 +22321,7 @@
         <v>1406</v>
       </c>
       <c r="B477" s="5">
-        <f>IF(ISNA(VLOOKUP(H477,$A$2:$C$1005,3,1)),C477,VLOOKUP(H477,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H477,$A$2:$C$1011,3,1)),C477,VLOOKUP(H477,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C477" s="1">
@@ -22278,7 +22354,7 @@
         <v>1409</v>
       </c>
       <c r="B478" s="5">
-        <f>IF(ISNA(VLOOKUP(H478,$A$2:$C$1005,3,1)),C478,VLOOKUP(H478,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H478,$A$2:$C$1011,3,1)),C478,VLOOKUP(H478,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C478" s="1">
@@ -22311,7 +22387,7 @@
         <v>1412</v>
       </c>
       <c r="B479" s="5">
-        <f>IF(ISNA(VLOOKUP(H479,$A$2:$C$1005,3,1)),C479,VLOOKUP(H479,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H479,$A$2:$C$1011,3,1)),C479,VLOOKUP(H479,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C479" s="1">
@@ -22344,7 +22420,7 @@
         <v>1415</v>
       </c>
       <c r="B480" s="5">
-        <f>IF(ISNA(VLOOKUP(H480,$A$2:$C$1005,3,1)),C480,VLOOKUP(H480,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H480,$A$2:$C$1011,3,1)),C480,VLOOKUP(H480,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C480" s="1">
@@ -22377,7 +22453,7 @@
         <v>1418</v>
       </c>
       <c r="B481" s="5">
-        <f>IF(ISNA(VLOOKUP(H481,$A$2:$C$1005,3,1)),C481,VLOOKUP(H481,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H481,$A$2:$C$1011,3,1)),C481,VLOOKUP(H481,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C481" s="1">
@@ -22410,7 +22486,7 @@
         <v>1421</v>
       </c>
       <c r="B482" s="5">
-        <f>IF(ISNA(VLOOKUP(H482,$A$2:$C$1005,3,1)),C482,VLOOKUP(H482,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H482,$A$2:$C$1011,3,1)),C482,VLOOKUP(H482,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C482" s="1">
@@ -22443,7 +22519,7 @@
         <v>1424</v>
       </c>
       <c r="B483" s="5">
-        <f>IF(ISNA(VLOOKUP(H483,$A$2:$C$1005,3,1)),C483,VLOOKUP(H483,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H483,$A$2:$C$1011,3,1)),C483,VLOOKUP(H483,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C483" s="1">
@@ -22476,7 +22552,7 @@
         <v>1427</v>
       </c>
       <c r="B484" s="5">
-        <f>IF(ISNA(VLOOKUP(H484,$A$2:$C$1005,3,1)),C484,VLOOKUP(H484,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H484,$A$2:$C$1011,3,1)),C484,VLOOKUP(H484,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C484" s="1">
@@ -22509,7 +22585,7 @@
         <v>1430</v>
       </c>
       <c r="B485" s="5">
-        <f>IF(ISNA(VLOOKUP(H485,$A$2:$C$1005,3,1)),C485,VLOOKUP(H485,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H485,$A$2:$C$1011,3,1)),C485,VLOOKUP(H485,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C485" s="1">
@@ -22542,7 +22618,7 @@
         <v>107</v>
       </c>
       <c r="B486" s="5">
-        <f>IF(ISNA(VLOOKUP(H486,$A$2:$C$1005,3,1)),C486,VLOOKUP(H486,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H486,$A$2:$C$1011,3,1)),C486,VLOOKUP(H486,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C486" s="1">
@@ -22575,7 +22651,7 @@
         <v>1435</v>
       </c>
       <c r="B487" s="5">
-        <f>IF(ISNA(VLOOKUP(H487,$A$2:$C$1005,3,1)),C487,VLOOKUP(H487,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H487,$A$2:$C$1011,3,1)),C487,VLOOKUP(H487,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C487" s="1">
@@ -22608,11 +22684,11 @@
         <v>1438</v>
       </c>
       <c r="B488" s="5">
-        <f>IF(ISNA(VLOOKUP(H488,$A$2:$C$1005,3,1)),C488,VLOOKUP(H488,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H488,$A$2:$C$1011,3,1)),C488,VLOOKUP(H488,$A$2:$C$1011,3,1))</f>
+        <v>676</v>
       </c>
       <c r="C488" s="1">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="D488" s="2" t="s">
         <v>1439</v>
@@ -22628,12 +22704,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A488,3,4)))</f>
         <v>⊂</v>
       </c>
-      <c r="H488" s="1" t="s">
-        <v>1289</v>
+      <c r="H488" s="17" t="str">
+        <f>A488</f>
+        <v>U+2282</v>
       </c>
       <c r="I488" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H488,3,4)))</f>
-        <v>Ɐ</v>
+        <v>⊂</v>
       </c>
     </row>
     <row r="489" spans="1:9" ht="17" customHeight="1">
@@ -22641,11 +22718,11 @@
         <v>1441</v>
       </c>
       <c r="B489" s="5">
-        <f>IF(ISNA(VLOOKUP(H489,$A$2:$C$1005,3,1)),C489,VLOOKUP(H489,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H489,$A$2:$C$1011,3,1)),C489,VLOOKUP(H489,$A$2:$C$1011,3,1))</f>
+        <v>677</v>
       </c>
       <c r="C489" s="1">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="D489" s="2" t="s">
         <v>1442</v>
@@ -22661,12 +22738,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A489,3,4)))</f>
         <v>⊄</v>
       </c>
-      <c r="H489" s="1" t="s">
-        <v>1289</v>
+      <c r="H489" s="17" t="str">
+        <f>A489</f>
+        <v>U+2284</v>
       </c>
       <c r="I489" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H489,3,4)))</f>
-        <v>Ɐ</v>
+        <v>⊄</v>
       </c>
     </row>
     <row r="490" spans="1:9" ht="17" customHeight="1">
@@ -22674,7 +22752,7 @@
         <v>1444</v>
       </c>
       <c r="B490" s="5">
-        <f>IF(ISNA(VLOOKUP(H490,$A$2:$C$1005,3,1)),C490,VLOOKUP(H490,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H490,$A$2:$C$1011,3,1)),C490,VLOOKUP(H490,$A$2:$C$1011,3,1))</f>
         <v>634</v>
       </c>
       <c r="C490" s="1">
@@ -22707,7 +22785,7 @@
         <v>1447</v>
       </c>
       <c r="B491" s="5">
-        <f>IF(ISNA(VLOOKUP(H491,$A$2:$C$1005,3,1)),C491,VLOOKUP(H491,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H491,$A$2:$C$1011,3,1)),C491,VLOOKUP(H491,$A$2:$C$1011,3,1))</f>
         <v>415</v>
       </c>
       <c r="C491" s="1">
@@ -22740,7 +22818,7 @@
         <v>1450</v>
       </c>
       <c r="B492" s="5">
-        <f>IF(ISNA(VLOOKUP(H492,$A$2:$C$1005,3,1)),C492,VLOOKUP(H492,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H492,$A$2:$C$1011,3,1)),C492,VLOOKUP(H492,$A$2:$C$1011,3,1))</f>
         <v>423</v>
       </c>
       <c r="C492" s="1">
@@ -22773,7 +22851,7 @@
         <v>1453</v>
       </c>
       <c r="B493" s="5">
-        <f>IF(ISNA(VLOOKUP(H493,$A$2:$C$1005,3,1)),C493,VLOOKUP(H493,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H493,$A$2:$C$1011,3,1)),C493,VLOOKUP(H493,$A$2:$C$1011,3,1))</f>
         <v>448</v>
       </c>
       <c r="C493" s="1">
@@ -22806,7 +22884,7 @@
         <v>1456</v>
       </c>
       <c r="B494" s="5">
-        <f>IF(ISNA(VLOOKUP(H494,$A$2:$C$1005,3,1)),C494,VLOOKUP(H494,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H494,$A$2:$C$1011,3,1)),C494,VLOOKUP(H494,$A$2:$C$1011,3,1))</f>
         <v>632</v>
       </c>
       <c r="C494" s="1">
@@ -22839,7 +22917,7 @@
         <v>1459</v>
       </c>
       <c r="B495" s="5">
-        <f>IF(ISNA(VLOOKUP(H495,$A$2:$C$1005,3,1)),C495,VLOOKUP(H495,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H495,$A$2:$C$1011,3,1)),C495,VLOOKUP(H495,$A$2:$C$1011,3,1))</f>
         <v>632</v>
       </c>
       <c r="C495" s="1">
@@ -22872,7 +22950,7 @@
         <v>1462</v>
       </c>
       <c r="B496" s="5">
-        <f>IF(ISNA(VLOOKUP(H496,$A$2:$C$1005,3,1)),C496,VLOOKUP(H496,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H496,$A$2:$C$1011,3,1)),C496,VLOOKUP(H496,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C496" s="1">
@@ -22905,7 +22983,7 @@
         <v>1465</v>
       </c>
       <c r="B497" s="5">
-        <f>IF(ISNA(VLOOKUP(H497,$A$2:$C$1005,3,1)),C497,VLOOKUP(H497,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H497,$A$2:$C$1011,3,1)),C497,VLOOKUP(H497,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C497" s="1">
@@ -22938,7 +23016,7 @@
         <v>1468</v>
       </c>
       <c r="B498" s="5">
-        <f>IF(ISNA(VLOOKUP(H498,$A$2:$C$1005,3,1)),C498,VLOOKUP(H498,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H498,$A$2:$C$1011,3,1)),C498,VLOOKUP(H498,$A$2:$C$1011,3,1))</f>
         <v>635</v>
       </c>
       <c r="C498" s="1">
@@ -22971,7 +23049,7 @@
         <v>1471</v>
       </c>
       <c r="B499" s="5">
-        <f>IF(ISNA(VLOOKUP(H499,$A$2:$C$1005,3,1)),C499,VLOOKUP(H499,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H499,$A$2:$C$1011,3,1)),C499,VLOOKUP(H499,$A$2:$C$1011,3,1))</f>
         <v>588</v>
       </c>
       <c r="C499" s="1">
@@ -23004,7 +23082,7 @@
         <v>1474</v>
       </c>
       <c r="B500" s="5">
-        <f>IF(ISNA(VLOOKUP(H500,$A$2:$C$1005,3,1)),C500,VLOOKUP(H500,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H500,$A$2:$C$1011,3,1)),C500,VLOOKUP(H500,$A$2:$C$1011,3,1))</f>
         <v>588</v>
       </c>
       <c r="C500" s="1">
@@ -23037,7 +23115,7 @@
         <v>1477</v>
       </c>
       <c r="B501" s="5">
-        <f>IF(ISNA(VLOOKUP(H501,$A$2:$C$1005,3,1)),C501,VLOOKUP(H501,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H501,$A$2:$C$1011,3,1)),C501,VLOOKUP(H501,$A$2:$C$1011,3,1))</f>
         <v>588</v>
       </c>
       <c r="C501" s="1">
@@ -23070,7 +23148,7 @@
         <v>1480</v>
       </c>
       <c r="B502" s="5">
-        <f>IF(ISNA(VLOOKUP(H502,$A$2:$C$1005,3,1)),C502,VLOOKUP(H502,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H502,$A$2:$C$1011,3,1)),C502,VLOOKUP(H502,$A$2:$C$1011,3,1))</f>
         <v>531</v>
       </c>
       <c r="C502" s="1">
@@ -23103,8 +23181,8 @@
         <v>1483</v>
       </c>
       <c r="B503" s="5">
-        <f>IF(ISNA(VLOOKUP(H503,$A$2:$C$1005,3,1)),C503,VLOOKUP(H503,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H503,$A$2:$C$1011,3,1)),C503,VLOOKUP(H503,$A$2:$C$1011,3,1))</f>
+        <v>643</v>
       </c>
       <c r="C503" s="1">
         <v>643</v>
@@ -23123,12 +23201,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A503,3,4)))</f>
         <v>⌚</v>
       </c>
-      <c r="H503" s="1" t="s">
-        <v>1486</v>
+      <c r="H503" s="17" t="str">
+        <f>A503</f>
+        <v>U+231a</v>
       </c>
       <c r="I503" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H503,3,4)))</f>
-        <v>⎙</v>
+        <v>⌚</v>
       </c>
     </row>
     <row r="504" spans="1:9" ht="17" customHeight="1">
@@ -23136,8 +23215,8 @@
         <v>1487</v>
       </c>
       <c r="B504" s="5">
-        <f>IF(ISNA(VLOOKUP(H504,$A$2:$C$1005,3,1)),C504,VLOOKUP(H504,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H504,$A$2:$C$1011,3,1)),C504,VLOOKUP(H504,$A$2:$C$1011,3,1))</f>
+        <v>641</v>
       </c>
       <c r="C504" s="1">
         <v>641</v>
@@ -23156,12 +23235,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A504,3,4)))</f>
         <v>⌛</v>
       </c>
-      <c r="H504" s="1" t="s">
-        <v>1486</v>
+      <c r="H504" s="17" t="str">
+        <f>A504</f>
+        <v>U+231b</v>
       </c>
       <c r="I504" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H504,3,4)))</f>
-        <v>⎙</v>
+        <v>⌛</v>
       </c>
     </row>
     <row r="505" spans="1:9" ht="17" customHeight="1">
@@ -23169,7 +23249,7 @@
         <v>1490</v>
       </c>
       <c r="B505" s="5">
-        <f>IF(ISNA(VLOOKUP(H505,$A$2:$C$1005,3,1)),C505,VLOOKUP(H505,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H505,$A$2:$C$1011,3,1)),C505,VLOOKUP(H505,$A$2:$C$1011,3,1))</f>
         <v>514</v>
       </c>
       <c r="C505" s="1">
@@ -23202,7 +23282,7 @@
         <v>1486</v>
       </c>
       <c r="B506" s="5">
-        <f>IF(ISNA(VLOOKUP(H506,$A$2:$C$1005,3,1)),C506,VLOOKUP(H506,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H506,$A$2:$C$1011,3,1)),C506,VLOOKUP(H506,$A$2:$C$1011,3,1))</f>
         <v>640</v>
       </c>
       <c r="C506" s="1">
@@ -23222,8 +23302,9 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A506,3,4)))</f>
         <v>⎙</v>
       </c>
-      <c r="H506" s="1" t="s">
-        <v>1486</v>
+      <c r="H506" s="17" t="str">
+        <f>A506</f>
+        <v>U+2399</v>
       </c>
       <c r="I506" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H506,3,4)))</f>
@@ -23235,7 +23316,7 @@
         <v>1495</v>
       </c>
       <c r="B507" s="5">
-        <f>IF(ISNA(VLOOKUP(H507,$A$2:$C$1005,3,1)),C507,VLOOKUP(H507,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H507,$A$2:$C$1011,3,1)),C507,VLOOKUP(H507,$A$2:$C$1011,3,1))</f>
         <v>496</v>
       </c>
       <c r="C507" s="1">
@@ -23268,7 +23349,7 @@
         <v>1498</v>
       </c>
       <c r="B508" s="5">
-        <f>IF(ISNA(VLOOKUP(H508,$A$2:$C$1005,3,1)),C508,VLOOKUP(H508,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H508,$A$2:$C$1011,3,1)),C508,VLOOKUP(H508,$A$2:$C$1011,3,1))</f>
         <v>496</v>
       </c>
       <c r="C508" s="1">
@@ -23301,7 +23382,7 @@
         <v>1501</v>
       </c>
       <c r="B509" s="5">
-        <f>IF(ISNA(VLOOKUP(H509,$A$2:$C$1005,3,1)),C509,VLOOKUP(H509,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H509,$A$2:$C$1011,3,1)),C509,VLOOKUP(H509,$A$2:$C$1011,3,1))</f>
         <v>496</v>
       </c>
       <c r="C509" s="1">
@@ -23334,7 +23415,7 @@
         <v>1504</v>
       </c>
       <c r="B510" s="5">
-        <f>IF(ISNA(VLOOKUP(H510,$A$2:$C$1005,3,1)),C510,VLOOKUP(H510,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H510,$A$2:$C$1011,3,1)),C510,VLOOKUP(H510,$A$2:$C$1011,3,1))</f>
         <v>496</v>
       </c>
       <c r="C510" s="1">
@@ -23367,7 +23448,7 @@
         <v>1507</v>
       </c>
       <c r="B511" s="5">
-        <f>IF(ISNA(VLOOKUP(H511,$A$2:$C$1005,3,1)),C511,VLOOKUP(H511,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H511,$A$2:$C$1011,3,1)),C511,VLOOKUP(H511,$A$2:$C$1011,3,1))</f>
         <v>496</v>
       </c>
       <c r="C511" s="1">
@@ -23400,7 +23481,7 @@
         <v>1510</v>
       </c>
       <c r="B512" s="5">
-        <f>IF(ISNA(VLOOKUP(H512,$A$2:$C$1005,3,1)),C512,VLOOKUP(H512,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H512,$A$2:$C$1011,3,1)),C512,VLOOKUP(H512,$A$2:$C$1011,3,1))</f>
         <v>496</v>
       </c>
       <c r="C512" s="1">
@@ -23433,7 +23514,7 @@
         <v>1513</v>
       </c>
       <c r="B513" s="5">
-        <f>IF(ISNA(VLOOKUP(H513,$A$2:$C$1005,3,1)),C513,VLOOKUP(H513,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H513,$A$2:$C$1011,3,1)),C513,VLOOKUP(H513,$A$2:$C$1011,3,1))</f>
         <v>1</v>
       </c>
       <c r="C513" s="1">
@@ -23466,7 +23547,7 @@
         <v>1516</v>
       </c>
       <c r="B514" s="5">
-        <f>IF(ISNA(VLOOKUP(H514,$A$2:$C$1005,3,1)),C514,VLOOKUP(H514,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H514,$A$2:$C$1011,3,1)),C514,VLOOKUP(H514,$A$2:$C$1011,3,1))</f>
         <v>560</v>
       </c>
       <c r="C514" s="1">
@@ -23499,8 +23580,8 @@
         <v>1519</v>
       </c>
       <c r="B515" s="5">
-        <f>IF(ISNA(VLOOKUP(H515,$A$2:$C$1005,3,1)),C515,VLOOKUP(H515,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H515,$A$2:$C$1011,3,1)),C515,VLOOKUP(H515,$A$2:$C$1011,3,1))</f>
+        <v>644</v>
       </c>
       <c r="C515" s="1">
         <v>644</v>
@@ -23519,12 +23600,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A515,3,4)))</f>
         <v>⏱</v>
       </c>
-      <c r="H515" s="1" t="s">
-        <v>1486</v>
+      <c r="H515" s="17" t="str">
+        <f>A515</f>
+        <v>U+23f1</v>
       </c>
       <c r="I515" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H515,3,4)))</f>
-        <v>⎙</v>
+        <v>⏱</v>
       </c>
     </row>
     <row r="516" spans="1:9" ht="17" customHeight="1">
@@ -23532,8 +23614,8 @@
         <v>1522</v>
       </c>
       <c r="B516" s="5">
-        <f>IF(ISNA(VLOOKUP(H516,$A$2:$C$1005,3,1)),C516,VLOOKUP(H516,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H516,$A$2:$C$1011,3,1)),C516,VLOOKUP(H516,$A$2:$C$1011,3,1))</f>
+        <v>651</v>
       </c>
       <c r="C516" s="1">
         <v>651</v>
@@ -23552,12 +23634,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A516,3,4)))</f>
         <v>⏻</v>
       </c>
-      <c r="H516" s="1" t="s">
-        <v>1486</v>
+      <c r="H516" s="17" t="str">
+        <f>A516</f>
+        <v>U+23fb</v>
       </c>
       <c r="I516" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H516,3,4)))</f>
-        <v>⎙</v>
+        <v>⏻</v>
       </c>
     </row>
     <row r="517" spans="1:9" ht="17" customHeight="1">
@@ -23565,11 +23648,11 @@
         <v>1525</v>
       </c>
       <c r="B517" s="5">
-        <f>IF(ISNA(VLOOKUP(H517,$A$2:$C$1005,3,1)),C517,VLOOKUP(H517,$A$2:$C$1005,3,1))</f>
-        <v>672</v>
+        <f>IF(ISNA(VLOOKUP(H517,$A$2:$C$1011,3,1)),C517,VLOOKUP(H517,$A$2:$C$1011,3,1))</f>
+        <v>678</v>
       </c>
       <c r="C517" s="1">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="D517" s="2" t="s">
         <v>1526</v>
@@ -23585,8 +23668,9 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A517,3,4)))</f>
         <v>␡</v>
       </c>
-      <c r="H517" s="1" t="s">
-        <v>1525</v>
+      <c r="H517" s="17" t="str">
+        <f>A517</f>
+        <v>U+2421</v>
       </c>
       <c r="I517" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H517,3,4)))</f>
@@ -23598,11 +23682,11 @@
         <v>1528</v>
       </c>
       <c r="B518" s="5">
-        <f>IF(ISNA(VLOOKUP(H518,$A$2:$C$1005,3,1)),C518,VLOOKUP(H518,$A$2:$C$1005,3,1))</f>
-        <v>672</v>
+        <f>IF(ISNA(VLOOKUP(H518,$A$2:$C$1011,3,1)),C518,VLOOKUP(H518,$A$2:$C$1011,3,1))</f>
+        <v>679</v>
       </c>
       <c r="C518" s="1">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="D518" s="2" t="s">
         <v>1529</v>
@@ -23618,12 +23702,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A518,3,4)))</f>
         <v>␢</v>
       </c>
-      <c r="H518" s="1" t="s">
-        <v>1525</v>
+      <c r="H518" s="17" t="str">
+        <f>A518</f>
+        <v>U+2422</v>
       </c>
       <c r="I518" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H518,3,4)))</f>
-        <v>␡</v>
+        <v>␢</v>
       </c>
     </row>
     <row r="519" spans="1:9" ht="17" customHeight="1">
@@ -23631,7 +23716,7 @@
         <v>1531</v>
       </c>
       <c r="B519" s="5">
-        <f>IF(ISNA(VLOOKUP(H519,$A$2:$C$1005,3,1)),C519,VLOOKUP(H519,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H519,$A$2:$C$1011,3,1)),C519,VLOOKUP(H519,$A$2:$C$1011,3,1))</f>
         <v>1</v>
       </c>
       <c r="C519" s="1">
@@ -23664,11 +23749,11 @@
         <v>1534</v>
       </c>
       <c r="B520" s="5">
-        <f>IF(ISNA(VLOOKUP(H520,$A$2:$C$1005,3,1)),C520,VLOOKUP(H520,$A$2:$C$1005,3,1))</f>
-        <v>672</v>
+        <f>IF(ISNA(VLOOKUP(H520,$A$2:$C$1011,3,1)),C520,VLOOKUP(H520,$A$2:$C$1011,3,1))</f>
+        <v>680</v>
       </c>
       <c r="C520" s="1">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="D520" s="2" t="s">
         <v>1535</v>
@@ -23684,12 +23769,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A520,3,4)))</f>
         <v>␥</v>
       </c>
-      <c r="H520" s="1" t="s">
-        <v>1525</v>
+      <c r="H520" s="17" t="str">
+        <f>A520</f>
+        <v>U+2425</v>
       </c>
       <c r="I520" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H520,3,4)))</f>
-        <v>␡</v>
+        <v>␥</v>
       </c>
     </row>
     <row r="521" spans="1:9" ht="17" customHeight="1">
@@ -23697,11 +23783,11 @@
         <v>1537</v>
       </c>
       <c r="B521" s="5">
-        <f>IF(ISNA(VLOOKUP(H521,$A$2:$C$1005,3,1)),C521,VLOOKUP(H521,$A$2:$C$1005,3,1))</f>
-        <v>672</v>
+        <f>IF(ISNA(VLOOKUP(H521,$A$2:$C$1011,3,1)),C521,VLOOKUP(H521,$A$2:$C$1011,3,1))</f>
+        <v>681</v>
       </c>
       <c r="C521" s="1">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="D521" s="2" t="s">
         <v>1538</v>
@@ -23717,12 +23803,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A521,3,4)))</f>
         <v>␦</v>
       </c>
-      <c r="H521" s="1" t="s">
-        <v>1525</v>
+      <c r="H521" s="17" t="str">
+        <f>A521</f>
+        <v>U+2426</v>
       </c>
       <c r="I521" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H521,3,4)))</f>
-        <v>␡</v>
+        <v>␦</v>
       </c>
     </row>
     <row r="522" spans="1:9" ht="17" customHeight="1">
@@ -23730,7 +23817,7 @@
         <v>1540</v>
       </c>
       <c r="B522" s="5">
-        <f>IF(ISNA(VLOOKUP(H522,$A$2:$C$1005,3,1)),C522,VLOOKUP(H522,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H522,$A$2:$C$1011,3,1)),C522,VLOOKUP(H522,$A$2:$C$1011,3,1))</f>
         <v>558</v>
       </c>
       <c r="C522" s="1">
@@ -23763,7 +23850,7 @@
         <v>1542</v>
       </c>
       <c r="B523" s="5">
-        <f>IF(ISNA(VLOOKUP(H523,$A$2:$C$1005,3,1)),C523,VLOOKUP(H523,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H523,$A$2:$C$1011,3,1)),C523,VLOOKUP(H523,$A$2:$C$1011,3,1))</f>
         <v>531</v>
       </c>
       <c r="C523" s="1">
@@ -23796,7 +23883,7 @@
         <v>1544</v>
       </c>
       <c r="B524" s="5">
-        <f>IF(ISNA(VLOOKUP(H524,$A$2:$C$1005,3,1)),C524,VLOOKUP(H524,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H524,$A$2:$C$1011,3,1)),C524,VLOOKUP(H524,$A$2:$C$1011,3,1))</f>
         <v>528</v>
       </c>
       <c r="C524" s="1">
@@ -23829,8 +23916,8 @@
         <v>1545</v>
       </c>
       <c r="B525" s="5">
-        <f>IF(ISNA(VLOOKUP(H525,$A$2:$C$1005,3,1)),C525,VLOOKUP(H525,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H525,$A$2:$C$1011,3,1)),C525,VLOOKUP(H525,$A$2:$C$1011,3,1))</f>
+        <v>645</v>
       </c>
       <c r="C525" s="1">
         <v>645</v>
@@ -23849,12 +23936,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A525,3,4)))</f>
         <v>␪</v>
       </c>
-      <c r="H525" s="1" t="s">
-        <v>1486</v>
+      <c r="H525" s="17" t="str">
+        <f>A525</f>
+        <v>U+242a</v>
       </c>
       <c r="I525" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H525,3,4)))</f>
-        <v>⎙</v>
+        <v>␪</v>
       </c>
     </row>
     <row r="526" spans="1:9" ht="17" customHeight="1">
@@ -23862,7 +23950,7 @@
         <v>1547</v>
       </c>
       <c r="B526" s="5">
-        <f>IF(ISNA(VLOOKUP(H526,$A$2:$C$1005,3,1)),C526,VLOOKUP(H526,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H526,$A$2:$C$1011,3,1)),C526,VLOOKUP(H526,$A$2:$C$1011,3,1))</f>
         <v>572</v>
       </c>
       <c r="C526" s="1">
@@ -23895,8 +23983,8 @@
         <v>1549</v>
       </c>
       <c r="B527" s="5">
-        <f>IF(ISNA(VLOOKUP(H527,$A$2:$C$1005,3,1)),C527,VLOOKUP(H527,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H527,$A$2:$C$1011,3,1)),C527,VLOOKUP(H527,$A$2:$C$1011,3,1))</f>
+        <v>647</v>
       </c>
       <c r="C527" s="1">
         <v>647</v>
@@ -23915,12 +24003,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A527,3,4)))</f>
         <v>␬</v>
       </c>
-      <c r="H527" s="1" t="s">
-        <v>1486</v>
+      <c r="H527" s="17" t="str">
+        <f>A527</f>
+        <v>U+242c</v>
       </c>
       <c r="I527" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H527,3,4)))</f>
-        <v>⎙</v>
+        <v>␬</v>
       </c>
     </row>
     <row r="528" spans="1:9" ht="17" customHeight="1">
@@ -23928,11 +24017,11 @@
         <v>1551</v>
       </c>
       <c r="B528" s="5">
-        <f>IF(ISNA(VLOOKUP(H528,$A$2:$C$1005,3,1)),C528,VLOOKUP(H528,$A$2:$C$1005,3,1))</f>
-        <v>655</v>
+        <f>IF(ISNA(VLOOKUP(H528,$A$2:$C$1011,3,1)),C528,VLOOKUP(H528,$A$2:$C$1011,3,1))</f>
+        <v>661</v>
       </c>
       <c r="C528" s="1">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="D528" s="2" t="s">
         <v>304</v>
@@ -23948,8 +24037,9 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A528,3,4)))</f>
         <v>␭</v>
       </c>
-      <c r="H528" s="1" t="s">
-        <v>1551</v>
+      <c r="H528" s="17" t="str">
+        <f>A528</f>
+        <v>U+242d</v>
       </c>
       <c r="I528" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H528,3,4)))</f>
@@ -23961,11 +24051,11 @@
         <v>1553</v>
       </c>
       <c r="B529" s="5">
-        <f>IF(ISNA(VLOOKUP(H529,$A$2:$C$1005,3,1)),C529,VLOOKUP(H529,$A$2:$C$1005,3,1))</f>
-        <v>655</v>
+        <f>IF(ISNA(VLOOKUP(H529,$A$2:$C$1011,3,1)),C529,VLOOKUP(H529,$A$2:$C$1011,3,1))</f>
+        <v>662</v>
       </c>
       <c r="C529" s="1">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D529" s="2" t="s">
         <v>304</v>
@@ -23981,12 +24071,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A529,3,4)))</f>
         <v>␮</v>
       </c>
-      <c r="H529" s="1" t="s">
-        <v>1551</v>
+      <c r="H529" s="17" t="str">
+        <f>A529</f>
+        <v>U+242e</v>
       </c>
       <c r="I529" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H529,3,4)))</f>
-        <v>␭</v>
+        <v>␮</v>
       </c>
     </row>
     <row r="530" spans="1:9" ht="17" customHeight="1">
@@ -23994,8 +24085,8 @@
         <v>1555</v>
       </c>
       <c r="B530" s="5">
-        <f>IF(ISNA(VLOOKUP(H530,$A$2:$C$1005,3,1)),C530,VLOOKUP(H530,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H530,$A$2:$C$1011,3,1)),C530,VLOOKUP(H530,$A$2:$C$1011,3,1))</f>
+        <v>648</v>
       </c>
       <c r="C530" s="1">
         <v>648</v>
@@ -24014,12 +24105,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A530,3,4)))</f>
         <v>␯</v>
       </c>
-      <c r="H530" s="1" t="s">
-        <v>1486</v>
+      <c r="H530" s="17" t="str">
+        <f>A530</f>
+        <v>U+242f</v>
       </c>
       <c r="I530" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H530,3,4)))</f>
-        <v>⎙</v>
+        <v>␯</v>
       </c>
     </row>
     <row r="531" spans="1:9" ht="17" customHeight="1">
@@ -24027,7 +24119,7 @@
         <v>1557</v>
       </c>
       <c r="B531" s="5">
-        <f>IF(ISNA(VLOOKUP(H531,$A$2:$C$1005,3,1)),C531,VLOOKUP(H531,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H531,$A$2:$C$1011,3,1)),C531,VLOOKUP(H531,$A$2:$C$1011,3,1))</f>
         <v>506</v>
       </c>
       <c r="C531" s="1">
@@ -24060,7 +24152,7 @@
         <v>1559</v>
       </c>
       <c r="B532" s="5">
-        <f>IF(ISNA(VLOOKUP(H532,$A$2:$C$1005,3,1)),C532,VLOOKUP(H532,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H532,$A$2:$C$1011,3,1)),C532,VLOOKUP(H532,$A$2:$C$1011,3,1))</f>
         <v>506</v>
       </c>
       <c r="C532" s="1">
@@ -24093,7 +24185,7 @@
         <v>1561</v>
       </c>
       <c r="B533" s="5">
-        <f>IF(ISNA(VLOOKUP(H533,$A$2:$C$1005,3,1)),C533,VLOOKUP(H533,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H533,$A$2:$C$1011,3,1)),C533,VLOOKUP(H533,$A$2:$C$1011,3,1))</f>
         <v>506</v>
       </c>
       <c r="C533" s="1">
@@ -24126,7 +24218,7 @@
         <v>1563</v>
       </c>
       <c r="B534" s="5">
-        <f>IF(ISNA(VLOOKUP(H534,$A$2:$C$1005,3,1)),C534,VLOOKUP(H534,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H534,$A$2:$C$1011,3,1)),C534,VLOOKUP(H534,$A$2:$C$1011,3,1))</f>
         <v>506</v>
       </c>
       <c r="C534" s="1">
@@ -24159,8 +24251,8 @@
         <v>1565</v>
       </c>
       <c r="B535" s="5">
-        <f>IF(ISNA(VLOOKUP(H535,$A$2:$C$1005,3,1)),C535,VLOOKUP(H535,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H535,$A$2:$C$1011,3,1)),C535,VLOOKUP(H535,$A$2:$C$1011,3,1))</f>
+        <v>649</v>
       </c>
       <c r="C535" s="1">
         <v>649</v>
@@ -24179,12 +24271,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A535,3,4)))</f>
         <v>␴</v>
       </c>
-      <c r="H535" s="1" t="s">
-        <v>1486</v>
+      <c r="H535" s="17" t="str">
+        <f>A535</f>
+        <v>U+2434</v>
       </c>
       <c r="I535" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H535,3,4)))</f>
-        <v>⎙</v>
+        <v>␴</v>
       </c>
     </row>
     <row r="536" spans="1:9" ht="17" customHeight="1">
@@ -24192,8 +24285,8 @@
         <v>1567</v>
       </c>
       <c r="B536" s="5">
-        <f>IF(ISNA(VLOOKUP(H536,$A$2:$C$1005,3,1)),C536,VLOOKUP(H536,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H536,$A$2:$C$1011,3,1)),C536,VLOOKUP(H536,$A$2:$C$1011,3,1))</f>
+        <v>646</v>
       </c>
       <c r="C536" s="1">
         <v>646</v>
@@ -24212,12 +24305,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A536,3,4)))</f>
         <v>␵</v>
       </c>
-      <c r="H536" s="1" t="s">
-        <v>1486</v>
+      <c r="H536" s="17" t="str">
+        <f>A536</f>
+        <v>U+2435</v>
       </c>
       <c r="I536" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H536,3,4)))</f>
-        <v>⎙</v>
+        <v>␵</v>
       </c>
     </row>
     <row r="537" spans="1:9" ht="17" customHeight="1">
@@ -24225,7 +24319,7 @@
         <v>1569</v>
       </c>
       <c r="B537" s="5">
-        <f>IF(ISNA(VLOOKUP(H537,$A$2:$C$1005,3,1)),C537,VLOOKUP(H537,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H537,$A$2:$C$1011,3,1)),C537,VLOOKUP(H537,$A$2:$C$1011,3,1))</f>
         <v>18</v>
       </c>
       <c r="C537" s="1">
@@ -24258,7 +24352,7 @@
         <v>1572</v>
       </c>
       <c r="B538" s="5">
-        <f>IF(ISNA(VLOOKUP(H538,$A$2:$C$1005,3,1)),C538,VLOOKUP(H538,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H538,$A$2:$C$1011,3,1)),C538,VLOOKUP(H538,$A$2:$C$1011,3,1))</f>
         <v>25</v>
       </c>
       <c r="C538" s="1">
@@ -24291,7 +24385,7 @@
         <v>1575</v>
       </c>
       <c r="B539" s="5">
-        <f>IF(ISNA(VLOOKUP(H539,$A$2:$C$1005,3,1)),C539,VLOOKUP(H539,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H539,$A$2:$C$1011,3,1)),C539,VLOOKUP(H539,$A$2:$C$1011,3,1))</f>
         <v>29</v>
       </c>
       <c r="C539" s="1">
@@ -24324,7 +24418,7 @@
         <v>1578</v>
       </c>
       <c r="B540" s="5">
-        <f>IF(ISNA(VLOOKUP(H540,$A$2:$C$1005,3,1)),C540,VLOOKUP(H540,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H540,$A$2:$C$1011,3,1)),C540,VLOOKUP(H540,$A$2:$C$1011,3,1))</f>
         <v>34</v>
       </c>
       <c r="C540" s="1">
@@ -24357,7 +24451,7 @@
         <v>1581</v>
       </c>
       <c r="B541" s="5">
-        <f>IF(ISNA(VLOOKUP(H541,$A$2:$C$1005,3,1)),C541,VLOOKUP(H541,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H541,$A$2:$C$1011,3,1)),C541,VLOOKUP(H541,$A$2:$C$1011,3,1))</f>
         <v>38</v>
       </c>
       <c r="C541" s="1">
@@ -24390,7 +24484,7 @@
         <v>1584</v>
       </c>
       <c r="B542" s="5">
-        <f>IF(ISNA(VLOOKUP(H542,$A$2:$C$1005,3,1)),C542,VLOOKUP(H542,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H542,$A$2:$C$1011,3,1)),C542,VLOOKUP(H542,$A$2:$C$1011,3,1))</f>
         <v>42</v>
       </c>
       <c r="C542" s="1">
@@ -24423,7 +24517,7 @@
         <v>1587</v>
       </c>
       <c r="B543" s="5">
-        <f>IF(ISNA(VLOOKUP(H543,$A$2:$C$1005,3,1)),C543,VLOOKUP(H543,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H543,$A$2:$C$1011,3,1)),C543,VLOOKUP(H543,$A$2:$C$1011,3,1))</f>
         <v>46</v>
       </c>
       <c r="C543" s="1">
@@ -24456,7 +24550,7 @@
         <v>1590</v>
       </c>
       <c r="B544" s="5">
-        <f>IF(ISNA(VLOOKUP(H544,$A$2:$C$1005,3,1)),C544,VLOOKUP(H544,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H544,$A$2:$C$1011,3,1)),C544,VLOOKUP(H544,$A$2:$C$1011,3,1))</f>
         <v>50</v>
       </c>
       <c r="C544" s="1">
@@ -24489,7 +24583,7 @@
         <v>1593</v>
       </c>
       <c r="B545" s="5">
-        <f>IF(ISNA(VLOOKUP(H545,$A$2:$C$1005,3,1)),C545,VLOOKUP(H545,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H545,$A$2:$C$1011,3,1)),C545,VLOOKUP(H545,$A$2:$C$1011,3,1))</f>
         <v>54</v>
       </c>
       <c r="C545" s="1">
@@ -24522,7 +24616,7 @@
         <v>1596</v>
       </c>
       <c r="B546" s="5">
-        <f>IF(ISNA(VLOOKUP(H546,$A$2:$C$1005,3,1)),C546,VLOOKUP(H546,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H546,$A$2:$C$1011,3,1)),C546,VLOOKUP(H546,$A$2:$C$1011,3,1))</f>
         <v>58</v>
       </c>
       <c r="C546" s="1">
@@ -24555,7 +24649,7 @@
         <v>1600</v>
       </c>
       <c r="B547" s="5">
-        <f>IF(ISNA(VLOOKUP(H547,$A$2:$C$1005,3,1)),C547,VLOOKUP(H547,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H547,$A$2:$C$1011,3,1)),C547,VLOOKUP(H547,$A$2:$C$1011,3,1))</f>
         <v>60</v>
       </c>
       <c r="C547" s="1">
@@ -24588,7 +24682,7 @@
         <v>1603</v>
       </c>
       <c r="B548" s="5">
-        <f>IF(ISNA(VLOOKUP(H548,$A$2:$C$1005,3,1)),C548,VLOOKUP(H548,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H548,$A$2:$C$1011,3,1)),C548,VLOOKUP(H548,$A$2:$C$1011,3,1))</f>
         <v>61</v>
       </c>
       <c r="C548" s="1">
@@ -24621,7 +24715,7 @@
         <v>1606</v>
       </c>
       <c r="B549" s="5">
-        <f>IF(ISNA(VLOOKUP(H549,$A$2:$C$1005,3,1)),C549,VLOOKUP(H549,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H549,$A$2:$C$1011,3,1)),C549,VLOOKUP(H549,$A$2:$C$1011,3,1))</f>
         <v>62</v>
       </c>
       <c r="C549" s="1">
@@ -24654,7 +24748,7 @@
         <v>1609</v>
       </c>
       <c r="B550" s="5">
-        <f>IF(ISNA(VLOOKUP(H550,$A$2:$C$1005,3,1)),C550,VLOOKUP(H550,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H550,$A$2:$C$1011,3,1)),C550,VLOOKUP(H550,$A$2:$C$1011,3,1))</f>
         <v>63</v>
       </c>
       <c r="C550" s="1">
@@ -24687,7 +24781,7 @@
         <v>1612</v>
       </c>
       <c r="B551" s="5">
-        <f>IF(ISNA(VLOOKUP(H551,$A$2:$C$1005,3,1)),C551,VLOOKUP(H551,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H551,$A$2:$C$1011,3,1)),C551,VLOOKUP(H551,$A$2:$C$1011,3,1))</f>
         <v>64</v>
       </c>
       <c r="C551" s="1">
@@ -24720,7 +24814,7 @@
         <v>1615</v>
       </c>
       <c r="B552" s="5">
-        <f>IF(ISNA(VLOOKUP(H552,$A$2:$C$1005,3,1)),C552,VLOOKUP(H552,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H552,$A$2:$C$1011,3,1)),C552,VLOOKUP(H552,$A$2:$C$1011,3,1))</f>
         <v>65</v>
       </c>
       <c r="C552" s="1">
@@ -24753,7 +24847,7 @@
         <v>1599</v>
       </c>
       <c r="B553" s="5">
-        <f>IF(ISNA(VLOOKUP(H553,$A$2:$C$1005,3,1)),C553,VLOOKUP(H553,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H553,$A$2:$C$1011,3,1)),C553,VLOOKUP(H553,$A$2:$C$1011,3,1))</f>
         <v>58</v>
       </c>
       <c r="C553" s="1">
@@ -24786,7 +24880,7 @@
         <v>1620</v>
       </c>
       <c r="B554" s="5">
-        <f>IF(ISNA(VLOOKUP(H554,$A$2:$C$1005,3,1)),C554,VLOOKUP(H554,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H554,$A$2:$C$1011,3,1)),C554,VLOOKUP(H554,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C554" s="1">
@@ -24819,7 +24913,7 @@
         <v>1623</v>
       </c>
       <c r="B555" s="5">
-        <f>IF(ISNA(VLOOKUP(H555,$A$2:$C$1005,3,1)),C555,VLOOKUP(H555,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H555,$A$2:$C$1011,3,1)),C555,VLOOKUP(H555,$A$2:$C$1011,3,1))</f>
         <v>92</v>
       </c>
       <c r="C555" s="1">
@@ -24852,7 +24946,7 @@
         <v>1626</v>
       </c>
       <c r="B556" s="5">
-        <f>IF(ISNA(VLOOKUP(H556,$A$2:$C$1005,3,1)),C556,VLOOKUP(H556,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H556,$A$2:$C$1011,3,1)),C556,VLOOKUP(H556,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C556" s="1">
@@ -24885,7 +24979,7 @@
         <v>1629</v>
       </c>
       <c r="B557" s="5">
-        <f>IF(ISNA(VLOOKUP(H557,$A$2:$C$1005,3,1)),C557,VLOOKUP(H557,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H557,$A$2:$C$1011,3,1)),C557,VLOOKUP(H557,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C557" s="1">
@@ -24918,7 +25012,7 @@
         <v>1632</v>
       </c>
       <c r="B558" s="5">
-        <f>IF(ISNA(VLOOKUP(H558,$A$2:$C$1005,3,1)),C558,VLOOKUP(H558,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H558,$A$2:$C$1011,3,1)),C558,VLOOKUP(H558,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C558" s="1">
@@ -24951,7 +25045,7 @@
         <v>1635</v>
       </c>
       <c r="B559" s="5">
-        <f>IF(ISNA(VLOOKUP(H559,$A$2:$C$1005,3,1)),C559,VLOOKUP(H559,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H559,$A$2:$C$1011,3,1)),C559,VLOOKUP(H559,$A$2:$C$1011,3,1))</f>
         <v>152</v>
       </c>
       <c r="C559" s="1">
@@ -24984,7 +25078,7 @@
         <v>1637</v>
       </c>
       <c r="B560" s="5">
-        <f>IF(ISNA(VLOOKUP(H560,$A$2:$C$1005,3,1)),C560,VLOOKUP(H560,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H560,$A$2:$C$1011,3,1)),C560,VLOOKUP(H560,$A$2:$C$1011,3,1))</f>
         <v>161</v>
       </c>
       <c r="C560" s="1">
@@ -25017,7 +25111,7 @@
         <v>1639</v>
       </c>
       <c r="B561" s="5">
-        <f>IF(ISNA(VLOOKUP(H561,$A$2:$C$1005,3,1)),C561,VLOOKUP(H561,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H561,$A$2:$C$1011,3,1)),C561,VLOOKUP(H561,$A$2:$C$1011,3,1))</f>
         <v>171</v>
       </c>
       <c r="C561" s="1">
@@ -25050,7 +25144,7 @@
         <v>1641</v>
       </c>
       <c r="B562" s="5">
-        <f>IF(ISNA(VLOOKUP(H562,$A$2:$C$1005,3,1)),C562,VLOOKUP(H562,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H562,$A$2:$C$1011,3,1)),C562,VLOOKUP(H562,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C562" s="1">
@@ -25083,7 +25177,7 @@
         <v>1644</v>
       </c>
       <c r="B563" s="5">
-        <f>IF(ISNA(VLOOKUP(H563,$A$2:$C$1005,3,1)),C563,VLOOKUP(H563,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H563,$A$2:$C$1011,3,1)),C563,VLOOKUP(H563,$A$2:$C$1011,3,1))</f>
         <v>205</v>
       </c>
       <c r="C563" s="1">
@@ -25116,7 +25210,7 @@
         <v>1647</v>
       </c>
       <c r="B564" s="5">
-        <f>IF(ISNA(VLOOKUP(H564,$A$2:$C$1005,3,1)),C564,VLOOKUP(H564,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H564,$A$2:$C$1011,3,1)),C564,VLOOKUP(H564,$A$2:$C$1011,3,1))</f>
         <v>213</v>
       </c>
       <c r="C564" s="1">
@@ -25149,7 +25243,7 @@
         <v>1650</v>
       </c>
       <c r="B565" s="5">
-        <f>IF(ISNA(VLOOKUP(H565,$A$2:$C$1005,3,1)),C565,VLOOKUP(H565,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H565,$A$2:$C$1011,3,1)),C565,VLOOKUP(H565,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C565" s="1">
@@ -25182,7 +25276,7 @@
         <v>1653</v>
       </c>
       <c r="B566" s="5">
-        <f>IF(ISNA(VLOOKUP(H566,$A$2:$C$1005,3,1)),C566,VLOOKUP(H566,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H566,$A$2:$C$1011,3,1)),C566,VLOOKUP(H566,$A$2:$C$1011,3,1))</f>
         <v>233</v>
       </c>
       <c r="C566" s="1">
@@ -25215,7 +25309,7 @@
         <v>1656</v>
       </c>
       <c r="B567" s="5">
-        <f>IF(ISNA(VLOOKUP(H567,$A$2:$C$1005,3,1)),C567,VLOOKUP(H567,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H567,$A$2:$C$1011,3,1)),C567,VLOOKUP(H567,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C567" s="1">
@@ -25248,7 +25342,7 @@
         <v>1659</v>
       </c>
       <c r="B568" s="5">
-        <f>IF(ISNA(VLOOKUP(H568,$A$2:$C$1005,3,1)),C568,VLOOKUP(H568,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H568,$A$2:$C$1011,3,1)),C568,VLOOKUP(H568,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C568" s="1">
@@ -25281,7 +25375,7 @@
         <v>1662</v>
       </c>
       <c r="B569" s="5">
-        <f>IF(ISNA(VLOOKUP(H569,$A$2:$C$1005,3,1)),C569,VLOOKUP(H569,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H569,$A$2:$C$1011,3,1)),C569,VLOOKUP(H569,$A$2:$C$1011,3,1))</f>
         <v>278</v>
       </c>
       <c r="C569" s="1">
@@ -25314,7 +25408,7 @@
         <v>1665</v>
       </c>
       <c r="B570" s="5">
-        <f>IF(ISNA(VLOOKUP(H570,$A$2:$C$1005,3,1)),C570,VLOOKUP(H570,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H570,$A$2:$C$1011,3,1)),C570,VLOOKUP(H570,$A$2:$C$1011,3,1))</f>
         <v>284</v>
       </c>
       <c r="C570" s="1">
@@ -25347,7 +25441,7 @@
         <v>1668</v>
       </c>
       <c r="B571" s="5">
-        <f>IF(ISNA(VLOOKUP(H571,$A$2:$C$1005,3,1)),C571,VLOOKUP(H571,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H571,$A$2:$C$1011,3,1)),C571,VLOOKUP(H571,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C571" s="1">
@@ -25380,7 +25474,7 @@
         <v>1670</v>
       </c>
       <c r="B572" s="5">
-        <f>IF(ISNA(VLOOKUP(H572,$A$2:$C$1005,3,1)),C572,VLOOKUP(H572,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H572,$A$2:$C$1011,3,1)),C572,VLOOKUP(H572,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C572" s="1">
@@ -25413,7 +25507,7 @@
         <v>1673</v>
       </c>
       <c r="B573" s="5">
-        <f>IF(ISNA(VLOOKUP(H573,$A$2:$C$1005,3,1)),C573,VLOOKUP(H573,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H573,$A$2:$C$1011,3,1)),C573,VLOOKUP(H573,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C573" s="1">
@@ -25446,7 +25540,7 @@
         <v>1676</v>
       </c>
       <c r="B574" s="5">
-        <f>IF(ISNA(VLOOKUP(H574,$A$2:$C$1005,3,1)),C574,VLOOKUP(H574,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H574,$A$2:$C$1011,3,1)),C574,VLOOKUP(H574,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C574" s="1">
@@ -25479,7 +25573,7 @@
         <v>1679</v>
       </c>
       <c r="B575" s="5">
-        <f>IF(ISNA(VLOOKUP(H575,$A$2:$C$1005,3,1)),C575,VLOOKUP(H575,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H575,$A$2:$C$1011,3,1)),C575,VLOOKUP(H575,$A$2:$C$1011,3,1))</f>
         <v>356</v>
       </c>
       <c r="C575" s="1">
@@ -25512,7 +25606,7 @@
         <v>1682</v>
       </c>
       <c r="B576" s="5">
-        <f>IF(ISNA(VLOOKUP(H576,$A$2:$C$1005,3,1)),C576,VLOOKUP(H576,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H576,$A$2:$C$1011,3,1)),C576,VLOOKUP(H576,$A$2:$C$1011,3,1))</f>
         <v>364</v>
       </c>
       <c r="C576" s="1">
@@ -25545,7 +25639,7 @@
         <v>1685</v>
       </c>
       <c r="B577" s="5">
-        <f>IF(ISNA(VLOOKUP(H577,$A$2:$C$1005,3,1)),C577,VLOOKUP(H577,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H577,$A$2:$C$1011,3,1)),C577,VLOOKUP(H577,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C577" s="1">
@@ -25578,7 +25672,7 @@
         <v>1687</v>
       </c>
       <c r="B578" s="5">
-        <f>IF(ISNA(VLOOKUP(H578,$A$2:$C$1005,3,1)),C578,VLOOKUP(H578,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H578,$A$2:$C$1011,3,1)),C578,VLOOKUP(H578,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C578" s="1">
@@ -25611,7 +25705,7 @@
         <v>1690</v>
       </c>
       <c r="B579" s="5">
-        <f>IF(ISNA(VLOOKUP(H579,$A$2:$C$1005,3,1)),C579,VLOOKUP(H579,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H579,$A$2:$C$1011,3,1)),C579,VLOOKUP(H579,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C579" s="1">
@@ -25644,7 +25738,7 @@
         <v>1693</v>
       </c>
       <c r="B580" s="5">
-        <f>IF(ISNA(VLOOKUP(H580,$A$2:$C$1005,3,1)),C580,VLOOKUP(H580,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H580,$A$2:$C$1011,3,1)),C580,VLOOKUP(H580,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C580" s="1">
@@ -25677,7 +25771,7 @@
         <v>1696</v>
       </c>
       <c r="B581" s="5">
-        <f>IF(ISNA(VLOOKUP(H581,$A$2:$C$1005,3,1)),C581,VLOOKUP(H581,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H581,$A$2:$C$1011,3,1)),C581,VLOOKUP(H581,$A$2:$C$1011,3,1))</f>
         <v>92</v>
       </c>
       <c r="C581" s="1">
@@ -25710,7 +25804,7 @@
         <v>1699</v>
       </c>
       <c r="B582" s="5">
-        <f>IF(ISNA(VLOOKUP(H582,$A$2:$C$1005,3,1)),C582,VLOOKUP(H582,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H582,$A$2:$C$1011,3,1)),C582,VLOOKUP(H582,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C582" s="1">
@@ -25743,7 +25837,7 @@
         <v>1702</v>
       </c>
       <c r="B583" s="5">
-        <f>IF(ISNA(VLOOKUP(H583,$A$2:$C$1005,3,1)),C583,VLOOKUP(H583,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H583,$A$2:$C$1011,3,1)),C583,VLOOKUP(H583,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C583" s="1">
@@ -25776,7 +25870,7 @@
         <v>1705</v>
       </c>
       <c r="B584" s="5">
-        <f>IF(ISNA(VLOOKUP(H584,$A$2:$C$1005,3,1)),C584,VLOOKUP(H584,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H584,$A$2:$C$1011,3,1)),C584,VLOOKUP(H584,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C584" s="1">
@@ -25809,7 +25903,7 @@
         <v>1708</v>
       </c>
       <c r="B585" s="5">
-        <f>IF(ISNA(VLOOKUP(H585,$A$2:$C$1005,3,1)),C585,VLOOKUP(H585,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H585,$A$2:$C$1011,3,1)),C585,VLOOKUP(H585,$A$2:$C$1011,3,1))</f>
         <v>152</v>
       </c>
       <c r="C585" s="1">
@@ -25842,7 +25936,7 @@
         <v>1711</v>
       </c>
       <c r="B586" s="5">
-        <f>IF(ISNA(VLOOKUP(H586,$A$2:$C$1005,3,1)),C586,VLOOKUP(H586,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H586,$A$2:$C$1011,3,1)),C586,VLOOKUP(H586,$A$2:$C$1011,3,1))</f>
         <v>161</v>
       </c>
       <c r="C586" s="1">
@@ -25875,7 +25969,7 @@
         <v>1714</v>
       </c>
       <c r="B587" s="5">
-        <f>IF(ISNA(VLOOKUP(H587,$A$2:$C$1005,3,1)),C587,VLOOKUP(H587,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H587,$A$2:$C$1011,3,1)),C587,VLOOKUP(H587,$A$2:$C$1011,3,1))</f>
         <v>171</v>
       </c>
       <c r="C587" s="1">
@@ -25909,7 +26003,7 @@
         <v>1717</v>
       </c>
       <c r="B588" s="5">
-        <f>IF(ISNA(VLOOKUP(H588,$A$2:$C$1005,3,1)),C588,VLOOKUP(H588,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H588,$A$2:$C$1011,3,1)),C588,VLOOKUP(H588,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C588" s="1">
@@ -25944,7 +26038,7 @@
         <v>1720</v>
       </c>
       <c r="B589" s="5">
-        <f>IF(ISNA(VLOOKUP(H589,$A$2:$C$1005,3,1)),C589,VLOOKUP(H589,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H589,$A$2:$C$1011,3,1)),C589,VLOOKUP(H589,$A$2:$C$1011,3,1))</f>
         <v>205</v>
       </c>
       <c r="C589" s="1">
@@ -25977,7 +26071,7 @@
         <v>1723</v>
       </c>
       <c r="B590" s="5">
-        <f>IF(ISNA(VLOOKUP(H590,$A$2:$C$1005,3,1)),C590,VLOOKUP(H590,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H590,$A$2:$C$1011,3,1)),C590,VLOOKUP(H590,$A$2:$C$1011,3,1))</f>
         <v>213</v>
       </c>
       <c r="C590" s="1">
@@ -26010,7 +26104,7 @@
         <v>1726</v>
       </c>
       <c r="B591" s="5">
-        <f>IF(ISNA(VLOOKUP(H591,$A$2:$C$1005,3,1)),C591,VLOOKUP(H591,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H591,$A$2:$C$1011,3,1)),C591,VLOOKUP(H591,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C591" s="1">
@@ -26043,7 +26137,7 @@
         <v>1729</v>
       </c>
       <c r="B592" s="5">
-        <f>IF(ISNA(VLOOKUP(H592,$A$2:$C$1005,3,1)),C592,VLOOKUP(H592,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H592,$A$2:$C$1011,3,1)),C592,VLOOKUP(H592,$A$2:$C$1011,3,1))</f>
         <v>233</v>
       </c>
       <c r="C592" s="1">
@@ -26076,7 +26170,7 @@
         <v>1732</v>
       </c>
       <c r="B593" s="5">
-        <f>IF(ISNA(VLOOKUP(H593,$A$2:$C$1005,3,1)),C593,VLOOKUP(H593,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H593,$A$2:$C$1011,3,1)),C593,VLOOKUP(H593,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C593" s="1">
@@ -26109,7 +26203,7 @@
         <v>1735</v>
       </c>
       <c r="B594" s="5">
-        <f>IF(ISNA(VLOOKUP(H594,$A$2:$C$1005,3,1)),C594,VLOOKUP(H594,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H594,$A$2:$C$1011,3,1)),C594,VLOOKUP(H594,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C594" s="1">
@@ -26142,7 +26236,7 @@
         <v>1738</v>
       </c>
       <c r="B595" s="5">
-        <f>IF(ISNA(VLOOKUP(H595,$A$2:$C$1005,3,1)),C595,VLOOKUP(H595,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H595,$A$2:$C$1011,3,1)),C595,VLOOKUP(H595,$A$2:$C$1011,3,1))</f>
         <v>278</v>
       </c>
       <c r="C595" s="1">
@@ -26175,7 +26269,7 @@
         <v>1741</v>
       </c>
       <c r="B596" s="5">
-        <f>IF(ISNA(VLOOKUP(H596,$A$2:$C$1005,3,1)),C596,VLOOKUP(H596,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H596,$A$2:$C$1011,3,1)),C596,VLOOKUP(H596,$A$2:$C$1011,3,1))</f>
         <v>284</v>
       </c>
       <c r="C596" s="1">
@@ -26208,7 +26302,7 @@
         <v>1744</v>
       </c>
       <c r="B597" s="5">
-        <f>IF(ISNA(VLOOKUP(H597,$A$2:$C$1005,3,1)),C597,VLOOKUP(H597,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H597,$A$2:$C$1011,3,1)),C597,VLOOKUP(H597,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C597" s="1">
@@ -26241,7 +26335,7 @@
         <v>1747</v>
       </c>
       <c r="B598" s="5">
-        <f>IF(ISNA(VLOOKUP(H598,$A$2:$C$1005,3,1)),C598,VLOOKUP(H598,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H598,$A$2:$C$1011,3,1)),C598,VLOOKUP(H598,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C598" s="1">
@@ -26274,7 +26368,7 @@
         <v>1750</v>
       </c>
       <c r="B599" s="5">
-        <f>IF(ISNA(VLOOKUP(H599,$A$2:$C$1005,3,1)),C599,VLOOKUP(H599,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H599,$A$2:$C$1011,3,1)),C599,VLOOKUP(H599,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C599" s="1">
@@ -26307,7 +26401,7 @@
         <v>1753</v>
       </c>
       <c r="B600" s="5">
-        <f>IF(ISNA(VLOOKUP(H600,$A$2:$C$1005,3,1)),C600,VLOOKUP(H600,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H600,$A$2:$C$1011,3,1)),C600,VLOOKUP(H600,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C600" s="1">
@@ -26340,7 +26434,7 @@
         <v>1756</v>
       </c>
       <c r="B601" s="5">
-        <f>IF(ISNA(VLOOKUP(H601,$A$2:$C$1005,3,1)),C601,VLOOKUP(H601,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H601,$A$2:$C$1011,3,1)),C601,VLOOKUP(H601,$A$2:$C$1011,3,1))</f>
         <v>356</v>
       </c>
       <c r="C601" s="1">
@@ -26373,7 +26467,7 @@
         <v>1759</v>
       </c>
       <c r="B602" s="5">
-        <f>IF(ISNA(VLOOKUP(H602,$A$2:$C$1005,3,1)),C602,VLOOKUP(H602,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H602,$A$2:$C$1011,3,1)),C602,VLOOKUP(H602,$A$2:$C$1011,3,1))</f>
         <v>364</v>
       </c>
       <c r="C602" s="1">
@@ -26406,7 +26500,7 @@
         <v>1762</v>
       </c>
       <c r="B603" s="5">
-        <f>IF(ISNA(VLOOKUP(H603,$A$2:$C$1005,3,1)),C603,VLOOKUP(H603,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H603,$A$2:$C$1011,3,1)),C603,VLOOKUP(H603,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C603" s="1">
@@ -26439,7 +26533,7 @@
         <v>1765</v>
       </c>
       <c r="B604" s="5">
-        <f>IF(ISNA(VLOOKUP(H604,$A$2:$C$1005,3,1)),C604,VLOOKUP(H604,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H604,$A$2:$C$1011,3,1)),C604,VLOOKUP(H604,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C604" s="1">
@@ -26472,7 +26566,7 @@
         <v>1768</v>
       </c>
       <c r="B605" s="5">
-        <f>IF(ISNA(VLOOKUP(H605,$A$2:$C$1005,3,1)),C605,VLOOKUP(H605,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H605,$A$2:$C$1011,3,1)),C605,VLOOKUP(H605,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C605" s="1">
@@ -26505,7 +26599,7 @@
         <v>1771</v>
       </c>
       <c r="B606" s="5">
-        <f>IF(ISNA(VLOOKUP(H606,$A$2:$C$1005,3,1)),C606,VLOOKUP(H606,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H606,$A$2:$C$1011,3,1)),C606,VLOOKUP(H606,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C606" s="1">
@@ -26538,7 +26632,7 @@
         <v>1774</v>
       </c>
       <c r="B607" s="5">
-        <f>IF(ISNA(VLOOKUP(H607,$A$2:$C$1005,3,1)),C607,VLOOKUP(H607,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H607,$A$2:$C$1011,3,1)),C607,VLOOKUP(H607,$A$2:$C$1011,3,1))</f>
         <v>92</v>
       </c>
       <c r="C607" s="1">
@@ -26571,7 +26665,7 @@
         <v>1777</v>
       </c>
       <c r="B608" s="5">
-        <f>IF(ISNA(VLOOKUP(H608,$A$2:$C$1005,3,1)),C608,VLOOKUP(H608,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H608,$A$2:$C$1011,3,1)),C608,VLOOKUP(H608,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C608" s="1">
@@ -26604,7 +26698,7 @@
         <v>1780</v>
       </c>
       <c r="B609" s="5">
-        <f>IF(ISNA(VLOOKUP(H609,$A$2:$C$1005,3,1)),C609,VLOOKUP(H609,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H609,$A$2:$C$1011,3,1)),C609,VLOOKUP(H609,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C609" s="1">
@@ -26637,7 +26731,7 @@
         <v>1783</v>
       </c>
       <c r="B610" s="5">
-        <f>IF(ISNA(VLOOKUP(H610,$A$2:$C$1005,3,1)),C610,VLOOKUP(H610,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H610,$A$2:$C$1011,3,1)),C610,VLOOKUP(H610,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C610" s="1">
@@ -26670,7 +26764,7 @@
         <v>1786</v>
       </c>
       <c r="B611" s="5">
-        <f>IF(ISNA(VLOOKUP(H611,$A$2:$C$1005,3,1)),C611,VLOOKUP(H611,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H611,$A$2:$C$1011,3,1)),C611,VLOOKUP(H611,$A$2:$C$1011,3,1))</f>
         <v>152</v>
       </c>
       <c r="C611" s="1">
@@ -26703,7 +26797,7 @@
         <v>1789</v>
       </c>
       <c r="B612" s="5">
-        <f>IF(ISNA(VLOOKUP(H612,$A$2:$C$1005,3,1)),C612,VLOOKUP(H612,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H612,$A$2:$C$1011,3,1)),C612,VLOOKUP(H612,$A$2:$C$1011,3,1))</f>
         <v>161</v>
       </c>
       <c r="C612" s="1">
@@ -26736,7 +26830,7 @@
         <v>1792</v>
       </c>
       <c r="B613" s="5">
-        <f>IF(ISNA(VLOOKUP(H613,$A$2:$C$1005,3,1)),C613,VLOOKUP(H613,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H613,$A$2:$C$1011,3,1)),C613,VLOOKUP(H613,$A$2:$C$1011,3,1))</f>
         <v>171</v>
       </c>
       <c r="C613" s="1">
@@ -26769,7 +26863,7 @@
         <v>1795</v>
       </c>
       <c r="B614" s="5">
-        <f>IF(ISNA(VLOOKUP(H614,$A$2:$C$1005,3,1)),C614,VLOOKUP(H614,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H614,$A$2:$C$1011,3,1)),C614,VLOOKUP(H614,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C614" s="1">
@@ -26802,7 +26896,7 @@
         <v>1798</v>
       </c>
       <c r="B615" s="5">
-        <f>IF(ISNA(VLOOKUP(H615,$A$2:$C$1005,3,1)),C615,VLOOKUP(H615,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H615,$A$2:$C$1011,3,1)),C615,VLOOKUP(H615,$A$2:$C$1011,3,1))</f>
         <v>205</v>
       </c>
       <c r="C615" s="1">
@@ -26835,7 +26929,7 @@
         <v>1801</v>
       </c>
       <c r="B616" s="5">
-        <f>IF(ISNA(VLOOKUP(H616,$A$2:$C$1005,3,1)),C616,VLOOKUP(H616,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H616,$A$2:$C$1011,3,1)),C616,VLOOKUP(H616,$A$2:$C$1011,3,1))</f>
         <v>213</v>
       </c>
       <c r="C616" s="1">
@@ -26868,7 +26962,7 @@
         <v>1804</v>
       </c>
       <c r="B617" s="5">
-        <f>IF(ISNA(VLOOKUP(H617,$A$2:$C$1005,3,1)),C617,VLOOKUP(H617,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H617,$A$2:$C$1011,3,1)),C617,VLOOKUP(H617,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C617" s="1">
@@ -26901,7 +26995,7 @@
         <v>1807</v>
       </c>
       <c r="B618" s="5">
-        <f>IF(ISNA(VLOOKUP(H618,$A$2:$C$1005,3,1)),C618,VLOOKUP(H618,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H618,$A$2:$C$1011,3,1)),C618,VLOOKUP(H618,$A$2:$C$1011,3,1))</f>
         <v>233</v>
       </c>
       <c r="C618" s="1">
@@ -26934,7 +27028,7 @@
         <v>1810</v>
       </c>
       <c r="B619" s="5">
-        <f>IF(ISNA(VLOOKUP(H619,$A$2:$C$1005,3,1)),C619,VLOOKUP(H619,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H619,$A$2:$C$1011,3,1)),C619,VLOOKUP(H619,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C619" s="1">
@@ -26967,7 +27061,7 @@
         <v>1813</v>
       </c>
       <c r="B620" s="5">
-        <f>IF(ISNA(VLOOKUP(H620,$A$2:$C$1005,3,1)),C620,VLOOKUP(H620,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H620,$A$2:$C$1011,3,1)),C620,VLOOKUP(H620,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C620" s="1">
@@ -27000,7 +27094,7 @@
         <v>1816</v>
       </c>
       <c r="B621" s="5">
-        <f>IF(ISNA(VLOOKUP(H621,$A$2:$C$1005,3,1)),C621,VLOOKUP(H621,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H621,$A$2:$C$1011,3,1)),C621,VLOOKUP(H621,$A$2:$C$1011,3,1))</f>
         <v>278</v>
       </c>
       <c r="C621" s="1">
@@ -27033,7 +27127,7 @@
         <v>1819</v>
       </c>
       <c r="B622" s="5">
-        <f>IF(ISNA(VLOOKUP(H622,$A$2:$C$1005,3,1)),C622,VLOOKUP(H622,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H622,$A$2:$C$1011,3,1)),C622,VLOOKUP(H622,$A$2:$C$1011,3,1))</f>
         <v>284</v>
       </c>
       <c r="C622" s="1">
@@ -27066,7 +27160,7 @@
         <v>1822</v>
       </c>
       <c r="B623" s="5">
-        <f>IF(ISNA(VLOOKUP(H623,$A$2:$C$1005,3,1)),C623,VLOOKUP(H623,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H623,$A$2:$C$1011,3,1)),C623,VLOOKUP(H623,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C623" s="1">
@@ -27099,7 +27193,7 @@
         <v>1825</v>
       </c>
       <c r="B624" s="5">
-        <f>IF(ISNA(VLOOKUP(H624,$A$2:$C$1005,3,1)),C624,VLOOKUP(H624,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H624,$A$2:$C$1011,3,1)),C624,VLOOKUP(H624,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C624" s="1">
@@ -27132,7 +27226,7 @@
         <v>1828</v>
       </c>
       <c r="B625" s="5">
-        <f>IF(ISNA(VLOOKUP(H625,$A$2:$C$1005,3,1)),C625,VLOOKUP(H625,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H625,$A$2:$C$1011,3,1)),C625,VLOOKUP(H625,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C625" s="1">
@@ -27165,7 +27259,7 @@
         <v>1830</v>
       </c>
       <c r="B626" s="5">
-        <f>IF(ISNA(VLOOKUP(H626,$A$2:$C$1005,3,1)),C626,VLOOKUP(H626,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H626,$A$2:$C$1011,3,1)),C626,VLOOKUP(H626,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C626" s="1">
@@ -27198,7 +27292,7 @@
         <v>1833</v>
       </c>
       <c r="B627" s="5">
-        <f>IF(ISNA(VLOOKUP(H627,$A$2:$C$1005,3,1)),C627,VLOOKUP(H627,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H627,$A$2:$C$1011,3,1)),C627,VLOOKUP(H627,$A$2:$C$1011,3,1))</f>
         <v>356</v>
       </c>
       <c r="C627" s="1">
@@ -27231,7 +27325,7 @@
         <v>1836</v>
       </c>
       <c r="B628" s="5">
-        <f>IF(ISNA(VLOOKUP(H628,$A$2:$C$1005,3,1)),C628,VLOOKUP(H628,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H628,$A$2:$C$1011,3,1)),C628,VLOOKUP(H628,$A$2:$C$1011,3,1))</f>
         <v>364</v>
       </c>
       <c r="C628" s="1">
@@ -27264,7 +27358,7 @@
         <v>1839</v>
       </c>
       <c r="B629" s="5">
-        <f>IF(ISNA(VLOOKUP(H629,$A$2:$C$1005,3,1)),C629,VLOOKUP(H629,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H629,$A$2:$C$1011,3,1)),C629,VLOOKUP(H629,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C629" s="1">
@@ -27297,7 +27391,7 @@
         <v>1842</v>
       </c>
       <c r="B630" s="5">
-        <f>IF(ISNA(VLOOKUP(H630,$A$2:$C$1005,3,1)),C630,VLOOKUP(H630,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H630,$A$2:$C$1011,3,1)),C630,VLOOKUP(H630,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C630" s="1">
@@ -27330,7 +27424,7 @@
         <v>1845</v>
       </c>
       <c r="B631" s="5">
-        <f>IF(ISNA(VLOOKUP(H631,$A$2:$C$1005,3,1)),C631,VLOOKUP(H631,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H631,$A$2:$C$1011,3,1)),C631,VLOOKUP(H631,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C631" s="1">
@@ -27363,7 +27457,7 @@
         <v>1848</v>
       </c>
       <c r="B632" s="5">
-        <f>IF(ISNA(VLOOKUP(H632,$A$2:$C$1005,3,1)),C632,VLOOKUP(H632,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H632,$A$2:$C$1011,3,1)),C632,VLOOKUP(H632,$A$2:$C$1011,3,1))</f>
         <v>66</v>
       </c>
       <c r="C632" s="1">
@@ -27396,7 +27490,7 @@
         <v>1851</v>
       </c>
       <c r="B633" s="5">
-        <f>IF(ISNA(VLOOKUP(H633,$A$2:$C$1005,3,1)),C633,VLOOKUP(H633,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H633,$A$2:$C$1011,3,1)),C633,VLOOKUP(H633,$A$2:$C$1011,3,1))</f>
         <v>92</v>
       </c>
       <c r="C633" s="1">
@@ -27429,7 +27523,7 @@
         <v>1854</v>
       </c>
       <c r="B634" s="5">
-        <f>IF(ISNA(VLOOKUP(H634,$A$2:$C$1005,3,1)),C634,VLOOKUP(H634,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H634,$A$2:$C$1011,3,1)),C634,VLOOKUP(H634,$A$2:$C$1011,3,1))</f>
         <v>98</v>
       </c>
       <c r="C634" s="1">
@@ -27462,7 +27556,7 @@
         <v>1857</v>
       </c>
       <c r="B635" s="5">
-        <f>IF(ISNA(VLOOKUP(H635,$A$2:$C$1005,3,1)),C635,VLOOKUP(H635,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H635,$A$2:$C$1011,3,1)),C635,VLOOKUP(H635,$A$2:$C$1011,3,1))</f>
         <v>113</v>
       </c>
       <c r="C635" s="1">
@@ -27495,7 +27589,7 @@
         <v>1860</v>
       </c>
       <c r="B636" s="5">
-        <f>IF(ISNA(VLOOKUP(H636,$A$2:$C$1005,3,1)),C636,VLOOKUP(H636,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H636,$A$2:$C$1011,3,1)),C636,VLOOKUP(H636,$A$2:$C$1011,3,1))</f>
         <v>126</v>
       </c>
       <c r="C636" s="1">
@@ -27528,7 +27622,7 @@
         <v>1862</v>
       </c>
       <c r="B637" s="5">
-        <f>IF(ISNA(VLOOKUP(H637,$A$2:$C$1005,3,1)),C637,VLOOKUP(H637,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H637,$A$2:$C$1011,3,1)),C637,VLOOKUP(H637,$A$2:$C$1011,3,1))</f>
         <v>152</v>
       </c>
       <c r="C637" s="1">
@@ -27561,7 +27655,7 @@
         <v>1865</v>
       </c>
       <c r="B638" s="5">
-        <f>IF(ISNA(VLOOKUP(H638,$A$2:$C$1005,3,1)),C638,VLOOKUP(H638,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H638,$A$2:$C$1011,3,1)),C638,VLOOKUP(H638,$A$2:$C$1011,3,1))</f>
         <v>161</v>
       </c>
       <c r="C638" s="1">
@@ -27594,7 +27688,7 @@
         <v>1868</v>
       </c>
       <c r="B639" s="5">
-        <f>IF(ISNA(VLOOKUP(H639,$A$2:$C$1005,3,1)),C639,VLOOKUP(H639,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H639,$A$2:$C$1011,3,1)),C639,VLOOKUP(H639,$A$2:$C$1011,3,1))</f>
         <v>171</v>
       </c>
       <c r="C639" s="1">
@@ -27627,7 +27721,7 @@
         <v>1871</v>
       </c>
       <c r="B640" s="5">
-        <f>IF(ISNA(VLOOKUP(H640,$A$2:$C$1005,3,1)),C640,VLOOKUP(H640,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H640,$A$2:$C$1011,3,1)),C640,VLOOKUP(H640,$A$2:$C$1011,3,1))</f>
         <v>181</v>
       </c>
       <c r="C640" s="1">
@@ -27660,7 +27754,7 @@
         <v>1874</v>
       </c>
       <c r="B641" s="5">
-        <f>IF(ISNA(VLOOKUP(H641,$A$2:$C$1005,3,1)),C641,VLOOKUP(H641,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H641,$A$2:$C$1011,3,1)),C641,VLOOKUP(H641,$A$2:$C$1011,3,1))</f>
         <v>205</v>
       </c>
       <c r="C641" s="1">
@@ -27693,7 +27787,7 @@
         <v>1877</v>
       </c>
       <c r="B642" s="5">
-        <f>IF(ISNA(VLOOKUP(H642,$A$2:$C$1005,3,1)),C642,VLOOKUP(H642,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H642,$A$2:$C$1011,3,1)),C642,VLOOKUP(H642,$A$2:$C$1011,3,1))</f>
         <v>213</v>
       </c>
       <c r="C642" s="1">
@@ -27726,7 +27820,7 @@
         <v>1880</v>
       </c>
       <c r="B643" s="5">
-        <f>IF(ISNA(VLOOKUP(H643,$A$2:$C$1005,3,1)),C643,VLOOKUP(H643,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H643,$A$2:$C$1011,3,1)),C643,VLOOKUP(H643,$A$2:$C$1011,3,1))</f>
         <v>220</v>
       </c>
       <c r="C643" s="1">
@@ -27759,7 +27853,7 @@
         <v>1883</v>
       </c>
       <c r="B644" s="5">
-        <f>IF(ISNA(VLOOKUP(H644,$A$2:$C$1005,3,1)),C644,VLOOKUP(H644,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H644,$A$2:$C$1011,3,1)),C644,VLOOKUP(H644,$A$2:$C$1011,3,1))</f>
         <v>233</v>
       </c>
       <c r="C644" s="1">
@@ -27792,7 +27886,7 @@
         <v>1886</v>
       </c>
       <c r="B645" s="5">
-        <f>IF(ISNA(VLOOKUP(H645,$A$2:$C$1005,3,1)),C645,VLOOKUP(H645,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H645,$A$2:$C$1011,3,1)),C645,VLOOKUP(H645,$A$2:$C$1011,3,1))</f>
         <v>239</v>
       </c>
       <c r="C645" s="1">
@@ -27825,7 +27919,7 @@
         <v>1889</v>
       </c>
       <c r="B646" s="5">
-        <f>IF(ISNA(VLOOKUP(H646,$A$2:$C$1005,3,1)),C646,VLOOKUP(H646,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H646,$A$2:$C$1011,3,1)),C646,VLOOKUP(H646,$A$2:$C$1011,3,1))</f>
         <v>253</v>
       </c>
       <c r="C646" s="1">
@@ -27858,7 +27952,7 @@
         <v>1892</v>
       </c>
       <c r="B647" s="5">
-        <f>IF(ISNA(VLOOKUP(H647,$A$2:$C$1005,3,1)),C647,VLOOKUP(H647,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H647,$A$2:$C$1011,3,1)),C647,VLOOKUP(H647,$A$2:$C$1011,3,1))</f>
         <v>278</v>
       </c>
       <c r="C647" s="1">
@@ -27891,7 +27985,7 @@
         <v>1895</v>
       </c>
       <c r="B648" s="5">
-        <f>IF(ISNA(VLOOKUP(H648,$A$2:$C$1005,3,1)),C648,VLOOKUP(H648,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H648,$A$2:$C$1011,3,1)),C648,VLOOKUP(H648,$A$2:$C$1011,3,1))</f>
         <v>284</v>
       </c>
       <c r="C648" s="1">
@@ -27924,7 +28018,7 @@
         <v>1898</v>
       </c>
       <c r="B649" s="5">
-        <f>IF(ISNA(VLOOKUP(H649,$A$2:$C$1005,3,1)),C649,VLOOKUP(H649,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H649,$A$2:$C$1011,3,1)),C649,VLOOKUP(H649,$A$2:$C$1011,3,1))</f>
         <v>291</v>
       </c>
       <c r="C649" s="1">
@@ -27957,7 +28051,7 @@
         <v>1901</v>
       </c>
       <c r="B650" s="5">
-        <f>IF(ISNA(VLOOKUP(H650,$A$2:$C$1005,3,1)),C650,VLOOKUP(H650,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H650,$A$2:$C$1011,3,1)),C650,VLOOKUP(H650,$A$2:$C$1011,3,1))</f>
         <v>303</v>
       </c>
       <c r="C650" s="1">
@@ -27990,7 +28084,7 @@
         <v>1904</v>
       </c>
       <c r="B651" s="5">
-        <f>IF(ISNA(VLOOKUP(H651,$A$2:$C$1005,3,1)),C651,VLOOKUP(H651,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H651,$A$2:$C$1011,3,1)),C651,VLOOKUP(H651,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C651" s="1">
@@ -28023,7 +28117,7 @@
         <v>1907</v>
       </c>
       <c r="B652" s="5">
-        <f>IF(ISNA(VLOOKUP(H652,$A$2:$C$1005,3,1)),C652,VLOOKUP(H652,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H652,$A$2:$C$1011,3,1)),C652,VLOOKUP(H652,$A$2:$C$1011,3,1))</f>
         <v>330</v>
       </c>
       <c r="C652" s="1">
@@ -28056,7 +28150,7 @@
         <v>1910</v>
       </c>
       <c r="B653" s="5">
-        <f>IF(ISNA(VLOOKUP(H653,$A$2:$C$1005,3,1)),C653,VLOOKUP(H653,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H653,$A$2:$C$1011,3,1)),C653,VLOOKUP(H653,$A$2:$C$1011,3,1))</f>
         <v>356</v>
       </c>
       <c r="C653" s="1">
@@ -28089,7 +28183,7 @@
         <v>1913</v>
       </c>
       <c r="B654" s="5">
-        <f>IF(ISNA(VLOOKUP(H654,$A$2:$C$1005,3,1)),C654,VLOOKUP(H654,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H654,$A$2:$C$1011,3,1)),C654,VLOOKUP(H654,$A$2:$C$1011,3,1))</f>
         <v>364</v>
       </c>
       <c r="C654" s="1">
@@ -28122,7 +28216,7 @@
         <v>1916</v>
       </c>
       <c r="B655" s="5">
-        <f>IF(ISNA(VLOOKUP(H655,$A$2:$C$1005,3,1)),C655,VLOOKUP(H655,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H655,$A$2:$C$1011,3,1)),C655,VLOOKUP(H655,$A$2:$C$1011,3,1))</f>
         <v>373</v>
       </c>
       <c r="C655" s="1">
@@ -28155,7 +28249,7 @@
         <v>1919</v>
       </c>
       <c r="B656" s="5">
-        <f>IF(ISNA(VLOOKUP(H656,$A$2:$C$1005,3,1)),C656,VLOOKUP(H656,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H656,$A$2:$C$1011,3,1)),C656,VLOOKUP(H656,$A$2:$C$1011,3,1))</f>
         <v>384</v>
       </c>
       <c r="C656" s="1">
@@ -28188,7 +28282,7 @@
         <v>1922</v>
       </c>
       <c r="B657" s="5">
-        <f>IF(ISNA(VLOOKUP(H657,$A$2:$C$1005,3,1)),C657,VLOOKUP(H657,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H657,$A$2:$C$1011,3,1)),C657,VLOOKUP(H657,$A$2:$C$1011,3,1))</f>
         <v>399</v>
       </c>
       <c r="C657" s="1">
@@ -28221,7 +28315,7 @@
         <v>2006</v>
       </c>
       <c r="B658" s="5">
-        <f>IF(ISNA(VLOOKUP(H658,$A$2:$C$1005,3,1)),C658,VLOOKUP(H658,$A$2:$C$1005,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H658,$A$2:$C$1011,3,1)),C658,VLOOKUP(H658,$A$2:$C$1011,3,1))</f>
         <v>11</v>
       </c>
       <c r="C658" s="1">
@@ -28254,8 +28348,8 @@
         <v>1925</v>
       </c>
       <c r="B659" s="5">
-        <f>IF(ISNA(VLOOKUP(H659,$A$2:$C$1005,3,1)),C659,VLOOKUP(H659,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H659,$A$2:$C$1011,3,1)),C659,VLOOKUP(H659,$A$2:$C$1011,3,1))</f>
+        <v>652</v>
       </c>
       <c r="C659" s="1">
         <v>652</v>
@@ -28274,12 +28368,13 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A659,3,4)))</f>
         <v>▢</v>
       </c>
-      <c r="H659" s="1" t="s">
-        <v>1486</v>
+      <c r="H659" s="17" t="str">
+        <f>A659</f>
+        <v>U+25a2</v>
       </c>
       <c r="I659" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H659,3,4)))</f>
-        <v>⎙</v>
+        <v>▢</v>
       </c>
     </row>
     <row r="660" spans="1:9" ht="17" customHeight="1">
@@ -28287,8 +28382,8 @@
         <v>1928</v>
       </c>
       <c r="B660" s="5">
-        <f>IF(ISNA(VLOOKUP(H660,$A$2:$C$1005,3,1)),C660,VLOOKUP(H660,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H660,$A$2:$C$1011,3,1)),C660,VLOOKUP(H660,$A$2:$C$1011,3,1))</f>
+        <v>653</v>
       </c>
       <c r="C660" s="1">
         <v>653</v>
@@ -28307,598 +28402,800 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A660,3,4)))</f>
         <v>▦</v>
       </c>
-      <c r="H660" s="1" t="s">
-        <v>1486</v>
+      <c r="H660" s="17" t="str">
+        <f>A660</f>
+        <v>U+25a6</v>
       </c>
       <c r="I660" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H660,3,4)))</f>
-        <v>⎙</v>
+        <v>▦</v>
       </c>
     </row>
     <row r="661" spans="1:9" ht="17" customHeight="1">
       <c r="A661" s="1" t="s">
-        <v>1931</v>
+        <v>2011</v>
       </c>
       <c r="B661" s="5">
-        <f>IF(ISNA(VLOOKUP(H661,$A$2:$C$1005,3,1)),C661,VLOOKUP(H661,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H661,$A$2:$C$1011,3,1)),C661,VLOOKUP(H661,$A$2:$C$1011,3,1))</f>
+        <v>658</v>
       </c>
       <c r="C661" s="1">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="D661" s="2" t="s">
-        <v>1932</v>
+        <v>2017</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>1933</v>
+        <v>2023</v>
       </c>
       <c r="F661" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A661,3,4)))</f>
-        <v>♺</v>
+        <v>◇</v>
       </c>
       <c r="G661" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A661,3,4)))</f>
-        <v>♺</v>
-      </c>
-      <c r="H661" s="1" t="s">
-        <v>1486</v>
+        <v>◇</v>
+      </c>
+      <c r="H661" s="17" t="str">
+        <f>A661</f>
+        <v>U+25c7</v>
       </c>
       <c r="I661" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H661,3,4)))</f>
-        <v>⎙</v>
+        <v>◇</v>
       </c>
     </row>
     <row r="662" spans="1:9" ht="17" customHeight="1">
       <c r="A662" s="1" t="s">
-        <v>1934</v>
+        <v>2012</v>
       </c>
       <c r="B662" s="5">
-        <f>IF(ISNA(VLOOKUP(H662,$A$2:$C$1005,3,1)),C662,VLOOKUP(H662,$A$2:$C$1005,3,1))</f>
-        <v>98</v>
+        <f>IF(ISNA(VLOOKUP(H662,$A$2:$C$1011,3,1)),C662,VLOOKUP(H662,$A$2:$C$1011,3,1))</f>
+        <v>659</v>
       </c>
       <c r="C662" s="1">
-        <v>112</v>
+        <v>659</v>
       </c>
       <c r="D662" s="2" t="s">
-        <v>1935</v>
+        <v>2018</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1936</v>
+        <v>2024</v>
       </c>
       <c r="F662" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A662,3,4)))</f>
-        <v>♻</v>
+        <v>◈</v>
       </c>
       <c r="G662" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A662,3,4)))</f>
-        <v>♻</v>
-      </c>
-      <c r="H662" s="1" t="s">
-        <v>126</v>
+        <v>◈</v>
+      </c>
+      <c r="H662" s="17" t="str">
+        <f>A662</f>
+        <v>U+25c8</v>
       </c>
       <c r="I662" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H662,3,4)))</f>
-        <v>C</v>
+        <v>◈</v>
       </c>
     </row>
     <row r="663" spans="1:9" ht="17" customHeight="1">
       <c r="A663" s="1" t="s">
-        <v>1937</v>
+        <v>2009</v>
       </c>
       <c r="B663" s="5">
-        <f>IF(ISNA(VLOOKUP(H663,$A$2:$C$1005,3,1)),C663,VLOOKUP(H663,$A$2:$C$1005,3,1))</f>
-        <v>239</v>
+        <f>IF(ISNA(VLOOKUP(H663,$A$2:$C$1011,3,1)),C663,VLOOKUP(H663,$A$2:$C$1011,3,1))</f>
+        <v>656</v>
       </c>
       <c r="C663" s="1">
-        <v>252</v>
+        <v>656</v>
       </c>
       <c r="D663" s="2" t="s">
-        <v>1938</v>
+        <v>2015</v>
       </c>
       <c r="E663" s="2" t="s">
-        <v>1939</v>
+        <v>2021</v>
       </c>
       <c r="F663" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A663,3,4)))</f>
-        <v>♾</v>
+        <v>◯</v>
       </c>
       <c r="G663" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A663,3,4)))</f>
-        <v>♾</v>
-      </c>
-      <c r="H663" s="1" t="s">
-        <v>159</v>
+        <v>◯</v>
+      </c>
+      <c r="H663" s="17" t="str">
+        <f>A663</f>
+        <v>U+25ef</v>
       </c>
       <c r="I663" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H663,3,4)))</f>
-        <v>N</v>
+        <v>◯</v>
       </c>
     </row>
     <row r="664" spans="1:9" ht="17" customHeight="1">
       <c r="A664" s="1" t="s">
-        <v>1940</v>
+        <v>2007</v>
       </c>
       <c r="B664" s="5">
-        <f>IF(ISNA(VLOOKUP(H664,$A$2:$C$1005,3,1)),C664,VLOOKUP(H664,$A$2:$C$1005,3,1))</f>
-        <v>676</v>
+        <f>IF(ISNA(VLOOKUP(H664,$A$2:$C$1011,3,1)),C664,VLOOKUP(H664,$A$2:$C$1011,3,1))</f>
+        <v>654</v>
       </c>
       <c r="C664" s="1">
-        <v>676</v>
+        <v>654</v>
       </c>
       <c r="D664" s="2" t="s">
-        <v>1941</v>
+        <v>2013</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1942</v>
+        <v>2019</v>
       </c>
       <c r="F664" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A664,3,4)))</f>
-        <v>✓</v>
+        <v>☐</v>
       </c>
       <c r="G664" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A664,3,4)))</f>
-        <v>✓</v>
-      </c>
-      <c r="H664" s="1" t="s">
-        <v>1940</v>
+        <v>☐</v>
+      </c>
+      <c r="H664" s="17" t="str">
+        <f>A664</f>
+        <v>U+2610</v>
       </c>
       <c r="I664" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H664,3,4)))</f>
-        <v>✓</v>
+        <v>☐</v>
       </c>
     </row>
     <row r="665" spans="1:9" ht="17" customHeight="1">
       <c r="A665" s="1" t="s">
-        <v>1943</v>
+        <v>2008</v>
       </c>
       <c r="B665" s="5">
-        <f>IF(ISNA(VLOOKUP(H665,$A$2:$C$1005,3,1)),C665,VLOOKUP(H665,$A$2:$C$1005,3,1))</f>
-        <v>528</v>
+        <f>IF(ISNA(VLOOKUP(H665,$A$2:$C$1011,3,1)),C665,VLOOKUP(H665,$A$2:$C$1011,3,1))</f>
+        <v>655</v>
       </c>
       <c r="C665" s="1">
-        <v>530</v>
+        <v>655</v>
       </c>
       <c r="D665" s="2" t="s">
-        <v>1944</v>
+        <v>2014</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>1945</v>
+        <v>2020</v>
       </c>
       <c r="F665" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A665,3,4)))</f>
-        <v>➈</v>
+        <v>☒</v>
       </c>
       <c r="G665" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A665,3,4)))</f>
-        <v>➈</v>
-      </c>
-      <c r="H665" s="1" t="s">
-        <v>51</v>
+        <v>☒</v>
+      </c>
+      <c r="H665" s="17" t="str">
+        <f>A665</f>
+        <v>U+2612</v>
       </c>
       <c r="I665" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H665,3,4)))</f>
-        <v>,</v>
+        <v>☒</v>
       </c>
     </row>
     <row r="666" spans="1:9" ht="17" customHeight="1">
       <c r="A666" s="1" t="s">
-        <v>1946</v>
+        <v>1931</v>
       </c>
       <c r="B666" s="5">
-        <f>IF(ISNA(VLOOKUP(H666,$A$2:$C$1005,3,1)),C666,VLOOKUP(H666,$A$2:$C$1005,3,1))</f>
-        <v>531</v>
+        <f>IF(ISNA(VLOOKUP(H666,$A$2:$C$1011,3,1)),C666,VLOOKUP(H666,$A$2:$C$1011,3,1))</f>
+        <v>650</v>
       </c>
       <c r="C666" s="1">
-        <v>534</v>
+        <v>650</v>
       </c>
       <c r="D666" s="2" t="s">
-        <v>1947</v>
+        <v>1932</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>1948</v>
+        <v>1933</v>
       </c>
       <c r="F666" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A666,3,4)))</f>
-        <v>➉</v>
+        <v>♺</v>
       </c>
       <c r="G666" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A666,3,4)))</f>
-        <v>➉</v>
-      </c>
-      <c r="H666" s="1" t="s">
-        <v>59</v>
+        <v>♺</v>
+      </c>
+      <c r="H666" s="17" t="str">
+        <f>A666</f>
+        <v>U+267A</v>
       </c>
       <c r="I666" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H666,3,4)))</f>
-        <v>.</v>
+        <v>♺</v>
       </c>
     </row>
     <row r="667" spans="1:9" ht="17" customHeight="1">
       <c r="A667" s="1" t="s">
-        <v>1949</v>
+        <v>1934</v>
       </c>
       <c r="B667" s="5">
-        <f>IF(ISNA(VLOOKUP(H667,$A$2:$C$1005,3,1)),C667,VLOOKUP(H667,$A$2:$C$1005,3,1))</f>
-        <v>640</v>
+        <f>IF(ISNA(VLOOKUP(H667,$A$2:$C$1011,3,1)),C667,VLOOKUP(H667,$A$2:$C$1011,3,1))</f>
+        <v>98</v>
       </c>
       <c r="C667" s="1">
-        <v>642</v>
+        <v>112</v>
       </c>
       <c r="D667" s="2" t="s">
-        <v>1950</v>
+        <v>1935</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1489</v>
+        <v>1936</v>
       </c>
       <c r="F667" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A667,3,4)))</f>
-        <v>⧖</v>
+        <v>♻</v>
       </c>
       <c r="G667" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A667,3,4)))</f>
-        <v>⧖</v>
+        <v>♻</v>
       </c>
       <c r="H667" s="1" t="s">
-        <v>1486</v>
+        <v>126</v>
       </c>
       <c r="I667" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H667,3,4)))</f>
-        <v>⎙</v>
+        <v>C</v>
       </c>
     </row>
     <row r="668" spans="1:9" ht="17" customHeight="1">
       <c r="A668" s="1" t="s">
-        <v>1951</v>
+        <v>1937</v>
       </c>
       <c r="B668" s="5">
-        <f>IF(ISNA(VLOOKUP(H668,$A$2:$C$1005,3,1)),C668,VLOOKUP(H668,$A$2:$C$1005,3,1))</f>
-        <v>384</v>
+        <f>IF(ISNA(VLOOKUP(H668,$A$2:$C$1011,3,1)),C668,VLOOKUP(H668,$A$2:$C$1011,3,1))</f>
+        <v>239</v>
       </c>
       <c r="C668" s="1">
-        <v>398</v>
+        <v>252</v>
       </c>
       <c r="D668" s="2" t="s">
-        <v>1952</v>
+        <v>1938</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1953</v>
+        <v>1939</v>
       </c>
       <c r="F668" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A668,3,4)))</f>
-        <v>⧰</v>
+        <v>♾</v>
       </c>
       <c r="G668" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A668,3,4)))</f>
-        <v>⧰</v>
+        <v>♾</v>
       </c>
       <c r="H668" s="1" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="I668" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H668,3,4)))</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
     </row>
     <row r="669" spans="1:9" ht="17" customHeight="1">
       <c r="A669" s="1" t="s">
-        <v>1954</v>
+        <v>1940</v>
       </c>
       <c r="B669" s="5">
-        <f>IF(ISNA(VLOOKUP(H669,$A$2:$C$1005,3,1)),C669,VLOOKUP(H669,$A$2:$C$1005,3,1))</f>
-        <v>152</v>
+        <f>IF(ISNA(VLOOKUP(H669,$A$2:$C$1011,3,1)),C669,VLOOKUP(H669,$A$2:$C$1011,3,1))</f>
+        <v>682</v>
       </c>
       <c r="C669" s="1">
-        <v>160</v>
+        <v>682</v>
       </c>
       <c r="D669" s="2" t="s">
-        <v>1955</v>
+        <v>1941</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>1956</v>
+        <v>1942</v>
       </c>
       <c r="F669" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A669,3,4)))</f>
-        <v>⧱</v>
+        <v>✓</v>
       </c>
       <c r="G669" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A669,3,4)))</f>
-        <v>⧱</v>
+        <v>✓</v>
       </c>
       <c r="H669" s="1" t="s">
-        <v>135</v>
+        <v>1940</v>
       </c>
       <c r="I669" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H669,3,4)))</f>
-        <v>F</v>
+        <v>✓</v>
       </c>
     </row>
     <row r="670" spans="1:9" ht="17" customHeight="1">
       <c r="A670" s="1" t="s">
-        <v>1957</v>
+        <v>1943</v>
       </c>
       <c r="B670" s="5">
-        <f>IF(ISNA(VLOOKUP(H670,$A$2:$C$1005,3,1)),C670,VLOOKUP(H670,$A$2:$C$1005,3,1))</f>
-        <v>567</v>
+        <f>IF(ISNA(VLOOKUP(H670,$A$2:$C$1011,3,1)),C670,VLOOKUP(H670,$A$2:$C$1011,3,1))</f>
+        <v>528</v>
       </c>
       <c r="C670" s="1">
-        <v>569</v>
+        <v>530</v>
       </c>
       <c r="D670" s="2" t="s">
-        <v>1958</v>
+        <v>1944</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1959</v>
+        <v>1945</v>
       </c>
       <c r="F670" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A670,3,4)))</f>
-        <v>⭠</v>
+        <v>➈</v>
       </c>
       <c r="G670" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A670,3,4)))</f>
-        <v>⭠</v>
+        <v>➈</v>
       </c>
       <c r="H670" s="1" t="s">
-        <v>1229</v>
+        <v>51</v>
       </c>
       <c r="I670" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H670,3,4)))</f>
-        <v>←</v>
+        <v>,</v>
       </c>
     </row>
     <row r="671" spans="1:9" ht="17" customHeight="1">
       <c r="A671" s="1" t="s">
-        <v>1960</v>
+        <v>1946</v>
       </c>
       <c r="B671" s="5">
-        <f>IF(ISNA(VLOOKUP(H671,$A$2:$C$1005,3,1)),C671,VLOOKUP(H671,$A$2:$C$1005,3,1))</f>
-        <v>572</v>
+        <f>IF(ISNA(VLOOKUP(H671,$A$2:$C$1011,3,1)),C671,VLOOKUP(H671,$A$2:$C$1011,3,1))</f>
+        <v>531</v>
       </c>
       <c r="C671" s="1">
-        <v>574</v>
+        <v>534</v>
       </c>
       <c r="D671" s="2" t="s">
-        <v>1961</v>
+        <v>1947</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>1962</v>
+        <v>1948</v>
       </c>
       <c r="F671" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A671,3,4)))</f>
-        <v>⭡</v>
+        <v>➉</v>
       </c>
       <c r="G671" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A671,3,4)))</f>
-        <v>⭡</v>
+        <v>➉</v>
       </c>
       <c r="H671" s="1" t="s">
-        <v>1232</v>
+        <v>59</v>
       </c>
       <c r="I671" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H671,3,4)))</f>
-        <v>↑</v>
+        <v>.</v>
       </c>
     </row>
     <row r="672" spans="1:9" ht="17" customHeight="1">
       <c r="A672" s="1" t="s">
-        <v>1963</v>
+        <v>2010</v>
       </c>
       <c r="B672" s="5">
-        <f>IF(ISNA(VLOOKUP(H672,$A$2:$C$1005,3,1)),C672,VLOOKUP(H672,$A$2:$C$1005,3,1))</f>
-        <v>562</v>
+        <f>IF(ISNA(VLOOKUP(H672,$A$2:$C$1011,3,1)),C672,VLOOKUP(H672,$A$2:$C$1011,3,1))</f>
+        <v>657</v>
       </c>
       <c r="C672" s="1">
-        <v>565</v>
+        <v>657</v>
       </c>
       <c r="D672" s="2" t="s">
-        <v>1964</v>
+        <v>2016</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>1965</v>
+        <v>2022</v>
       </c>
       <c r="F672" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A672,3,4)))</f>
-        <v>⭢</v>
+        <v>⦿</v>
       </c>
       <c r="G672" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A672,3,4)))</f>
-        <v>⭢</v>
-      </c>
-      <c r="H672" s="1" t="s">
-        <v>1235</v>
+        <v>⦿</v>
+      </c>
+      <c r="H672" s="17" t="str">
+        <f>A672</f>
+        <v>U+29bf</v>
       </c>
       <c r="I672" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H672,3,4)))</f>
-        <v>→</v>
+        <v>⦿</v>
       </c>
     </row>
     <row r="673" spans="1:11" ht="17" customHeight="1">
       <c r="A673" s="1" t="s">
-        <v>1966</v>
+        <v>1949</v>
       </c>
       <c r="B673" s="5">
-        <f>IF(ISNA(VLOOKUP(H673,$A$2:$C$1005,3,1)),C673,VLOOKUP(H673,$A$2:$C$1005,3,1))</f>
-        <v>578</v>
+        <f>IF(ISNA(VLOOKUP(H673,$A$2:$C$1011,3,1)),C673,VLOOKUP(H673,$A$2:$C$1011,3,1))</f>
+        <v>642</v>
       </c>
       <c r="C673" s="1">
-        <v>580</v>
+        <v>642</v>
       </c>
       <c r="D673" s="2" t="s">
-        <v>1967</v>
+        <v>1950</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1968</v>
+        <v>1489</v>
       </c>
       <c r="F673" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A673,3,4)))</f>
-        <v>⭣</v>
+        <v>⧖</v>
       </c>
       <c r="G673" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A673,3,4)))</f>
-        <v>⭣</v>
-      </c>
-      <c r="H673" s="1" t="s">
-        <v>1238</v>
+        <v>⧖</v>
+      </c>
+      <c r="H673" s="17" t="str">
+        <f>A673</f>
+        <v>U+29d6</v>
       </c>
       <c r="I673" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H673,3,4)))</f>
-        <v>↓</v>
+        <v>⧖</v>
       </c>
     </row>
     <row r="674" spans="1:11" ht="17" customHeight="1">
       <c r="A674" s="1" t="s">
-        <v>1969</v>
+        <v>1951</v>
       </c>
       <c r="B674" s="5">
-        <f>IF(ISNA(VLOOKUP(H674,$A$2:$C$1005,3,1)),C674,VLOOKUP(H674,$A$2:$C$1005,3,1))</f>
-        <v>459</v>
+        <f>IF(ISNA(VLOOKUP(H674,$A$2:$C$1011,3,1)),C674,VLOOKUP(H674,$A$2:$C$1011,3,1))</f>
+        <v>384</v>
       </c>
       <c r="C674" s="1">
-        <v>462</v>
+        <v>398</v>
       </c>
       <c r="D674" s="2" t="s">
-        <v>1970</v>
+        <v>1952</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>1971</v>
+        <v>1953</v>
       </c>
       <c r="F674" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A674,3,4)))</f>
-        <v>Ɽ</v>
+        <v>⧰</v>
       </c>
       <c r="G674" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A674,3,4)))</f>
-        <v>Ɽ</v>
+        <v>⧰</v>
       </c>
       <c r="H674" s="1" t="s">
-        <v>882</v>
+        <v>192</v>
       </c>
       <c r="I674" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H674,3,4)))</f>
-        <v>Π</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="675" spans="1:11" ht="17" customHeight="1">
       <c r="A675" s="1" t="s">
-        <v>1972</v>
+        <v>1954</v>
       </c>
       <c r="B675" s="5">
-        <f>IF(ISNA(VLOOKUP(H675,$A$2:$C$1005,3,1)),C675,VLOOKUP(H675,$A$2:$C$1005,3,1))</f>
-        <v>459</v>
+        <f>IF(ISNA(VLOOKUP(H675,$A$2:$C$1011,3,1)),C675,VLOOKUP(H675,$A$2:$C$1011,3,1))</f>
+        <v>152</v>
       </c>
       <c r="C675" s="1">
-        <v>463</v>
+        <v>160</v>
       </c>
       <c r="D675" s="2" t="s">
-        <v>1973</v>
+        <v>1955</v>
       </c>
       <c r="E675" s="2" t="s">
-        <v>1974</v>
+        <v>1956</v>
       </c>
       <c r="F675" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A675,3,4)))</f>
-        <v>ⱥ</v>
+        <v>⧱</v>
       </c>
       <c r="G675" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A675,3,4)))</f>
-        <v>ⱥ</v>
+        <v>⧱</v>
       </c>
       <c r="H675" s="1" t="s">
-        <v>882</v>
+        <v>135</v>
       </c>
       <c r="I675" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H675,3,4)))</f>
-        <v>Π</v>
+        <v>F</v>
       </c>
     </row>
     <row r="676" spans="1:11" ht="17" customHeight="1">
       <c r="A676" s="1" t="s">
-        <v>1975</v>
+        <v>1957</v>
       </c>
       <c r="B676" s="5">
-        <f>IF(ISNA(VLOOKUP(H676,$A$2:$C$1005,3,1)),C676,VLOOKUP(H676,$A$2:$C$1005,3,1))</f>
-        <v>459</v>
+        <f>IF(ISNA(VLOOKUP(H676,$A$2:$C$1011,3,1)),C676,VLOOKUP(H676,$A$2:$C$1011,3,1))</f>
+        <v>567</v>
       </c>
       <c r="C676" s="1">
-        <v>464</v>
+        <v>569</v>
       </c>
       <c r="D676" s="2" t="s">
-        <v>1976</v>
+        <v>1958</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>1977</v>
+        <v>1959</v>
       </c>
       <c r="F676" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A676,3,4)))</f>
-        <v>ⱦ</v>
+        <v>⭠</v>
       </c>
       <c r="G676" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A676,3,4)))</f>
-        <v>ⱦ</v>
+        <v>⭠</v>
       </c>
       <c r="H676" s="1" t="s">
-        <v>882</v>
+        <v>1229</v>
       </c>
       <c r="I676" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H676,3,4)))</f>
-        <v>Π</v>
+        <v>←</v>
       </c>
     </row>
     <row r="677" spans="1:11" ht="17" customHeight="1">
       <c r="A677" s="1" t="s">
-        <v>1289</v>
+        <v>1960</v>
       </c>
       <c r="B677" s="5">
-        <f>IF(ISNA(VLOOKUP(H677,$A$2:$C$1005,3,1)),C677,VLOOKUP(H677,$A$2:$C$1005,3,1))</f>
-        <v>657</v>
+        <f>IF(ISNA(VLOOKUP(H677,$A$2:$C$1011,3,1)),C677,VLOOKUP(H677,$A$2:$C$1011,3,1))</f>
+        <v>572</v>
       </c>
       <c r="C677" s="1">
-        <v>657</v>
+        <v>574</v>
       </c>
       <c r="D677" s="2" t="s">
-        <v>1978</v>
+        <v>1961</v>
       </c>
       <c r="E677" s="2" t="s">
-        <v>1979</v>
+        <v>1962</v>
       </c>
       <c r="F677" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A677,3,4)))</f>
-        <v>Ɐ</v>
+        <v>⭡</v>
       </c>
       <c r="G677" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A677,3,4)))</f>
-        <v>Ɐ</v>
+        <v>⭡</v>
       </c>
       <c r="H677" s="1" t="s">
-        <v>1289</v>
+        <v>1232</v>
       </c>
       <c r="I677" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H677,3,4)))</f>
-        <v>Ɐ</v>
+        <v>↑</v>
       </c>
     </row>
     <row r="678" spans="1:11" ht="17" customHeight="1">
       <c r="A678" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B678" s="5">
+        <f>IF(ISNA(VLOOKUP(H678,$A$2:$C$1011,3,1)),C678,VLOOKUP(H678,$A$2:$C$1011,3,1))</f>
+        <v>562</v>
+      </c>
+      <c r="C678" s="1">
+        <v>565</v>
+      </c>
+      <c r="D678" s="2" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E678" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="F678" s="5" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A678,3,4)))</f>
+        <v>⭢</v>
+      </c>
+      <c r="G678" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A678,3,4)))</f>
+        <v>⭢</v>
+      </c>
+      <c r="H678" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="I678" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(H678,3,4)))</f>
+        <v>→</v>
+      </c>
+    </row>
+    <row r="679" spans="1:11" ht="17" customHeight="1">
+      <c r="A679" s="1" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B679" s="5">
+        <f>IF(ISNA(VLOOKUP(H679,$A$2:$C$1011,3,1)),C679,VLOOKUP(H679,$A$2:$C$1011,3,1))</f>
+        <v>578</v>
+      </c>
+      <c r="C679" s="1">
+        <v>580</v>
+      </c>
+      <c r="D679" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="E679" s="2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="F679" s="5" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A679,3,4)))</f>
+        <v>⭣</v>
+      </c>
+      <c r="G679" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A679,3,4)))</f>
+        <v>⭣</v>
+      </c>
+      <c r="H679" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="I679" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(H679,3,4)))</f>
+        <v>↓</v>
+      </c>
+    </row>
+    <row r="680" spans="1:11" ht="17" customHeight="1">
+      <c r="A680" s="1" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B680" s="5">
+        <f>IF(ISNA(VLOOKUP(H680,$A$2:$C$1011,3,1)),C680,VLOOKUP(H680,$A$2:$C$1011,3,1))</f>
+        <v>459</v>
+      </c>
+      <c r="C680" s="1">
+        <v>462</v>
+      </c>
+      <c r="D680" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E680" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F680" s="5" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A680,3,4)))</f>
+        <v>Ɽ</v>
+      </c>
+      <c r="G680" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A680,3,4)))</f>
+        <v>Ɽ</v>
+      </c>
+      <c r="H680" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="I680" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(H680,3,4)))</f>
+        <v>Π</v>
+      </c>
+    </row>
+    <row r="681" spans="1:11" ht="17" customHeight="1">
+      <c r="A681" s="1" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B681" s="5">
+        <f>IF(ISNA(VLOOKUP(H681,$A$2:$C$1011,3,1)),C681,VLOOKUP(H681,$A$2:$C$1011,3,1))</f>
+        <v>459</v>
+      </c>
+      <c r="C681" s="1">
+        <v>463</v>
+      </c>
+      <c r="D681" s="2" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E681" s="2" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F681" s="5" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A681,3,4)))</f>
+        <v>ⱥ</v>
+      </c>
+      <c r="G681" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A681,3,4)))</f>
+        <v>ⱥ</v>
+      </c>
+      <c r="H681" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="I681" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(H681,3,4)))</f>
+        <v>Π</v>
+      </c>
+    </row>
+    <row r="682" spans="1:11" ht="17" customHeight="1">
+      <c r="A682" s="1" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B682" s="5">
+        <f>IF(ISNA(VLOOKUP(H682,$A$2:$C$1011,3,1)),C682,VLOOKUP(H682,$A$2:$C$1011,3,1))</f>
+        <v>459</v>
+      </c>
+      <c r="C682" s="1">
+        <v>464</v>
+      </c>
+      <c r="D682" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E682" s="2" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F682" s="5" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A682,3,4)))</f>
+        <v>ⱦ</v>
+      </c>
+      <c r="G682" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A682,3,4)))</f>
+        <v>ⱦ</v>
+      </c>
+      <c r="H682" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="I682" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(H682,3,4)))</f>
+        <v>Π</v>
+      </c>
+    </row>
+    <row r="683" spans="1:11" ht="17" customHeight="1">
+      <c r="A683" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B683" s="5">
+        <f>IF(ISNA(VLOOKUP(H683,$A$2:$C$1011,3,1)),C683,VLOOKUP(H683,$A$2:$C$1011,3,1))</f>
+        <v>663</v>
+      </c>
+      <c r="C683" s="1">
+        <v>663</v>
+      </c>
+      <c r="D683" s="2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E683" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="F683" s="5" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A683,3,4)))</f>
+        <v>Ɐ</v>
+      </c>
+      <c r="G683" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A683,3,4)))</f>
+        <v>Ɐ</v>
+      </c>
+      <c r="H683" s="17" t="str">
+        <f>A683</f>
+        <v>U+2c6f</v>
+      </c>
+      <c r="I683" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(H683,3,4)))</f>
+        <v>Ɐ</v>
+      </c>
+    </row>
+    <row r="684" spans="1:11" ht="17" customHeight="1">
+      <c r="A684" s="1" t="s">
         <v>1980</v>
       </c>
-      <c r="B678" s="5">
-        <f>IF(ISNA(VLOOKUP(H678,$A$2:$C$1005,3,1)),C678,VLOOKUP(H678,$A$2:$C$1005,3,1))</f>
+      <c r="B684" s="5">
+        <f>IF(ISNA(VLOOKUP(H684,$A$2:$C$1011,3,1)),C684,VLOOKUP(H684,$A$2:$C$1011,3,1))</f>
         <v>9999</v>
       </c>
-      <c r="C678" s="1">
+      <c r="C684" s="1">
         <v>9999</v>
       </c>
-      <c r="D678" s="2" t="s">
+      <c r="D684" s="2" t="s">
         <v>1981</v>
       </c>
-      <c r="E678" s="2" t="s">
+      <c r="E684" s="2" t="s">
         <v>1982</v>
       </c>
-    </row>
-    <row r="682" spans="1:11" customFormat="1" ht="17" customHeight="1">
-      <c r="K682" s="2"/>
-    </row>
-    <row r="683" spans="1:11" customFormat="1" ht="17" customHeight="1">
-      <c r="K683" s="2"/>
     </row>
     <row r="688" spans="1:11" customFormat="1" ht="17" customHeight="1">
       <c r="K688" s="2"/>
@@ -28906,18 +29203,6 @@
     <row r="689" spans="11:11" customFormat="1" ht="17" customHeight="1">
       <c r="K689" s="2"/>
     </row>
-    <row r="690" spans="11:11" customFormat="1" ht="17" customHeight="1">
-      <c r="K690" s="2"/>
-    </row>
-    <row r="691" spans="11:11" customFormat="1" ht="17" customHeight="1">
-      <c r="K691" s="2"/>
-    </row>
-    <row r="692" spans="11:11" customFormat="1" ht="17" customHeight="1">
-      <c r="K692" s="2"/>
-    </row>
-    <row r="693" spans="11:11" customFormat="1" ht="17" customHeight="1">
-      <c r="K693" s="2"/>
-    </row>
     <row r="694" spans="11:11" customFormat="1" ht="17" customHeight="1">
       <c r="K694" s="2"/>
     </row>
@@ -28963,9 +29248,27 @@
     <row r="708" spans="11:11" customFormat="1" ht="17" customHeight="1">
       <c r="K708" s="2"/>
     </row>
+    <row r="709" spans="11:11" customFormat="1" ht="17" customHeight="1">
+      <c r="K709" s="2"/>
+    </row>
+    <row r="710" spans="11:11" customFormat="1" ht="17" customHeight="1">
+      <c r="K710" s="2"/>
+    </row>
+    <row r="711" spans="11:11" customFormat="1" ht="17" customHeight="1">
+      <c r="K711" s="2"/>
+    </row>
+    <row r="712" spans="11:11" customFormat="1" ht="17" customHeight="1">
+      <c r="K712" s="2"/>
+    </row>
+    <row r="713" spans="11:11" customFormat="1" ht="17" customHeight="1">
+      <c r="K713" s="2"/>
+    </row>
+    <row r="714" spans="11:11" customFormat="1" ht="17" customHeight="1">
+      <c r="K714" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K709">
-    <sortCondition ref="A2:A709"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I715">
+    <sortCondition ref="A2:A715"/>
   </sortState>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>

--- a/res/fonts/sortingOrder.xlsx
+++ b/res/fonts/sortingOrder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/c43/res/fonts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B747BC-E483-2B44-B015-A613396B4BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605FAC2C-347D-394F-B466-C1177A483B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19340" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sortingOrder" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="2025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="2025">
   <si>
     <t>Code point</t>
   </si>
@@ -6298,7 +6298,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6313,7 +6313,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6330,7 +6354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6367,6 +6391,18 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6681,9 +6717,8 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A5,3,4)))</f>
         <v>#</v>
       </c>
-      <c r="H5" s="17" t="str">
-        <f>A5</f>
-        <v>U+0023</v>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="I5" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H5,3,4)))</f>
@@ -20988,7 +21023,7 @@
       </c>
       <c r="B437" s="5">
         <f>IF(ISNA(VLOOKUP(H437,$A$2:$C$1011,3,1)),C437,VLOOKUP(H437,$A$2:$C$1011,3,1))</f>
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C437" s="1">
         <v>664</v>
@@ -21007,13 +21042,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A437,3,4)))</f>
         <v>∂</v>
       </c>
-      <c r="H437" s="17" t="str">
-        <f>A437</f>
-        <v>U+2202</v>
+      <c r="H437" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I437" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H437,3,4)))</f>
-        <v>∂</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="438" spans="1:11" s="16" customFormat="1" ht="17" customHeight="1">
@@ -21022,7 +21056,7 @@
       </c>
       <c r="B438" s="5">
         <f>IF(ISNA(VLOOKUP(H438,$A$2:$C$1011,3,1)),C438,VLOOKUP(H438,$A$2:$C$1011,3,1))</f>
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C438" s="1">
         <v>665</v>
@@ -21041,13 +21075,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A438,3,4)))</f>
         <v>∃</v>
       </c>
-      <c r="H438" s="17" t="str">
-        <f>A438</f>
-        <v>U+2203</v>
+      <c r="H438" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I438" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H438,3,4)))</f>
-        <v>∃</v>
+        <v>Ɐ</v>
       </c>
       <c r="J438" s="4"/>
       <c r="K438" s="2"/>
@@ -21058,7 +21091,7 @@
       </c>
       <c r="B439" s="5">
         <f>IF(ISNA(VLOOKUP(H439,$A$2:$C$1011,3,1)),C439,VLOOKUP(H439,$A$2:$C$1011,3,1))</f>
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C439" s="1">
         <v>666</v>
@@ -21077,13 +21110,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A439,3,4)))</f>
         <v>∄</v>
       </c>
-      <c r="H439" s="17" t="str">
-        <f>A439</f>
-        <v>U+2204</v>
+      <c r="H439" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I439" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H439,3,4)))</f>
-        <v>∄</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="440" spans="1:11" ht="17" customHeight="1">
@@ -21092,7 +21124,7 @@
       </c>
       <c r="B440" s="5">
         <f>IF(ISNA(VLOOKUP(H440,$A$2:$C$1011,3,1)),C440,VLOOKUP(H440,$A$2:$C$1011,3,1))</f>
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C440" s="1">
         <v>667</v>
@@ -21111,13 +21143,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A440,3,4)))</f>
         <v>∅</v>
       </c>
-      <c r="H440" s="17" t="str">
-        <f>A440</f>
-        <v>U+2205</v>
+      <c r="H440" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I440" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H440,3,4)))</f>
-        <v>∅</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="441" spans="1:11" ht="17" customHeight="1">
@@ -21126,7 +21157,7 @@
       </c>
       <c r="B441" s="5">
         <f>IF(ISNA(VLOOKUP(H441,$A$2:$C$1011,3,1)),C441,VLOOKUP(H441,$A$2:$C$1011,3,1))</f>
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C441" s="1">
         <v>668</v>
@@ -21145,13 +21176,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A441,3,4)))</f>
         <v>∆</v>
       </c>
-      <c r="H441" s="17" t="str">
-        <f>A441</f>
-        <v>U+2206</v>
+      <c r="H441" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I441" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H441,3,4)))</f>
-        <v>∆</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="442" spans="1:11" ht="17" customHeight="1">
@@ -21160,7 +21190,7 @@
       </c>
       <c r="B442" s="5">
         <f>IF(ISNA(VLOOKUP(H442,$A$2:$C$1011,3,1)),C442,VLOOKUP(H442,$A$2:$C$1011,3,1))</f>
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C442" s="1">
         <v>669</v>
@@ -21179,13 +21209,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A442,3,4)))</f>
         <v>∇</v>
       </c>
-      <c r="H442" s="17" t="str">
-        <f>A442</f>
-        <v>U+2207</v>
+      <c r="H442" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I442" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H442,3,4)))</f>
-        <v>∇</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="443" spans="1:11" ht="17" customHeight="1">
@@ -21194,7 +21223,7 @@
       </c>
       <c r="B443" s="5">
         <f>IF(ISNA(VLOOKUP(H443,$A$2:$C$1011,3,1)),C443,VLOOKUP(H443,$A$2:$C$1011,3,1))</f>
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C443" s="1">
         <v>670</v>
@@ -21213,13 +21242,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A443,3,4)))</f>
         <v>∈</v>
       </c>
-      <c r="H443" s="17" t="str">
-        <f>A443</f>
-        <v>U+2208</v>
+      <c r="H443" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I443" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H443,3,4)))</f>
-        <v>∈</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="444" spans="1:11" ht="17" customHeight="1">
@@ -21228,7 +21256,7 @@
       </c>
       <c r="B444" s="5">
         <f>IF(ISNA(VLOOKUP(H444,$A$2:$C$1011,3,1)),C444,VLOOKUP(H444,$A$2:$C$1011,3,1))</f>
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C444" s="1">
         <v>671</v>
@@ -21247,13 +21275,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A444,3,4)))</f>
         <v>∉</v>
       </c>
-      <c r="H444" s="17" t="str">
-        <f>A444</f>
-        <v>U+2209</v>
+      <c r="H444" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I444" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H444,3,4)))</f>
-        <v>∉</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="445" spans="1:11" ht="17" customHeight="1">
@@ -21262,7 +21289,7 @@
       </c>
       <c r="B445" s="5">
         <f>IF(ISNA(VLOOKUP(H445,$A$2:$C$1011,3,1)),C445,VLOOKUP(H445,$A$2:$C$1011,3,1))</f>
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="C445" s="1">
         <v>672</v>
@@ -21281,13 +21308,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A445,3,4)))</f>
         <v>∋</v>
       </c>
-      <c r="H445" s="17" t="str">
-        <f>A445</f>
-        <v>U+220b</v>
+      <c r="H445" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I445" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H445,3,4)))</f>
-        <v>∋</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="446" spans="1:11" ht="17" customHeight="1">
@@ -21296,7 +21322,7 @@
       </c>
       <c r="B446" s="5">
         <f>IF(ISNA(VLOOKUP(H446,$A$2:$C$1011,3,1)),C446,VLOOKUP(H446,$A$2:$C$1011,3,1))</f>
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C446" s="1">
         <v>673</v>
@@ -21315,13 +21341,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A446,3,4)))</f>
         <v>∌</v>
       </c>
-      <c r="H446" s="17" t="str">
-        <f>A446</f>
-        <v>U+220c</v>
+      <c r="H446" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I446" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H446,3,4)))</f>
-        <v>∌</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="447" spans="1:11" ht="17" customHeight="1">
@@ -22023,7 +22048,7 @@
       </c>
       <c r="B468" s="5">
         <f>IF(ISNA(VLOOKUP(H468,$A$2:$C$1011,3,1)),C468,VLOOKUP(H468,$A$2:$C$1011,3,1))</f>
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="C468" s="1">
         <v>674</v>
@@ -22042,13 +22067,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A468,3,4)))</f>
         <v>∩</v>
       </c>
-      <c r="H468" s="17" t="str">
-        <f>A468</f>
-        <v>U+2229</v>
+      <c r="H468" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I468" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H468,3,4)))</f>
-        <v>∩</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="469" spans="1:9" ht="17" customHeight="1">
@@ -22057,7 +22081,7 @@
       </c>
       <c r="B469" s="5">
         <f>IF(ISNA(VLOOKUP(H469,$A$2:$C$1011,3,1)),C469,VLOOKUP(H469,$A$2:$C$1011,3,1))</f>
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="C469" s="1">
         <v>675</v>
@@ -22076,13 +22100,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A469,3,4)))</f>
         <v>∪</v>
       </c>
-      <c r="H469" s="17" t="str">
-        <f>A469</f>
-        <v>U+222a</v>
+      <c r="H469" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I469" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H469,3,4)))</f>
-        <v>∪</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="470" spans="1:9" ht="17" customHeight="1">
@@ -22685,7 +22708,7 @@
       </c>
       <c r="B488" s="5">
         <f>IF(ISNA(VLOOKUP(H488,$A$2:$C$1011,3,1)),C488,VLOOKUP(H488,$A$2:$C$1011,3,1))</f>
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="C488" s="1">
         <v>676</v>
@@ -22704,13 +22727,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A488,3,4)))</f>
         <v>⊂</v>
       </c>
-      <c r="H488" s="17" t="str">
-        <f>A488</f>
-        <v>U+2282</v>
+      <c r="H488" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I488" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H488,3,4)))</f>
-        <v>⊂</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="489" spans="1:9" ht="17" customHeight="1">
@@ -22719,7 +22741,7 @@
       </c>
       <c r="B489" s="5">
         <f>IF(ISNA(VLOOKUP(H489,$A$2:$C$1011,3,1)),C489,VLOOKUP(H489,$A$2:$C$1011,3,1))</f>
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="C489" s="1">
         <v>677</v>
@@ -22738,13 +22760,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A489,3,4)))</f>
         <v>⊄</v>
       </c>
-      <c r="H489" s="17" t="str">
-        <f>A489</f>
-        <v>U+2284</v>
+      <c r="H489" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I489" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H489,3,4)))</f>
-        <v>⊄</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="490" spans="1:9" ht="17" customHeight="1">
@@ -23182,7 +23203,7 @@
       </c>
       <c r="B503" s="5">
         <f>IF(ISNA(VLOOKUP(H503,$A$2:$C$1011,3,1)),C503,VLOOKUP(H503,$A$2:$C$1011,3,1))</f>
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C503" s="1">
         <v>643</v>
@@ -23201,13 +23222,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A503,3,4)))</f>
         <v>⌚</v>
       </c>
-      <c r="H503" s="17" t="str">
-        <f>A503</f>
-        <v>U+231a</v>
+      <c r="H503" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I503" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H503,3,4)))</f>
-        <v>⌚</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="504" spans="1:9" ht="17" customHeight="1">
@@ -23216,7 +23236,7 @@
       </c>
       <c r="B504" s="5">
         <f>IF(ISNA(VLOOKUP(H504,$A$2:$C$1011,3,1)),C504,VLOOKUP(H504,$A$2:$C$1011,3,1))</f>
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C504" s="1">
         <v>641</v>
@@ -23235,13 +23255,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A504,3,4)))</f>
         <v>⌛</v>
       </c>
-      <c r="H504" s="17" t="str">
-        <f>A504</f>
-        <v>U+231b</v>
+      <c r="H504" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I504" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H504,3,4)))</f>
-        <v>⌛</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="505" spans="1:9" ht="17" customHeight="1">
@@ -23302,9 +23321,8 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A506,3,4)))</f>
         <v>⎙</v>
       </c>
-      <c r="H506" s="17" t="str">
-        <f>A506</f>
-        <v>U+2399</v>
+      <c r="H506" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I506" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H506,3,4)))</f>
@@ -23581,7 +23599,7 @@
       </c>
       <c r="B515" s="5">
         <f>IF(ISNA(VLOOKUP(H515,$A$2:$C$1011,3,1)),C515,VLOOKUP(H515,$A$2:$C$1011,3,1))</f>
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C515" s="1">
         <v>644</v>
@@ -23600,13 +23618,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A515,3,4)))</f>
         <v>⏱</v>
       </c>
-      <c r="H515" s="17" t="str">
-        <f>A515</f>
-        <v>U+23f1</v>
+      <c r="H515" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I515" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H515,3,4)))</f>
-        <v>⏱</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="516" spans="1:9" ht="17" customHeight="1">
@@ -23615,7 +23632,7 @@
       </c>
       <c r="B516" s="5">
         <f>IF(ISNA(VLOOKUP(H516,$A$2:$C$1011,3,1)),C516,VLOOKUP(H516,$A$2:$C$1011,3,1))</f>
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="C516" s="1">
         <v>651</v>
@@ -23634,13 +23651,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A516,3,4)))</f>
         <v>⏻</v>
       </c>
-      <c r="H516" s="17" t="str">
-        <f>A516</f>
-        <v>U+23fb</v>
+      <c r="H516" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I516" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H516,3,4)))</f>
-        <v>⏻</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="517" spans="1:9" ht="17" customHeight="1">
@@ -23668,9 +23684,8 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A517,3,4)))</f>
         <v>␡</v>
       </c>
-      <c r="H517" s="17" t="str">
-        <f>A517</f>
-        <v>U+2421</v>
+      <c r="H517" s="21" t="s">
+        <v>1525</v>
       </c>
       <c r="I517" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H517,3,4)))</f>
@@ -23683,7 +23698,7 @@
       </c>
       <c r="B518" s="5">
         <f>IF(ISNA(VLOOKUP(H518,$A$2:$C$1011,3,1)),C518,VLOOKUP(H518,$A$2:$C$1011,3,1))</f>
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C518" s="1">
         <v>679</v>
@@ -23702,13 +23717,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A518,3,4)))</f>
         <v>␢</v>
       </c>
-      <c r="H518" s="17" t="str">
-        <f>A518</f>
-        <v>U+2422</v>
+      <c r="H518" s="21" t="s">
+        <v>1525</v>
       </c>
       <c r="I518" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H518,3,4)))</f>
-        <v>␢</v>
+        <v>␡</v>
       </c>
     </row>
     <row r="519" spans="1:9" ht="17" customHeight="1">
@@ -23750,7 +23764,7 @@
       </c>
       <c r="B520" s="5">
         <f>IF(ISNA(VLOOKUP(H520,$A$2:$C$1011,3,1)),C520,VLOOKUP(H520,$A$2:$C$1011,3,1))</f>
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C520" s="1">
         <v>680</v>
@@ -23769,13 +23783,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A520,3,4)))</f>
         <v>␥</v>
       </c>
-      <c r="H520" s="17" t="str">
-        <f>A520</f>
-        <v>U+2425</v>
+      <c r="H520" s="21" t="s">
+        <v>1525</v>
       </c>
       <c r="I520" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H520,3,4)))</f>
-        <v>␥</v>
+        <v>␡</v>
       </c>
     </row>
     <row r="521" spans="1:9" ht="17" customHeight="1">
@@ -23784,7 +23797,7 @@
       </c>
       <c r="B521" s="5">
         <f>IF(ISNA(VLOOKUP(H521,$A$2:$C$1011,3,1)),C521,VLOOKUP(H521,$A$2:$C$1011,3,1))</f>
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C521" s="1">
         <v>681</v>
@@ -23803,13 +23816,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A521,3,4)))</f>
         <v>␦</v>
       </c>
-      <c r="H521" s="17" t="str">
-        <f>A521</f>
-        <v>U+2426</v>
+      <c r="H521" s="21" t="s">
+        <v>1525</v>
       </c>
       <c r="I521" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H521,3,4)))</f>
-        <v>␦</v>
+        <v>␡</v>
       </c>
     </row>
     <row r="522" spans="1:9" ht="17" customHeight="1">
@@ -23917,7 +23929,7 @@
       </c>
       <c r="B525" s="5">
         <f>IF(ISNA(VLOOKUP(H525,$A$2:$C$1011,3,1)),C525,VLOOKUP(H525,$A$2:$C$1011,3,1))</f>
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="C525" s="1">
         <v>645</v>
@@ -23936,13 +23948,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A525,3,4)))</f>
         <v>␪</v>
       </c>
-      <c r="H525" s="17" t="str">
-        <f>A525</f>
-        <v>U+242a</v>
+      <c r="H525" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I525" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H525,3,4)))</f>
-        <v>␪</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="526" spans="1:9" ht="17" customHeight="1">
@@ -23984,7 +23995,7 @@
       </c>
       <c r="B527" s="5">
         <f>IF(ISNA(VLOOKUP(H527,$A$2:$C$1011,3,1)),C527,VLOOKUP(H527,$A$2:$C$1011,3,1))</f>
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="C527" s="1">
         <v>647</v>
@@ -24003,13 +24014,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A527,3,4)))</f>
         <v>␬</v>
       </c>
-      <c r="H527" s="17" t="str">
-        <f>A527</f>
-        <v>U+242c</v>
+      <c r="H527" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I527" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H527,3,4)))</f>
-        <v>␬</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="528" spans="1:9" ht="17" customHeight="1">
@@ -24037,9 +24047,8 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A528,3,4)))</f>
         <v>␭</v>
       </c>
-      <c r="H528" s="17" t="str">
-        <f>A528</f>
-        <v>U+242d</v>
+      <c r="H528" s="19" t="s">
+        <v>1551</v>
       </c>
       <c r="I528" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H528,3,4)))</f>
@@ -24052,7 +24061,7 @@
       </c>
       <c r="B529" s="5">
         <f>IF(ISNA(VLOOKUP(H529,$A$2:$C$1011,3,1)),C529,VLOOKUP(H529,$A$2:$C$1011,3,1))</f>
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C529" s="1">
         <v>662</v>
@@ -24071,13 +24080,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A529,3,4)))</f>
         <v>␮</v>
       </c>
-      <c r="H529" s="17" t="str">
-        <f>A529</f>
-        <v>U+242e</v>
+      <c r="H529" s="19" t="s">
+        <v>1551</v>
       </c>
       <c r="I529" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H529,3,4)))</f>
-        <v>␮</v>
+        <v>␭</v>
       </c>
     </row>
     <row r="530" spans="1:9" ht="17" customHeight="1">
@@ -24086,7 +24094,7 @@
       </c>
       <c r="B530" s="5">
         <f>IF(ISNA(VLOOKUP(H530,$A$2:$C$1011,3,1)),C530,VLOOKUP(H530,$A$2:$C$1011,3,1))</f>
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="C530" s="1">
         <v>648</v>
@@ -24105,13 +24113,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A530,3,4)))</f>
         <v>␯</v>
       </c>
-      <c r="H530" s="17" t="str">
-        <f>A530</f>
-        <v>U+242f</v>
+      <c r="H530" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I530" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H530,3,4)))</f>
-        <v>␯</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="531" spans="1:9" ht="17" customHeight="1">
@@ -24252,7 +24259,7 @@
       </c>
       <c r="B535" s="5">
         <f>IF(ISNA(VLOOKUP(H535,$A$2:$C$1011,3,1)),C535,VLOOKUP(H535,$A$2:$C$1011,3,1))</f>
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="C535" s="1">
         <v>649</v>
@@ -24271,13 +24278,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A535,3,4)))</f>
         <v>␴</v>
       </c>
-      <c r="H535" s="17" t="str">
-        <f>A535</f>
-        <v>U+2434</v>
+      <c r="H535" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I535" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H535,3,4)))</f>
-        <v>␴</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="536" spans="1:9" ht="17" customHeight="1">
@@ -24286,7 +24292,7 @@
       </c>
       <c r="B536" s="5">
         <f>IF(ISNA(VLOOKUP(H536,$A$2:$C$1011,3,1)),C536,VLOOKUP(H536,$A$2:$C$1011,3,1))</f>
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C536" s="1">
         <v>646</v>
@@ -24305,13 +24311,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A536,3,4)))</f>
         <v>␵</v>
       </c>
-      <c r="H536" s="17" t="str">
-        <f>A536</f>
-        <v>U+2435</v>
+      <c r="H536" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I536" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H536,3,4)))</f>
-        <v>␵</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="537" spans="1:9" ht="17" customHeight="1">
@@ -28349,7 +28354,7 @@
       </c>
       <c r="B659" s="5">
         <f>IF(ISNA(VLOOKUP(H659,$A$2:$C$1011,3,1)),C659,VLOOKUP(H659,$A$2:$C$1011,3,1))</f>
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="C659" s="1">
         <v>652</v>
@@ -28368,13 +28373,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A659,3,4)))</f>
         <v>▢</v>
       </c>
-      <c r="H659" s="17" t="str">
-        <f>A659</f>
-        <v>U+25a2</v>
+      <c r="H659" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I659" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H659,3,4)))</f>
-        <v>▢</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="660" spans="1:9" ht="17" customHeight="1">
@@ -28383,7 +28387,7 @@
       </c>
       <c r="B660" s="5">
         <f>IF(ISNA(VLOOKUP(H660,$A$2:$C$1011,3,1)),C660,VLOOKUP(H660,$A$2:$C$1011,3,1))</f>
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="C660" s="1">
         <v>653</v>
@@ -28402,13 +28406,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A660,3,4)))</f>
         <v>▦</v>
       </c>
-      <c r="H660" s="17" t="str">
-        <f>A660</f>
-        <v>U+25a6</v>
+      <c r="H660" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I660" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H660,3,4)))</f>
-        <v>▦</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="661" spans="1:9" ht="17" customHeight="1">
@@ -28417,7 +28420,7 @@
       </c>
       <c r="B661" s="5">
         <f>IF(ISNA(VLOOKUP(H661,$A$2:$C$1011,3,1)),C661,VLOOKUP(H661,$A$2:$C$1011,3,1))</f>
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C661" s="1">
         <v>658</v>
@@ -28436,13 +28439,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A661,3,4)))</f>
         <v>◇</v>
       </c>
-      <c r="H661" s="17" t="str">
-        <f>A661</f>
-        <v>U+25c7</v>
+      <c r="H661" s="18" t="s">
+        <v>2009</v>
       </c>
       <c r="I661" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H661,3,4)))</f>
-        <v>◇</v>
+        <v>◯</v>
       </c>
     </row>
     <row r="662" spans="1:9" ht="17" customHeight="1">
@@ -28451,7 +28453,7 @@
       </c>
       <c r="B662" s="5">
         <f>IF(ISNA(VLOOKUP(H662,$A$2:$C$1011,3,1)),C662,VLOOKUP(H662,$A$2:$C$1011,3,1))</f>
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C662" s="1">
         <v>659</v>
@@ -28470,13 +28472,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A662,3,4)))</f>
         <v>◈</v>
       </c>
-      <c r="H662" s="17" t="str">
-        <f>A662</f>
-        <v>U+25c8</v>
+      <c r="H662" s="18" t="s">
+        <v>2009</v>
       </c>
       <c r="I662" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H662,3,4)))</f>
-        <v>◈</v>
+        <v>◯</v>
       </c>
     </row>
     <row r="663" spans="1:9" ht="17" customHeight="1">
@@ -28504,9 +28505,8 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A663,3,4)))</f>
         <v>◯</v>
       </c>
-      <c r="H663" s="17" t="str">
-        <f>A663</f>
-        <v>U+25ef</v>
+      <c r="H663" s="18" t="s">
+        <v>2009</v>
       </c>
       <c r="I663" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H663,3,4)))</f>
@@ -28519,7 +28519,7 @@
       </c>
       <c r="B664" s="5">
         <f>IF(ISNA(VLOOKUP(H664,$A$2:$C$1011,3,1)),C664,VLOOKUP(H664,$A$2:$C$1011,3,1))</f>
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C664" s="1">
         <v>654</v>
@@ -28538,13 +28538,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A664,3,4)))</f>
         <v>☐</v>
       </c>
-      <c r="H664" s="17" t="str">
-        <f>A664</f>
-        <v>U+2610</v>
+      <c r="H664" s="18" t="s">
+        <v>2009</v>
       </c>
       <c r="I664" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H664,3,4)))</f>
-        <v>☐</v>
+        <v>◯</v>
       </c>
     </row>
     <row r="665" spans="1:9" ht="17" customHeight="1">
@@ -28553,7 +28552,7 @@
       </c>
       <c r="B665" s="5">
         <f>IF(ISNA(VLOOKUP(H665,$A$2:$C$1011,3,1)),C665,VLOOKUP(H665,$A$2:$C$1011,3,1))</f>
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C665" s="1">
         <v>655</v>
@@ -28572,13 +28571,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A665,3,4)))</f>
         <v>☒</v>
       </c>
-      <c r="H665" s="17" t="str">
-        <f>A665</f>
-        <v>U+2612</v>
+      <c r="H665" s="18" t="s">
+        <v>2009</v>
       </c>
       <c r="I665" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H665,3,4)))</f>
-        <v>☒</v>
+        <v>◯</v>
       </c>
     </row>
     <row r="666" spans="1:9" ht="17" customHeight="1">
@@ -28587,7 +28585,7 @@
       </c>
       <c r="B666" s="5">
         <f>IF(ISNA(VLOOKUP(H666,$A$2:$C$1011,3,1)),C666,VLOOKUP(H666,$A$2:$C$1011,3,1))</f>
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="C666" s="1">
         <v>650</v>
@@ -28606,13 +28604,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A666,3,4)))</f>
         <v>♺</v>
       </c>
-      <c r="H666" s="17" t="str">
-        <f>A666</f>
-        <v>U+267A</v>
+      <c r="H666" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I666" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H666,3,4)))</f>
-        <v>♺</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="667" spans="1:9" ht="17" customHeight="1">
@@ -28786,7 +28783,7 @@
       </c>
       <c r="B672" s="5">
         <f>IF(ISNA(VLOOKUP(H672,$A$2:$C$1011,3,1)),C672,VLOOKUP(H672,$A$2:$C$1011,3,1))</f>
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C672" s="1">
         <v>657</v>
@@ -28805,13 +28802,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A672,3,4)))</f>
         <v>⦿</v>
       </c>
-      <c r="H672" s="17" t="str">
-        <f>A672</f>
-        <v>U+29bf</v>
+      <c r="H672" s="18" t="s">
+        <v>2009</v>
       </c>
       <c r="I672" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H672,3,4)))</f>
-        <v>⦿</v>
+        <v>◯</v>
       </c>
     </row>
     <row r="673" spans="1:11" ht="17" customHeight="1">
@@ -28820,7 +28816,7 @@
       </c>
       <c r="B673" s="5">
         <f>IF(ISNA(VLOOKUP(H673,$A$2:$C$1011,3,1)),C673,VLOOKUP(H673,$A$2:$C$1011,3,1))</f>
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C673" s="1">
         <v>642</v>
@@ -28839,13 +28835,12 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A673,3,4)))</f>
         <v>⧖</v>
       </c>
-      <c r="H673" s="17" t="str">
-        <f>A673</f>
-        <v>U+29d6</v>
+      <c r="H673" s="17" t="s">
+        <v>1486</v>
       </c>
       <c r="I673" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H673,3,4)))</f>
-        <v>⧖</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="674" spans="1:11" ht="17" customHeight="1">
@@ -29170,9 +29165,8 @@
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A683,3,4)))</f>
         <v>Ɐ</v>
       </c>
-      <c r="H683" s="17" t="str">
-        <f>A683</f>
-        <v>U+2c6f</v>
+      <c r="H683" s="20" t="s">
+        <v>1289</v>
       </c>
       <c r="I683" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H683,3,4)))</f>
@@ -29267,8 +29261,8 @@
       <c r="K714" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I715">
-    <sortCondition ref="A2:A715"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K714">
+    <sortCondition ref="A2:A714"/>
   </sortState>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>

--- a/res/fonts/sortingOrder.xlsx
+++ b/res/fonts/sortingOrder.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/c43/res/fonts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605FAC2C-347D-394F-B466-C1177A483B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0E9F5D-EAF2-FA4F-8BFA-D6C3D83F1B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19340" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3833,12 +3833,6 @@
     <t>List</t>
   </si>
   <si>
-    <t>U+21cd</t>
-  </si>
-  <si>
-    <t>LEFTWARDS DOUBLE ARROW WITH STROKE</t>
-  </si>
-  <si>
     <t>Undo</t>
   </si>
   <si>
@@ -6211,6 +6205,12 @@
   </si>
   <si>
     <t xml:space="preserve">DIA_ON </t>
+  </si>
+  <si>
+    <t>U+238c</t>
+  </si>
+  <si>
+    <t>HELM SYMBOL</t>
   </si>
 </sst>
 </file>
@@ -6354,7 +6354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6405,6 +6405,10 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6620,7 +6624,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="17" customHeight="1">
@@ -6656,7 +6660,7 @@
         <v>!</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="17" customHeight="1">
@@ -6725,7 +6729,7 @@
         <v>#</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="17" customHeight="1">
@@ -7007,7 +7011,7 @@
         <v>+</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="17" customHeight="1">
@@ -7220,7 +7224,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="17" customHeight="1">
@@ -7256,7 +7260,7 @@
         <v>2</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="17" customHeight="1">
@@ -7292,7 +7296,7 @@
         <v>3</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="17" customHeight="1">
@@ -13476,7 +13480,7 @@
     </row>
     <row r="209" spans="1:11" s="16" customFormat="1" ht="17" customHeight="1">
       <c r="A209" s="12" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="B209" s="13">
         <f>IF(ISNA(VLOOKUP(H209,$A$2:$C$1011,3,1)),C209,VLOOKUP(H209,$A$2:$C$1011,3,1))</f>
@@ -13486,10 +13490,10 @@
         <v>211</v>
       </c>
       <c r="D209" s="14" t="s">
+        <v>1990</v>
+      </c>
+      <c r="E209" s="14" t="s">
         <v>1992</v>
-      </c>
-      <c r="E209" s="14" t="s">
-        <v>1994</v>
       </c>
       <c r="F209" s="13" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A209,3,4)))</f>
@@ -13507,12 +13511,12 @@
         <v>J</v>
       </c>
       <c r="K209" s="14" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="210" spans="1:11" ht="17" customHeight="1">
       <c r="A210" s="12" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="B210" s="13">
         <f>IF(ISNA(VLOOKUP(H210,$A$2:$C$1011,3,1)),C210,VLOOKUP(H210,$A$2:$C$1011,3,1))</f>
@@ -13522,10 +13526,10 @@
         <v>219</v>
       </c>
       <c r="D210" s="14" t="s">
+        <v>1991</v>
+      </c>
+      <c r="E210" s="14" t="s">
         <v>1993</v>
-      </c>
-      <c r="E210" s="14" t="s">
-        <v>1995</v>
       </c>
       <c r="F210" s="13" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A210,3,4)))</f>
@@ -13544,7 +13548,7 @@
       </c>
       <c r="J210" s="16"/>
       <c r="K210" s="14" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="211" spans="1:11" ht="17" customHeight="1">
@@ -17093,7 +17097,7 @@
         <v>953</v>
       </c>
       <c r="E318" s="14" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="F318" s="13" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A318,3,4)))</f>
@@ -17112,7 +17116,7 @@
       </c>
       <c r="J318" s="16"/>
       <c r="K318" s="14" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="319" spans="1:11" ht="17" customHeight="1">
@@ -17843,7 +17847,7 @@
     </row>
     <row r="341" spans="1:11" ht="17" customHeight="1">
       <c r="A341" s="12" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="B341" s="13">
         <f>IF(ISNA(VLOOKUP(H341,$A$2:$C$1011,3,1)),C341,VLOOKUP(H341,$A$2:$C$1011,3,1))</f>
@@ -17856,7 +17860,7 @@
         <v>953</v>
       </c>
       <c r="E341" s="14" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="F341" s="13" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A341,3,4)))</f>
@@ -17875,12 +17879,12 @@
       </c>
       <c r="J341" s="16"/>
       <c r="K341" s="14" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="342" spans="1:11" ht="17" customHeight="1">
       <c r="A342" s="12" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B342" s="13">
         <f>IF(ISNA(VLOOKUP(H342,$A$2:$C$1011,3,1)),C342,VLOOKUP(H342,$A$2:$C$1011,3,1))</f>
@@ -17893,7 +17897,7 @@
         <v>993</v>
       </c>
       <c r="E342" s="14" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="F342" s="13" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A342,3,4)))</f>
@@ -17912,7 +17916,7 @@
       </c>
       <c r="J342" s="16"/>
       <c r="K342" s="14" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="343" spans="1:11" ht="17" customHeight="1">
@@ -20689,361 +20693,361 @@
     </row>
     <row r="427" spans="1:9" ht="17" customHeight="1">
       <c r="A427" s="1" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B427" s="5">
         <f>IF(ISNA(VLOOKUP(H427,$A$2:$C$1011,3,1)),C427,VLOOKUP(H427,$A$2:$C$1011,3,1))</f>
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C427" s="1">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F427" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A427,3,4)))</f>
-        <v>⇍</v>
+        <v>⇒</v>
       </c>
       <c r="G427" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A427,3,4)))</f>
-        <v>⇍</v>
+        <v>⇒</v>
       </c>
       <c r="H427" s="1" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="I427" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H427,3,4)))</f>
-        <v>←</v>
+        <v>→</v>
       </c>
     </row>
     <row r="428" spans="1:9" ht="17" customHeight="1">
       <c r="A428" s="1" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B428" s="5">
         <f>IF(ISNA(VLOOKUP(H428,$A$2:$C$1011,3,1)),C428,VLOOKUP(H428,$A$2:$C$1011,3,1))</f>
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="C428" s="1">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="F428" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A428,3,4)))</f>
-        <v>⇒</v>
+        <v>⇔</v>
       </c>
       <c r="G428" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A428,3,4)))</f>
-        <v>⇒</v>
+        <v>⇔</v>
       </c>
       <c r="H428" s="1" t="s">
-        <v>1235</v>
+        <v>1244</v>
       </c>
       <c r="I428" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H428,3,4)))</f>
-        <v>→</v>
+        <v>⇄</v>
       </c>
     </row>
     <row r="429" spans="1:9" ht="17" customHeight="1">
       <c r="A429" s="1" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B429" s="5">
         <f>IF(ISNA(VLOOKUP(H429,$A$2:$C$1011,3,1)),C429,VLOOKUP(H429,$A$2:$C$1011,3,1))</f>
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="C429" s="1">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>1271</v>
+        <v>1230</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>1272</v>
+        <v>1231</v>
       </c>
       <c r="F429" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A429,3,4)))</f>
-        <v>⇔</v>
+        <v>⇠</v>
       </c>
       <c r="G429" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A429,3,4)))</f>
-        <v>⇔</v>
+        <v>⇠</v>
       </c>
       <c r="H429" s="1" t="s">
-        <v>1244</v>
+        <v>1229</v>
       </c>
       <c r="I429" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H429,3,4)))</f>
-        <v>⇄</v>
+        <v>←</v>
       </c>
     </row>
     <row r="430" spans="1:9" ht="17" customHeight="1">
       <c r="A430" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B430" s="5">
         <f>IF(ISNA(VLOOKUP(H430,$A$2:$C$1011,3,1)),C430,VLOOKUP(H430,$A$2:$C$1011,3,1))</f>
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C430" s="1">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="F430" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A430,3,4)))</f>
-        <v>⇠</v>
+        <v>⇡</v>
       </c>
       <c r="G430" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A430,3,4)))</f>
-        <v>⇠</v>
+        <v>⇡</v>
       </c>
       <c r="H430" s="1" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="I430" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H430,3,4)))</f>
-        <v>←</v>
+        <v>↑</v>
       </c>
     </row>
     <row r="431" spans="1:9" ht="17" customHeight="1">
       <c r="A431" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B431" s="5">
         <f>IF(ISNA(VLOOKUP(H431,$A$2:$C$1011,3,1)),C431,VLOOKUP(H431,$A$2:$C$1011,3,1))</f>
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C431" s="1">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="F431" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A431,3,4)))</f>
-        <v>⇡</v>
+        <v>⇢</v>
       </c>
       <c r="G431" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A431,3,4)))</f>
-        <v>⇡</v>
+        <v>⇢</v>
       </c>
       <c r="H431" s="1" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="I431" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H431,3,4)))</f>
-        <v>↑</v>
+        <v>→</v>
       </c>
     </row>
     <row r="432" spans="1:9" ht="17" customHeight="1">
       <c r="A432" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B432" s="5">
         <f>IF(ISNA(VLOOKUP(H432,$A$2:$C$1011,3,1)),C432,VLOOKUP(H432,$A$2:$C$1011,3,1))</f>
-        <v>562</v>
+        <v>578</v>
       </c>
       <c r="C432" s="1">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="F432" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A432,3,4)))</f>
-        <v>⇢</v>
+        <v>⇣</v>
       </c>
       <c r="G432" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A432,3,4)))</f>
-        <v>⇢</v>
+        <v>⇣</v>
       </c>
       <c r="H432" s="1" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="I432" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H432,3,4)))</f>
-        <v>→</v>
+        <v>↓</v>
       </c>
     </row>
     <row r="433" spans="1:11" ht="17" customHeight="1">
       <c r="A433" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B433" s="5">
         <f>IF(ISNA(VLOOKUP(H433,$A$2:$C$1011,3,1)),C433,VLOOKUP(H433,$A$2:$C$1011,3,1))</f>
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="C433" s="1">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1239</v>
+        <v>1276</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>1240</v>
+        <v>1277</v>
       </c>
       <c r="F433" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A433,3,4)))</f>
-        <v>⇣</v>
+        <v>⇧</v>
       </c>
       <c r="G433" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A433,3,4)))</f>
-        <v>⇣</v>
+        <v>⇧</v>
       </c>
       <c r="H433" s="1" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
       <c r="I433" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H433,3,4)))</f>
-        <v>↓</v>
+        <v>↑</v>
       </c>
     </row>
     <row r="434" spans="1:11" ht="17" customHeight="1">
       <c r="A434" s="1" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B434" s="5">
         <f>IF(ISNA(VLOOKUP(H434,$A$2:$C$1011,3,1)),C434,VLOOKUP(H434,$A$2:$C$1011,3,1))</f>
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C434" s="1">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="F434" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A434,3,4)))</f>
-        <v>⇧</v>
+        <v>⇩</v>
       </c>
       <c r="G434" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A434,3,4)))</f>
-        <v>⇧</v>
+        <v>⇩</v>
       </c>
       <c r="H434" s="1" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="I434" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H434,3,4)))</f>
-        <v>↑</v>
+        <v>↓</v>
       </c>
     </row>
     <row r="435" spans="1:11" ht="17" customHeight="1">
       <c r="A435" s="1" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B435" s="5">
         <f>IF(ISNA(VLOOKUP(H435,$A$2:$C$1011,3,1)),C435,VLOOKUP(H435,$A$2:$C$1011,3,1))</f>
-        <v>578</v>
+        <v>98</v>
       </c>
       <c r="C435" s="1">
-        <v>581</v>
+        <v>111</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="F435" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A435,3,4)))</f>
-        <v>⇩</v>
+        <v>∁</v>
       </c>
       <c r="G435" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A435,3,4)))</f>
-        <v>⇩</v>
+        <v>∁</v>
       </c>
       <c r="H435" s="1" t="s">
-        <v>1238</v>
+        <v>126</v>
       </c>
       <c r="I435" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H435,3,4)))</f>
-        <v>↓</v>
+        <v>C</v>
       </c>
     </row>
     <row r="436" spans="1:11" ht="17" customHeight="1">
       <c r="A436" s="1" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B436" s="5">
         <f>IF(ISNA(VLOOKUP(H436,$A$2:$C$1011,3,1)),C436,VLOOKUP(H436,$A$2:$C$1011,3,1))</f>
-        <v>98</v>
+        <v>663</v>
       </c>
       <c r="C436" s="1">
-        <v>111</v>
+        <v>664</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="F436" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A436,3,4)))</f>
-        <v>∁</v>
+        <v>∂</v>
       </c>
       <c r="G436" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A436,3,4)))</f>
-        <v>∁</v>
-      </c>
-      <c r="H436" s="1" t="s">
-        <v>126</v>
+        <v>∂</v>
+      </c>
+      <c r="H436" s="20" t="s">
+        <v>1287</v>
       </c>
       <c r="I436" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H436,3,4)))</f>
-        <v>C</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="437" spans="1:11" ht="17" customHeight="1">
       <c r="A437" s="1" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="B437" s="5">
         <f>IF(ISNA(VLOOKUP(H437,$A$2:$C$1011,3,1)),C437,VLOOKUP(H437,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C437" s="1">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="F437" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A437,3,4)))</f>
-        <v>∂</v>
+        <v>∃</v>
       </c>
       <c r="G437" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A437,3,4)))</f>
-        <v>∂</v>
+        <v>∃</v>
       </c>
       <c r="H437" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I437" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H437,3,4)))</f>
@@ -21052,31 +21056,31 @@
     </row>
     <row r="438" spans="1:11" s="16" customFormat="1" ht="17" customHeight="1">
       <c r="A438" s="1" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B438" s="5">
         <f>IF(ISNA(VLOOKUP(H438,$A$2:$C$1011,3,1)),C438,VLOOKUP(H438,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C438" s="1">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="F438" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A438,3,4)))</f>
-        <v>∃</v>
+        <v>∄</v>
       </c>
       <c r="G438" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A438,3,4)))</f>
-        <v>∃</v>
+        <v>∄</v>
       </c>
       <c r="H438" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I438" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H438,3,4)))</f>
@@ -21087,31 +21091,31 @@
     </row>
     <row r="439" spans="1:11" ht="17" customHeight="1">
       <c r="A439" s="1" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B439" s="5">
         <f>IF(ISNA(VLOOKUP(H439,$A$2:$C$1011,3,1)),C439,VLOOKUP(H439,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C439" s="1">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="F439" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A439,3,4)))</f>
-        <v>∄</v>
+        <v>∅</v>
       </c>
       <c r="G439" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A439,3,4)))</f>
-        <v>∄</v>
+        <v>∅</v>
       </c>
       <c r="H439" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I439" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H439,3,4)))</f>
@@ -21120,31 +21124,31 @@
     </row>
     <row r="440" spans="1:11" ht="17" customHeight="1">
       <c r="A440" s="1" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B440" s="5">
         <f>IF(ISNA(VLOOKUP(H440,$A$2:$C$1011,3,1)),C440,VLOOKUP(H440,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C440" s="1">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F440" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A440,3,4)))</f>
-        <v>∅</v>
+        <v>∆</v>
       </c>
       <c r="G440" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A440,3,4)))</f>
-        <v>∅</v>
+        <v>∆</v>
       </c>
       <c r="H440" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I440" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H440,3,4)))</f>
@@ -21153,31 +21157,31 @@
     </row>
     <row r="441" spans="1:11" ht="17" customHeight="1">
       <c r="A441" s="1" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B441" s="5">
         <f>IF(ISNA(VLOOKUP(H441,$A$2:$C$1011,3,1)),C441,VLOOKUP(H441,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C441" s="1">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="F441" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A441,3,4)))</f>
-        <v>∆</v>
+        <v>∇</v>
       </c>
       <c r="G441" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A441,3,4)))</f>
-        <v>∆</v>
+        <v>∇</v>
       </c>
       <c r="H441" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I441" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H441,3,4)))</f>
@@ -21186,31 +21190,31 @@
     </row>
     <row r="442" spans="1:11" ht="17" customHeight="1">
       <c r="A442" s="1" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B442" s="5">
         <f>IF(ISNA(VLOOKUP(H442,$A$2:$C$1011,3,1)),C442,VLOOKUP(H442,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C442" s="1">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="F442" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A442,3,4)))</f>
-        <v>∇</v>
+        <v>∈</v>
       </c>
       <c r="G442" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A442,3,4)))</f>
-        <v>∇</v>
+        <v>∈</v>
       </c>
       <c r="H442" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I442" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H442,3,4)))</f>
@@ -21219,31 +21223,31 @@
     </row>
     <row r="443" spans="1:11" ht="17" customHeight="1">
       <c r="A443" s="1" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B443" s="5">
         <f>IF(ISNA(VLOOKUP(H443,$A$2:$C$1011,3,1)),C443,VLOOKUP(H443,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C443" s="1">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="F443" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A443,3,4)))</f>
-        <v>∈</v>
+        <v>∉</v>
       </c>
       <c r="G443" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A443,3,4)))</f>
-        <v>∈</v>
+        <v>∉</v>
       </c>
       <c r="H443" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I443" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H443,3,4)))</f>
@@ -21252,31 +21256,31 @@
     </row>
     <row r="444" spans="1:11" ht="17" customHeight="1">
       <c r="A444" s="1" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B444" s="5">
         <f>IF(ISNA(VLOOKUP(H444,$A$2:$C$1011,3,1)),C444,VLOOKUP(H444,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C444" s="1">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="F444" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A444,3,4)))</f>
-        <v>∉</v>
+        <v>∋</v>
       </c>
       <c r="G444" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A444,3,4)))</f>
-        <v>∉</v>
+        <v>∋</v>
       </c>
       <c r="H444" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I444" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H444,3,4)))</f>
@@ -21285,31 +21289,31 @@
     </row>
     <row r="445" spans="1:11" ht="17" customHeight="1">
       <c r="A445" s="1" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B445" s="5">
         <f>IF(ISNA(VLOOKUP(H445,$A$2:$C$1011,3,1)),C445,VLOOKUP(H445,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C445" s="1">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="F445" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A445,3,4)))</f>
-        <v>∋</v>
+        <v>∌</v>
       </c>
       <c r="G445" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A445,3,4)))</f>
-        <v>∋</v>
+        <v>∌</v>
       </c>
       <c r="H445" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I445" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H445,3,4)))</f>
@@ -21318,193 +21322,193 @@
     </row>
     <row r="446" spans="1:11" ht="17" customHeight="1">
       <c r="A446" s="1" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B446" s="5">
         <f>IF(ISNA(VLOOKUP(H446,$A$2:$C$1011,3,1)),C446,VLOOKUP(H446,$A$2:$C$1011,3,1))</f>
-        <v>663</v>
+        <v>11</v>
       </c>
       <c r="C446" s="1">
-        <v>673</v>
+        <v>12</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="F446" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A446,3,4)))</f>
-        <v>∌</v>
+        <v>∎</v>
       </c>
       <c r="G446" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A446,3,4)))</f>
-        <v>∌</v>
-      </c>
-      <c r="H446" s="20" t="s">
-        <v>1289</v>
+        <v>∎</v>
+      </c>
+      <c r="H446" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="I446" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H446,3,4)))</f>
-        <v>Ɐ</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447" spans="1:11" ht="17" customHeight="1">
       <c r="A447" s="1" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B447" s="5">
         <f>IF(ISNA(VLOOKUP(H447,$A$2:$C$1011,3,1)),C447,VLOOKUP(H447,$A$2:$C$1011,3,1))</f>
-        <v>11</v>
+        <v>459</v>
       </c>
       <c r="C447" s="1">
-        <v>12</v>
+        <v>460</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="F447" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A447,3,4)))</f>
-        <v>∎</v>
+        <v>∏</v>
       </c>
       <c r="G447" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A447,3,4)))</f>
-        <v>∎</v>
+        <v>∏</v>
       </c>
       <c r="H447" s="1" t="s">
-        <v>67</v>
+        <v>882</v>
       </c>
       <c r="I447" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H447,3,4)))</f>
-        <v>0</v>
+        <v>Π</v>
       </c>
     </row>
     <row r="448" spans="1:11" ht="17" customHeight="1">
       <c r="A448" s="1" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B448" s="5">
         <f>IF(ISNA(VLOOKUP(H448,$A$2:$C$1011,3,1)),C448,VLOOKUP(H448,$A$2:$C$1011,3,1))</f>
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C448" s="1">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="F448" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A448,3,4)))</f>
-        <v>∏</v>
+        <v>∑</v>
       </c>
       <c r="G448" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A448,3,4)))</f>
-        <v>∏</v>
+        <v>∑</v>
       </c>
       <c r="H448" s="1" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="I448" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H448,3,4)))</f>
-        <v>Π</v>
+        <v>Σ</v>
       </c>
     </row>
     <row r="449" spans="1:9" ht="17" customHeight="1">
       <c r="A449" s="1" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B449" s="5">
         <f>IF(ISNA(VLOOKUP(H449,$A$2:$C$1011,3,1)),C449,VLOOKUP(H449,$A$2:$C$1011,3,1))</f>
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="C449" s="1">
-        <v>470</v>
+        <v>517</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="F449" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A449,3,4)))</f>
-        <v>∑</v>
+        <v>∓</v>
       </c>
       <c r="G449" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A449,3,4)))</f>
-        <v>∑</v>
+        <v>∓</v>
       </c>
       <c r="H449" s="1" t="s">
-        <v>889</v>
+        <v>55</v>
       </c>
       <c r="I449" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H449,3,4)))</f>
-        <v>Σ</v>
+        <v>-</v>
       </c>
     </row>
     <row r="450" spans="1:9" ht="17" customHeight="1">
       <c r="A450" s="1" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B450" s="5">
         <f>IF(ISNA(VLOOKUP(H450,$A$2:$C$1011,3,1)),C450,VLOOKUP(H450,$A$2:$C$1011,3,1))</f>
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C450" s="1">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="F450" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A450,3,4)))</f>
-        <v>∓</v>
+        <v>∘</v>
       </c>
       <c r="G450" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A450,3,4)))</f>
-        <v>∓</v>
+        <v>∘</v>
       </c>
       <c r="H450" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I450" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H450,3,4)))</f>
-        <v>-</v>
+        <v>×</v>
       </c>
     </row>
     <row r="451" spans="1:9" ht="17" customHeight="1">
       <c r="A451" s="1" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B451" s="5">
         <f>IF(ISNA(VLOOKUP(H451,$A$2:$C$1011,3,1)),C451,VLOOKUP(H451,$A$2:$C$1011,3,1))</f>
         <v>519</v>
       </c>
       <c r="C451" s="1">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="F451" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A451,3,4)))</f>
-        <v>∘</v>
+        <v>∙</v>
       </c>
       <c r="G451" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A451,3,4)))</f>
-        <v>∘</v>
+        <v>∙</v>
       </c>
       <c r="H451" s="1" t="s">
         <v>47</v>
@@ -21516,146 +21520,146 @@
     </row>
     <row r="452" spans="1:9" ht="17" customHeight="1">
       <c r="A452" s="1" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B452" s="5">
         <f>IF(ISNA(VLOOKUP(H452,$A$2:$C$1011,3,1)),C452,VLOOKUP(H452,$A$2:$C$1011,3,1))</f>
-        <v>519</v>
+        <v>621</v>
       </c>
       <c r="C452" s="1">
-        <v>521</v>
+        <v>621</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="F452" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A452,3,4)))</f>
-        <v>∙</v>
+        <v>√</v>
       </c>
       <c r="G452" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A452,3,4)))</f>
-        <v>∙</v>
+        <v>√</v>
       </c>
       <c r="H452" s="1" t="s">
-        <v>47</v>
+        <v>1333</v>
       </c>
       <c r="I452" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H452,3,4)))</f>
-        <v>×</v>
+        <v>√</v>
       </c>
     </row>
     <row r="453" spans="1:9" ht="17" customHeight="1">
       <c r="A453" s="1" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B453" s="5">
         <f>IF(ISNA(VLOOKUP(H453,$A$2:$C$1011,3,1)),C453,VLOOKUP(H453,$A$2:$C$1011,3,1))</f>
-        <v>621</v>
+        <v>29</v>
       </c>
       <c r="C453" s="1">
-        <v>621</v>
+        <v>33</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F453" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A453,3,4)))</f>
-        <v>√</v>
+        <v>∛</v>
       </c>
       <c r="G453" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A453,3,4)))</f>
-        <v>√</v>
+        <v>∛</v>
       </c>
       <c r="H453" s="1" t="s">
-        <v>1335</v>
+        <v>76</v>
       </c>
       <c r="I453" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H453,3,4)))</f>
-        <v>√</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454" spans="1:9" ht="17" customHeight="1">
       <c r="A454" s="1" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B454" s="5">
         <f>IF(ISNA(VLOOKUP(H454,$A$2:$C$1011,3,1)),C454,VLOOKUP(H454,$A$2:$C$1011,3,1))</f>
-        <v>29</v>
+        <v>373</v>
       </c>
       <c r="C454" s="1">
-        <v>33</v>
+        <v>383</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="F454" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A454,3,4)))</f>
-        <v>∛</v>
+        <v>∜</v>
       </c>
       <c r="G454" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A454,3,4)))</f>
-        <v>∛</v>
+        <v>∜</v>
       </c>
       <c r="H454" s="1" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="I454" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H454,3,4)))</f>
-        <v>3</v>
+        <v>X</v>
       </c>
     </row>
     <row r="455" spans="1:9" ht="17" customHeight="1">
       <c r="A455" s="1" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B455" s="5">
         <f>IF(ISNA(VLOOKUP(H455,$A$2:$C$1011,3,1)),C455,VLOOKUP(H455,$A$2:$C$1011,3,1))</f>
-        <v>373</v>
+        <v>621</v>
       </c>
       <c r="C455" s="1">
-        <v>383</v>
+        <v>622</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="F455" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A455,3,4)))</f>
-        <v>∜</v>
+        <v>∝</v>
       </c>
       <c r="G455" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A455,3,4)))</f>
-        <v>∜</v>
+        <v>∝</v>
       </c>
       <c r="H455" s="1" t="s">
-        <v>189</v>
+        <v>1333</v>
       </c>
       <c r="I455" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H455,3,4)))</f>
-        <v>X</v>
+        <v>√</v>
       </c>
     </row>
     <row r="456" spans="1:9" ht="17" customHeight="1">
       <c r="A456" s="1" t="s">
-        <v>1344</v>
+        <v>1144</v>
       </c>
       <c r="B456" s="5">
         <f>IF(ISNA(VLOOKUP(H456,$A$2:$C$1011,3,1)),C456,VLOOKUP(H456,$A$2:$C$1011,3,1))</f>
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C456" s="1">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D456" s="2" t="s">
         <v>1345</v>
@@ -21665,113 +21669,113 @@
       </c>
       <c r="F456" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A456,3,4)))</f>
-        <v>∝</v>
+        <v>∞</v>
       </c>
       <c r="G456" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A456,3,4)))</f>
-        <v>∝</v>
+        <v>∞</v>
       </c>
       <c r="H456" s="1" t="s">
-        <v>1335</v>
+        <v>1144</v>
       </c>
       <c r="I456" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H456,3,4)))</f>
-        <v>√</v>
+        <v>∞</v>
       </c>
     </row>
     <row r="457" spans="1:9" ht="17" customHeight="1">
       <c r="A457" s="1" t="s">
-        <v>1144</v>
+        <v>1347</v>
       </c>
       <c r="B457" s="5">
         <f>IF(ISNA(VLOOKUP(H457,$A$2:$C$1011,3,1)),C457,VLOOKUP(H457,$A$2:$C$1011,3,1))</f>
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="C457" s="1">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="F457" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A457,3,4)))</f>
-        <v>∞</v>
+        <v>∟</v>
       </c>
       <c r="G457" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A457,3,4)))</f>
-        <v>∞</v>
+        <v>∟</v>
       </c>
       <c r="H457" s="1" t="s">
-        <v>1144</v>
+        <v>1347</v>
       </c>
       <c r="I457" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H457,3,4)))</f>
-        <v>∞</v>
+        <v>∟</v>
       </c>
     </row>
     <row r="458" spans="1:9" ht="17" customHeight="1">
       <c r="A458" s="1" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B458" s="5">
         <f>IF(ISNA(VLOOKUP(H458,$A$2:$C$1011,3,1)),C458,VLOOKUP(H458,$A$2:$C$1011,3,1))</f>
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C458" s="1">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="F458" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A458,3,4)))</f>
-        <v>∟</v>
+        <v>∠</v>
       </c>
       <c r="G458" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A458,3,4)))</f>
-        <v>∟</v>
+        <v>∠</v>
       </c>
       <c r="H458" s="1" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="I458" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H458,3,4)))</f>
-        <v>∟</v>
+        <v>∠</v>
       </c>
     </row>
     <row r="459" spans="1:9" ht="17" customHeight="1">
       <c r="A459" s="1" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B459" s="5">
         <f>IF(ISNA(VLOOKUP(H459,$A$2:$C$1011,3,1)),C459,VLOOKUP(H459,$A$2:$C$1011,3,1))</f>
         <v>637</v>
       </c>
       <c r="C459" s="1">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="F459" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A459,3,4)))</f>
-        <v>∠</v>
+        <v>∡</v>
       </c>
       <c r="G459" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A459,3,4)))</f>
-        <v>∠</v>
+        <v>∡</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="I459" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H459,3,4)))</f>
@@ -21780,31 +21784,31 @@
     </row>
     <row r="460" spans="1:9" ht="17" customHeight="1">
       <c r="A460" s="1" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B460" s="5">
         <f>IF(ISNA(VLOOKUP(H460,$A$2:$C$1011,3,1)),C460,VLOOKUP(H460,$A$2:$C$1011,3,1))</f>
         <v>637</v>
       </c>
       <c r="C460" s="1">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="F460" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A460,3,4)))</f>
-        <v>∡</v>
+        <v>∢</v>
       </c>
       <c r="G460" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A460,3,4)))</f>
-        <v>∡</v>
+        <v>∢</v>
       </c>
       <c r="H460" s="1" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="I460" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H460,3,4)))</f>
@@ -21813,61 +21817,61 @@
     </row>
     <row r="461" spans="1:9" ht="17" customHeight="1">
       <c r="A461" s="1" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B461" s="5">
         <f>IF(ISNA(VLOOKUP(H461,$A$2:$C$1011,3,1)),C461,VLOOKUP(H461,$A$2:$C$1011,3,1))</f>
-        <v>637</v>
+        <v>595</v>
       </c>
       <c r="C461" s="1">
-        <v>639</v>
+        <v>596</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F461" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A461,3,4)))</f>
-        <v>∢</v>
+        <v>∣</v>
       </c>
       <c r="G461" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A461,3,4)))</f>
-        <v>∢</v>
+        <v>∣</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>1352</v>
+        <v>294</v>
       </c>
       <c r="I461" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H461,3,4)))</f>
-        <v>∠</v>
+        <v>|</v>
       </c>
     </row>
     <row r="462" spans="1:9" ht="17" customHeight="1">
       <c r="A462" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B462" s="5">
         <f>IF(ISNA(VLOOKUP(H462,$A$2:$C$1011,3,1)),C462,VLOOKUP(H462,$A$2:$C$1011,3,1))</f>
         <v>595</v>
       </c>
       <c r="C462" s="1">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="F462" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A462,3,4)))</f>
-        <v>∣</v>
+        <v>∤</v>
       </c>
       <c r="G462" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A462,3,4)))</f>
-        <v>∣</v>
+        <v>∤</v>
       </c>
       <c r="H462" s="1" t="s">
         <v>294</v>
@@ -21879,28 +21883,28 @@
     </row>
     <row r="463" spans="1:9" ht="17" customHeight="1">
       <c r="A463" s="1" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B463" s="5">
         <f>IF(ISNA(VLOOKUP(H463,$A$2:$C$1011,3,1)),C463,VLOOKUP(H463,$A$2:$C$1011,3,1))</f>
         <v>595</v>
       </c>
       <c r="C463" s="1">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="F463" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A463,3,4)))</f>
-        <v>∤</v>
+        <v>∥</v>
       </c>
       <c r="G463" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A463,3,4)))</f>
-        <v>∤</v>
+        <v>∥</v>
       </c>
       <c r="H463" s="1" t="s">
         <v>294</v>
@@ -21912,28 +21916,28 @@
     </row>
     <row r="464" spans="1:9" ht="17" customHeight="1">
       <c r="A464" s="1" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B464" s="5">
         <f>IF(ISNA(VLOOKUP(H464,$A$2:$C$1011,3,1)),C464,VLOOKUP(H464,$A$2:$C$1011,3,1))</f>
         <v>595</v>
       </c>
       <c r="C464" s="1">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="F464" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A464,3,4)))</f>
-        <v>∥</v>
+        <v>∦</v>
       </c>
       <c r="G464" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A464,3,4)))</f>
-        <v>∥</v>
+        <v>∦</v>
       </c>
       <c r="H464" s="1" t="s">
         <v>294</v>
@@ -21945,61 +21949,61 @@
     </row>
     <row r="465" spans="1:9" ht="17" customHeight="1">
       <c r="A465" s="1" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B465" s="5">
         <f>IF(ISNA(VLOOKUP(H465,$A$2:$C$1011,3,1)),C465,VLOOKUP(H465,$A$2:$C$1011,3,1))</f>
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="C465" s="1">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="F465" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A465,3,4)))</f>
-        <v>∦</v>
+        <v>∧</v>
       </c>
       <c r="G465" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A465,3,4)))</f>
-        <v>∦</v>
+        <v>∧</v>
       </c>
       <c r="H465" s="1" t="s">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="I465" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H465,3,4)))</f>
-        <v>|</v>
+        <v>¬</v>
       </c>
     </row>
     <row r="466" spans="1:9" ht="17" customHeight="1">
       <c r="A466" s="1" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B466" s="5">
         <f>IF(ISNA(VLOOKUP(H466,$A$2:$C$1011,3,1)),C466,VLOOKUP(H466,$A$2:$C$1011,3,1))</f>
         <v>588</v>
       </c>
       <c r="C466" s="1">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="F466" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A466,3,4)))</f>
-        <v>∧</v>
+        <v>∨</v>
       </c>
       <c r="G466" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A466,3,4)))</f>
-        <v>∧</v>
+        <v>∨</v>
       </c>
       <c r="H466" s="1" t="s">
         <v>327</v>
@@ -22011,64 +22015,64 @@
     </row>
     <row r="467" spans="1:9" ht="17" customHeight="1">
       <c r="A467" s="1" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B467" s="5">
         <f>IF(ISNA(VLOOKUP(H467,$A$2:$C$1011,3,1)),C467,VLOOKUP(H467,$A$2:$C$1011,3,1))</f>
-        <v>588</v>
+        <v>663</v>
       </c>
       <c r="C467" s="1">
-        <v>590</v>
+        <v>674</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="F467" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A467,3,4)))</f>
-        <v>∨</v>
+        <v>∩</v>
       </c>
       <c r="G467" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A467,3,4)))</f>
-        <v>∨</v>
-      </c>
-      <c r="H467" s="1" t="s">
-        <v>327</v>
+        <v>∩</v>
+      </c>
+      <c r="H467" s="20" t="s">
+        <v>1287</v>
       </c>
       <c r="I467" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H467,3,4)))</f>
-        <v>¬</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="468" spans="1:9" ht="17" customHeight="1">
       <c r="A468" s="1" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B468" s="5">
         <f>IF(ISNA(VLOOKUP(H468,$A$2:$C$1011,3,1)),C468,VLOOKUP(H468,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C468" s="1">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="F468" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A468,3,4)))</f>
-        <v>∩</v>
+        <v>∪</v>
       </c>
       <c r="G468" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A468,3,4)))</f>
-        <v>∩</v>
+        <v>∪</v>
       </c>
       <c r="H468" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I468" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H468,3,4)))</f>
@@ -22077,64 +22081,64 @@
     </row>
     <row r="469" spans="1:9" ht="17" customHeight="1">
       <c r="A469" s="1" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B469" s="5">
         <f>IF(ISNA(VLOOKUP(H469,$A$2:$C$1011,3,1)),C469,VLOOKUP(H469,$A$2:$C$1011,3,1))</f>
-        <v>663</v>
+        <v>626</v>
       </c>
       <c r="C469" s="1">
-        <v>675</v>
+        <v>626</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="F469" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A469,3,4)))</f>
-        <v>∪</v>
+        <v>∫</v>
       </c>
       <c r="G469" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A469,3,4)))</f>
-        <v>∪</v>
-      </c>
-      <c r="H469" s="20" t="s">
-        <v>1289</v>
+        <v>∫</v>
+      </c>
+      <c r="H469" s="1" t="s">
+        <v>1383</v>
       </c>
       <c r="I469" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H469,3,4)))</f>
-        <v>Ɐ</v>
+        <v>∫</v>
       </c>
     </row>
     <row r="470" spans="1:9" ht="17" customHeight="1">
       <c r="A470" s="1" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B470" s="5">
         <f>IF(ISNA(VLOOKUP(H470,$A$2:$C$1011,3,1)),C470,VLOOKUP(H470,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C470" s="1">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="F470" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A470,3,4)))</f>
-        <v>∫</v>
+        <v>∬</v>
       </c>
       <c r="G470" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A470,3,4)))</f>
-        <v>∫</v>
+        <v>∬</v>
       </c>
       <c r="H470" s="1" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="I470" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H470,3,4)))</f>
@@ -22143,31 +22147,31 @@
     </row>
     <row r="471" spans="1:9" ht="17" customHeight="1">
       <c r="A471" s="1" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B471" s="5">
         <f>IF(ISNA(VLOOKUP(H471,$A$2:$C$1011,3,1)),C471,VLOOKUP(H471,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C471" s="1">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="F471" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A471,3,4)))</f>
-        <v>∬</v>
+        <v>∭</v>
       </c>
       <c r="G471" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A471,3,4)))</f>
-        <v>∬</v>
+        <v>∭</v>
       </c>
       <c r="H471" s="1" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="I471" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H471,3,4)))</f>
@@ -22176,31 +22180,31 @@
     </row>
     <row r="472" spans="1:9" ht="17" customHeight="1">
       <c r="A472" s="1" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B472" s="5">
         <f>IF(ISNA(VLOOKUP(H472,$A$2:$C$1011,3,1)),C472,VLOOKUP(H472,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C472" s="1">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="F472" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A472,3,4)))</f>
-        <v>∭</v>
+        <v>∮</v>
       </c>
       <c r="G472" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A472,3,4)))</f>
-        <v>∭</v>
+        <v>∮</v>
       </c>
       <c r="H472" s="1" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="I472" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H472,3,4)))</f>
@@ -22209,31 +22213,31 @@
     </row>
     <row r="473" spans="1:9" ht="17" customHeight="1">
       <c r="A473" s="1" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B473" s="5">
         <f>IF(ISNA(VLOOKUP(H473,$A$2:$C$1011,3,1)),C473,VLOOKUP(H473,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C473" s="1">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F473" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A473,3,4)))</f>
-        <v>∮</v>
+        <v>∯</v>
       </c>
       <c r="G473" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A473,3,4)))</f>
-        <v>∮</v>
+        <v>∯</v>
       </c>
       <c r="H473" s="1" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="I473" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H473,3,4)))</f>
@@ -22242,31 +22246,31 @@
     </row>
     <row r="474" spans="1:9" ht="17" customHeight="1">
       <c r="A474" s="1" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B474" s="5">
         <f>IF(ISNA(VLOOKUP(H474,$A$2:$C$1011,3,1)),C474,VLOOKUP(H474,$A$2:$C$1011,3,1))</f>
         <v>626</v>
       </c>
       <c r="C474" s="1">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F474" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A474,3,4)))</f>
-        <v>∯</v>
+        <v>∰</v>
       </c>
       <c r="G474" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A474,3,4)))</f>
-        <v>∯</v>
+        <v>∰</v>
       </c>
       <c r="H474" s="1" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="I474" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H474,3,4)))</f>
@@ -22275,94 +22279,94 @@
     </row>
     <row r="475" spans="1:9" ht="17" customHeight="1">
       <c r="A475" s="1" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B475" s="5">
         <f>IF(ISNA(VLOOKUP(H475,$A$2:$C$1011,3,1)),C475,VLOOKUP(H475,$A$2:$C$1011,3,1))</f>
-        <v>626</v>
+        <v>540</v>
       </c>
       <c r="C475" s="1">
-        <v>631</v>
+        <v>541</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F475" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A475,3,4)))</f>
-        <v>∰</v>
+        <v>∶</v>
       </c>
       <c r="G475" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A475,3,4)))</f>
-        <v>∰</v>
+        <v>∶</v>
       </c>
       <c r="H475" s="1" t="s">
-        <v>1385</v>
+        <v>98</v>
       </c>
       <c r="I475" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H475,3,4)))</f>
-        <v>∫</v>
+        <v>:</v>
       </c>
     </row>
     <row r="476" spans="1:9" ht="17" customHeight="1">
       <c r="A476" s="1" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B476" s="5">
         <f>IF(ISNA(VLOOKUP(H476,$A$2:$C$1011,3,1)),C476,VLOOKUP(H476,$A$2:$C$1011,3,1))</f>
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="C476" s="1">
-        <v>541</v>
+        <v>606</v>
       </c>
       <c r="D476" s="2" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="F476" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A476,3,4)))</f>
-        <v>∶</v>
+        <v>≃</v>
       </c>
       <c r="G476" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A476,3,4)))</f>
-        <v>∶</v>
+        <v>≃</v>
       </c>
       <c r="H476" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I476" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H476,3,4)))</f>
-        <v>:</v>
+        <v>≪</v>
       </c>
     </row>
     <row r="477" spans="1:9" ht="17" customHeight="1">
       <c r="A477" s="1" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B477" s="5">
         <f>IF(ISNA(VLOOKUP(H477,$A$2:$C$1011,3,1)),C477,VLOOKUP(H477,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C477" s="1">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="F477" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A477,3,4)))</f>
-        <v>≃</v>
+        <v>≈</v>
       </c>
       <c r="G477" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A477,3,4)))</f>
-        <v>≃</v>
+        <v>≈</v>
       </c>
       <c r="H477" s="1" t="s">
         <v>107</v>
@@ -22374,28 +22378,28 @@
     </row>
     <row r="478" spans="1:9" ht="17" customHeight="1">
       <c r="A478" s="1" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B478" s="5">
         <f>IF(ISNA(VLOOKUP(H478,$A$2:$C$1011,3,1)),C478,VLOOKUP(H478,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C478" s="1">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F478" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A478,3,4)))</f>
-        <v>≈</v>
+        <v>≔</v>
       </c>
       <c r="G478" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A478,3,4)))</f>
-        <v>≈</v>
+        <v>≔</v>
       </c>
       <c r="H478" s="1" t="s">
         <v>107</v>
@@ -22407,28 +22411,28 @@
     </row>
     <row r="479" spans="1:9" ht="17" customHeight="1">
       <c r="A479" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B479" s="5">
         <f>IF(ISNA(VLOOKUP(H479,$A$2:$C$1011,3,1)),C479,VLOOKUP(H479,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C479" s="1">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="F479" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A479,3,4)))</f>
-        <v>≔</v>
+        <v>≘</v>
       </c>
       <c r="G479" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A479,3,4)))</f>
-        <v>≔</v>
+        <v>≘</v>
       </c>
       <c r="H479" s="1" t="s">
         <v>107</v>
@@ -22440,28 +22444,28 @@
     </row>
     <row r="480" spans="1:9" ht="17" customHeight="1">
       <c r="A480" s="1" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B480" s="5">
         <f>IF(ISNA(VLOOKUP(H480,$A$2:$C$1011,3,1)),C480,VLOOKUP(H480,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C480" s="1">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="F480" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A480,3,4)))</f>
-        <v>≘</v>
+        <v>≙</v>
       </c>
       <c r="G480" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A480,3,4)))</f>
-        <v>≘</v>
+        <v>≙</v>
       </c>
       <c r="H480" s="1" t="s">
         <v>107</v>
@@ -22473,28 +22477,28 @@
     </row>
     <row r="481" spans="1:9" ht="17" customHeight="1">
       <c r="A481" s="1" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B481" s="5">
         <f>IF(ISNA(VLOOKUP(H481,$A$2:$C$1011,3,1)),C481,VLOOKUP(H481,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C481" s="1">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="F481" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A481,3,4)))</f>
-        <v>≙</v>
+        <v>≠</v>
       </c>
       <c r="G481" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A481,3,4)))</f>
-        <v>≙</v>
+        <v>≠</v>
       </c>
       <c r="H481" s="1" t="s">
         <v>107</v>
@@ -22506,28 +22510,28 @@
     </row>
     <row r="482" spans="1:9" ht="17" customHeight="1">
       <c r="A482" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B482" s="5">
         <f>IF(ISNA(VLOOKUP(H482,$A$2:$C$1011,3,1)),C482,VLOOKUP(H482,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C482" s="1">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="F482" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A482,3,4)))</f>
-        <v>≠</v>
+        <v>≡</v>
       </c>
       <c r="G482" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A482,3,4)))</f>
-        <v>≠</v>
+        <v>≡</v>
       </c>
       <c r="H482" s="1" t="s">
         <v>107</v>
@@ -22539,28 +22543,28 @@
     </row>
     <row r="483" spans="1:9" ht="17" customHeight="1">
       <c r="A483" s="1" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B483" s="5">
         <f>IF(ISNA(VLOOKUP(H483,$A$2:$C$1011,3,1)),C483,VLOOKUP(H483,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C483" s="1">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="F483" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A483,3,4)))</f>
-        <v>≡</v>
+        <v>≤</v>
       </c>
       <c r="G483" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A483,3,4)))</f>
-        <v>≡</v>
+        <v>≤</v>
       </c>
       <c r="H483" s="1" t="s">
         <v>107</v>
@@ -22572,28 +22576,28 @@
     </row>
     <row r="484" spans="1:9" ht="17" customHeight="1">
       <c r="A484" s="1" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B484" s="5">
         <f>IF(ISNA(VLOOKUP(H484,$A$2:$C$1011,3,1)),C484,VLOOKUP(H484,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C484" s="1">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="F484" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A484,3,4)))</f>
-        <v>≤</v>
+        <v>≥</v>
       </c>
       <c r="G484" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A484,3,4)))</f>
-        <v>≤</v>
+        <v>≥</v>
       </c>
       <c r="H484" s="1" t="s">
         <v>107</v>
@@ -22605,14 +22609,14 @@
     </row>
     <row r="485" spans="1:9" ht="17" customHeight="1">
       <c r="A485" s="1" t="s">
-        <v>1430</v>
+        <v>107</v>
       </c>
       <c r="B485" s="5">
         <f>IF(ISNA(VLOOKUP(H485,$A$2:$C$1011,3,1)),C485,VLOOKUP(H485,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C485" s="1">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="D485" s="2" t="s">
         <v>1431</v>
@@ -22622,11 +22626,11 @@
       </c>
       <c r="F485" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A485,3,4)))</f>
-        <v>≥</v>
+        <v>≪</v>
       </c>
       <c r="G485" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A485,3,4)))</f>
-        <v>≥</v>
+        <v>≪</v>
       </c>
       <c r="H485" s="1" t="s">
         <v>107</v>
@@ -22638,28 +22642,28 @@
     </row>
     <row r="486" spans="1:9" ht="17" customHeight="1">
       <c r="A486" s="1" t="s">
-        <v>107</v>
+        <v>1433</v>
       </c>
       <c r="B486" s="5">
         <f>IF(ISNA(VLOOKUP(H486,$A$2:$C$1011,3,1)),C486,VLOOKUP(H486,$A$2:$C$1011,3,1))</f>
         <v>600</v>
       </c>
       <c r="C486" s="1">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="F486" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A486,3,4)))</f>
-        <v>≪</v>
+        <v>≫</v>
       </c>
       <c r="G486" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A486,3,4)))</f>
-        <v>≪</v>
+        <v>≫</v>
       </c>
       <c r="H486" s="1" t="s">
         <v>107</v>
@@ -22671,64 +22675,64 @@
     </row>
     <row r="487" spans="1:9" ht="17" customHeight="1">
       <c r="A487" s="1" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B487" s="5">
         <f>IF(ISNA(VLOOKUP(H487,$A$2:$C$1011,3,1)),C487,VLOOKUP(H487,$A$2:$C$1011,3,1))</f>
-        <v>600</v>
+        <v>663</v>
       </c>
       <c r="C487" s="1">
-        <v>613</v>
+        <v>676</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="F487" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A487,3,4)))</f>
-        <v>≫</v>
+        <v>⊂</v>
       </c>
       <c r="G487" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A487,3,4)))</f>
-        <v>≫</v>
-      </c>
-      <c r="H487" s="1" t="s">
-        <v>107</v>
+        <v>⊂</v>
+      </c>
+      <c r="H487" s="20" t="s">
+        <v>1287</v>
       </c>
       <c r="I487" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H487,3,4)))</f>
-        <v>≪</v>
+        <v>Ɐ</v>
       </c>
     </row>
     <row r="488" spans="1:9" ht="17" customHeight="1">
       <c r="A488" s="1" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B488" s="5">
         <f>IF(ISNA(VLOOKUP(H488,$A$2:$C$1011,3,1)),C488,VLOOKUP(H488,$A$2:$C$1011,3,1))</f>
         <v>663</v>
       </c>
       <c r="C488" s="1">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="F488" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A488,3,4)))</f>
-        <v>⊂</v>
+        <v>⊄</v>
       </c>
       <c r="G488" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A488,3,4)))</f>
-        <v>⊂</v>
+        <v>⊄</v>
       </c>
       <c r="H488" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I488" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H488,3,4)))</f>
@@ -22737,196 +22741,196 @@
     </row>
     <row r="489" spans="1:9" ht="17" customHeight="1">
       <c r="A489" s="1" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B489" s="5">
         <f>IF(ISNA(VLOOKUP(H489,$A$2:$C$1011,3,1)),C489,VLOOKUP(H489,$A$2:$C$1011,3,1))</f>
-        <v>663</v>
+        <v>634</v>
       </c>
       <c r="C489" s="1">
-        <v>677</v>
+        <v>634</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="F489" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A489,3,4)))</f>
-        <v>⊄</v>
+        <v>⊕</v>
       </c>
       <c r="G489" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A489,3,4)))</f>
-        <v>⊄</v>
-      </c>
-      <c r="H489" s="20" t="s">
-        <v>1289</v>
+        <v>⊕</v>
+      </c>
+      <c r="H489" s="1" t="s">
+        <v>1442</v>
       </c>
       <c r="I489" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H489,3,4)))</f>
-        <v>Ɐ</v>
+        <v>⊕</v>
       </c>
     </row>
     <row r="490" spans="1:9" ht="17" customHeight="1">
       <c r="A490" s="1" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B490" s="5">
         <f>IF(ISNA(VLOOKUP(H490,$A$2:$C$1011,3,1)),C490,VLOOKUP(H490,$A$2:$C$1011,3,1))</f>
-        <v>634</v>
+        <v>415</v>
       </c>
       <c r="C490" s="1">
-        <v>634</v>
+        <v>417</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="F490" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A490,3,4)))</f>
-        <v>⊕</v>
+        <v>⊖</v>
       </c>
       <c r="G490" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A490,3,4)))</f>
-        <v>⊕</v>
+        <v>⊖</v>
       </c>
       <c r="H490" s="1" t="s">
-        <v>1444</v>
+        <v>839</v>
       </c>
       <c r="I490" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H490,3,4)))</f>
-        <v>⊕</v>
+        <v>Α</v>
       </c>
     </row>
     <row r="491" spans="1:9" ht="17" customHeight="1">
       <c r="A491" s="1" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B491" s="5">
         <f>IF(ISNA(VLOOKUP(H491,$A$2:$C$1011,3,1)),C491,VLOOKUP(H491,$A$2:$C$1011,3,1))</f>
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C491" s="1">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="D491" s="2" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F491" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A491,3,4)))</f>
-        <v>⊖</v>
+        <v>⊗</v>
       </c>
       <c r="G491" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A491,3,4)))</f>
-        <v>⊖</v>
+        <v>⊗</v>
       </c>
       <c r="H491" s="1" t="s">
-        <v>839</v>
+        <v>848</v>
       </c>
       <c r="I491" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H491,3,4)))</f>
-        <v>Α</v>
+        <v>Δ</v>
       </c>
     </row>
     <row r="492" spans="1:9" ht="17" customHeight="1">
       <c r="A492" s="1" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B492" s="5">
         <f>IF(ISNA(VLOOKUP(H492,$A$2:$C$1011,3,1)),C492,VLOOKUP(H492,$A$2:$C$1011,3,1))</f>
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="C492" s="1">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="D492" s="2" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="F492" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A492,3,4)))</f>
-        <v>⊗</v>
+        <v>⊘</v>
       </c>
       <c r="G492" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A492,3,4)))</f>
-        <v>⊗</v>
+        <v>⊘</v>
       </c>
       <c r="H492" s="1" t="s">
-        <v>848</v>
+        <v>339</v>
       </c>
       <c r="I492" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H492,3,4)))</f>
-        <v>Δ</v>
+        <v>Μ</v>
       </c>
     </row>
     <row r="493" spans="1:9" ht="17" customHeight="1">
       <c r="A493" s="1" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B493" s="5">
         <f>IF(ISNA(VLOOKUP(H493,$A$2:$C$1011,3,1)),C493,VLOOKUP(H493,$A$2:$C$1011,3,1))</f>
-        <v>448</v>
+        <v>632</v>
       </c>
       <c r="C493" s="1">
-        <v>451</v>
+        <v>632</v>
       </c>
       <c r="D493" s="2" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="F493" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A493,3,4)))</f>
-        <v>⊘</v>
+        <v>⊙</v>
       </c>
       <c r="G493" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A493,3,4)))</f>
-        <v>⊘</v>
+        <v>⊙</v>
       </c>
       <c r="H493" s="1" t="s">
-        <v>339</v>
+        <v>1454</v>
       </c>
       <c r="I493" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H493,3,4)))</f>
-        <v>Μ</v>
+        <v>⊙</v>
       </c>
     </row>
     <row r="494" spans="1:9" ht="17" customHeight="1">
       <c r="A494" s="1" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B494" s="5">
         <f>IF(ISNA(VLOOKUP(H494,$A$2:$C$1011,3,1)),C494,VLOOKUP(H494,$A$2:$C$1011,3,1))</f>
         <v>632</v>
       </c>
       <c r="C494" s="1">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D494" s="2" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="F494" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A494,3,4)))</f>
-        <v>⊙</v>
+        <v>⊚</v>
       </c>
       <c r="G494" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A494,3,4)))</f>
-        <v>⊙</v>
+        <v>⊚</v>
       </c>
       <c r="H494" s="1" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="I494" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H494,3,4)))</f>
@@ -22935,61 +22939,61 @@
     </row>
     <row r="495" spans="1:9" ht="17" customHeight="1">
       <c r="A495" s="1" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B495" s="5">
         <f>IF(ISNA(VLOOKUP(H495,$A$2:$C$1011,3,1)),C495,VLOOKUP(H495,$A$2:$C$1011,3,1))</f>
-        <v>632</v>
+        <v>316</v>
       </c>
       <c r="C495" s="1">
-        <v>633</v>
+        <v>329</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="F495" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A495,3,4)))</f>
-        <v>⊚</v>
+        <v>⊢</v>
       </c>
       <c r="G495" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A495,3,4)))</f>
-        <v>⊚</v>
+        <v>⊢</v>
       </c>
       <c r="H495" s="1" t="s">
-        <v>1456</v>
+        <v>177</v>
       </c>
       <c r="I495" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H495,3,4)))</f>
-        <v>⊙</v>
+        <v>T</v>
       </c>
     </row>
     <row r="496" spans="1:9" ht="17" customHeight="1">
       <c r="A496" s="1" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B496" s="5">
         <f>IF(ISNA(VLOOKUP(H496,$A$2:$C$1011,3,1)),C496,VLOOKUP(H496,$A$2:$C$1011,3,1))</f>
         <v>316</v>
       </c>
       <c r="C496" s="1">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F496" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A496,3,4)))</f>
-        <v>⊢</v>
+        <v>⊤</v>
       </c>
       <c r="G496" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A496,3,4)))</f>
-        <v>⊢</v>
+        <v>⊤</v>
       </c>
       <c r="H496" s="1" t="s">
         <v>177</v>
@@ -23001,94 +23005,94 @@
     </row>
     <row r="497" spans="1:9" ht="17" customHeight="1">
       <c r="A497" s="1" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B497" s="5">
         <f>IF(ISNA(VLOOKUP(H497,$A$2:$C$1011,3,1)),C497,VLOOKUP(H497,$A$2:$C$1011,3,1))</f>
-        <v>316</v>
+        <v>635</v>
       </c>
       <c r="C497" s="1">
-        <v>319</v>
+        <v>636</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="F497" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A497,3,4)))</f>
-        <v>⊤</v>
+        <v>⊥</v>
       </c>
       <c r="G497" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A497,3,4)))</f>
-        <v>⊤</v>
+        <v>⊥</v>
       </c>
       <c r="H497" s="1" t="s">
-        <v>177</v>
+        <v>1347</v>
       </c>
       <c r="I497" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H497,3,4)))</f>
-        <v>T</v>
+        <v>∟</v>
       </c>
     </row>
     <row r="498" spans="1:9" ht="17" customHeight="1">
       <c r="A498" s="1" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B498" s="5">
         <f>IF(ISNA(VLOOKUP(H498,$A$2:$C$1011,3,1)),C498,VLOOKUP(H498,$A$2:$C$1011,3,1))</f>
-        <v>635</v>
+        <v>588</v>
       </c>
       <c r="C498" s="1">
-        <v>636</v>
+        <v>591</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F498" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A498,3,4)))</f>
-        <v>⊥</v>
+        <v>⊻</v>
       </c>
       <c r="G498" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A498,3,4)))</f>
-        <v>⊥</v>
+        <v>⊻</v>
       </c>
       <c r="H498" s="1" t="s">
-        <v>1349</v>
+        <v>327</v>
       </c>
       <c r="I498" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H498,3,4)))</f>
-        <v>∟</v>
+        <v>¬</v>
       </c>
     </row>
     <row r="499" spans="1:9" ht="17" customHeight="1">
       <c r="A499" s="1" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B499" s="5">
         <f>IF(ISNA(VLOOKUP(H499,$A$2:$C$1011,3,1)),C499,VLOOKUP(H499,$A$2:$C$1011,3,1))</f>
         <v>588</v>
       </c>
       <c r="C499" s="1">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="F499" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A499,3,4)))</f>
-        <v>⊻</v>
+        <v>⊼</v>
       </c>
       <c r="G499" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A499,3,4)))</f>
-        <v>⊻</v>
+        <v>⊼</v>
       </c>
       <c r="H499" s="1" t="s">
         <v>327</v>
@@ -23100,28 +23104,28 @@
     </row>
     <row r="500" spans="1:9" ht="17" customHeight="1">
       <c r="A500" s="1" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B500" s="5">
         <f>IF(ISNA(VLOOKUP(H500,$A$2:$C$1011,3,1)),C500,VLOOKUP(H500,$A$2:$C$1011,3,1))</f>
         <v>588</v>
       </c>
       <c r="C500" s="1">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="F500" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A500,3,4)))</f>
-        <v>⊼</v>
+        <v>⊽</v>
       </c>
       <c r="G500" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A500,3,4)))</f>
-        <v>⊼</v>
+        <v>⊽</v>
       </c>
       <c r="H500" s="1" t="s">
         <v>327</v>
@@ -23133,97 +23137,97 @@
     </row>
     <row r="501" spans="1:9" ht="17" customHeight="1">
       <c r="A501" s="1" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B501" s="5">
         <f>IF(ISNA(VLOOKUP(H501,$A$2:$C$1011,3,1)),C501,VLOOKUP(H501,$A$2:$C$1011,3,1))</f>
-        <v>588</v>
+        <v>531</v>
       </c>
       <c r="C501" s="1">
-        <v>593</v>
+        <v>535</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="F501" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A501,3,4)))</f>
-        <v>⊽</v>
+        <v>⋅</v>
       </c>
       <c r="G501" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A501,3,4)))</f>
-        <v>⊽</v>
+        <v>⋅</v>
       </c>
       <c r="H501" s="1" t="s">
-        <v>327</v>
+        <v>59</v>
       </c>
       <c r="I501" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H501,3,4)))</f>
-        <v>¬</v>
+        <v>.</v>
       </c>
     </row>
     <row r="502" spans="1:9" ht="17" customHeight="1">
       <c r="A502" s="1" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B502" s="5">
         <f>IF(ISNA(VLOOKUP(H502,$A$2:$C$1011,3,1)),C502,VLOOKUP(H502,$A$2:$C$1011,3,1))</f>
-        <v>531</v>
+        <v>640</v>
       </c>
       <c r="C502" s="1">
-        <v>535</v>
+        <v>643</v>
       </c>
       <c r="D502" s="2" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="F502" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A502,3,4)))</f>
-        <v>⋅</v>
+        <v>⌚</v>
       </c>
       <c r="G502" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A502,3,4)))</f>
-        <v>⋅</v>
-      </c>
-      <c r="H502" s="1" t="s">
-        <v>59</v>
+        <v>⌚</v>
+      </c>
+      <c r="H502" s="17" t="s">
+        <v>1484</v>
       </c>
       <c r="I502" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H502,3,4)))</f>
-        <v>.</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="503" spans="1:9" ht="17" customHeight="1">
       <c r="A503" s="1" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B503" s="5">
         <f>IF(ISNA(VLOOKUP(H503,$A$2:$C$1011,3,1)),C503,VLOOKUP(H503,$A$2:$C$1011,3,1))</f>
         <v>640</v>
       </c>
       <c r="C503" s="1">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D503" s="2" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="F503" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A503,3,4)))</f>
-        <v>⌚</v>
+        <v>⌛</v>
       </c>
       <c r="G503" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A503,3,4)))</f>
-        <v>⌚</v>
+        <v>⌛</v>
       </c>
       <c r="H503" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I503" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H503,3,4)))</f>
@@ -23231,41 +23235,41 @@
       </c>
     </row>
     <row r="504" spans="1:9" ht="17" customHeight="1">
-      <c r="A504" s="1" t="s">
-        <v>1487</v>
+      <c r="A504" s="22" t="s">
+        <v>2023</v>
       </c>
       <c r="B504" s="5">
         <f>IF(ISNA(VLOOKUP(H504,$A$2:$C$1011,3,1)),C504,VLOOKUP(H504,$A$2:$C$1011,3,1))</f>
-        <v>640</v>
+        <v>567</v>
       </c>
       <c r="C504" s="1">
-        <v>641</v>
-      </c>
-      <c r="D504" s="2" t="s">
-        <v>1488</v>
+        <v>570</v>
+      </c>
+      <c r="D504" s="23" t="s">
+        <v>2024</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>1489</v>
+        <v>1264</v>
       </c>
       <c r="F504" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A504,3,4)))</f>
-        <v>⌛</v>
+        <v>⎌</v>
       </c>
       <c r="G504" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A504,3,4)))</f>
-        <v>⌛</v>
-      </c>
-      <c r="H504" s="17" t="s">
-        <v>1486</v>
+        <v>⎌</v>
+      </c>
+      <c r="H504" s="1" t="s">
+        <v>1229</v>
       </c>
       <c r="I504" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H504,3,4)))</f>
-        <v>⎙</v>
+        <v>←</v>
       </c>
     </row>
     <row r="505" spans="1:9" ht="17" customHeight="1">
       <c r="A505" s="1" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="B505" s="5">
         <f>IF(ISNA(VLOOKUP(H505,$A$2:$C$1011,3,1)),C505,VLOOKUP(H505,$A$2:$C$1011,3,1))</f>
@@ -23275,10 +23279,10 @@
         <v>518</v>
       </c>
       <c r="D505" s="2" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="F505" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A505,3,4)))</f>
@@ -23298,7 +23302,7 @@
     </row>
     <row r="506" spans="1:9" ht="17" customHeight="1">
       <c r="A506" s="1" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="B506" s="5">
         <f>IF(ISNA(VLOOKUP(H506,$A$2:$C$1011,3,1)),C506,VLOOKUP(H506,$A$2:$C$1011,3,1))</f>
@@ -23308,10 +23312,10 @@
         <v>640</v>
       </c>
       <c r="D506" s="2" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="F506" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A506,3,4)))</f>
@@ -23322,7 +23326,7 @@
         <v>⎙</v>
       </c>
       <c r="H506" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I506" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H506,3,4)))</f>
@@ -23331,7 +23335,7 @@
     </row>
     <row r="507" spans="1:9" ht="17" customHeight="1">
       <c r="A507" s="1" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="B507" s="5">
         <f>IF(ISNA(VLOOKUP(H507,$A$2:$C$1011,3,1)),C507,VLOOKUP(H507,$A$2:$C$1011,3,1))</f>
@@ -23341,10 +23345,10 @@
         <v>497</v>
       </c>
       <c r="D507" s="2" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="F507" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A507,3,4)))</f>
@@ -23364,7 +23368,7 @@
     </row>
     <row r="508" spans="1:9" ht="17" customHeight="1">
       <c r="A508" s="1" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="B508" s="5">
         <f>IF(ISNA(VLOOKUP(H508,$A$2:$C$1011,3,1)),C508,VLOOKUP(H508,$A$2:$C$1011,3,1))</f>
@@ -23374,10 +23378,10 @@
         <v>498</v>
       </c>
       <c r="D508" s="2" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="F508" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A508,3,4)))</f>
@@ -23397,7 +23401,7 @@
     </row>
     <row r="509" spans="1:9" ht="17" customHeight="1">
       <c r="A509" s="1" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B509" s="5">
         <f>IF(ISNA(VLOOKUP(H509,$A$2:$C$1011,3,1)),C509,VLOOKUP(H509,$A$2:$C$1011,3,1))</f>
@@ -23407,10 +23411,10 @@
         <v>499</v>
       </c>
       <c r="D509" s="2" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="F509" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A509,3,4)))</f>
@@ -23430,7 +23434,7 @@
     </row>
     <row r="510" spans="1:9" ht="17" customHeight="1">
       <c r="A510" s="1" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="B510" s="5">
         <f>IF(ISNA(VLOOKUP(H510,$A$2:$C$1011,3,1)),C510,VLOOKUP(H510,$A$2:$C$1011,3,1))</f>
@@ -23440,10 +23444,10 @@
         <v>501</v>
       </c>
       <c r="D510" s="2" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="F510" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A510,3,4)))</f>
@@ -23463,7 +23467,7 @@
     </row>
     <row r="511" spans="1:9" ht="17" customHeight="1">
       <c r="A511" s="1" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="B511" s="5">
         <f>IF(ISNA(VLOOKUP(H511,$A$2:$C$1011,3,1)),C511,VLOOKUP(H511,$A$2:$C$1011,3,1))</f>
@@ -23473,10 +23477,10 @@
         <v>502</v>
       </c>
       <c r="D511" s="2" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="F511" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A511,3,4)))</f>
@@ -23496,7 +23500,7 @@
     </row>
     <row r="512" spans="1:9" ht="17" customHeight="1">
       <c r="A512" s="1" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="B512" s="5">
         <f>IF(ISNA(VLOOKUP(H512,$A$2:$C$1011,3,1)),C512,VLOOKUP(H512,$A$2:$C$1011,3,1))</f>
@@ -23506,10 +23510,10 @@
         <v>503</v>
       </c>
       <c r="D512" s="2" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="F512" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A512,3,4)))</f>
@@ -23529,7 +23533,7 @@
     </row>
     <row r="513" spans="1:9" ht="17" customHeight="1">
       <c r="A513" s="1" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="B513" s="5">
         <f>IF(ISNA(VLOOKUP(H513,$A$2:$C$1011,3,1)),C513,VLOOKUP(H513,$A$2:$C$1011,3,1))</f>
@@ -23539,10 +23543,10 @@
         <v>10</v>
       </c>
       <c r="D513" s="2" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="F513" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A513,3,4)))</f>
@@ -23562,7 +23566,7 @@
     </row>
     <row r="514" spans="1:9" ht="17" customHeight="1">
       <c r="A514" s="1" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B514" s="5">
         <f>IF(ISNA(VLOOKUP(H514,$A$2:$C$1011,3,1)),C514,VLOOKUP(H514,$A$2:$C$1011,3,1))</f>
@@ -23572,10 +23576,10 @@
         <v>561</v>
       </c>
       <c r="D514" s="2" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="F514" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A514,3,4)))</f>
@@ -23595,7 +23599,7 @@
     </row>
     <row r="515" spans="1:9" ht="17" customHeight="1">
       <c r="A515" s="1" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="B515" s="5">
         <f>IF(ISNA(VLOOKUP(H515,$A$2:$C$1011,3,1)),C515,VLOOKUP(H515,$A$2:$C$1011,3,1))</f>
@@ -23605,10 +23609,10 @@
         <v>644</v>
       </c>
       <c r="D515" s="2" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="F515" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A515,3,4)))</f>
@@ -23619,7 +23623,7 @@
         <v>⏱</v>
       </c>
       <c r="H515" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I515" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H515,3,4)))</f>
@@ -23628,7 +23632,7 @@
     </row>
     <row r="516" spans="1:9" ht="17" customHeight="1">
       <c r="A516" s="1" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="B516" s="5">
         <f>IF(ISNA(VLOOKUP(H516,$A$2:$C$1011,3,1)),C516,VLOOKUP(H516,$A$2:$C$1011,3,1))</f>
@@ -23638,10 +23642,10 @@
         <v>651</v>
       </c>
       <c r="D516" s="2" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="F516" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A516,3,4)))</f>
@@ -23652,7 +23656,7 @@
         <v>⏻</v>
       </c>
       <c r="H516" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I516" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H516,3,4)))</f>
@@ -23661,7 +23665,7 @@
     </row>
     <row r="517" spans="1:9" ht="17" customHeight="1">
       <c r="A517" s="1" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="B517" s="5">
         <f>IF(ISNA(VLOOKUP(H517,$A$2:$C$1011,3,1)),C517,VLOOKUP(H517,$A$2:$C$1011,3,1))</f>
@@ -23671,10 +23675,10 @@
         <v>678</v>
       </c>
       <c r="D517" s="2" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="F517" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A517,3,4)))</f>
@@ -23685,7 +23689,7 @@
         <v>␡</v>
       </c>
       <c r="H517" s="21" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="I517" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H517,3,4)))</f>
@@ -23694,7 +23698,7 @@
     </row>
     <row r="518" spans="1:9" ht="17" customHeight="1">
       <c r="A518" s="1" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="B518" s="5">
         <f>IF(ISNA(VLOOKUP(H518,$A$2:$C$1011,3,1)),C518,VLOOKUP(H518,$A$2:$C$1011,3,1))</f>
@@ -23704,10 +23708,10 @@
         <v>679</v>
       </c>
       <c r="D518" s="2" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="F518" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A518,3,4)))</f>
@@ -23718,7 +23722,7 @@
         <v>␢</v>
       </c>
       <c r="H518" s="21" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="I518" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H518,3,4)))</f>
@@ -23727,7 +23731,7 @@
     </row>
     <row r="519" spans="1:9" ht="17" customHeight="1">
       <c r="A519" s="1" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="B519" s="5">
         <f>IF(ISNA(VLOOKUP(H519,$A$2:$C$1011,3,1)),C519,VLOOKUP(H519,$A$2:$C$1011,3,1))</f>
@@ -23737,10 +23741,10 @@
         <v>9</v>
       </c>
       <c r="D519" s="2" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="F519" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A519,3,4)))</f>
@@ -23760,7 +23764,7 @@
     </row>
     <row r="520" spans="1:9" ht="17" customHeight="1">
       <c r="A520" s="1" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="B520" s="5">
         <f>IF(ISNA(VLOOKUP(H520,$A$2:$C$1011,3,1)),C520,VLOOKUP(H520,$A$2:$C$1011,3,1))</f>
@@ -23770,10 +23774,10 @@
         <v>680</v>
       </c>
       <c r="D520" s="2" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="F520" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A520,3,4)))</f>
@@ -23784,7 +23788,7 @@
         <v>␥</v>
       </c>
       <c r="H520" s="21" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="I520" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H520,3,4)))</f>
@@ -23793,7 +23797,7 @@
     </row>
     <row r="521" spans="1:9" ht="17" customHeight="1">
       <c r="A521" s="1" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="B521" s="5">
         <f>IF(ISNA(VLOOKUP(H521,$A$2:$C$1011,3,1)),C521,VLOOKUP(H521,$A$2:$C$1011,3,1))</f>
@@ -23803,10 +23807,10 @@
         <v>681</v>
       </c>
       <c r="D521" s="2" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="F521" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A521,3,4)))</f>
@@ -23817,7 +23821,7 @@
         <v>␦</v>
       </c>
       <c r="H521" s="21" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="I521" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H521,3,4)))</f>
@@ -23826,7 +23830,7 @@
     </row>
     <row r="522" spans="1:9" ht="17" customHeight="1">
       <c r="A522" s="1" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="B522" s="5">
         <f>IF(ISNA(VLOOKUP(H522,$A$2:$C$1011,3,1)),C522,VLOOKUP(H522,$A$2:$C$1011,3,1))</f>
@@ -23839,7 +23843,7 @@
         <v>304</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="F522" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A522,3,4)))</f>
@@ -23859,7 +23863,7 @@
     </row>
     <row r="523" spans="1:9" ht="17" customHeight="1">
       <c r="A523" s="1" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="B523" s="5">
         <f>IF(ISNA(VLOOKUP(H523,$A$2:$C$1011,3,1)),C523,VLOOKUP(H523,$A$2:$C$1011,3,1))</f>
@@ -23872,7 +23876,7 @@
         <v>304</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="F523" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A523,3,4)))</f>
@@ -23892,7 +23896,7 @@
     </row>
     <row r="524" spans="1:9" ht="17" customHeight="1">
       <c r="A524" s="1" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B524" s="5">
         <f>IF(ISNA(VLOOKUP(H524,$A$2:$C$1011,3,1)),C524,VLOOKUP(H524,$A$2:$C$1011,3,1))</f>
@@ -23905,7 +23909,7 @@
         <v>304</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="F524" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A524,3,4)))</f>
@@ -23925,7 +23929,7 @@
     </row>
     <row r="525" spans="1:9" ht="17" customHeight="1">
       <c r="A525" s="1" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="B525" s="5">
         <f>IF(ISNA(VLOOKUP(H525,$A$2:$C$1011,3,1)),C525,VLOOKUP(H525,$A$2:$C$1011,3,1))</f>
@@ -23938,7 +23942,7 @@
         <v>304</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="F525" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A525,3,4)))</f>
@@ -23949,7 +23953,7 @@
         <v>␪</v>
       </c>
       <c r="H525" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I525" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H525,3,4)))</f>
@@ -23958,7 +23962,7 @@
     </row>
     <row r="526" spans="1:9" ht="17" customHeight="1">
       <c r="A526" s="1" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="B526" s="5">
         <f>IF(ISNA(VLOOKUP(H526,$A$2:$C$1011,3,1)),C526,VLOOKUP(H526,$A$2:$C$1011,3,1))</f>
@@ -23971,7 +23975,7 @@
         <v>304</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="F526" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A526,3,4)))</f>
@@ -23991,7 +23995,7 @@
     </row>
     <row r="527" spans="1:9" ht="17" customHeight="1">
       <c r="A527" s="1" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="B527" s="5">
         <f>IF(ISNA(VLOOKUP(H527,$A$2:$C$1011,3,1)),C527,VLOOKUP(H527,$A$2:$C$1011,3,1))</f>
@@ -24004,7 +24008,7 @@
         <v>304</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="F527" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A527,3,4)))</f>
@@ -24015,7 +24019,7 @@
         <v>␬</v>
       </c>
       <c r="H527" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I527" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H527,3,4)))</f>
@@ -24024,7 +24028,7 @@
     </row>
     <row r="528" spans="1:9" ht="17" customHeight="1">
       <c r="A528" s="1" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="B528" s="5">
         <f>IF(ISNA(VLOOKUP(H528,$A$2:$C$1011,3,1)),C528,VLOOKUP(H528,$A$2:$C$1011,3,1))</f>
@@ -24037,7 +24041,7 @@
         <v>304</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F528" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A528,3,4)))</f>
@@ -24048,7 +24052,7 @@
         <v>␭</v>
       </c>
       <c r="H528" s="19" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="I528" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H528,3,4)))</f>
@@ -24057,7 +24061,7 @@
     </row>
     <row r="529" spans="1:9" ht="17" customHeight="1">
       <c r="A529" s="1" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="B529" s="5">
         <f>IF(ISNA(VLOOKUP(H529,$A$2:$C$1011,3,1)),C529,VLOOKUP(H529,$A$2:$C$1011,3,1))</f>
@@ -24070,7 +24074,7 @@
         <v>304</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="F529" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A529,3,4)))</f>
@@ -24081,7 +24085,7 @@
         <v>␮</v>
       </c>
       <c r="H529" s="19" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="I529" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H529,3,4)))</f>
@@ -24090,7 +24094,7 @@
     </row>
     <row r="530" spans="1:9" ht="17" customHeight="1">
       <c r="A530" s="1" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="B530" s="5">
         <f>IF(ISNA(VLOOKUP(H530,$A$2:$C$1011,3,1)),C530,VLOOKUP(H530,$A$2:$C$1011,3,1))</f>
@@ -24103,7 +24107,7 @@
         <v>304</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="F530" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A530,3,4)))</f>
@@ -24114,7 +24118,7 @@
         <v>␯</v>
       </c>
       <c r="H530" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I530" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H530,3,4)))</f>
@@ -24123,7 +24127,7 @@
     </row>
     <row r="531" spans="1:9" ht="17" customHeight="1">
       <c r="A531" s="1" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="B531" s="5">
         <f>IF(ISNA(VLOOKUP(H531,$A$2:$C$1011,3,1)),C531,VLOOKUP(H531,$A$2:$C$1011,3,1))</f>
@@ -24136,7 +24140,7 @@
         <v>304</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="F531" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A531,3,4)))</f>
@@ -24147,7 +24151,7 @@
         <v>␰</v>
       </c>
       <c r="H531" s="1" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="I531" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H531,3,4)))</f>
@@ -24156,7 +24160,7 @@
     </row>
     <row r="532" spans="1:9" ht="17" customHeight="1">
       <c r="A532" s="1" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="B532" s="5">
         <f>IF(ISNA(VLOOKUP(H532,$A$2:$C$1011,3,1)),C532,VLOOKUP(H532,$A$2:$C$1011,3,1))</f>
@@ -24169,7 +24173,7 @@
         <v>304</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="F532" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A532,3,4)))</f>
@@ -24180,7 +24184,7 @@
         <v>␱</v>
       </c>
       <c r="H532" s="1" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="I532" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H532,3,4)))</f>
@@ -24189,7 +24193,7 @@
     </row>
     <row r="533" spans="1:9" ht="17" customHeight="1">
       <c r="A533" s="1" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="B533" s="5">
         <f>IF(ISNA(VLOOKUP(H533,$A$2:$C$1011,3,1)),C533,VLOOKUP(H533,$A$2:$C$1011,3,1))</f>
@@ -24202,7 +24206,7 @@
         <v>304</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="F533" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A533,3,4)))</f>
@@ -24213,7 +24217,7 @@
         <v>␲</v>
       </c>
       <c r="H533" s="1" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="I533" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H533,3,4)))</f>
@@ -24222,7 +24226,7 @@
     </row>
     <row r="534" spans="1:9" ht="17" customHeight="1">
       <c r="A534" s="1" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="B534" s="5">
         <f>IF(ISNA(VLOOKUP(H534,$A$2:$C$1011,3,1)),C534,VLOOKUP(H534,$A$2:$C$1011,3,1))</f>
@@ -24235,7 +24239,7 @@
         <v>304</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="F534" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A534,3,4)))</f>
@@ -24246,7 +24250,7 @@
         <v>␳</v>
       </c>
       <c r="H534" s="1" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="I534" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H534,3,4)))</f>
@@ -24255,7 +24259,7 @@
     </row>
     <row r="535" spans="1:9" ht="17" customHeight="1">
       <c r="A535" s="1" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="B535" s="5">
         <f>IF(ISNA(VLOOKUP(H535,$A$2:$C$1011,3,1)),C535,VLOOKUP(H535,$A$2:$C$1011,3,1))</f>
@@ -24268,7 +24272,7 @@
         <v>304</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="F535" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A535,3,4)))</f>
@@ -24279,7 +24283,7 @@
         <v>␴</v>
       </c>
       <c r="H535" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I535" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H535,3,4)))</f>
@@ -24288,7 +24292,7 @@
     </row>
     <row r="536" spans="1:9" ht="17" customHeight="1">
       <c r="A536" s="1" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="B536" s="5">
         <f>IF(ISNA(VLOOKUP(H536,$A$2:$C$1011,3,1)),C536,VLOOKUP(H536,$A$2:$C$1011,3,1))</f>
@@ -24301,7 +24305,7 @@
         <v>304</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="F536" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A536,3,4)))</f>
@@ -24312,7 +24316,7 @@
         <v>␵</v>
       </c>
       <c r="H536" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I536" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H536,3,4)))</f>
@@ -24321,7 +24325,7 @@
     </row>
     <row r="537" spans="1:9" ht="17" customHeight="1">
       <c r="A537" s="1" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="B537" s="5">
         <f>IF(ISNA(VLOOKUP(H537,$A$2:$C$1011,3,1)),C537,VLOOKUP(H537,$A$2:$C$1011,3,1))</f>
@@ -24331,10 +24335,10 @@
         <v>24</v>
       </c>
       <c r="D537" s="2" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="F537" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A537,3,4)))</f>
@@ -24354,7 +24358,7 @@
     </row>
     <row r="538" spans="1:9" ht="17" customHeight="1">
       <c r="A538" s="1" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="B538" s="5">
         <f>IF(ISNA(VLOOKUP(H538,$A$2:$C$1011,3,1)),C538,VLOOKUP(H538,$A$2:$C$1011,3,1))</f>
@@ -24364,10 +24368,10 @@
         <v>28</v>
       </c>
       <c r="D538" s="2" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="F538" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A538,3,4)))</f>
@@ -24387,7 +24391,7 @@
     </row>
     <row r="539" spans="1:9" ht="17" customHeight="1">
       <c r="A539" s="1" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="B539" s="5">
         <f>IF(ISNA(VLOOKUP(H539,$A$2:$C$1011,3,1)),C539,VLOOKUP(H539,$A$2:$C$1011,3,1))</f>
@@ -24397,10 +24401,10 @@
         <v>32</v>
       </c>
       <c r="D539" s="2" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="F539" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A539,3,4)))</f>
@@ -24420,7 +24424,7 @@
     </row>
     <row r="540" spans="1:9" ht="17" customHeight="1">
       <c r="A540" s="1" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="B540" s="5">
         <f>IF(ISNA(VLOOKUP(H540,$A$2:$C$1011,3,1)),C540,VLOOKUP(H540,$A$2:$C$1011,3,1))</f>
@@ -24430,10 +24434,10 @@
         <v>37</v>
       </c>
       <c r="D540" s="2" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F540" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A540,3,4)))</f>
@@ -24453,7 +24457,7 @@
     </row>
     <row r="541" spans="1:9" ht="17" customHeight="1">
       <c r="A541" s="1" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="B541" s="5">
         <f>IF(ISNA(VLOOKUP(H541,$A$2:$C$1011,3,1)),C541,VLOOKUP(H541,$A$2:$C$1011,3,1))</f>
@@ -24463,10 +24467,10 @@
         <v>41</v>
       </c>
       <c r="D541" s="2" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="F541" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A541,3,4)))</f>
@@ -24486,7 +24490,7 @@
     </row>
     <row r="542" spans="1:9" ht="17" customHeight="1">
       <c r="A542" s="1" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="B542" s="5">
         <f>IF(ISNA(VLOOKUP(H542,$A$2:$C$1011,3,1)),C542,VLOOKUP(H542,$A$2:$C$1011,3,1))</f>
@@ -24496,10 +24500,10 @@
         <v>45</v>
       </c>
       <c r="D542" s="2" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="F542" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A542,3,4)))</f>
@@ -24519,7 +24523,7 @@
     </row>
     <row r="543" spans="1:9" ht="17" customHeight="1">
       <c r="A543" s="1" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="B543" s="5">
         <f>IF(ISNA(VLOOKUP(H543,$A$2:$C$1011,3,1)),C543,VLOOKUP(H543,$A$2:$C$1011,3,1))</f>
@@ -24529,10 +24533,10 @@
         <v>49</v>
       </c>
       <c r="D543" s="2" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="F543" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A543,3,4)))</f>
@@ -24552,7 +24556,7 @@
     </row>
     <row r="544" spans="1:9" ht="17" customHeight="1">
       <c r="A544" s="1" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="B544" s="5">
         <f>IF(ISNA(VLOOKUP(H544,$A$2:$C$1011,3,1)),C544,VLOOKUP(H544,$A$2:$C$1011,3,1))</f>
@@ -24562,10 +24566,10 @@
         <v>53</v>
       </c>
       <c r="D544" s="2" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="F544" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A544,3,4)))</f>
@@ -24585,7 +24589,7 @@
     </row>
     <row r="545" spans="1:9" ht="17" customHeight="1">
       <c r="A545" s="1" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="B545" s="5">
         <f>IF(ISNA(VLOOKUP(H545,$A$2:$C$1011,3,1)),C545,VLOOKUP(H545,$A$2:$C$1011,3,1))</f>
@@ -24595,10 +24599,10 @@
         <v>57</v>
       </c>
       <c r="D545" s="2" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="F545" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A545,3,4)))</f>
@@ -24618,7 +24622,7 @@
     </row>
     <row r="546" spans="1:9" ht="17" customHeight="1">
       <c r="A546" s="1" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="B546" s="5">
         <f>IF(ISNA(VLOOKUP(H546,$A$2:$C$1011,3,1)),C546,VLOOKUP(H546,$A$2:$C$1011,3,1))</f>
@@ -24628,10 +24632,10 @@
         <v>59</v>
       </c>
       <c r="D546" s="2" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="F546" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A546,3,4)))</f>
@@ -24642,7 +24646,7 @@
         <v>⑩</v>
       </c>
       <c r="H546" s="1" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="I546" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H546,3,4)))</f>
@@ -24651,7 +24655,7 @@
     </row>
     <row r="547" spans="1:9" ht="17" customHeight="1">
       <c r="A547" s="1" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="B547" s="5">
         <f>IF(ISNA(VLOOKUP(H547,$A$2:$C$1011,3,1)),C547,VLOOKUP(H547,$A$2:$C$1011,3,1))</f>
@@ -24661,10 +24665,10 @@
         <v>60</v>
       </c>
       <c r="D547" s="2" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="F547" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A547,3,4)))</f>
@@ -24675,7 +24679,7 @@
         <v>⑪</v>
       </c>
       <c r="H547" s="1" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="I547" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H547,3,4)))</f>
@@ -24684,7 +24688,7 @@
     </row>
     <row r="548" spans="1:9" ht="17" customHeight="1">
       <c r="A548" s="1" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="B548" s="5">
         <f>IF(ISNA(VLOOKUP(H548,$A$2:$C$1011,3,1)),C548,VLOOKUP(H548,$A$2:$C$1011,3,1))</f>
@@ -24694,10 +24698,10 @@
         <v>61</v>
       </c>
       <c r="D548" s="2" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="F548" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A548,3,4)))</f>
@@ -24708,7 +24712,7 @@
         <v>⑫</v>
       </c>
       <c r="H548" s="1" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="I548" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H548,3,4)))</f>
@@ -24717,7 +24721,7 @@
     </row>
     <row r="549" spans="1:9" ht="17" customHeight="1">
       <c r="A549" s="1" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="B549" s="5">
         <f>IF(ISNA(VLOOKUP(H549,$A$2:$C$1011,3,1)),C549,VLOOKUP(H549,$A$2:$C$1011,3,1))</f>
@@ -24727,10 +24731,10 @@
         <v>62</v>
       </c>
       <c r="D549" s="2" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="F549" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A549,3,4)))</f>
@@ -24741,7 +24745,7 @@
         <v>⑬</v>
       </c>
       <c r="H549" s="1" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I549" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H549,3,4)))</f>
@@ -24750,7 +24754,7 @@
     </row>
     <row r="550" spans="1:9" ht="17" customHeight="1">
       <c r="A550" s="1" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="B550" s="5">
         <f>IF(ISNA(VLOOKUP(H550,$A$2:$C$1011,3,1)),C550,VLOOKUP(H550,$A$2:$C$1011,3,1))</f>
@@ -24760,10 +24764,10 @@
         <v>63</v>
       </c>
       <c r="D550" s="2" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="F550" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A550,3,4)))</f>
@@ -24774,7 +24778,7 @@
         <v>⑭</v>
       </c>
       <c r="H550" s="1" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="I550" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H550,3,4)))</f>
@@ -24783,7 +24787,7 @@
     </row>
     <row r="551" spans="1:9" ht="17" customHeight="1">
       <c r="A551" s="1" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="B551" s="5">
         <f>IF(ISNA(VLOOKUP(H551,$A$2:$C$1011,3,1)),C551,VLOOKUP(H551,$A$2:$C$1011,3,1))</f>
@@ -24793,10 +24797,10 @@
         <v>64</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="F551" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A551,3,4)))</f>
@@ -24807,7 +24811,7 @@
         <v>⑮</v>
       </c>
       <c r="H551" s="1" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="I551" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H551,3,4)))</f>
@@ -24816,7 +24820,7 @@
     </row>
     <row r="552" spans="1:9" ht="17" customHeight="1">
       <c r="A552" s="1" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="B552" s="5">
         <f>IF(ISNA(VLOOKUP(H552,$A$2:$C$1011,3,1)),C552,VLOOKUP(H552,$A$2:$C$1011,3,1))</f>
@@ -24826,10 +24830,10 @@
         <v>65</v>
       </c>
       <c r="D552" s="2" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="F552" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A552,3,4)))</f>
@@ -24840,7 +24844,7 @@
         <v>⑯</v>
       </c>
       <c r="H552" s="1" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="I552" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H552,3,4)))</f>
@@ -24849,7 +24853,7 @@
     </row>
     <row r="553" spans="1:9" ht="17" customHeight="1">
       <c r="A553" s="1" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="B553" s="5">
         <f>IF(ISNA(VLOOKUP(H553,$A$2:$C$1011,3,1)),C553,VLOOKUP(H553,$A$2:$C$1011,3,1))</f>
@@ -24859,10 +24863,10 @@
         <v>58</v>
       </c>
       <c r="D553" s="2" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="F553" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A553,3,4)))</f>
@@ -24873,7 +24877,7 @@
         <v>⑽</v>
       </c>
       <c r="H553" s="1" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="I553" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H553,3,4)))</f>
@@ -24882,7 +24886,7 @@
     </row>
     <row r="554" spans="1:9" ht="17" customHeight="1">
       <c r="A554" s="1" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="B554" s="5">
         <f>IF(ISNA(VLOOKUP(H554,$A$2:$C$1011,3,1)),C554,VLOOKUP(H554,$A$2:$C$1011,3,1))</f>
@@ -24892,10 +24896,10 @@
         <v>69</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="F554" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A554,3,4)))</f>
@@ -24915,7 +24919,7 @@
     </row>
     <row r="555" spans="1:9" ht="17" customHeight="1">
       <c r="A555" s="1" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="B555" s="5">
         <f>IF(ISNA(VLOOKUP(H555,$A$2:$C$1011,3,1)),C555,VLOOKUP(H555,$A$2:$C$1011,3,1))</f>
@@ -24925,10 +24929,10 @@
         <v>95</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="F555" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A555,3,4)))</f>
@@ -24948,7 +24952,7 @@
     </row>
     <row r="556" spans="1:9" ht="17" customHeight="1">
       <c r="A556" s="1" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="B556" s="5">
         <f>IF(ISNA(VLOOKUP(H556,$A$2:$C$1011,3,1)),C556,VLOOKUP(H556,$A$2:$C$1011,3,1))</f>
@@ -24958,10 +24962,10 @@
         <v>101</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="F556" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A556,3,4)))</f>
@@ -24981,7 +24985,7 @@
     </row>
     <row r="557" spans="1:9" ht="17" customHeight="1">
       <c r="A557" s="1" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="B557" s="5">
         <f>IF(ISNA(VLOOKUP(H557,$A$2:$C$1011,3,1)),C557,VLOOKUP(H557,$A$2:$C$1011,3,1))</f>
@@ -24991,10 +24995,10 @@
         <v>116</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="F557" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A557,3,4)))</f>
@@ -25014,7 +25018,7 @@
     </row>
     <row r="558" spans="1:9" ht="17" customHeight="1">
       <c r="A558" s="1" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="B558" s="5">
         <f>IF(ISNA(VLOOKUP(H558,$A$2:$C$1011,3,1)),C558,VLOOKUP(H558,$A$2:$C$1011,3,1))</f>
@@ -25024,10 +25028,10 @@
         <v>129</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="F558" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A558,3,4)))</f>
@@ -25047,7 +25051,7 @@
     </row>
     <row r="559" spans="1:9" ht="17" customHeight="1">
       <c r="A559" s="1" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="B559" s="5">
         <f>IF(ISNA(VLOOKUP(H559,$A$2:$C$1011,3,1)),C559,VLOOKUP(H559,$A$2:$C$1011,3,1))</f>
@@ -25057,7 +25061,7 @@
         <v>155</v>
       </c>
       <c r="D559" s="2" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="E559" s="2" t="s">
         <v>1045</v>
@@ -25080,7 +25084,7 @@
     </row>
     <row r="560" spans="1:9" ht="17" customHeight="1">
       <c r="A560" s="1" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="B560" s="5">
         <f>IF(ISNA(VLOOKUP(H560,$A$2:$C$1011,3,1)),C560,VLOOKUP(H560,$A$2:$C$1011,3,1))</f>
@@ -25090,7 +25094,7 @@
         <v>164</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="E560" s="2" t="s">
         <v>1042</v>
@@ -25113,7 +25117,7 @@
     </row>
     <row r="561" spans="1:9" ht="17" customHeight="1">
       <c r="A561" s="1" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="B561" s="5">
         <f>IF(ISNA(VLOOKUP(H561,$A$2:$C$1011,3,1)),C561,VLOOKUP(H561,$A$2:$C$1011,3,1))</f>
@@ -25123,7 +25127,7 @@
         <v>175</v>
       </c>
       <c r="D561" s="2" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="E561" s="2" t="s">
         <v>807</v>
@@ -25146,7 +25150,7 @@
     </row>
     <row r="562" spans="1:9" ht="17" customHeight="1">
       <c r="A562" s="1" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="B562" s="5">
         <f>IF(ISNA(VLOOKUP(H562,$A$2:$C$1011,3,1)),C562,VLOOKUP(H562,$A$2:$C$1011,3,1))</f>
@@ -25156,10 +25160,10 @@
         <v>184</v>
       </c>
       <c r="D562" s="2" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="F562" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A562,3,4)))</f>
@@ -25179,7 +25183,7 @@
     </row>
     <row r="563" spans="1:9" ht="17" customHeight="1">
       <c r="A563" s="1" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="B563" s="5">
         <f>IF(ISNA(VLOOKUP(H563,$A$2:$C$1011,3,1)),C563,VLOOKUP(H563,$A$2:$C$1011,3,1))</f>
@@ -25189,10 +25193,10 @@
         <v>208</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="F563" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A563,3,4)))</f>
@@ -25212,7 +25216,7 @@
     </row>
     <row r="564" spans="1:9" ht="17" customHeight="1">
       <c r="A564" s="1" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="B564" s="5">
         <f>IF(ISNA(VLOOKUP(H564,$A$2:$C$1011,3,1)),C564,VLOOKUP(H564,$A$2:$C$1011,3,1))</f>
@@ -25222,10 +25226,10 @@
         <v>216</v>
       </c>
       <c r="D564" s="2" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="F564" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A564,3,4)))</f>
@@ -25245,7 +25249,7 @@
     </row>
     <row r="565" spans="1:9" ht="17" customHeight="1">
       <c r="A565" s="1" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="B565" s="5">
         <f>IF(ISNA(VLOOKUP(H565,$A$2:$C$1011,3,1)),C565,VLOOKUP(H565,$A$2:$C$1011,3,1))</f>
@@ -25255,10 +25259,10 @@
         <v>223</v>
       </c>
       <c r="D565" s="2" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="F565" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A565,3,4)))</f>
@@ -25278,7 +25282,7 @@
     </row>
     <row r="566" spans="1:9" ht="17" customHeight="1">
       <c r="A566" s="1" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="B566" s="5">
         <f>IF(ISNA(VLOOKUP(H566,$A$2:$C$1011,3,1)),C566,VLOOKUP(H566,$A$2:$C$1011,3,1))</f>
@@ -25288,10 +25292,10 @@
         <v>236</v>
       </c>
       <c r="D566" s="2" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="F566" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A566,3,4)))</f>
@@ -25311,7 +25315,7 @@
     </row>
     <row r="567" spans="1:9" ht="17" customHeight="1">
       <c r="A567" s="1" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="B567" s="5">
         <f>IF(ISNA(VLOOKUP(H567,$A$2:$C$1011,3,1)),C567,VLOOKUP(H567,$A$2:$C$1011,3,1))</f>
@@ -25321,10 +25325,10 @@
         <v>242</v>
       </c>
       <c r="D567" s="2" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="F567" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A567,3,4)))</f>
@@ -25344,7 +25348,7 @@
     </row>
     <row r="568" spans="1:9" ht="17" customHeight="1">
       <c r="A568" s="1" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="B568" s="5">
         <f>IF(ISNA(VLOOKUP(H568,$A$2:$C$1011,3,1)),C568,VLOOKUP(H568,$A$2:$C$1011,3,1))</f>
@@ -25354,10 +25358,10 @@
         <v>256</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="F568" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A568,3,4)))</f>
@@ -25377,7 +25381,7 @@
     </row>
     <row r="569" spans="1:9" ht="17" customHeight="1">
       <c r="A569" s="1" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="B569" s="5">
         <f>IF(ISNA(VLOOKUP(H569,$A$2:$C$1011,3,1)),C569,VLOOKUP(H569,$A$2:$C$1011,3,1))</f>
@@ -25387,10 +25391,10 @@
         <v>281</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="F569" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A569,3,4)))</f>
@@ -25410,7 +25414,7 @@
     </row>
     <row r="570" spans="1:9" ht="17" customHeight="1">
       <c r="A570" s="1" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="B570" s="5">
         <f>IF(ISNA(VLOOKUP(H570,$A$2:$C$1011,3,1)),C570,VLOOKUP(H570,$A$2:$C$1011,3,1))</f>
@@ -25420,10 +25424,10 @@
         <v>287</v>
       </c>
       <c r="D570" s="2" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="F570" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A570,3,4)))</f>
@@ -25443,7 +25447,7 @@
     </row>
     <row r="571" spans="1:9" ht="17" customHeight="1">
       <c r="A571" s="1" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="B571" s="5">
         <f>IF(ISNA(VLOOKUP(H571,$A$2:$C$1011,3,1)),C571,VLOOKUP(H571,$A$2:$C$1011,3,1))</f>
@@ -25453,7 +25457,7 @@
         <v>294</v>
       </c>
       <c r="D571" s="2" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="E571" s="2" t="s">
         <v>810</v>
@@ -25476,7 +25480,7 @@
     </row>
     <row r="572" spans="1:9" ht="17" customHeight="1">
       <c r="A572" s="1" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="B572" s="5">
         <f>IF(ISNA(VLOOKUP(H572,$A$2:$C$1011,3,1)),C572,VLOOKUP(H572,$A$2:$C$1011,3,1))</f>
@@ -25486,10 +25490,10 @@
         <v>306</v>
       </c>
       <c r="D572" s="2" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="F572" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A572,3,4)))</f>
@@ -25509,7 +25513,7 @@
     </row>
     <row r="573" spans="1:9" ht="17" customHeight="1">
       <c r="A573" s="1" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="B573" s="5">
         <f>IF(ISNA(VLOOKUP(H573,$A$2:$C$1011,3,1)),C573,VLOOKUP(H573,$A$2:$C$1011,3,1))</f>
@@ -25519,10 +25523,10 @@
         <v>321</v>
       </c>
       <c r="D573" s="2" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="F573" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A573,3,4)))</f>
@@ -25542,7 +25546,7 @@
     </row>
     <row r="574" spans="1:9" ht="17" customHeight="1">
       <c r="A574" s="1" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="B574" s="5">
         <f>IF(ISNA(VLOOKUP(H574,$A$2:$C$1011,3,1)),C574,VLOOKUP(H574,$A$2:$C$1011,3,1))</f>
@@ -25552,10 +25556,10 @@
         <v>333</v>
       </c>
       <c r="D574" s="2" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="F574" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A574,3,4)))</f>
@@ -25575,7 +25579,7 @@
     </row>
     <row r="575" spans="1:9" ht="17" customHeight="1">
       <c r="A575" s="1" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="B575" s="5">
         <f>IF(ISNA(VLOOKUP(H575,$A$2:$C$1011,3,1)),C575,VLOOKUP(H575,$A$2:$C$1011,3,1))</f>
@@ -25585,10 +25589,10 @@
         <v>359</v>
       </c>
       <c r="D575" s="2" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="F575" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A575,3,4)))</f>
@@ -25608,7 +25612,7 @@
     </row>
     <row r="576" spans="1:9" ht="17" customHeight="1">
       <c r="A576" s="1" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="B576" s="5">
         <f>IF(ISNA(VLOOKUP(H576,$A$2:$C$1011,3,1)),C576,VLOOKUP(H576,$A$2:$C$1011,3,1))</f>
@@ -25618,10 +25622,10 @@
         <v>367</v>
       </c>
       <c r="D576" s="2" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="F576" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A576,3,4)))</f>
@@ -25641,7 +25645,7 @@
     </row>
     <row r="577" spans="1:11" ht="17" customHeight="1">
       <c r="A577" s="1" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="B577" s="5">
         <f>IF(ISNA(VLOOKUP(H577,$A$2:$C$1011,3,1)),C577,VLOOKUP(H577,$A$2:$C$1011,3,1))</f>
@@ -25651,7 +25655,7 @@
         <v>376</v>
       </c>
       <c r="D577" s="2" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>816</v>
@@ -25674,7 +25678,7 @@
     </row>
     <row r="578" spans="1:11" ht="17" customHeight="1">
       <c r="A578" s="1" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="B578" s="5">
         <f>IF(ISNA(VLOOKUP(H578,$A$2:$C$1011,3,1)),C578,VLOOKUP(H578,$A$2:$C$1011,3,1))</f>
@@ -25684,10 +25688,10 @@
         <v>387</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="F578" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A578,3,4)))</f>
@@ -25707,7 +25711,7 @@
     </row>
     <row r="579" spans="1:11" ht="17" customHeight="1">
       <c r="A579" s="1" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="B579" s="5">
         <f>IF(ISNA(VLOOKUP(H579,$A$2:$C$1011,3,1)),C579,VLOOKUP(H579,$A$2:$C$1011,3,1))</f>
@@ -25717,10 +25721,10 @@
         <v>402</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="F579" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A579,3,4)))</f>
@@ -25740,7 +25744,7 @@
     </row>
     <row r="580" spans="1:11" ht="17" customHeight="1">
       <c r="A580" s="1" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="B580" s="5">
         <f>IF(ISNA(VLOOKUP(H580,$A$2:$C$1011,3,1)),C580,VLOOKUP(H580,$A$2:$C$1011,3,1))</f>
@@ -25750,10 +25754,10 @@
         <v>71</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="F580" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A580,3,4)))</f>
@@ -25773,7 +25777,7 @@
     </row>
     <row r="581" spans="1:11" ht="17" customHeight="1">
       <c r="A581" s="1" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="B581" s="5">
         <f>IF(ISNA(VLOOKUP(H581,$A$2:$C$1011,3,1)),C581,VLOOKUP(H581,$A$2:$C$1011,3,1))</f>
@@ -25783,10 +25787,10 @@
         <v>97</v>
       </c>
       <c r="D581" s="2" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="F581" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A581,3,4)))</f>
@@ -25806,7 +25810,7 @@
     </row>
     <row r="582" spans="1:11" ht="17" customHeight="1">
       <c r="A582" s="1" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="B582" s="5">
         <f>IF(ISNA(VLOOKUP(H582,$A$2:$C$1011,3,1)),C582,VLOOKUP(H582,$A$2:$C$1011,3,1))</f>
@@ -25816,10 +25820,10 @@
         <v>103</v>
       </c>
       <c r="D582" s="2" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="F582" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A582,3,4)))</f>
@@ -25839,7 +25843,7 @@
     </row>
     <row r="583" spans="1:11" ht="17" customHeight="1">
       <c r="A583" s="1" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="B583" s="5">
         <f>IF(ISNA(VLOOKUP(H583,$A$2:$C$1011,3,1)),C583,VLOOKUP(H583,$A$2:$C$1011,3,1))</f>
@@ -25849,10 +25853,10 @@
         <v>118</v>
       </c>
       <c r="D583" s="2" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="F583" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A583,3,4)))</f>
@@ -25872,7 +25876,7 @@
     </row>
     <row r="584" spans="1:11" ht="17" customHeight="1">
       <c r="A584" s="1" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="B584" s="5">
         <f>IF(ISNA(VLOOKUP(H584,$A$2:$C$1011,3,1)),C584,VLOOKUP(H584,$A$2:$C$1011,3,1))</f>
@@ -25882,10 +25886,10 @@
         <v>131</v>
       </c>
       <c r="D584" s="2" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="F584" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A584,3,4)))</f>
@@ -25905,7 +25909,7 @@
     </row>
     <row r="585" spans="1:11" ht="17" customHeight="1">
       <c r="A585" s="1" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="B585" s="5">
         <f>IF(ISNA(VLOOKUP(H585,$A$2:$C$1011,3,1)),C585,VLOOKUP(H585,$A$2:$C$1011,3,1))</f>
@@ -25915,10 +25919,10 @@
         <v>158</v>
       </c>
       <c r="D585" s="2" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="F585" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A585,3,4)))</f>
@@ -25938,7 +25942,7 @@
     </row>
     <row r="586" spans="1:11" ht="17" customHeight="1">
       <c r="A586" s="1" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="B586" s="5">
         <f>IF(ISNA(VLOOKUP(H586,$A$2:$C$1011,3,1)),C586,VLOOKUP(H586,$A$2:$C$1011,3,1))</f>
@@ -25948,10 +25952,10 @@
         <v>167</v>
       </c>
       <c r="D586" s="2" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="F586" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A586,3,4)))</f>
@@ -25971,7 +25975,7 @@
     </row>
     <row r="587" spans="1:11" ht="17" customHeight="1">
       <c r="A587" s="1" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="B587" s="5">
         <f>IF(ISNA(VLOOKUP(H587,$A$2:$C$1011,3,1)),C587,VLOOKUP(H587,$A$2:$C$1011,3,1))</f>
@@ -25981,10 +25985,10 @@
         <v>178</v>
       </c>
       <c r="D587" s="2" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="F587" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A587,3,4)))</f>
@@ -26005,7 +26009,7 @@
     </row>
     <row r="588" spans="1:11" customFormat="1" ht="17" customHeight="1">
       <c r="A588" s="1" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="B588" s="5">
         <f>IF(ISNA(VLOOKUP(H588,$A$2:$C$1011,3,1)),C588,VLOOKUP(H588,$A$2:$C$1011,3,1))</f>
@@ -26015,10 +26019,10 @@
         <v>186</v>
       </c>
       <c r="D588" s="2" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="F588" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A588,3,4)))</f>
@@ -26040,7 +26044,7 @@
     </row>
     <row r="589" spans="1:11" ht="17" customHeight="1">
       <c r="A589" s="1" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="B589" s="5">
         <f>IF(ISNA(VLOOKUP(H589,$A$2:$C$1011,3,1)),C589,VLOOKUP(H589,$A$2:$C$1011,3,1))</f>
@@ -26050,10 +26054,10 @@
         <v>210</v>
       </c>
       <c r="D589" s="2" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="F589" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A589,3,4)))</f>
@@ -26073,7 +26077,7 @@
     </row>
     <row r="590" spans="1:11" ht="17" customHeight="1">
       <c r="A590" s="1" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="B590" s="5">
         <f>IF(ISNA(VLOOKUP(H590,$A$2:$C$1011,3,1)),C590,VLOOKUP(H590,$A$2:$C$1011,3,1))</f>
@@ -26083,10 +26087,10 @@
         <v>218</v>
       </c>
       <c r="D590" s="2" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="F590" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A590,3,4)))</f>
@@ -26106,7 +26110,7 @@
     </row>
     <row r="591" spans="1:11" ht="17" customHeight="1">
       <c r="A591" s="1" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="B591" s="5">
         <f>IF(ISNA(VLOOKUP(H591,$A$2:$C$1011,3,1)),C591,VLOOKUP(H591,$A$2:$C$1011,3,1))</f>
@@ -26116,10 +26120,10 @@
         <v>225</v>
       </c>
       <c r="D591" s="2" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="F591" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A591,3,4)))</f>
@@ -26139,7 +26143,7 @@
     </row>
     <row r="592" spans="1:11" ht="17" customHeight="1">
       <c r="A592" s="1" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="B592" s="5">
         <f>IF(ISNA(VLOOKUP(H592,$A$2:$C$1011,3,1)),C592,VLOOKUP(H592,$A$2:$C$1011,3,1))</f>
@@ -26149,10 +26153,10 @@
         <v>238</v>
       </c>
       <c r="D592" s="2" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="F592" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A592,3,4)))</f>
@@ -26172,7 +26176,7 @@
     </row>
     <row r="593" spans="1:9" ht="17" customHeight="1">
       <c r="A593" s="1" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="B593" s="5">
         <f>IF(ISNA(VLOOKUP(H593,$A$2:$C$1011,3,1)),C593,VLOOKUP(H593,$A$2:$C$1011,3,1))</f>
@@ -26182,10 +26186,10 @@
         <v>244</v>
       </c>
       <c r="D593" s="2" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="F593" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A593,3,4)))</f>
@@ -26205,7 +26209,7 @@
     </row>
     <row r="594" spans="1:9" ht="17" customHeight="1">
       <c r="A594" s="1" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="B594" s="5">
         <f>IF(ISNA(VLOOKUP(H594,$A$2:$C$1011,3,1)),C594,VLOOKUP(H594,$A$2:$C$1011,3,1))</f>
@@ -26215,10 +26219,10 @@
         <v>259</v>
       </c>
       <c r="D594" s="2" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="F594" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A594,3,4)))</f>
@@ -26238,7 +26242,7 @@
     </row>
     <row r="595" spans="1:9" ht="17" customHeight="1">
       <c r="A595" s="1" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="B595" s="5">
         <f>IF(ISNA(VLOOKUP(H595,$A$2:$C$1011,3,1)),C595,VLOOKUP(H595,$A$2:$C$1011,3,1))</f>
@@ -26248,10 +26252,10 @@
         <v>283</v>
       </c>
       <c r="D595" s="2" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="F595" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A595,3,4)))</f>
@@ -26271,7 +26275,7 @@
     </row>
     <row r="596" spans="1:9" ht="17" customHeight="1">
       <c r="A596" s="1" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="B596" s="5">
         <f>IF(ISNA(VLOOKUP(H596,$A$2:$C$1011,3,1)),C596,VLOOKUP(H596,$A$2:$C$1011,3,1))</f>
@@ -26281,10 +26285,10 @@
         <v>289</v>
       </c>
       <c r="D596" s="2" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="F596" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A596,3,4)))</f>
@@ -26304,7 +26308,7 @@
     </row>
     <row r="597" spans="1:9" ht="17" customHeight="1">
       <c r="A597" s="1" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="B597" s="5">
         <f>IF(ISNA(VLOOKUP(H597,$A$2:$C$1011,3,1)),C597,VLOOKUP(H597,$A$2:$C$1011,3,1))</f>
@@ -26314,10 +26318,10 @@
         <v>297</v>
       </c>
       <c r="D597" s="2" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="F597" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A597,3,4)))</f>
@@ -26337,7 +26341,7 @@
     </row>
     <row r="598" spans="1:9" ht="17" customHeight="1">
       <c r="A598" s="1" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B598" s="5">
         <f>IF(ISNA(VLOOKUP(H598,$A$2:$C$1011,3,1)),C598,VLOOKUP(H598,$A$2:$C$1011,3,1))</f>
@@ -26347,10 +26351,10 @@
         <v>308</v>
       </c>
       <c r="D598" s="2" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="F598" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A598,3,4)))</f>
@@ -26370,7 +26374,7 @@
     </row>
     <row r="599" spans="1:9" ht="17" customHeight="1">
       <c r="A599" s="1" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="B599" s="5">
         <f>IF(ISNA(VLOOKUP(H599,$A$2:$C$1011,3,1)),C599,VLOOKUP(H599,$A$2:$C$1011,3,1))</f>
@@ -26380,10 +26384,10 @@
         <v>323</v>
       </c>
       <c r="D599" s="2" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="F599" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A599,3,4)))</f>
@@ -26403,7 +26407,7 @@
     </row>
     <row r="600" spans="1:9" ht="17" customHeight="1">
       <c r="A600" s="1" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="B600" s="5">
         <f>IF(ISNA(VLOOKUP(H600,$A$2:$C$1011,3,1)),C600,VLOOKUP(H600,$A$2:$C$1011,3,1))</f>
@@ -26413,10 +26417,10 @@
         <v>335</v>
       </c>
       <c r="D600" s="2" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="F600" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A600,3,4)))</f>
@@ -26436,7 +26440,7 @@
     </row>
     <row r="601" spans="1:9" ht="17" customHeight="1">
       <c r="A601" s="1" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="B601" s="5">
         <f>IF(ISNA(VLOOKUP(H601,$A$2:$C$1011,3,1)),C601,VLOOKUP(H601,$A$2:$C$1011,3,1))</f>
@@ -26446,10 +26450,10 @@
         <v>361</v>
       </c>
       <c r="D601" s="2" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="F601" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A601,3,4)))</f>
@@ -26469,7 +26473,7 @@
     </row>
     <row r="602" spans="1:9" ht="17" customHeight="1">
       <c r="A602" s="1" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="B602" s="5">
         <f>IF(ISNA(VLOOKUP(H602,$A$2:$C$1011,3,1)),C602,VLOOKUP(H602,$A$2:$C$1011,3,1))</f>
@@ -26479,10 +26483,10 @@
         <v>369</v>
       </c>
       <c r="D602" s="2" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="F602" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A602,3,4)))</f>
@@ -26502,7 +26506,7 @@
     </row>
     <row r="603" spans="1:9" ht="17" customHeight="1">
       <c r="A603" s="1" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="B603" s="5">
         <f>IF(ISNA(VLOOKUP(H603,$A$2:$C$1011,3,1)),C603,VLOOKUP(H603,$A$2:$C$1011,3,1))</f>
@@ -26512,10 +26516,10 @@
         <v>379</v>
       </c>
       <c r="D603" s="2" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="F603" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A603,3,4)))</f>
@@ -26535,7 +26539,7 @@
     </row>
     <row r="604" spans="1:9" ht="17" customHeight="1">
       <c r="A604" s="1" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="B604" s="5">
         <f>IF(ISNA(VLOOKUP(H604,$A$2:$C$1011,3,1)),C604,VLOOKUP(H604,$A$2:$C$1011,3,1))</f>
@@ -26545,10 +26549,10 @@
         <v>389</v>
       </c>
       <c r="D604" s="2" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="F604" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A604,3,4)))</f>
@@ -26568,7 +26572,7 @@
     </row>
     <row r="605" spans="1:9" ht="17" customHeight="1">
       <c r="A605" s="1" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="B605" s="5">
         <f>IF(ISNA(VLOOKUP(H605,$A$2:$C$1011,3,1)),C605,VLOOKUP(H605,$A$2:$C$1011,3,1))</f>
@@ -26578,10 +26582,10 @@
         <v>404</v>
       </c>
       <c r="D605" s="2" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="F605" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A605,3,4)))</f>
@@ -26601,7 +26605,7 @@
     </row>
     <row r="606" spans="1:9" ht="17" customHeight="1">
       <c r="A606" s="1" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="B606" s="5">
         <f>IF(ISNA(VLOOKUP(H606,$A$2:$C$1011,3,1)),C606,VLOOKUP(H606,$A$2:$C$1011,3,1))</f>
@@ -26611,10 +26615,10 @@
         <v>68</v>
       </c>
       <c r="D606" s="2" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="F606" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A606,3,4)))</f>
@@ -26634,7 +26638,7 @@
     </row>
     <row r="607" spans="1:9" ht="17" customHeight="1">
       <c r="A607" s="1" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="B607" s="5">
         <f>IF(ISNA(VLOOKUP(H607,$A$2:$C$1011,3,1)),C607,VLOOKUP(H607,$A$2:$C$1011,3,1))</f>
@@ -26644,10 +26648,10 @@
         <v>94</v>
       </c>
       <c r="D607" s="2" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="F607" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A607,3,4)))</f>
@@ -26667,7 +26671,7 @@
     </row>
     <row r="608" spans="1:9" ht="17" customHeight="1">
       <c r="A608" s="1" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="B608" s="5">
         <f>IF(ISNA(VLOOKUP(H608,$A$2:$C$1011,3,1)),C608,VLOOKUP(H608,$A$2:$C$1011,3,1))</f>
@@ -26677,10 +26681,10 @@
         <v>100</v>
       </c>
       <c r="D608" s="2" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="F608" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A608,3,4)))</f>
@@ -26700,7 +26704,7 @@
     </row>
     <row r="609" spans="1:9" ht="17" customHeight="1">
       <c r="A609" s="1" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="B609" s="5">
         <f>IF(ISNA(VLOOKUP(H609,$A$2:$C$1011,3,1)),C609,VLOOKUP(H609,$A$2:$C$1011,3,1))</f>
@@ -26710,10 +26714,10 @@
         <v>115</v>
       </c>
       <c r="D609" s="2" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="F609" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A609,3,4)))</f>
@@ -26733,7 +26737,7 @@
     </row>
     <row r="610" spans="1:9" ht="17" customHeight="1">
       <c r="A610" s="1" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="B610" s="5">
         <f>IF(ISNA(VLOOKUP(H610,$A$2:$C$1011,3,1)),C610,VLOOKUP(H610,$A$2:$C$1011,3,1))</f>
@@ -26743,10 +26747,10 @@
         <v>128</v>
       </c>
       <c r="D610" s="2" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="F610" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A610,3,4)))</f>
@@ -26766,7 +26770,7 @@
     </row>
     <row r="611" spans="1:9" ht="17" customHeight="1">
       <c r="A611" s="1" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="B611" s="5">
         <f>IF(ISNA(VLOOKUP(H611,$A$2:$C$1011,3,1)),C611,VLOOKUP(H611,$A$2:$C$1011,3,1))</f>
@@ -26776,10 +26780,10 @@
         <v>154</v>
       </c>
       <c r="D611" s="2" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="F611" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A611,3,4)))</f>
@@ -26799,7 +26803,7 @@
     </row>
     <row r="612" spans="1:9" ht="17" customHeight="1">
       <c r="A612" s="1" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="B612" s="5">
         <f>IF(ISNA(VLOOKUP(H612,$A$2:$C$1011,3,1)),C612,VLOOKUP(H612,$A$2:$C$1011,3,1))</f>
@@ -26809,10 +26813,10 @@
         <v>163</v>
       </c>
       <c r="D612" s="2" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="F612" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A612,3,4)))</f>
@@ -26832,7 +26836,7 @@
     </row>
     <row r="613" spans="1:9" ht="17" customHeight="1">
       <c r="A613" s="1" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="B613" s="5">
         <f>IF(ISNA(VLOOKUP(H613,$A$2:$C$1011,3,1)),C613,VLOOKUP(H613,$A$2:$C$1011,3,1))</f>
@@ -26842,10 +26846,10 @@
         <v>174</v>
       </c>
       <c r="D613" s="2" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="F613" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A613,3,4)))</f>
@@ -26865,7 +26869,7 @@
     </row>
     <row r="614" spans="1:9" ht="17" customHeight="1">
       <c r="A614" s="1" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="B614" s="5">
         <f>IF(ISNA(VLOOKUP(H614,$A$2:$C$1011,3,1)),C614,VLOOKUP(H614,$A$2:$C$1011,3,1))</f>
@@ -26875,10 +26879,10 @@
         <v>183</v>
       </c>
       <c r="D614" s="2" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="F614" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A614,3,4)))</f>
@@ -26898,7 +26902,7 @@
     </row>
     <row r="615" spans="1:9" ht="17" customHeight="1">
       <c r="A615" s="1" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="B615" s="5">
         <f>IF(ISNA(VLOOKUP(H615,$A$2:$C$1011,3,1)),C615,VLOOKUP(H615,$A$2:$C$1011,3,1))</f>
@@ -26908,10 +26912,10 @@
         <v>207</v>
       </c>
       <c r="D615" s="2" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="F615" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A615,3,4)))</f>
@@ -26931,7 +26935,7 @@
     </row>
     <row r="616" spans="1:9" ht="17" customHeight="1">
       <c r="A616" s="1" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="B616" s="5">
         <f>IF(ISNA(VLOOKUP(H616,$A$2:$C$1011,3,1)),C616,VLOOKUP(H616,$A$2:$C$1011,3,1))</f>
@@ -26941,10 +26945,10 @@
         <v>215</v>
       </c>
       <c r="D616" s="2" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="F616" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A616,3,4)))</f>
@@ -26964,7 +26968,7 @@
     </row>
     <row r="617" spans="1:9" ht="17" customHeight="1">
       <c r="A617" s="1" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="B617" s="5">
         <f>IF(ISNA(VLOOKUP(H617,$A$2:$C$1011,3,1)),C617,VLOOKUP(H617,$A$2:$C$1011,3,1))</f>
@@ -26974,10 +26978,10 @@
         <v>222</v>
       </c>
       <c r="D617" s="2" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="F617" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A617,3,4)))</f>
@@ -26997,7 +27001,7 @@
     </row>
     <row r="618" spans="1:9" ht="17" customHeight="1">
       <c r="A618" s="1" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="B618" s="5">
         <f>IF(ISNA(VLOOKUP(H618,$A$2:$C$1011,3,1)),C618,VLOOKUP(H618,$A$2:$C$1011,3,1))</f>
@@ -27007,10 +27011,10 @@
         <v>235</v>
       </c>
       <c r="D618" s="2" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="F618" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A618,3,4)))</f>
@@ -27030,7 +27034,7 @@
     </row>
     <row r="619" spans="1:9" ht="17" customHeight="1">
       <c r="A619" s="1" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="B619" s="5">
         <f>IF(ISNA(VLOOKUP(H619,$A$2:$C$1011,3,1)),C619,VLOOKUP(H619,$A$2:$C$1011,3,1))</f>
@@ -27040,10 +27044,10 @@
         <v>241</v>
       </c>
       <c r="D619" s="2" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="F619" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A619,3,4)))</f>
@@ -27063,7 +27067,7 @@
     </row>
     <row r="620" spans="1:9" ht="17" customHeight="1">
       <c r="A620" s="1" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="B620" s="5">
         <f>IF(ISNA(VLOOKUP(H620,$A$2:$C$1011,3,1)),C620,VLOOKUP(H620,$A$2:$C$1011,3,1))</f>
@@ -27073,10 +27077,10 @@
         <v>255</v>
       </c>
       <c r="D620" s="2" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="F620" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A620,3,4)))</f>
@@ -27096,7 +27100,7 @@
     </row>
     <row r="621" spans="1:9" ht="17" customHeight="1">
       <c r="A621" s="1" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="B621" s="5">
         <f>IF(ISNA(VLOOKUP(H621,$A$2:$C$1011,3,1)),C621,VLOOKUP(H621,$A$2:$C$1011,3,1))</f>
@@ -27106,10 +27110,10 @@
         <v>280</v>
       </c>
       <c r="D621" s="2" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="F621" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A621,3,4)))</f>
@@ -27129,7 +27133,7 @@
     </row>
     <row r="622" spans="1:9" ht="17" customHeight="1">
       <c r="A622" s="1" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="B622" s="5">
         <f>IF(ISNA(VLOOKUP(H622,$A$2:$C$1011,3,1)),C622,VLOOKUP(H622,$A$2:$C$1011,3,1))</f>
@@ -27139,10 +27143,10 @@
         <v>286</v>
       </c>
       <c r="D622" s="2" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="F622" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A622,3,4)))</f>
@@ -27162,7 +27166,7 @@
     </row>
     <row r="623" spans="1:9" ht="17" customHeight="1">
       <c r="A623" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="B623" s="5">
         <f>IF(ISNA(VLOOKUP(H623,$A$2:$C$1011,3,1)),C623,VLOOKUP(H623,$A$2:$C$1011,3,1))</f>
@@ -27172,10 +27176,10 @@
         <v>293</v>
       </c>
       <c r="D623" s="2" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="F623" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A623,3,4)))</f>
@@ -27195,7 +27199,7 @@
     </row>
     <row r="624" spans="1:9" ht="17" customHeight="1">
       <c r="A624" s="1" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="B624" s="5">
         <f>IF(ISNA(VLOOKUP(H624,$A$2:$C$1011,3,1)),C624,VLOOKUP(H624,$A$2:$C$1011,3,1))</f>
@@ -27205,10 +27209,10 @@
         <v>305</v>
       </c>
       <c r="D624" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="F624" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A624,3,4)))</f>
@@ -27228,7 +27232,7 @@
     </row>
     <row r="625" spans="1:9" ht="17" customHeight="1">
       <c r="A625" s="1" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="B625" s="5">
         <f>IF(ISNA(VLOOKUP(H625,$A$2:$C$1011,3,1)),C625,VLOOKUP(H625,$A$2:$C$1011,3,1))</f>
@@ -27238,7 +27242,7 @@
         <v>318</v>
       </c>
       <c r="D625" s="2" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="E625" s="2" t="s">
         <v>1039</v>
@@ -27261,7 +27265,7 @@
     </row>
     <row r="626" spans="1:9" ht="17" customHeight="1">
       <c r="A626" s="1" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="B626" s="5">
         <f>IF(ISNA(VLOOKUP(H626,$A$2:$C$1011,3,1)),C626,VLOOKUP(H626,$A$2:$C$1011,3,1))</f>
@@ -27271,10 +27275,10 @@
         <v>332</v>
       </c>
       <c r="D626" s="2" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="F626" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A626,3,4)))</f>
@@ -27294,7 +27298,7 @@
     </row>
     <row r="627" spans="1:9" ht="17" customHeight="1">
       <c r="A627" s="1" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="B627" s="5">
         <f>IF(ISNA(VLOOKUP(H627,$A$2:$C$1011,3,1)),C627,VLOOKUP(H627,$A$2:$C$1011,3,1))</f>
@@ -27304,10 +27308,10 @@
         <v>358</v>
       </c>
       <c r="D627" s="2" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="F627" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A627,3,4)))</f>
@@ -27327,7 +27331,7 @@
     </row>
     <row r="628" spans="1:9" ht="17" customHeight="1">
       <c r="A628" s="1" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="B628" s="5">
         <f>IF(ISNA(VLOOKUP(H628,$A$2:$C$1011,3,1)),C628,VLOOKUP(H628,$A$2:$C$1011,3,1))</f>
@@ -27337,10 +27341,10 @@
         <v>366</v>
       </c>
       <c r="D628" s="2" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="F628" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A628,3,4)))</f>
@@ -27360,7 +27364,7 @@
     </row>
     <row r="629" spans="1:9" ht="17" customHeight="1">
       <c r="A629" s="1" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="B629" s="5">
         <f>IF(ISNA(VLOOKUP(H629,$A$2:$C$1011,3,1)),C629,VLOOKUP(H629,$A$2:$C$1011,3,1))</f>
@@ -27370,10 +27374,10 @@
         <v>375</v>
       </c>
       <c r="D629" s="2" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="E629" s="2" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="F629" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A629,3,4)))</f>
@@ -27393,7 +27397,7 @@
     </row>
     <row r="630" spans="1:9" ht="17" customHeight="1">
       <c r="A630" s="1" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="B630" s="5">
         <f>IF(ISNA(VLOOKUP(H630,$A$2:$C$1011,3,1)),C630,VLOOKUP(H630,$A$2:$C$1011,3,1))</f>
@@ -27403,10 +27407,10 @@
         <v>386</v>
       </c>
       <c r="D630" s="2" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="F630" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A630,3,4)))</f>
@@ -27426,7 +27430,7 @@
     </row>
     <row r="631" spans="1:9" ht="17" customHeight="1">
       <c r="A631" s="1" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="B631" s="5">
         <f>IF(ISNA(VLOOKUP(H631,$A$2:$C$1011,3,1)),C631,VLOOKUP(H631,$A$2:$C$1011,3,1))</f>
@@ -27436,10 +27440,10 @@
         <v>401</v>
       </c>
       <c r="D631" s="2" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="F631" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A631,3,4)))</f>
@@ -27459,7 +27463,7 @@
     </row>
     <row r="632" spans="1:9" ht="17" customHeight="1">
       <c r="A632" s="1" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="B632" s="5">
         <f>IF(ISNA(VLOOKUP(H632,$A$2:$C$1011,3,1)),C632,VLOOKUP(H632,$A$2:$C$1011,3,1))</f>
@@ -27469,10 +27473,10 @@
         <v>70</v>
       </c>
       <c r="D632" s="2" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="F632" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A632,3,4)))</f>
@@ -27492,7 +27496,7 @@
     </row>
     <row r="633" spans="1:9" ht="17" customHeight="1">
       <c r="A633" s="1" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="B633" s="5">
         <f>IF(ISNA(VLOOKUP(H633,$A$2:$C$1011,3,1)),C633,VLOOKUP(H633,$A$2:$C$1011,3,1))</f>
@@ -27502,10 +27506,10 @@
         <v>96</v>
       </c>
       <c r="D633" s="2" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="F633" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A633,3,4)))</f>
@@ -27525,7 +27529,7 @@
     </row>
     <row r="634" spans="1:9" ht="17" customHeight="1">
       <c r="A634" s="1" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="B634" s="5">
         <f>IF(ISNA(VLOOKUP(H634,$A$2:$C$1011,3,1)),C634,VLOOKUP(H634,$A$2:$C$1011,3,1))</f>
@@ -27535,10 +27539,10 @@
         <v>102</v>
       </c>
       <c r="D634" s="2" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="F634" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A634,3,4)))</f>
@@ -27558,7 +27562,7 @@
     </row>
     <row r="635" spans="1:9" ht="17" customHeight="1">
       <c r="A635" s="1" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="B635" s="5">
         <f>IF(ISNA(VLOOKUP(H635,$A$2:$C$1011,3,1)),C635,VLOOKUP(H635,$A$2:$C$1011,3,1))</f>
@@ -27568,10 +27572,10 @@
         <v>117</v>
       </c>
       <c r="D635" s="2" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="F635" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A635,3,4)))</f>
@@ -27591,7 +27595,7 @@
     </row>
     <row r="636" spans="1:9" ht="17" customHeight="1">
       <c r="A636" s="1" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="B636" s="5">
         <f>IF(ISNA(VLOOKUP(H636,$A$2:$C$1011,3,1)),C636,VLOOKUP(H636,$A$2:$C$1011,3,1))</f>
@@ -27601,7 +27605,7 @@
         <v>130</v>
       </c>
       <c r="D636" s="2" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="E636" s="2" t="s">
         <v>1103</v>
@@ -27624,7 +27628,7 @@
     </row>
     <row r="637" spans="1:9" ht="17" customHeight="1">
       <c r="A637" s="1" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="B637" s="5">
         <f>IF(ISNA(VLOOKUP(H637,$A$2:$C$1011,3,1)),C637,VLOOKUP(H637,$A$2:$C$1011,3,1))</f>
@@ -27634,10 +27638,10 @@
         <v>157</v>
       </c>
       <c r="D637" s="2" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="E637" s="2" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="F637" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A637,3,4)))</f>
@@ -27657,7 +27661,7 @@
     </row>
     <row r="638" spans="1:9" ht="17" customHeight="1">
       <c r="A638" s="1" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="B638" s="5">
         <f>IF(ISNA(VLOOKUP(H638,$A$2:$C$1011,3,1)),C638,VLOOKUP(H638,$A$2:$C$1011,3,1))</f>
@@ -27667,10 +27671,10 @@
         <v>166</v>
       </c>
       <c r="D638" s="2" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="E638" s="2" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="F638" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A638,3,4)))</f>
@@ -27690,7 +27694,7 @@
     </row>
     <row r="639" spans="1:9" ht="17" customHeight="1">
       <c r="A639" s="1" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="B639" s="5">
         <f>IF(ISNA(VLOOKUP(H639,$A$2:$C$1011,3,1)),C639,VLOOKUP(H639,$A$2:$C$1011,3,1))</f>
@@ -27700,10 +27704,10 @@
         <v>177</v>
       </c>
       <c r="D639" s="2" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="F639" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A639,3,4)))</f>
@@ -27723,7 +27727,7 @@
     </row>
     <row r="640" spans="1:9" ht="17" customHeight="1">
       <c r="A640" s="1" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="B640" s="5">
         <f>IF(ISNA(VLOOKUP(H640,$A$2:$C$1011,3,1)),C640,VLOOKUP(H640,$A$2:$C$1011,3,1))</f>
@@ -27733,10 +27737,10 @@
         <v>185</v>
       </c>
       <c r="D640" s="2" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="E640" s="2" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="F640" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A640,3,4)))</f>
@@ -27756,7 +27760,7 @@
     </row>
     <row r="641" spans="1:9" ht="17" customHeight="1">
       <c r="A641" s="1" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="B641" s="5">
         <f>IF(ISNA(VLOOKUP(H641,$A$2:$C$1011,3,1)),C641,VLOOKUP(H641,$A$2:$C$1011,3,1))</f>
@@ -27766,10 +27770,10 @@
         <v>209</v>
       </c>
       <c r="D641" s="2" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="E641" s="2" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="F641" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A641,3,4)))</f>
@@ -27789,7 +27793,7 @@
     </row>
     <row r="642" spans="1:9" ht="17" customHeight="1">
       <c r="A642" s="1" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="B642" s="5">
         <f>IF(ISNA(VLOOKUP(H642,$A$2:$C$1011,3,1)),C642,VLOOKUP(H642,$A$2:$C$1011,3,1))</f>
@@ -27799,10 +27803,10 @@
         <v>217</v>
       </c>
       <c r="D642" s="2" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="F642" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A642,3,4)))</f>
@@ -27822,7 +27826,7 @@
     </row>
     <row r="643" spans="1:9" ht="17" customHeight="1">
       <c r="A643" s="1" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="B643" s="5">
         <f>IF(ISNA(VLOOKUP(H643,$A$2:$C$1011,3,1)),C643,VLOOKUP(H643,$A$2:$C$1011,3,1))</f>
@@ -27832,10 +27836,10 @@
         <v>224</v>
       </c>
       <c r="D643" s="2" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="E643" s="2" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="F643" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A643,3,4)))</f>
@@ -27855,7 +27859,7 @@
     </row>
     <row r="644" spans="1:9" ht="17" customHeight="1">
       <c r="A644" s="1" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="B644" s="5">
         <f>IF(ISNA(VLOOKUP(H644,$A$2:$C$1011,3,1)),C644,VLOOKUP(H644,$A$2:$C$1011,3,1))</f>
@@ -27865,10 +27869,10 @@
         <v>237</v>
       </c>
       <c r="D644" s="2" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="E644" s="2" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="F644" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A644,3,4)))</f>
@@ -27888,7 +27892,7 @@
     </row>
     <row r="645" spans="1:9" ht="17" customHeight="1">
       <c r="A645" s="1" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="B645" s="5">
         <f>IF(ISNA(VLOOKUP(H645,$A$2:$C$1011,3,1)),C645,VLOOKUP(H645,$A$2:$C$1011,3,1))</f>
@@ -27898,10 +27902,10 @@
         <v>243</v>
       </c>
       <c r="D645" s="2" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="E645" s="2" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="F645" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A645,3,4)))</f>
@@ -27921,7 +27925,7 @@
     </row>
     <row r="646" spans="1:9" ht="17" customHeight="1">
       <c r="A646" s="1" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="B646" s="5">
         <f>IF(ISNA(VLOOKUP(H646,$A$2:$C$1011,3,1)),C646,VLOOKUP(H646,$A$2:$C$1011,3,1))</f>
@@ -27931,10 +27935,10 @@
         <v>258</v>
       </c>
       <c r="D646" s="2" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="F646" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A646,3,4)))</f>
@@ -27954,7 +27958,7 @@
     </row>
     <row r="647" spans="1:9" ht="17" customHeight="1">
       <c r="A647" s="1" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="B647" s="5">
         <f>IF(ISNA(VLOOKUP(H647,$A$2:$C$1011,3,1)),C647,VLOOKUP(H647,$A$2:$C$1011,3,1))</f>
@@ -27964,10 +27968,10 @@
         <v>282</v>
       </c>
       <c r="D647" s="2" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="F647" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A647,3,4)))</f>
@@ -27987,7 +27991,7 @@
     </row>
     <row r="648" spans="1:9" ht="17" customHeight="1">
       <c r="A648" s="1" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="B648" s="5">
         <f>IF(ISNA(VLOOKUP(H648,$A$2:$C$1011,3,1)),C648,VLOOKUP(H648,$A$2:$C$1011,3,1))</f>
@@ -27997,10 +28001,10 @@
         <v>288</v>
       </c>
       <c r="D648" s="2" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="F648" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A648,3,4)))</f>
@@ -28020,7 +28024,7 @@
     </row>
     <row r="649" spans="1:9" ht="17" customHeight="1">
       <c r="A649" s="1" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="B649" s="5">
         <f>IF(ISNA(VLOOKUP(H649,$A$2:$C$1011,3,1)),C649,VLOOKUP(H649,$A$2:$C$1011,3,1))</f>
@@ -28030,10 +28034,10 @@
         <v>296</v>
       </c>
       <c r="D649" s="2" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="E649" s="2" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="F649" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A649,3,4)))</f>
@@ -28053,7 +28057,7 @@
     </row>
     <row r="650" spans="1:9" ht="17" customHeight="1">
       <c r="A650" s="1" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="B650" s="5">
         <f>IF(ISNA(VLOOKUP(H650,$A$2:$C$1011,3,1)),C650,VLOOKUP(H650,$A$2:$C$1011,3,1))</f>
@@ -28063,10 +28067,10 @@
         <v>307</v>
       </c>
       <c r="D650" s="2" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="E650" s="2" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="F650" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A650,3,4)))</f>
@@ -28086,7 +28090,7 @@
     </row>
     <row r="651" spans="1:9" ht="17" customHeight="1">
       <c r="A651" s="1" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="B651" s="5">
         <f>IF(ISNA(VLOOKUP(H651,$A$2:$C$1011,3,1)),C651,VLOOKUP(H651,$A$2:$C$1011,3,1))</f>
@@ -28096,10 +28100,10 @@
         <v>322</v>
       </c>
       <c r="D651" s="2" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="F651" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A651,3,4)))</f>
@@ -28119,7 +28123,7 @@
     </row>
     <row r="652" spans="1:9" ht="17" customHeight="1">
       <c r="A652" s="1" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="B652" s="5">
         <f>IF(ISNA(VLOOKUP(H652,$A$2:$C$1011,3,1)),C652,VLOOKUP(H652,$A$2:$C$1011,3,1))</f>
@@ -28129,10 +28133,10 @@
         <v>334</v>
       </c>
       <c r="D652" s="2" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="E652" s="2" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="F652" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A652,3,4)))</f>
@@ -28152,7 +28156,7 @@
     </row>
     <row r="653" spans="1:9" ht="17" customHeight="1">
       <c r="A653" s="1" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="B653" s="5">
         <f>IF(ISNA(VLOOKUP(H653,$A$2:$C$1011,3,1)),C653,VLOOKUP(H653,$A$2:$C$1011,3,1))</f>
@@ -28162,10 +28166,10 @@
         <v>360</v>
       </c>
       <c r="D653" s="2" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="E653" s="2" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="F653" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A653,3,4)))</f>
@@ -28185,7 +28189,7 @@
     </row>
     <row r="654" spans="1:9" ht="17" customHeight="1">
       <c r="A654" s="1" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="B654" s="5">
         <f>IF(ISNA(VLOOKUP(H654,$A$2:$C$1011,3,1)),C654,VLOOKUP(H654,$A$2:$C$1011,3,1))</f>
@@ -28195,10 +28199,10 @@
         <v>368</v>
       </c>
       <c r="D654" s="2" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="E654" s="2" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F654" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A654,3,4)))</f>
@@ -28218,7 +28222,7 @@
     </row>
     <row r="655" spans="1:9" ht="17" customHeight="1">
       <c r="A655" s="1" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="B655" s="5">
         <f>IF(ISNA(VLOOKUP(H655,$A$2:$C$1011,3,1)),C655,VLOOKUP(H655,$A$2:$C$1011,3,1))</f>
@@ -28228,10 +28232,10 @@
         <v>378</v>
       </c>
       <c r="D655" s="2" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="F655" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A655,3,4)))</f>
@@ -28251,7 +28255,7 @@
     </row>
     <row r="656" spans="1:9" ht="17" customHeight="1">
       <c r="A656" s="1" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="B656" s="5">
         <f>IF(ISNA(VLOOKUP(H656,$A$2:$C$1011,3,1)),C656,VLOOKUP(H656,$A$2:$C$1011,3,1))</f>
@@ -28261,10 +28265,10 @@
         <v>388</v>
       </c>
       <c r="D656" s="2" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="F656" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A656,3,4)))</f>
@@ -28284,7 +28288,7 @@
     </row>
     <row r="657" spans="1:9" ht="17" customHeight="1">
       <c r="A657" s="1" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="B657" s="5">
         <f>IF(ISNA(VLOOKUP(H657,$A$2:$C$1011,3,1)),C657,VLOOKUP(H657,$A$2:$C$1011,3,1))</f>
@@ -28294,10 +28298,10 @@
         <v>403</v>
       </c>
       <c r="D657" s="2" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="F657" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A657,3,4)))</f>
@@ -28317,7 +28321,7 @@
     </row>
     <row r="658" spans="1:9" ht="17" customHeight="1">
       <c r="A658" s="1" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B658" s="5">
         <f>IF(ISNA(VLOOKUP(H658,$A$2:$C$1011,3,1)),C658,VLOOKUP(H658,$A$2:$C$1011,3,1))</f>
@@ -28327,10 +28331,10 @@
         <v>17</v>
       </c>
       <c r="D658" s="2" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="F658" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A658,3,4)))</f>
@@ -28350,7 +28354,7 @@
     </row>
     <row r="659" spans="1:9" ht="17" customHeight="1">
       <c r="A659" s="1" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="B659" s="5">
         <f>IF(ISNA(VLOOKUP(H659,$A$2:$C$1011,3,1)),C659,VLOOKUP(H659,$A$2:$C$1011,3,1))</f>
@@ -28360,10 +28364,10 @@
         <v>652</v>
       </c>
       <c r="D659" s="2" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="F659" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A659,3,4)))</f>
@@ -28374,7 +28378,7 @@
         <v>▢</v>
       </c>
       <c r="H659" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I659" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H659,3,4)))</f>
@@ -28383,7 +28387,7 @@
     </row>
     <row r="660" spans="1:9" ht="17" customHeight="1">
       <c r="A660" s="1" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="B660" s="5">
         <f>IF(ISNA(VLOOKUP(H660,$A$2:$C$1011,3,1)),C660,VLOOKUP(H660,$A$2:$C$1011,3,1))</f>
@@ -28393,10 +28397,10 @@
         <v>653</v>
       </c>
       <c r="D660" s="2" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="F660" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A660,3,4)))</f>
@@ -28407,7 +28411,7 @@
         <v>▦</v>
       </c>
       <c r="H660" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I660" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H660,3,4)))</f>
@@ -28416,7 +28420,7 @@
     </row>
     <row r="661" spans="1:9" ht="17" customHeight="1">
       <c r="A661" s="1" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B661" s="5">
         <f>IF(ISNA(VLOOKUP(H661,$A$2:$C$1011,3,1)),C661,VLOOKUP(H661,$A$2:$C$1011,3,1))</f>
@@ -28426,10 +28430,10 @@
         <v>658</v>
       </c>
       <c r="D661" s="2" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="F661" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A661,3,4)))</f>
@@ -28440,7 +28444,7 @@
         <v>◇</v>
       </c>
       <c r="H661" s="18" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="I661" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H661,3,4)))</f>
@@ -28449,7 +28453,7 @@
     </row>
     <row r="662" spans="1:9" ht="17" customHeight="1">
       <c r="A662" s="1" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B662" s="5">
         <f>IF(ISNA(VLOOKUP(H662,$A$2:$C$1011,3,1)),C662,VLOOKUP(H662,$A$2:$C$1011,3,1))</f>
@@ -28459,10 +28463,10 @@
         <v>659</v>
       </c>
       <c r="D662" s="2" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F662" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A662,3,4)))</f>
@@ -28473,7 +28477,7 @@
         <v>◈</v>
       </c>
       <c r="H662" s="18" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="I662" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H662,3,4)))</f>
@@ -28482,7 +28486,7 @@
     </row>
     <row r="663" spans="1:9" ht="17" customHeight="1">
       <c r="A663" s="1" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B663" s="5">
         <f>IF(ISNA(VLOOKUP(H663,$A$2:$C$1011,3,1)),C663,VLOOKUP(H663,$A$2:$C$1011,3,1))</f>
@@ -28492,10 +28496,10 @@
         <v>656</v>
       </c>
       <c r="D663" s="2" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="E663" s="2" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="F663" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A663,3,4)))</f>
@@ -28506,7 +28510,7 @@
         <v>◯</v>
       </c>
       <c r="H663" s="18" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="I663" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H663,3,4)))</f>
@@ -28515,7 +28519,7 @@
     </row>
     <row r="664" spans="1:9" ht="17" customHeight="1">
       <c r="A664" s="1" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B664" s="5">
         <f>IF(ISNA(VLOOKUP(H664,$A$2:$C$1011,3,1)),C664,VLOOKUP(H664,$A$2:$C$1011,3,1))</f>
@@ -28525,10 +28529,10 @@
         <v>654</v>
       </c>
       <c r="D664" s="2" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="F664" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A664,3,4)))</f>
@@ -28539,7 +28543,7 @@
         <v>☐</v>
       </c>
       <c r="H664" s="18" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="I664" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H664,3,4)))</f>
@@ -28548,7 +28552,7 @@
     </row>
     <row r="665" spans="1:9" ht="17" customHeight="1">
       <c r="A665" s="1" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B665" s="5">
         <f>IF(ISNA(VLOOKUP(H665,$A$2:$C$1011,3,1)),C665,VLOOKUP(H665,$A$2:$C$1011,3,1))</f>
@@ -28558,10 +28562,10 @@
         <v>655</v>
       </c>
       <c r="D665" s="2" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="F665" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A665,3,4)))</f>
@@ -28572,7 +28576,7 @@
         <v>☒</v>
       </c>
       <c r="H665" s="18" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="I665" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H665,3,4)))</f>
@@ -28581,7 +28585,7 @@
     </row>
     <row r="666" spans="1:9" ht="17" customHeight="1">
       <c r="A666" s="1" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="B666" s="5">
         <f>IF(ISNA(VLOOKUP(H666,$A$2:$C$1011,3,1)),C666,VLOOKUP(H666,$A$2:$C$1011,3,1))</f>
@@ -28591,10 +28595,10 @@
         <v>650</v>
       </c>
       <c r="D666" s="2" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="F666" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A666,3,4)))</f>
@@ -28605,7 +28609,7 @@
         <v>♺</v>
       </c>
       <c r="H666" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I666" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H666,3,4)))</f>
@@ -28614,7 +28618,7 @@
     </row>
     <row r="667" spans="1:9" ht="17" customHeight="1">
       <c r="A667" s="1" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="B667" s="5">
         <f>IF(ISNA(VLOOKUP(H667,$A$2:$C$1011,3,1)),C667,VLOOKUP(H667,$A$2:$C$1011,3,1))</f>
@@ -28624,10 +28628,10 @@
         <v>112</v>
       </c>
       <c r="D667" s="2" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="F667" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A667,3,4)))</f>
@@ -28647,7 +28651,7 @@
     </row>
     <row r="668" spans="1:9" ht="17" customHeight="1">
       <c r="A668" s="1" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="B668" s="5">
         <f>IF(ISNA(VLOOKUP(H668,$A$2:$C$1011,3,1)),C668,VLOOKUP(H668,$A$2:$C$1011,3,1))</f>
@@ -28657,10 +28661,10 @@
         <v>252</v>
       </c>
       <c r="D668" s="2" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="F668" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A668,3,4)))</f>
@@ -28680,7 +28684,7 @@
     </row>
     <row r="669" spans="1:9" ht="17" customHeight="1">
       <c r="A669" s="1" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="B669" s="5">
         <f>IF(ISNA(VLOOKUP(H669,$A$2:$C$1011,3,1)),C669,VLOOKUP(H669,$A$2:$C$1011,3,1))</f>
@@ -28690,10 +28694,10 @@
         <v>682</v>
       </c>
       <c r="D669" s="2" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="F669" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A669,3,4)))</f>
@@ -28704,7 +28708,7 @@
         <v>✓</v>
       </c>
       <c r="H669" s="1" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="I669" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H669,3,4)))</f>
@@ -28713,7 +28717,7 @@
     </row>
     <row r="670" spans="1:9" ht="17" customHeight="1">
       <c r="A670" s="1" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="B670" s="5">
         <f>IF(ISNA(VLOOKUP(H670,$A$2:$C$1011,3,1)),C670,VLOOKUP(H670,$A$2:$C$1011,3,1))</f>
@@ -28723,10 +28727,10 @@
         <v>530</v>
       </c>
       <c r="D670" s="2" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="F670" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A670,3,4)))</f>
@@ -28746,7 +28750,7 @@
     </row>
     <row r="671" spans="1:9" ht="17" customHeight="1">
       <c r="A671" s="1" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="B671" s="5">
         <f>IF(ISNA(VLOOKUP(H671,$A$2:$C$1011,3,1)),C671,VLOOKUP(H671,$A$2:$C$1011,3,1))</f>
@@ -28756,10 +28760,10 @@
         <v>534</v>
       </c>
       <c r="D671" s="2" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="F671" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A671,3,4)))</f>
@@ -28779,7 +28783,7 @@
     </row>
     <row r="672" spans="1:9" ht="17" customHeight="1">
       <c r="A672" s="1" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B672" s="5">
         <f>IF(ISNA(VLOOKUP(H672,$A$2:$C$1011,3,1)),C672,VLOOKUP(H672,$A$2:$C$1011,3,1))</f>
@@ -28789,10 +28793,10 @@
         <v>657</v>
       </c>
       <c r="D672" s="2" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F672" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A672,3,4)))</f>
@@ -28803,7 +28807,7 @@
         <v>⦿</v>
       </c>
       <c r="H672" s="18" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="I672" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H672,3,4)))</f>
@@ -28812,7 +28816,7 @@
     </row>
     <row r="673" spans="1:11" ht="17" customHeight="1">
       <c r="A673" s="1" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="B673" s="5">
         <f>IF(ISNA(VLOOKUP(H673,$A$2:$C$1011,3,1)),C673,VLOOKUP(H673,$A$2:$C$1011,3,1))</f>
@@ -28822,10 +28826,10 @@
         <v>642</v>
       </c>
       <c r="D673" s="2" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="F673" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A673,3,4)))</f>
@@ -28836,7 +28840,7 @@
         <v>⧖</v>
       </c>
       <c r="H673" s="17" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="I673" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H673,3,4)))</f>
@@ -28845,7 +28849,7 @@
     </row>
     <row r="674" spans="1:11" ht="17" customHeight="1">
       <c r="A674" s="1" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="B674" s="5">
         <f>IF(ISNA(VLOOKUP(H674,$A$2:$C$1011,3,1)),C674,VLOOKUP(H674,$A$2:$C$1011,3,1))</f>
@@ -28855,10 +28859,10 @@
         <v>398</v>
       </c>
       <c r="D674" s="2" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="F674" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A674,3,4)))</f>
@@ -28878,7 +28882,7 @@
     </row>
     <row r="675" spans="1:11" ht="17" customHeight="1">
       <c r="A675" s="1" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B675" s="5">
         <f>IF(ISNA(VLOOKUP(H675,$A$2:$C$1011,3,1)),C675,VLOOKUP(H675,$A$2:$C$1011,3,1))</f>
@@ -28888,10 +28892,10 @@
         <v>160</v>
       </c>
       <c r="D675" s="2" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="E675" s="2" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="F675" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A675,3,4)))</f>
@@ -28911,7 +28915,7 @@
     </row>
     <row r="676" spans="1:11" ht="17" customHeight="1">
       <c r="A676" s="1" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B676" s="5">
         <f>IF(ISNA(VLOOKUP(H676,$A$2:$C$1011,3,1)),C676,VLOOKUP(H676,$A$2:$C$1011,3,1))</f>
@@ -28921,10 +28925,10 @@
         <v>569</v>
       </c>
       <c r="D676" s="2" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="F676" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A676,3,4)))</f>
@@ -28944,7 +28948,7 @@
     </row>
     <row r="677" spans="1:11" ht="17" customHeight="1">
       <c r="A677" s="1" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="B677" s="5">
         <f>IF(ISNA(VLOOKUP(H677,$A$2:$C$1011,3,1)),C677,VLOOKUP(H677,$A$2:$C$1011,3,1))</f>
@@ -28954,10 +28958,10 @@
         <v>574</v>
       </c>
       <c r="D677" s="2" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="E677" s="2" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="F677" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A677,3,4)))</f>
@@ -28977,7 +28981,7 @@
     </row>
     <row r="678" spans="1:11" ht="17" customHeight="1">
       <c r="A678" s="1" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="B678" s="5">
         <f>IF(ISNA(VLOOKUP(H678,$A$2:$C$1011,3,1)),C678,VLOOKUP(H678,$A$2:$C$1011,3,1))</f>
@@ -28987,10 +28991,10 @@
         <v>565</v>
       </c>
       <c r="D678" s="2" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="E678" s="2" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="F678" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A678,3,4)))</f>
@@ -29010,7 +29014,7 @@
     </row>
     <row r="679" spans="1:11" ht="17" customHeight="1">
       <c r="A679" s="1" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="B679" s="5">
         <f>IF(ISNA(VLOOKUP(H679,$A$2:$C$1011,3,1)),C679,VLOOKUP(H679,$A$2:$C$1011,3,1))</f>
@@ -29020,10 +29024,10 @@
         <v>580</v>
       </c>
       <c r="D679" s="2" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="E679" s="2" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="F679" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A679,3,4)))</f>
@@ -29043,7 +29047,7 @@
     </row>
     <row r="680" spans="1:11" ht="17" customHeight="1">
       <c r="A680" s="1" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="B680" s="5">
         <f>IF(ISNA(VLOOKUP(H680,$A$2:$C$1011,3,1)),C680,VLOOKUP(H680,$A$2:$C$1011,3,1))</f>
@@ -29053,10 +29057,10 @@
         <v>462</v>
       </c>
       <c r="D680" s="2" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="E680" s="2" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="F680" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A680,3,4)))</f>
@@ -29076,7 +29080,7 @@
     </row>
     <row r="681" spans="1:11" ht="17" customHeight="1">
       <c r="A681" s="1" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B681" s="5">
         <f>IF(ISNA(VLOOKUP(H681,$A$2:$C$1011,3,1)),C681,VLOOKUP(H681,$A$2:$C$1011,3,1))</f>
@@ -29086,10 +29090,10 @@
         <v>463</v>
       </c>
       <c r="D681" s="2" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="E681" s="2" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="F681" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A681,3,4)))</f>
@@ -29109,7 +29113,7 @@
     </row>
     <row r="682" spans="1:11" ht="17" customHeight="1">
       <c r="A682" s="1" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B682" s="5">
         <f>IF(ISNA(VLOOKUP(H682,$A$2:$C$1011,3,1)),C682,VLOOKUP(H682,$A$2:$C$1011,3,1))</f>
@@ -29119,10 +29123,10 @@
         <v>464</v>
       </c>
       <c r="D682" s="2" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="E682" s="2" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="F682" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A682,3,4)))</f>
@@ -29142,7 +29146,7 @@
     </row>
     <row r="683" spans="1:11" ht="17" customHeight="1">
       <c r="A683" s="1" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="B683" s="5">
         <f>IF(ISNA(VLOOKUP(H683,$A$2:$C$1011,3,1)),C683,VLOOKUP(H683,$A$2:$C$1011,3,1))</f>
@@ -29152,10 +29156,10 @@
         <v>663</v>
       </c>
       <c r="D683" s="2" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="E683" s="2" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="F683" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A683,3,4)))</f>
@@ -29166,7 +29170,7 @@
         <v>Ɐ</v>
       </c>
       <c r="H683" s="20" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="I683" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H683,3,4)))</f>
@@ -29175,7 +29179,7 @@
     </row>
     <row r="684" spans="1:11" ht="17" customHeight="1">
       <c r="A684" s="1" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B684" s="5">
         <f>IF(ISNA(VLOOKUP(H684,$A$2:$C$1011,3,1)),C684,VLOOKUP(H684,$A$2:$C$1011,3,1))</f>
@@ -29185,10 +29189,10 @@
         <v>9999</v>
       </c>
       <c r="D684" s="2" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="688" spans="1:11" customFormat="1" ht="17" customHeight="1">
@@ -29261,8 +29265,8 @@
       <c r="K714" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K714">
-    <sortCondition ref="A2:A714"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K716">
+    <sortCondition ref="A2:A716"/>
   </sortState>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>

--- a/res/fonts/sortingOrder.xlsx
+++ b/res/fonts/sortingOrder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/c43/res/fonts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A759FF1F-CEB6-2749-954C-C719155D1544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D24197-0D50-574B-BBFF-C006364CBFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19340" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6240,9 +6240,6 @@
     <t>CYRILLIC SMALL LETTER UKRAINIAN IE</t>
   </si>
   <si>
-    <t>for inverse G function g_d^-1</t>
-  </si>
-  <si>
     <t>k^* for unitary divisor function</t>
   </si>
   <si>
@@ -6307,6 +6304,9 @@
   </si>
   <si>
     <t>Superscript 2 subscript p</t>
+  </si>
+  <si>
+    <t>*n for B*n</t>
   </si>
 </sst>
 </file>
@@ -18267,7 +18267,7 @@
         <v>2031</v>
       </c>
       <c r="E350" s="23" t="s">
-        <v>2034</v>
+        <v>2056</v>
       </c>
       <c r="F350" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A350,3,4)))</f>
@@ -18287,7 +18287,7 @@
     </row>
     <row r="351" spans="1:11" ht="17" customHeight="1">
       <c r="A351" s="24" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B351" s="5">
         <f>IF(ISNA(VLOOKUP(H351,$A$2:$C$1022,3,1)),C351,VLOOKUP(H351,$A$2:$C$1022,3,1))</f>
@@ -18300,7 +18300,7 @@
         <v>2031</v>
       </c>
       <c r="E351" s="23" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="F351" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A351,3,4)))</f>
@@ -18313,7 +18313,10 @@
       <c r="H351" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I351" s="6"/>
+      <c r="I351" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(H351,3,4)))</f>
+        <v>D</v>
+      </c>
     </row>
     <row r="352" spans="1:11" ht="17" customHeight="1">
       <c r="A352" s="22" t="s">
@@ -18321,16 +18324,16 @@
       </c>
       <c r="B352" s="5">
         <f>IF(ISNA(VLOOKUP(H352,$A$2:$C$1022,3,1)),C352,VLOOKUP(H352,$A$2:$C$1022,3,1))</f>
-        <v>526</v>
+        <v>214</v>
       </c>
       <c r="C352" s="1">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D352" s="23" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="E352" s="23" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="F352" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A352,3,4)))</f>
@@ -18341,11 +18344,11 @@
         <v>ѓ</v>
       </c>
       <c r="H352" s="1" t="s">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="I352" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H352,3,4)))</f>
-        <v>×</v>
+        <v>K</v>
       </c>
     </row>
     <row r="353" spans="1:9" ht="17" customHeight="1">
@@ -18354,13 +18357,13 @@
       </c>
       <c r="B353" s="5">
         <f>IF(ISNA(VLOOKUP(H353,$A$2:$C$1022,3,1)),C353,VLOOKUP(H353,$A$2:$C$1022,3,1))</f>
-        <v>526</v>
+        <v>18</v>
       </c>
       <c r="C353" s="1">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D353" s="23" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E353" s="23" t="s">
         <v>2035</v>
@@ -18374,16 +18377,16 @@
         <v>є</v>
       </c>
       <c r="H353" s="1" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="I353" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H353,3,4)))</f>
-        <v>×</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354" spans="1:9" ht="17" customHeight="1">
       <c r="A354" s="24" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B354" s="5">
         <f>IF(ISNA(VLOOKUP(H354,$A$2:$C$1022,3,1)),C354,VLOOKUP(H354,$A$2:$C$1022,3,1))</f>
@@ -18393,10 +18396,10 @@
         <v>616</v>
       </c>
       <c r="D354" s="23" t="s">
+        <v>2037</v>
+      </c>
+      <c r="E354" s="2" t="s">
         <v>2038</v>
-      </c>
-      <c r="E354" s="2" t="s">
-        <v>2039</v>
       </c>
       <c r="F354" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A354,3,4)))</f>
@@ -18416,7 +18419,7 @@
     </row>
     <row r="355" spans="1:9" ht="17" customHeight="1">
       <c r="A355" s="22" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B355" s="5">
         <f>IF(ISNA(VLOOKUP(H355,$A$2:$C$1022,3,1)),C355,VLOOKUP(H355,$A$2:$C$1022,3,1))</f>
@@ -18426,10 +18429,10 @@
         <v>286</v>
       </c>
       <c r="D355" s="23" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E355" s="2" t="s">
         <v>2055</v>
-      </c>
-      <c r="E355" s="2" t="s">
-        <v>2056</v>
       </c>
       <c r="F355" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A355,3,4)))</f>
@@ -18449,7 +18452,7 @@
     </row>
     <row r="356" spans="1:9" ht="17" customHeight="1">
       <c r="A356" s="22" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B356" s="5">
         <f>IF(ISNA(VLOOKUP(H356,$A$2:$C$1022,3,1)),C356,VLOOKUP(H356,$A$2:$C$1022,3,1))</f>
@@ -18459,10 +18462,10 @@
         <v>513</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F356" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A356,3,4)))</f>
@@ -18482,7 +18485,7 @@
     </row>
     <row r="357" spans="1:9" ht="17" customHeight="1">
       <c r="A357" s="22" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B357" s="5">
         <f>IF(ISNA(VLOOKUP(H357,$A$2:$C$1022,3,1)),C357,VLOOKUP(H357,$A$2:$C$1022,3,1))</f>
@@ -18492,10 +18495,10 @@
         <v>514</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="F357" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A357,3,4)))</f>
@@ -28882,7 +28885,7 @@
     </row>
     <row r="672" spans="1:9" ht="17" customHeight="1">
       <c r="A672" s="22" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B672" s="5">
         <f>IF(ISNA(VLOOKUP(H672,$A$2:$C$1022,3,1)),C672,VLOOKUP(H672,$A$2:$C$1022,3,1))</f>
@@ -28892,10 +28895,10 @@
         <v>515</v>
       </c>
       <c r="D672" s="2" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="F672" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A672,3,4)))</f>
@@ -28915,7 +28918,7 @@
     </row>
     <row r="673" spans="1:9" ht="17" customHeight="1">
       <c r="A673" s="22" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B673" s="5">
         <f>IF(ISNA(VLOOKUP(H673,$A$2:$C$1022,3,1)),C673,VLOOKUP(H673,$A$2:$C$1022,3,1))</f>
@@ -28925,10 +28928,10 @@
         <v>516</v>
       </c>
       <c r="D673" s="2" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="F673" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A673,3,4)))</f>

--- a/res/fonts/sortingOrder.xlsx
+++ b/res/fonts/sortingOrder.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\msys64\c47\c43\res\fonts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacomostert/c43/res/fonts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FAC5585-79CE-4FCA-BF8A-C7B0FB7DBE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49696D1C-D245-D74F-87FC-D3153593D9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="20860" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20860" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sortingOrder" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="table">sortingOrder!$A$1:$I$1106</definedName>
+    <definedName name="table">sortingOrder!$A$1:$I$1107</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="2114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="2117">
   <si>
     <t>Code point</t>
   </si>
@@ -6478,6 +6478,15 @@
   </si>
   <si>
     <t>HP42S White right pointing small triangle</t>
+  </si>
+  <si>
+    <t>U+2592</t>
+  </si>
+  <si>
+    <t>MEDIUM SHADE</t>
+  </si>
+  <si>
+    <t>HP42S EOT</t>
   </si>
 </sst>
 </file>
@@ -6818,20 +6827,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K743"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="17" customHeight="1"/>
+  <dimension ref="A1:K744"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="17" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.453125" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.81640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="72.453125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="53.08984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="32.08984375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.08984375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="4.36328125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="93.36328125" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="11.453125" style="4"/>
+    <col min="1" max="1" width="15.5" style="1" customWidth="1"/>
+    <col min="2" max="3" width="9.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="72.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="53.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="32.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="93.33203125" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="11.5" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17" customHeight="1">
@@ -6872,7 +6881,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="5">
-        <f>IF(ISNA(VLOOKUP(H2,$A$2:$C$1040,3,1)),C2,VLOOKUP(H2,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H2,$A$2:$C$1041,3,1)),C2,VLOOKUP(H2,$A$2:$C$1041,3,1))</f>
         <v>1</v>
       </c>
       <c r="C2" s="1">
@@ -6908,7 +6917,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="5">
-        <f>IF(ISNA(VLOOKUP(H3,$A$2:$C$1040,3,1)),C3,VLOOKUP(H3,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H3,$A$2:$C$1041,3,1)),C3,VLOOKUP(H3,$A$2:$C$1041,3,1))</f>
         <v>547</v>
       </c>
       <c r="C3" s="1">
@@ -6944,7 +6953,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="5">
-        <f>IF(ISNA(VLOOKUP(H4,$A$2:$C$1040,3,1)),C4,VLOOKUP(H4,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H4,$A$2:$C$1041,3,1)),C4,VLOOKUP(H4,$A$2:$C$1041,3,1))</f>
         <v>561</v>
       </c>
       <c r="C4" s="1">
@@ -6977,7 +6986,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="5">
-        <f>IF(ISNA(VLOOKUP(H5,$A$2:$C$1040,3,1)),C5,VLOOKUP(H5,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H5,$A$2:$C$1041,3,1)),C5,VLOOKUP(H5,$A$2:$C$1041,3,1))</f>
         <v>672</v>
       </c>
       <c r="C5" s="1">
@@ -7013,7 +7022,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="5">
-        <f>IF(ISNA(VLOOKUP(H6,$A$2:$C$1040,3,1)),C6,VLOOKUP(H6,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H6,$A$2:$C$1041,3,1)),C6,VLOOKUP(H6,$A$2:$C$1041,3,1))</f>
         <v>626</v>
       </c>
       <c r="C6" s="1">
@@ -7049,7 +7058,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="5">
-        <f>IF(ISNA(VLOOKUP(H7,$A$2:$C$1040,3,1)),C7,VLOOKUP(H7,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H7,$A$2:$C$1041,3,1)),C7,VLOOKUP(H7,$A$2:$C$1041,3,1))</f>
         <v>626</v>
       </c>
       <c r="C7" s="1">
@@ -7085,7 +7094,7 @@
         <v>29</v>
       </c>
       <c r="B8" s="5">
-        <f>IF(ISNA(VLOOKUP(H8,$A$2:$C$1040,3,1)),C8,VLOOKUP(H8,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H8,$A$2:$C$1041,3,1)),C8,VLOOKUP(H8,$A$2:$C$1041,3,1))</f>
         <v>605</v>
       </c>
       <c r="C8" s="1">
@@ -7118,7 +7127,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="5">
-        <f>IF(ISNA(VLOOKUP(H9,$A$2:$C$1040,3,1)),C9,VLOOKUP(H9,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H9,$A$2:$C$1041,3,1)),C9,VLOOKUP(H9,$A$2:$C$1041,3,1))</f>
         <v>555</v>
       </c>
       <c r="C9" s="1">
@@ -7154,7 +7163,7 @@
         <v>36</v>
       </c>
       <c r="B10" s="5">
-        <f>IF(ISNA(VLOOKUP(H10,$A$2:$C$1040,3,1)),C10,VLOOKUP(H10,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H10,$A$2:$C$1041,3,1)),C10,VLOOKUP(H10,$A$2:$C$1041,3,1))</f>
         <v>497</v>
       </c>
       <c r="C10" s="1">
@@ -7190,7 +7199,7 @@
         <v>40</v>
       </c>
       <c r="B11" s="5">
-        <f>IF(ISNA(VLOOKUP(H11,$A$2:$C$1040,3,1)),C11,VLOOKUP(H11,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H11,$A$2:$C$1041,3,1)),C11,VLOOKUP(H11,$A$2:$C$1041,3,1))</f>
         <v>497</v>
       </c>
       <c r="C11" s="1">
@@ -7226,7 +7235,7 @@
         <v>44</v>
       </c>
       <c r="B12" s="5">
-        <f>IF(ISNA(VLOOKUP(H12,$A$2:$C$1040,3,1)),C12,VLOOKUP(H12,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H12,$A$2:$C$1041,3,1)),C12,VLOOKUP(H12,$A$2:$C$1041,3,1))</f>
         <v>526</v>
       </c>
       <c r="C12" s="1">
@@ -7259,7 +7268,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="5">
-        <f>IF(ISNA(VLOOKUP(H13,$A$2:$C$1040,3,1)),C13,VLOOKUP(H13,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H13,$A$2:$C$1041,3,1)),C13,VLOOKUP(H13,$A$2:$C$1041,3,1))</f>
         <v>517</v>
       </c>
       <c r="C13" s="1">
@@ -7295,7 +7304,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="5">
-        <f>IF(ISNA(VLOOKUP(H14,$A$2:$C$1040,3,1)),C14,VLOOKUP(H14,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H14,$A$2:$C$1041,3,1)),C14,VLOOKUP(H14,$A$2:$C$1041,3,1))</f>
         <v>538</v>
       </c>
       <c r="C14" s="1">
@@ -7331,7 +7340,7 @@
         <v>55</v>
       </c>
       <c r="B15" s="5">
-        <f>IF(ISNA(VLOOKUP(H15,$A$2:$C$1040,3,1)),C15,VLOOKUP(H15,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H15,$A$2:$C$1041,3,1)),C15,VLOOKUP(H15,$A$2:$C$1041,3,1))</f>
         <v>521</v>
       </c>
       <c r="C15" s="1">
@@ -7367,7 +7376,7 @@
         <v>59</v>
       </c>
       <c r="B16" s="5">
-        <f>IF(ISNA(VLOOKUP(H16,$A$2:$C$1040,3,1)),C16,VLOOKUP(H16,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H16,$A$2:$C$1041,3,1)),C16,VLOOKUP(H16,$A$2:$C$1041,3,1))</f>
         <v>541</v>
       </c>
       <c r="C16" s="1">
@@ -7403,7 +7412,7 @@
         <v>63</v>
       </c>
       <c r="B17" s="5">
-        <f>IF(ISNA(VLOOKUP(H17,$A$2:$C$1040,3,1)),C17,VLOOKUP(H17,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H17,$A$2:$C$1041,3,1)),C17,VLOOKUP(H17,$A$2:$C$1041,3,1))</f>
         <v>535</v>
       </c>
       <c r="C17" s="1">
@@ -7439,7 +7448,7 @@
         <v>67</v>
       </c>
       <c r="B18" s="5">
-        <f>IF(ISNA(VLOOKUP(H18,$A$2:$C$1040,3,1)),C18,VLOOKUP(H18,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H18,$A$2:$C$1041,3,1)),C18,VLOOKUP(H18,$A$2:$C$1041,3,1))</f>
         <v>11</v>
       </c>
       <c r="C18" s="1">
@@ -7472,7 +7481,7 @@
         <v>70</v>
       </c>
       <c r="B19" s="5">
-        <f>IF(ISNA(VLOOKUP(H19,$A$2:$C$1040,3,1)),C19,VLOOKUP(H19,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H19,$A$2:$C$1041,3,1)),C19,VLOOKUP(H19,$A$2:$C$1041,3,1))</f>
         <v>18</v>
       </c>
       <c r="C19" s="1">
@@ -7508,7 +7517,7 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <f>IF(ISNA(VLOOKUP(H20,$A$2:$C$1040,3,1)),C20,VLOOKUP(H20,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H20,$A$2:$C$1041,3,1)),C20,VLOOKUP(H20,$A$2:$C$1041,3,1))</f>
         <v>25</v>
       </c>
       <c r="C20" s="1">
@@ -7544,7 +7553,7 @@
         <v>76</v>
       </c>
       <c r="B21" s="5">
-        <f>IF(ISNA(VLOOKUP(H21,$A$2:$C$1040,3,1)),C21,VLOOKUP(H21,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H21,$A$2:$C$1041,3,1)),C21,VLOOKUP(H21,$A$2:$C$1041,3,1))</f>
         <v>29</v>
       </c>
       <c r="C21" s="1">
@@ -7580,7 +7589,7 @@
         <v>79</v>
       </c>
       <c r="B22" s="5">
-        <f>IF(ISNA(VLOOKUP(H22,$A$2:$C$1040,3,1)),C22,VLOOKUP(H22,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H22,$A$2:$C$1041,3,1)),C22,VLOOKUP(H22,$A$2:$C$1041,3,1))</f>
         <v>34</v>
       </c>
       <c r="C22" s="1">
@@ -7613,7 +7622,7 @@
         <v>83</v>
       </c>
       <c r="B23" s="5">
-        <f>IF(ISNA(VLOOKUP(H23,$A$2:$C$1040,3,1)),C23,VLOOKUP(H23,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H23,$A$2:$C$1041,3,1)),C23,VLOOKUP(H23,$A$2:$C$1041,3,1))</f>
         <v>38</v>
       </c>
       <c r="C23" s="1">
@@ -7649,7 +7658,7 @@
         <v>86</v>
       </c>
       <c r="B24" s="5">
-        <f>IF(ISNA(VLOOKUP(H24,$A$2:$C$1040,3,1)),C24,VLOOKUP(H24,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H24,$A$2:$C$1041,3,1)),C24,VLOOKUP(H24,$A$2:$C$1041,3,1))</f>
         <v>42</v>
       </c>
       <c r="C24" s="1">
@@ -7682,7 +7691,7 @@
         <v>89</v>
       </c>
       <c r="B25" s="5">
-        <f>IF(ISNA(VLOOKUP(H25,$A$2:$C$1040,3,1)),C25,VLOOKUP(H25,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H25,$A$2:$C$1041,3,1)),C25,VLOOKUP(H25,$A$2:$C$1041,3,1))</f>
         <v>46</v>
       </c>
       <c r="C25" s="1">
@@ -7715,7 +7724,7 @@
         <v>92</v>
       </c>
       <c r="B26" s="5">
-        <f>IF(ISNA(VLOOKUP(H26,$A$2:$C$1040,3,1)),C26,VLOOKUP(H26,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H26,$A$2:$C$1041,3,1)),C26,VLOOKUP(H26,$A$2:$C$1041,3,1))</f>
         <v>50</v>
       </c>
       <c r="C26" s="1">
@@ -7748,7 +7757,7 @@
         <v>95</v>
       </c>
       <c r="B27" s="5">
-        <f>IF(ISNA(VLOOKUP(H27,$A$2:$C$1040,3,1)),C27,VLOOKUP(H27,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H27,$A$2:$C$1041,3,1)),C27,VLOOKUP(H27,$A$2:$C$1041,3,1))</f>
         <v>54</v>
       </c>
       <c r="C27" s="1">
@@ -7781,7 +7790,7 @@
         <v>98</v>
       </c>
       <c r="B28" s="5">
-        <f>IF(ISNA(VLOOKUP(H28,$A$2:$C$1040,3,1)),C28,VLOOKUP(H28,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H28,$A$2:$C$1041,3,1)),C28,VLOOKUP(H28,$A$2:$C$1041,3,1))</f>
         <v>551</v>
       </c>
       <c r="C28" s="1">
@@ -7814,7 +7823,7 @@
         <v>101</v>
       </c>
       <c r="B29" s="5">
-        <f>IF(ISNA(VLOOKUP(H29,$A$2:$C$1040,3,1)),C29,VLOOKUP(H29,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H29,$A$2:$C$1041,3,1)),C29,VLOOKUP(H29,$A$2:$C$1041,3,1))</f>
         <v>554</v>
       </c>
       <c r="C29" s="1">
@@ -7847,7 +7856,7 @@
         <v>104</v>
       </c>
       <c r="B30" s="5">
-        <f>IF(ISNA(VLOOKUP(H30,$A$2:$C$1040,3,1)),C30,VLOOKUP(H30,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H30,$A$2:$C$1041,3,1)),C30,VLOOKUP(H30,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C30" s="1">
@@ -7880,7 +7889,7 @@
         <v>108</v>
       </c>
       <c r="B31" s="5">
-        <f>IF(ISNA(VLOOKUP(H31,$A$2:$C$1040,3,1)),C31,VLOOKUP(H31,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H31,$A$2:$C$1041,3,1)),C31,VLOOKUP(H31,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C31" s="1">
@@ -7913,7 +7922,7 @@
         <v>111</v>
       </c>
       <c r="B32" s="5">
-        <f>IF(ISNA(VLOOKUP(H32,$A$2:$C$1040,3,1)),C32,VLOOKUP(H32,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H32,$A$2:$C$1041,3,1)),C32,VLOOKUP(H32,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C32" s="1">
@@ -7946,7 +7955,7 @@
         <v>114</v>
       </c>
       <c r="B33" s="5">
-        <f>IF(ISNA(VLOOKUP(H33,$A$2:$C$1040,3,1)),C33,VLOOKUP(H33,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H33,$A$2:$C$1041,3,1)),C33,VLOOKUP(H33,$A$2:$C$1041,3,1))</f>
         <v>549</v>
       </c>
       <c r="C33" s="1">
@@ -7979,7 +7988,7 @@
         <v>117</v>
       </c>
       <c r="B34" s="5">
-        <f>IF(ISNA(VLOOKUP(H34,$A$2:$C$1040,3,1)),C34,VLOOKUP(H34,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H34,$A$2:$C$1041,3,1)),C34,VLOOKUP(H34,$A$2:$C$1041,3,1))</f>
         <v>568</v>
       </c>
       <c r="C34" s="1">
@@ -8012,7 +8021,7 @@
         <v>120</v>
       </c>
       <c r="B35" s="5">
-        <f>IF(ISNA(VLOOKUP(H35,$A$2:$C$1040,3,1)),C35,VLOOKUP(H35,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H35,$A$2:$C$1041,3,1)),C35,VLOOKUP(H35,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C35" s="1">
@@ -8045,7 +8054,7 @@
         <v>123</v>
       </c>
       <c r="B36" s="5">
-        <f>IF(ISNA(VLOOKUP(H36,$A$2:$C$1040,3,1)),C36,VLOOKUP(H36,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H36,$A$2:$C$1041,3,1)),C36,VLOOKUP(H36,$A$2:$C$1041,3,1))</f>
         <v>92</v>
       </c>
       <c r="C36" s="1">
@@ -8078,7 +8087,7 @@
         <v>126</v>
       </c>
       <c r="B37" s="5">
-        <f>IF(ISNA(VLOOKUP(H37,$A$2:$C$1040,3,1)),C37,VLOOKUP(H37,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H37,$A$2:$C$1041,3,1)),C37,VLOOKUP(H37,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C37" s="1">
@@ -8111,7 +8120,7 @@
         <v>129</v>
       </c>
       <c r="B38" s="5">
-        <f>IF(ISNA(VLOOKUP(H38,$A$2:$C$1040,3,1)),C38,VLOOKUP(H38,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H38,$A$2:$C$1041,3,1)),C38,VLOOKUP(H38,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C38" s="1">
@@ -8144,7 +8153,7 @@
         <v>132</v>
       </c>
       <c r="B39" s="5">
-        <f>IF(ISNA(VLOOKUP(H39,$A$2:$C$1040,3,1)),C39,VLOOKUP(H39,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H39,$A$2:$C$1041,3,1)),C39,VLOOKUP(H39,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C39" s="1">
@@ -8177,7 +8186,7 @@
         <v>135</v>
       </c>
       <c r="B40" s="5">
-        <f>IF(ISNA(VLOOKUP(H40,$A$2:$C$1040,3,1)),C40,VLOOKUP(H40,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H40,$A$2:$C$1041,3,1)),C40,VLOOKUP(H40,$A$2:$C$1041,3,1))</f>
         <v>153</v>
       </c>
       <c r="C40" s="1">
@@ -8210,7 +8219,7 @@
         <v>138</v>
       </c>
       <c r="B41" s="5">
-        <f>IF(ISNA(VLOOKUP(H41,$A$2:$C$1040,3,1)),C41,VLOOKUP(H41,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H41,$A$2:$C$1041,3,1)),C41,VLOOKUP(H41,$A$2:$C$1041,3,1))</f>
         <v>162</v>
       </c>
       <c r="C41" s="1">
@@ -8243,7 +8252,7 @@
         <v>141</v>
       </c>
       <c r="B42" s="5">
-        <f>IF(ISNA(VLOOKUP(H42,$A$2:$C$1040,3,1)),C42,VLOOKUP(H42,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H42,$A$2:$C$1041,3,1)),C42,VLOOKUP(H42,$A$2:$C$1041,3,1))</f>
         <v>172</v>
       </c>
       <c r="C42" s="1">
@@ -8276,7 +8285,7 @@
         <v>144</v>
       </c>
       <c r="B43" s="5">
-        <f>IF(ISNA(VLOOKUP(H43,$A$2:$C$1040,3,1)),C43,VLOOKUP(H43,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H43,$A$2:$C$1041,3,1)),C43,VLOOKUP(H43,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C43" s="1">
@@ -8309,7 +8318,7 @@
         <v>147</v>
       </c>
       <c r="B44" s="5">
-        <f>IF(ISNA(VLOOKUP(H44,$A$2:$C$1040,3,1)),C44,VLOOKUP(H44,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H44,$A$2:$C$1041,3,1)),C44,VLOOKUP(H44,$A$2:$C$1041,3,1))</f>
         <v>206</v>
       </c>
       <c r="C44" s="1">
@@ -8342,7 +8351,7 @@
         <v>150</v>
       </c>
       <c r="B45" s="5">
-        <f>IF(ISNA(VLOOKUP(H45,$A$2:$C$1040,3,1)),C45,VLOOKUP(H45,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H45,$A$2:$C$1041,3,1)),C45,VLOOKUP(H45,$A$2:$C$1041,3,1))</f>
         <v>214</v>
       </c>
       <c r="C45" s="1">
@@ -8375,7 +8384,7 @@
         <v>153</v>
       </c>
       <c r="B46" s="5">
-        <f>IF(ISNA(VLOOKUP(H46,$A$2:$C$1040,3,1)),C46,VLOOKUP(H46,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H46,$A$2:$C$1041,3,1)),C46,VLOOKUP(H46,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C46" s="1">
@@ -8408,7 +8417,7 @@
         <v>156</v>
       </c>
       <c r="B47" s="5">
-        <f>IF(ISNA(VLOOKUP(H47,$A$2:$C$1040,3,1)),C47,VLOOKUP(H47,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H47,$A$2:$C$1041,3,1)),C47,VLOOKUP(H47,$A$2:$C$1041,3,1))</f>
         <v>234</v>
       </c>
       <c r="C47" s="1">
@@ -8441,7 +8450,7 @@
         <v>159</v>
       </c>
       <c r="B48" s="5">
-        <f>IF(ISNA(VLOOKUP(H48,$A$2:$C$1040,3,1)),C48,VLOOKUP(H48,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H48,$A$2:$C$1041,3,1)),C48,VLOOKUP(H48,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C48" s="1">
@@ -8474,7 +8483,7 @@
         <v>162</v>
       </c>
       <c r="B49" s="5">
-        <f>IF(ISNA(VLOOKUP(H49,$A$2:$C$1040,3,1)),C49,VLOOKUP(H49,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H49,$A$2:$C$1041,3,1)),C49,VLOOKUP(H49,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C49" s="1">
@@ -8507,7 +8516,7 @@
         <v>165</v>
       </c>
       <c r="B50" s="5">
-        <f>IF(ISNA(VLOOKUP(H50,$A$2:$C$1040,3,1)),C50,VLOOKUP(H50,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H50,$A$2:$C$1041,3,1)),C50,VLOOKUP(H50,$A$2:$C$1041,3,1))</f>
         <v>280</v>
       </c>
       <c r="C50" s="1">
@@ -8540,7 +8549,7 @@
         <v>168</v>
       </c>
       <c r="B51" s="5">
-        <f>IF(ISNA(VLOOKUP(H51,$A$2:$C$1040,3,1)),C51,VLOOKUP(H51,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H51,$A$2:$C$1041,3,1)),C51,VLOOKUP(H51,$A$2:$C$1041,3,1))</f>
         <v>287</v>
       </c>
       <c r="C51" s="1">
@@ -8573,7 +8582,7 @@
         <v>171</v>
       </c>
       <c r="B52" s="5">
-        <f>IF(ISNA(VLOOKUP(H52,$A$2:$C$1040,3,1)),C52,VLOOKUP(H52,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H52,$A$2:$C$1041,3,1)),C52,VLOOKUP(H52,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C52" s="1">
@@ -8606,7 +8615,7 @@
         <v>174</v>
       </c>
       <c r="B53" s="5">
-        <f>IF(ISNA(VLOOKUP(H53,$A$2:$C$1040,3,1)),C53,VLOOKUP(H53,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H53,$A$2:$C$1041,3,1)),C53,VLOOKUP(H53,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C53" s="1">
@@ -8639,7 +8648,7 @@
         <v>177</v>
       </c>
       <c r="B54" s="5">
-        <f>IF(ISNA(VLOOKUP(H54,$A$2:$C$1040,3,1)),C54,VLOOKUP(H54,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H54,$A$2:$C$1041,3,1)),C54,VLOOKUP(H54,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C54" s="1">
@@ -8672,7 +8681,7 @@
         <v>180</v>
       </c>
       <c r="B55" s="5">
-        <f>IF(ISNA(VLOOKUP(H55,$A$2:$C$1040,3,1)),C55,VLOOKUP(H55,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H55,$A$2:$C$1041,3,1)),C55,VLOOKUP(H55,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C55" s="1">
@@ -8705,7 +8714,7 @@
         <v>183</v>
       </c>
       <c r="B56" s="5">
-        <f>IF(ISNA(VLOOKUP(H56,$A$2:$C$1040,3,1)),C56,VLOOKUP(H56,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H56,$A$2:$C$1041,3,1)),C56,VLOOKUP(H56,$A$2:$C$1041,3,1))</f>
         <v>359</v>
       </c>
       <c r="C56" s="1">
@@ -8738,7 +8747,7 @@
         <v>186</v>
       </c>
       <c r="B57" s="5">
-        <f>IF(ISNA(VLOOKUP(H57,$A$2:$C$1040,3,1)),C57,VLOOKUP(H57,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H57,$A$2:$C$1041,3,1)),C57,VLOOKUP(H57,$A$2:$C$1041,3,1))</f>
         <v>367</v>
       </c>
       <c r="C57" s="1">
@@ -8771,7 +8780,7 @@
         <v>189</v>
       </c>
       <c r="B58" s="5">
-        <f>IF(ISNA(VLOOKUP(H58,$A$2:$C$1040,3,1)),C58,VLOOKUP(H58,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H58,$A$2:$C$1041,3,1)),C58,VLOOKUP(H58,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C58" s="1">
@@ -8804,7 +8813,7 @@
         <v>192</v>
       </c>
       <c r="B59" s="5">
-        <f>IF(ISNA(VLOOKUP(H59,$A$2:$C$1040,3,1)),C59,VLOOKUP(H59,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H59,$A$2:$C$1041,3,1)),C59,VLOOKUP(H59,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C59" s="1">
@@ -8837,7 +8846,7 @@
         <v>195</v>
       </c>
       <c r="B60" s="5">
-        <f>IF(ISNA(VLOOKUP(H60,$A$2:$C$1040,3,1)),C60,VLOOKUP(H60,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H60,$A$2:$C$1041,3,1)),C60,VLOOKUP(H60,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C60" s="1">
@@ -8870,7 +8879,7 @@
         <v>198</v>
       </c>
       <c r="B61" s="5">
-        <f>IF(ISNA(VLOOKUP(H61,$A$2:$C$1040,3,1)),C61,VLOOKUP(H61,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H61,$A$2:$C$1041,3,1)),C61,VLOOKUP(H61,$A$2:$C$1041,3,1))</f>
         <v>499</v>
       </c>
       <c r="C61" s="1">
@@ -8903,7 +8912,7 @@
         <v>201</v>
       </c>
       <c r="B62" s="5">
-        <f>IF(ISNA(VLOOKUP(H62,$A$2:$C$1040,3,1)),C62,VLOOKUP(H62,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H62,$A$2:$C$1041,3,1)),C62,VLOOKUP(H62,$A$2:$C$1041,3,1))</f>
         <v>535</v>
       </c>
       <c r="C62" s="1">
@@ -8936,7 +8945,7 @@
         <v>204</v>
       </c>
       <c r="B63" s="5">
-        <f>IF(ISNA(VLOOKUP(H63,$A$2:$C$1040,3,1)),C63,VLOOKUP(H63,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H63,$A$2:$C$1041,3,1)),C63,VLOOKUP(H63,$A$2:$C$1041,3,1))</f>
         <v>499</v>
       </c>
       <c r="C63" s="1">
@@ -8969,7 +8978,7 @@
         <v>207</v>
       </c>
       <c r="B64" s="5">
-        <f>IF(ISNA(VLOOKUP(H64,$A$2:$C$1040,3,1)),C64,VLOOKUP(H64,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H64,$A$2:$C$1041,3,1)),C64,VLOOKUP(H64,$A$2:$C$1041,3,1))</f>
         <v>537</v>
       </c>
       <c r="C64" s="1">
@@ -9002,7 +9011,7 @@
         <v>209</v>
       </c>
       <c r="B65" s="5">
-        <f>IF(ISNA(VLOOKUP(H65,$A$2:$C$1040,3,1)),C65,VLOOKUP(H65,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H65,$A$2:$C$1041,3,1)),C65,VLOOKUP(H65,$A$2:$C$1041,3,1))</f>
         <v>569</v>
       </c>
       <c r="C65" s="1">
@@ -9035,7 +9044,7 @@
         <v>212</v>
       </c>
       <c r="B66" s="5">
-        <f>IF(ISNA(VLOOKUP(H66,$A$2:$C$1040,3,1)),C66,VLOOKUP(H66,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H66,$A$2:$C$1041,3,1)),C66,VLOOKUP(H66,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C66" s="1">
@@ -9068,7 +9077,7 @@
         <v>215</v>
       </c>
       <c r="B67" s="5">
-        <f>IF(ISNA(VLOOKUP(H67,$A$2:$C$1040,3,1)),C67,VLOOKUP(H67,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H67,$A$2:$C$1041,3,1)),C67,VLOOKUP(H67,$A$2:$C$1041,3,1))</f>
         <v>92</v>
       </c>
       <c r="C67" s="1">
@@ -9101,7 +9110,7 @@
         <v>218</v>
       </c>
       <c r="B68" s="5">
-        <f>IF(ISNA(VLOOKUP(H68,$A$2:$C$1040,3,1)),C68,VLOOKUP(H68,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H68,$A$2:$C$1041,3,1)),C68,VLOOKUP(H68,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C68" s="1">
@@ -9134,7 +9143,7 @@
         <v>221</v>
       </c>
       <c r="B69" s="5">
-        <f>IF(ISNA(VLOOKUP(H69,$A$2:$C$1040,3,1)),C69,VLOOKUP(H69,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H69,$A$2:$C$1041,3,1)),C69,VLOOKUP(H69,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C69" s="1">
@@ -9167,7 +9176,7 @@
         <v>224</v>
       </c>
       <c r="B70" s="5">
-        <f>IF(ISNA(VLOOKUP(H70,$A$2:$C$1040,3,1)),C70,VLOOKUP(H70,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H70,$A$2:$C$1041,3,1)),C70,VLOOKUP(H70,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C70" s="1">
@@ -9200,7 +9209,7 @@
         <v>227</v>
       </c>
       <c r="B71" s="5">
-        <f>IF(ISNA(VLOOKUP(H71,$A$2:$C$1040,3,1)),C71,VLOOKUP(H71,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H71,$A$2:$C$1041,3,1)),C71,VLOOKUP(H71,$A$2:$C$1041,3,1))</f>
         <v>153</v>
       </c>
       <c r="C71" s="1">
@@ -9233,7 +9242,7 @@
         <v>230</v>
       </c>
       <c r="B72" s="5">
-        <f>IF(ISNA(VLOOKUP(H72,$A$2:$C$1040,3,1)),C72,VLOOKUP(H72,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H72,$A$2:$C$1041,3,1)),C72,VLOOKUP(H72,$A$2:$C$1041,3,1))</f>
         <v>162</v>
       </c>
       <c r="C72" s="1">
@@ -9266,7 +9275,7 @@
         <v>233</v>
       </c>
       <c r="B73" s="5">
-        <f>IF(ISNA(VLOOKUP(H73,$A$2:$C$1040,3,1)),C73,VLOOKUP(H73,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H73,$A$2:$C$1041,3,1)),C73,VLOOKUP(H73,$A$2:$C$1041,3,1))</f>
         <v>172</v>
       </c>
       <c r="C73" s="1">
@@ -9299,7 +9308,7 @@
         <v>236</v>
       </c>
       <c r="B74" s="5">
-        <f>IF(ISNA(VLOOKUP(H74,$A$2:$C$1040,3,1)),C74,VLOOKUP(H74,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H74,$A$2:$C$1041,3,1)),C74,VLOOKUP(H74,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C74" s="1">
@@ -9332,7 +9341,7 @@
         <v>239</v>
       </c>
       <c r="B75" s="5">
-        <f>IF(ISNA(VLOOKUP(H75,$A$2:$C$1040,3,1)),C75,VLOOKUP(H75,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H75,$A$2:$C$1041,3,1)),C75,VLOOKUP(H75,$A$2:$C$1041,3,1))</f>
         <v>206</v>
       </c>
       <c r="C75" s="1">
@@ -9365,7 +9374,7 @@
         <v>242</v>
       </c>
       <c r="B76" s="5">
-        <f>IF(ISNA(VLOOKUP(H76,$A$2:$C$1040,3,1)),C76,VLOOKUP(H76,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H76,$A$2:$C$1041,3,1)),C76,VLOOKUP(H76,$A$2:$C$1041,3,1))</f>
         <v>214</v>
       </c>
       <c r="C76" s="1">
@@ -9398,7 +9407,7 @@
         <v>245</v>
       </c>
       <c r="B77" s="5">
-        <f>IF(ISNA(VLOOKUP(H77,$A$2:$C$1040,3,1)),C77,VLOOKUP(H77,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H77,$A$2:$C$1041,3,1)),C77,VLOOKUP(H77,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C77" s="1">
@@ -9431,7 +9440,7 @@
         <v>248</v>
       </c>
       <c r="B78" s="5">
-        <f>IF(ISNA(VLOOKUP(H78,$A$2:$C$1040,3,1)),C78,VLOOKUP(H78,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H78,$A$2:$C$1041,3,1)),C78,VLOOKUP(H78,$A$2:$C$1041,3,1))</f>
         <v>234</v>
       </c>
       <c r="C78" s="1">
@@ -9464,7 +9473,7 @@
         <v>251</v>
       </c>
       <c r="B79" s="5">
-        <f>IF(ISNA(VLOOKUP(H79,$A$2:$C$1040,3,1)),C79,VLOOKUP(H79,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H79,$A$2:$C$1041,3,1)),C79,VLOOKUP(H79,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C79" s="1">
@@ -9497,7 +9506,7 @@
         <v>254</v>
       </c>
       <c r="B80" s="5">
-        <f>IF(ISNA(VLOOKUP(H80,$A$2:$C$1040,3,1)),C80,VLOOKUP(H80,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H80,$A$2:$C$1041,3,1)),C80,VLOOKUP(H80,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C80" s="1">
@@ -9530,7 +9539,7 @@
         <v>257</v>
       </c>
       <c r="B81" s="5">
-        <f>IF(ISNA(VLOOKUP(H81,$A$2:$C$1040,3,1)),C81,VLOOKUP(H81,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H81,$A$2:$C$1041,3,1)),C81,VLOOKUP(H81,$A$2:$C$1041,3,1))</f>
         <v>280</v>
       </c>
       <c r="C81" s="1">
@@ -9563,7 +9572,7 @@
         <v>260</v>
       </c>
       <c r="B82" s="5">
-        <f>IF(ISNA(VLOOKUP(H82,$A$2:$C$1040,3,1)),C82,VLOOKUP(H82,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H82,$A$2:$C$1041,3,1)),C82,VLOOKUP(H82,$A$2:$C$1041,3,1))</f>
         <v>287</v>
       </c>
       <c r="C82" s="1">
@@ -9596,7 +9605,7 @@
         <v>263</v>
       </c>
       <c r="B83" s="5">
-        <f>IF(ISNA(VLOOKUP(H83,$A$2:$C$1040,3,1)),C83,VLOOKUP(H83,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H83,$A$2:$C$1041,3,1)),C83,VLOOKUP(H83,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C83" s="1">
@@ -9629,7 +9638,7 @@
         <v>266</v>
       </c>
       <c r="B84" s="5">
-        <f>IF(ISNA(VLOOKUP(H84,$A$2:$C$1040,3,1)),C84,VLOOKUP(H84,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H84,$A$2:$C$1041,3,1)),C84,VLOOKUP(H84,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C84" s="1">
@@ -9662,7 +9671,7 @@
         <v>269</v>
       </c>
       <c r="B85" s="5">
-        <f>IF(ISNA(VLOOKUP(H85,$A$2:$C$1040,3,1)),C85,VLOOKUP(H85,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H85,$A$2:$C$1041,3,1)),C85,VLOOKUP(H85,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C85" s="1">
@@ -9695,7 +9704,7 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <f>IF(ISNA(VLOOKUP(H86,$A$2:$C$1040,3,1)),C86,VLOOKUP(H86,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H86,$A$2:$C$1041,3,1)),C86,VLOOKUP(H86,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C86" s="1">
@@ -9728,7 +9737,7 @@
         <v>275</v>
       </c>
       <c r="B87" s="5">
-        <f>IF(ISNA(VLOOKUP(H87,$A$2:$C$1040,3,1)),C87,VLOOKUP(H87,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H87,$A$2:$C$1041,3,1)),C87,VLOOKUP(H87,$A$2:$C$1041,3,1))</f>
         <v>359</v>
       </c>
       <c r="C87" s="1">
@@ -9761,7 +9770,7 @@
         <v>278</v>
       </c>
       <c r="B88" s="5">
-        <f>IF(ISNA(VLOOKUP(H88,$A$2:$C$1040,3,1)),C88,VLOOKUP(H88,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H88,$A$2:$C$1041,3,1)),C88,VLOOKUP(H88,$A$2:$C$1041,3,1))</f>
         <v>367</v>
       </c>
       <c r="C88" s="1">
@@ -9794,7 +9803,7 @@
         <v>281</v>
       </c>
       <c r="B89" s="5">
-        <f>IF(ISNA(VLOOKUP(H89,$A$2:$C$1040,3,1)),C89,VLOOKUP(H89,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H89,$A$2:$C$1041,3,1)),C89,VLOOKUP(H89,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C89" s="1">
@@ -9827,7 +9836,7 @@
         <v>284</v>
       </c>
       <c r="B90" s="5">
-        <f>IF(ISNA(VLOOKUP(H90,$A$2:$C$1040,3,1)),C90,VLOOKUP(H90,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H90,$A$2:$C$1041,3,1)),C90,VLOOKUP(H90,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C90" s="1">
@@ -9860,7 +9869,7 @@
         <v>287</v>
       </c>
       <c r="B91" s="5">
-        <f>IF(ISNA(VLOOKUP(H91,$A$2:$C$1040,3,1)),C91,VLOOKUP(H91,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H91,$A$2:$C$1041,3,1)),C91,VLOOKUP(H91,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C91" s="1">
@@ -9893,7 +9902,7 @@
         <v>290</v>
       </c>
       <c r="B92" s="5">
-        <f>IF(ISNA(VLOOKUP(H92,$A$2:$C$1040,3,1)),C92,VLOOKUP(H92,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H92,$A$2:$C$1041,3,1)),C92,VLOOKUP(H92,$A$2:$C$1041,3,1))</f>
         <v>507</v>
       </c>
       <c r="C92" s="1">
@@ -9926,7 +9935,7 @@
         <v>293</v>
       </c>
       <c r="B93" s="5">
-        <f>IF(ISNA(VLOOKUP(H93,$A$2:$C$1040,3,1)),C93,VLOOKUP(H93,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H93,$A$2:$C$1041,3,1)),C93,VLOOKUP(H93,$A$2:$C$1041,3,1))</f>
         <v>606</v>
       </c>
       <c r="C93" s="1">
@@ -9959,7 +9968,7 @@
         <v>296</v>
       </c>
       <c r="B94" s="5">
-        <f>IF(ISNA(VLOOKUP(H94,$A$2:$C$1040,3,1)),C94,VLOOKUP(H94,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H94,$A$2:$C$1041,3,1)),C94,VLOOKUP(H94,$A$2:$C$1041,3,1))</f>
         <v>507</v>
       </c>
       <c r="C94" s="1">
@@ -9992,7 +10001,7 @@
         <v>299</v>
       </c>
       <c r="B95" s="5">
-        <f>IF(ISNA(VLOOKUP(H95,$A$2:$C$1040,3,1)),C95,VLOOKUP(H95,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H95,$A$2:$C$1041,3,1)),C95,VLOOKUP(H95,$A$2:$C$1041,3,1))</f>
         <v>571</v>
       </c>
       <c r="C95" s="1">
@@ -10025,7 +10034,7 @@
         <v>302</v>
       </c>
       <c r="B96" s="5">
-        <f>IF(ISNA(VLOOKUP(H96,$A$2:$C$1040,3,1)),C96,VLOOKUP(H96,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H96,$A$2:$C$1041,3,1)),C96,VLOOKUP(H96,$A$2:$C$1041,3,1))</f>
         <v>11</v>
       </c>
       <c r="C96" s="1">
@@ -10058,7 +10067,7 @@
         <v>305</v>
       </c>
       <c r="B97" s="5">
-        <f>IF(ISNA(VLOOKUP(H97,$A$2:$C$1040,3,1)),C97,VLOOKUP(H97,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H97,$A$2:$C$1041,3,1)),C97,VLOOKUP(H97,$A$2:$C$1041,3,1))</f>
         <v>547</v>
       </c>
       <c r="C97" s="1">
@@ -10091,7 +10100,7 @@
         <v>308</v>
       </c>
       <c r="B98" s="5">
-        <f>IF(ISNA(VLOOKUP(H98,$A$2:$C$1040,3,1)),C98,VLOOKUP(H98,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H98,$A$2:$C$1041,3,1)),C98,VLOOKUP(H98,$A$2:$C$1041,3,1))</f>
         <v>626</v>
       </c>
       <c r="C98" s="1">
@@ -10124,7 +10133,7 @@
         <v>311</v>
       </c>
       <c r="B99" s="5">
-        <f>IF(ISNA(VLOOKUP(H99,$A$2:$C$1040,3,1)),C99,VLOOKUP(H99,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H99,$A$2:$C$1041,3,1)),C99,VLOOKUP(H99,$A$2:$C$1041,3,1))</f>
         <v>626</v>
       </c>
       <c r="C99" s="1">
@@ -10157,7 +10166,7 @@
         <v>314</v>
       </c>
       <c r="B100" s="5">
-        <f>IF(ISNA(VLOOKUP(H100,$A$2:$C$1040,3,1)),C100,VLOOKUP(H100,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H100,$A$2:$C$1041,3,1)),C100,VLOOKUP(H100,$A$2:$C$1041,3,1))</f>
         <v>626</v>
       </c>
       <c r="C100" s="1">
@@ -10190,7 +10199,7 @@
         <v>317</v>
       </c>
       <c r="B101" s="5">
-        <f>IF(ISNA(VLOOKUP(H101,$A$2:$C$1040,3,1)),C101,VLOOKUP(H101,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H101,$A$2:$C$1041,3,1)),C101,VLOOKUP(H101,$A$2:$C$1041,3,1))</f>
         <v>626</v>
       </c>
       <c r="C101" s="1">
@@ -10223,7 +10232,7 @@
         <v>320</v>
       </c>
       <c r="B102" s="5">
-        <f>IF(ISNA(VLOOKUP(H102,$A$2:$C$1040,3,1)),C102,VLOOKUP(H102,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H102,$A$2:$C$1041,3,1)),C102,VLOOKUP(H102,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C102" s="1">
@@ -10256,7 +10265,7 @@
         <v>323</v>
       </c>
       <c r="B103" s="5">
-        <f>IF(ISNA(VLOOKUP(H103,$A$2:$C$1040,3,1)),C103,VLOOKUP(H103,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H103,$A$2:$C$1041,3,1)),C103,VLOOKUP(H103,$A$2:$C$1041,3,1))</f>
         <v>561</v>
       </c>
       <c r="C103" s="1">
@@ -10289,7 +10298,7 @@
         <v>326</v>
       </c>
       <c r="B104" s="5">
-        <f>IF(ISNA(VLOOKUP(H104,$A$2:$C$1040,3,1)),C104,VLOOKUP(H104,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H104,$A$2:$C$1041,3,1)),C104,VLOOKUP(H104,$A$2:$C$1041,3,1))</f>
         <v>599</v>
       </c>
       <c r="C104" s="1">
@@ -10322,7 +10331,7 @@
         <v>329</v>
       </c>
       <c r="B105" s="5">
-        <f>IF(ISNA(VLOOKUP(H105,$A$2:$C$1040,3,1)),C105,VLOOKUP(H105,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H105,$A$2:$C$1041,3,1)),C105,VLOOKUP(H105,$A$2:$C$1041,3,1))</f>
         <v>11</v>
       </c>
       <c r="C105" s="1">
@@ -10355,7 +10364,7 @@
         <v>332</v>
       </c>
       <c r="B106" s="5">
-        <f>IF(ISNA(VLOOKUP(H106,$A$2:$C$1040,3,1)),C106,VLOOKUP(H106,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H106,$A$2:$C$1041,3,1)),C106,VLOOKUP(H106,$A$2:$C$1041,3,1))</f>
         <v>517</v>
       </c>
       <c r="C106" s="1">
@@ -10388,7 +10397,7 @@
         <v>335</v>
       </c>
       <c r="B107" s="5">
-        <f>IF(ISNA(VLOOKUP(H107,$A$2:$C$1040,3,1)),C107,VLOOKUP(H107,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H107,$A$2:$C$1041,3,1)),C107,VLOOKUP(H107,$A$2:$C$1041,3,1))</f>
         <v>451</v>
       </c>
       <c r="C107" s="1">
@@ -10421,7 +10430,7 @@
         <v>339</v>
       </c>
       <c r="B108" s="5">
-        <f>IF(ISNA(VLOOKUP(H108,$A$2:$C$1040,3,1)),C108,VLOOKUP(H108,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H108,$A$2:$C$1041,3,1)),C108,VLOOKUP(H108,$A$2:$C$1041,3,1))</f>
         <v>526</v>
       </c>
       <c r="C108" s="1">
@@ -10454,7 +10463,7 @@
         <v>342</v>
       </c>
       <c r="B109" s="5">
-        <f>IF(ISNA(VLOOKUP(H109,$A$2:$C$1040,3,1)),C109,VLOOKUP(H109,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H109,$A$2:$C$1041,3,1)),C109,VLOOKUP(H109,$A$2:$C$1041,3,1))</f>
         <v>561</v>
       </c>
       <c r="C109" s="1">
@@ -10487,7 +10496,7 @@
         <v>345</v>
       </c>
       <c r="B110" s="5">
-        <f>IF(ISNA(VLOOKUP(H110,$A$2:$C$1040,3,1)),C110,VLOOKUP(H110,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H110,$A$2:$C$1041,3,1)),C110,VLOOKUP(H110,$A$2:$C$1041,3,1))</f>
         <v>18</v>
       </c>
       <c r="C110" s="1">
@@ -10520,7 +10529,7 @@
         <v>348</v>
       </c>
       <c r="B111" s="5">
-        <f>IF(ISNA(VLOOKUP(H111,$A$2:$C$1040,3,1)),C111,VLOOKUP(H111,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H111,$A$2:$C$1041,3,1)),C111,VLOOKUP(H111,$A$2:$C$1041,3,1))</f>
         <v>18</v>
       </c>
       <c r="C111" s="1">
@@ -10553,7 +10562,7 @@
         <v>351</v>
       </c>
       <c r="B112" s="5">
-        <f>IF(ISNA(VLOOKUP(H112,$A$2:$C$1040,3,1)),C112,VLOOKUP(H112,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H112,$A$2:$C$1041,3,1)),C112,VLOOKUP(H112,$A$2:$C$1041,3,1))</f>
         <v>549</v>
       </c>
       <c r="C112" s="1">
@@ -10586,7 +10595,7 @@
         <v>354</v>
       </c>
       <c r="B113" s="5">
-        <f>IF(ISNA(VLOOKUP(H113,$A$2:$C$1040,3,1)),C113,VLOOKUP(H113,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H113,$A$2:$C$1041,3,1)),C113,VLOOKUP(H113,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C113" s="1">
@@ -10619,7 +10628,7 @@
         <v>357</v>
       </c>
       <c r="B114" s="5">
-        <f>IF(ISNA(VLOOKUP(H114,$A$2:$C$1040,3,1)),C114,VLOOKUP(H114,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H114,$A$2:$C$1041,3,1)),C114,VLOOKUP(H114,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C114" s="1">
@@ -10652,7 +10661,7 @@
         <v>360</v>
       </c>
       <c r="B115" s="5">
-        <f>IF(ISNA(VLOOKUP(H115,$A$2:$C$1040,3,1)),C115,VLOOKUP(H115,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H115,$A$2:$C$1041,3,1)),C115,VLOOKUP(H115,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C115" s="1">
@@ -10685,7 +10694,7 @@
         <v>363</v>
       </c>
       <c r="B116" s="5">
-        <f>IF(ISNA(VLOOKUP(H116,$A$2:$C$1040,3,1)),C116,VLOOKUP(H116,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H116,$A$2:$C$1041,3,1)),C116,VLOOKUP(H116,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C116" s="1">
@@ -10718,7 +10727,7 @@
         <v>366</v>
       </c>
       <c r="B117" s="5">
-        <f>IF(ISNA(VLOOKUP(H117,$A$2:$C$1040,3,1)),C117,VLOOKUP(H117,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H117,$A$2:$C$1041,3,1)),C117,VLOOKUP(H117,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C117" s="1">
@@ -10751,7 +10760,7 @@
         <v>369</v>
       </c>
       <c r="B118" s="5">
-        <f>IF(ISNA(VLOOKUP(H118,$A$2:$C$1040,3,1)),C118,VLOOKUP(H118,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H118,$A$2:$C$1041,3,1)),C118,VLOOKUP(H118,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C118" s="1">
@@ -10784,7 +10793,7 @@
         <v>372</v>
       </c>
       <c r="B119" s="5">
-        <f>IF(ISNA(VLOOKUP(H119,$A$2:$C$1040,3,1)),C119,VLOOKUP(H119,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H119,$A$2:$C$1041,3,1)),C119,VLOOKUP(H119,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C119" s="1">
@@ -10817,7 +10826,7 @@
         <v>375</v>
       </c>
       <c r="B120" s="5">
-        <f>IF(ISNA(VLOOKUP(H120,$A$2:$C$1040,3,1)),C120,VLOOKUP(H120,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H120,$A$2:$C$1041,3,1)),C120,VLOOKUP(H120,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C120" s="1">
@@ -10850,7 +10859,7 @@
         <v>378</v>
       </c>
       <c r="B121" s="5">
-        <f>IF(ISNA(VLOOKUP(H121,$A$2:$C$1040,3,1)),C121,VLOOKUP(H121,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H121,$A$2:$C$1041,3,1)),C121,VLOOKUP(H121,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C121" s="1">
@@ -10883,7 +10892,7 @@
         <v>381</v>
       </c>
       <c r="B122" s="5">
-        <f>IF(ISNA(VLOOKUP(H122,$A$2:$C$1040,3,1)),C122,VLOOKUP(H122,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H122,$A$2:$C$1041,3,1)),C122,VLOOKUP(H122,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C122" s="1">
@@ -10916,7 +10925,7 @@
         <v>384</v>
       </c>
       <c r="B123" s="5">
-        <f>IF(ISNA(VLOOKUP(H123,$A$2:$C$1040,3,1)),C123,VLOOKUP(H123,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H123,$A$2:$C$1041,3,1)),C123,VLOOKUP(H123,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C123" s="1">
@@ -10949,7 +10958,7 @@
         <v>387</v>
       </c>
       <c r="B124" s="5">
-        <f>IF(ISNA(VLOOKUP(H124,$A$2:$C$1040,3,1)),C124,VLOOKUP(H124,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H124,$A$2:$C$1041,3,1)),C124,VLOOKUP(H124,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C124" s="1">
@@ -10982,7 +10991,7 @@
         <v>390</v>
       </c>
       <c r="B125" s="5">
-        <f>IF(ISNA(VLOOKUP(H125,$A$2:$C$1040,3,1)),C125,VLOOKUP(H125,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H125,$A$2:$C$1041,3,1)),C125,VLOOKUP(H125,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C125" s="1">
@@ -11015,7 +11024,7 @@
         <v>393</v>
       </c>
       <c r="B126" s="5">
-        <f>IF(ISNA(VLOOKUP(H126,$A$2:$C$1040,3,1)),C126,VLOOKUP(H126,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H126,$A$2:$C$1041,3,1)),C126,VLOOKUP(H126,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C126" s="1">
@@ -11048,7 +11057,7 @@
         <v>396</v>
       </c>
       <c r="B127" s="5">
-        <f>IF(ISNA(VLOOKUP(H127,$A$2:$C$1040,3,1)),C127,VLOOKUP(H127,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H127,$A$2:$C$1041,3,1)),C127,VLOOKUP(H127,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C127" s="1">
@@ -11081,7 +11090,7 @@
         <v>399</v>
       </c>
       <c r="B128" s="5">
-        <f>IF(ISNA(VLOOKUP(H128,$A$2:$C$1040,3,1)),C128,VLOOKUP(H128,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H128,$A$2:$C$1041,3,1)),C128,VLOOKUP(H128,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C128" s="1">
@@ -11114,7 +11123,7 @@
         <v>402</v>
       </c>
       <c r="B129" s="5">
-        <f>IF(ISNA(VLOOKUP(H129,$A$2:$C$1040,3,1)),C129,VLOOKUP(H129,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H129,$A$2:$C$1041,3,1)),C129,VLOOKUP(H129,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C129" s="1">
@@ -11147,7 +11156,7 @@
         <v>405</v>
       </c>
       <c r="B130" s="5">
-        <f>IF(ISNA(VLOOKUP(H130,$A$2:$C$1040,3,1)),C130,VLOOKUP(H130,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H130,$A$2:$C$1041,3,1)),C130,VLOOKUP(H130,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C130" s="1">
@@ -11180,7 +11189,7 @@
         <v>409</v>
       </c>
       <c r="B131" s="5">
-        <f>IF(ISNA(VLOOKUP(H131,$A$2:$C$1040,3,1)),C131,VLOOKUP(H131,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H131,$A$2:$C$1041,3,1)),C131,VLOOKUP(H131,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C131" s="1">
@@ -11213,7 +11222,7 @@
         <v>412</v>
       </c>
       <c r="B132" s="5">
-        <f>IF(ISNA(VLOOKUP(H132,$A$2:$C$1040,3,1)),C132,VLOOKUP(H132,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H132,$A$2:$C$1041,3,1)),C132,VLOOKUP(H132,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C132" s="1">
@@ -11246,7 +11255,7 @@
         <v>415</v>
       </c>
       <c r="B133" s="5">
-        <f>IF(ISNA(VLOOKUP(H133,$A$2:$C$1040,3,1)),C133,VLOOKUP(H133,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H133,$A$2:$C$1041,3,1)),C133,VLOOKUP(H133,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C133" s="1">
@@ -11279,7 +11288,7 @@
         <v>418</v>
       </c>
       <c r="B134" s="5">
-        <f>IF(ISNA(VLOOKUP(H134,$A$2:$C$1040,3,1)),C134,VLOOKUP(H134,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H134,$A$2:$C$1041,3,1)),C134,VLOOKUP(H134,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C134" s="1">
@@ -11312,7 +11321,7 @@
         <v>421</v>
       </c>
       <c r="B135" s="5">
-        <f>IF(ISNA(VLOOKUP(H135,$A$2:$C$1040,3,1)),C135,VLOOKUP(H135,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H135,$A$2:$C$1041,3,1)),C135,VLOOKUP(H135,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C135" s="1">
@@ -11345,7 +11354,7 @@
         <v>47</v>
       </c>
       <c r="B136" s="5">
-        <f>IF(ISNA(VLOOKUP(H136,$A$2:$C$1040,3,1)),C136,VLOOKUP(H136,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H136,$A$2:$C$1041,3,1)),C136,VLOOKUP(H136,$A$2:$C$1041,3,1))</f>
         <v>526</v>
       </c>
       <c r="C136" s="1">
@@ -11378,7 +11387,7 @@
         <v>426</v>
       </c>
       <c r="B137" s="5">
-        <f>IF(ISNA(VLOOKUP(H137,$A$2:$C$1040,3,1)),C137,VLOOKUP(H137,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H137,$A$2:$C$1041,3,1)),C137,VLOOKUP(H137,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C137" s="1">
@@ -11411,7 +11420,7 @@
         <v>429</v>
       </c>
       <c r="B138" s="5">
-        <f>IF(ISNA(VLOOKUP(H138,$A$2:$C$1040,3,1)),C138,VLOOKUP(H138,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H138,$A$2:$C$1041,3,1)),C138,VLOOKUP(H138,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C138" s="1">
@@ -11444,7 +11453,7 @@
         <v>432</v>
       </c>
       <c r="B139" s="5">
-        <f>IF(ISNA(VLOOKUP(H139,$A$2:$C$1040,3,1)),C139,VLOOKUP(H139,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H139,$A$2:$C$1041,3,1)),C139,VLOOKUP(H139,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C139" s="1">
@@ -11477,7 +11486,7 @@
         <v>435</v>
       </c>
       <c r="B140" s="5">
-        <f>IF(ISNA(VLOOKUP(H140,$A$2:$C$1040,3,1)),C140,VLOOKUP(H140,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H140,$A$2:$C$1041,3,1)),C140,VLOOKUP(H140,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C140" s="1">
@@ -11510,7 +11519,7 @@
         <v>438</v>
       </c>
       <c r="B141" s="5">
-        <f>IF(ISNA(VLOOKUP(H141,$A$2:$C$1040,3,1)),C141,VLOOKUP(H141,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H141,$A$2:$C$1041,3,1)),C141,VLOOKUP(H141,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C141" s="1">
@@ -11543,7 +11552,7 @@
         <v>441</v>
       </c>
       <c r="B142" s="5">
-        <f>IF(ISNA(VLOOKUP(H142,$A$2:$C$1040,3,1)),C142,VLOOKUP(H142,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H142,$A$2:$C$1041,3,1)),C142,VLOOKUP(H142,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C142" s="1">
@@ -11576,7 +11585,7 @@
         <v>444</v>
       </c>
       <c r="B143" s="5">
-        <f>IF(ISNA(VLOOKUP(H143,$A$2:$C$1040,3,1)),C143,VLOOKUP(H143,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H143,$A$2:$C$1041,3,1)),C143,VLOOKUP(H143,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C143" s="1">
@@ -11609,7 +11618,7 @@
         <v>447</v>
       </c>
       <c r="B144" s="5">
-        <f>IF(ISNA(VLOOKUP(H144,$A$2:$C$1040,3,1)),C144,VLOOKUP(H144,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H144,$A$2:$C$1041,3,1)),C144,VLOOKUP(H144,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C144" s="1">
@@ -11642,7 +11651,7 @@
         <v>450</v>
       </c>
       <c r="B145" s="5">
-        <f>IF(ISNA(VLOOKUP(H145,$A$2:$C$1040,3,1)),C145,VLOOKUP(H145,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H145,$A$2:$C$1041,3,1)),C145,VLOOKUP(H145,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C145" s="1">
@@ -11675,7 +11684,7 @@
         <v>453</v>
       </c>
       <c r="B146" s="5">
-        <f>IF(ISNA(VLOOKUP(H146,$A$2:$C$1040,3,1)),C146,VLOOKUP(H146,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H146,$A$2:$C$1041,3,1)),C146,VLOOKUP(H146,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C146" s="1">
@@ -11708,7 +11717,7 @@
         <v>456</v>
       </c>
       <c r="B147" s="5">
-        <f>IF(ISNA(VLOOKUP(H147,$A$2:$C$1040,3,1)),C147,VLOOKUP(H147,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H147,$A$2:$C$1041,3,1)),C147,VLOOKUP(H147,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C147" s="1">
@@ -11741,7 +11750,7 @@
         <v>459</v>
       </c>
       <c r="B148" s="5">
-        <f>IF(ISNA(VLOOKUP(H148,$A$2:$C$1040,3,1)),C148,VLOOKUP(H148,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H148,$A$2:$C$1041,3,1)),C148,VLOOKUP(H148,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C148" s="1">
@@ -11774,7 +11783,7 @@
         <v>462</v>
       </c>
       <c r="B149" s="5">
-        <f>IF(ISNA(VLOOKUP(H149,$A$2:$C$1040,3,1)),C149,VLOOKUP(H149,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H149,$A$2:$C$1041,3,1)),C149,VLOOKUP(H149,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C149" s="1">
@@ -11807,7 +11816,7 @@
         <v>465</v>
       </c>
       <c r="B150" s="5">
-        <f>IF(ISNA(VLOOKUP(H150,$A$2:$C$1040,3,1)),C150,VLOOKUP(H150,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H150,$A$2:$C$1041,3,1)),C150,VLOOKUP(H150,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C150" s="1">
@@ -11840,7 +11849,7 @@
         <v>468</v>
       </c>
       <c r="B151" s="5">
-        <f>IF(ISNA(VLOOKUP(H151,$A$2:$C$1040,3,1)),C151,VLOOKUP(H151,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H151,$A$2:$C$1041,3,1)),C151,VLOOKUP(H151,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C151" s="1">
@@ -11873,7 +11882,7 @@
         <v>471</v>
       </c>
       <c r="B152" s="5">
-        <f>IF(ISNA(VLOOKUP(H152,$A$2:$C$1040,3,1)),C152,VLOOKUP(H152,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H152,$A$2:$C$1041,3,1)),C152,VLOOKUP(H152,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C152" s="1">
@@ -11906,7 +11915,7 @@
         <v>474</v>
       </c>
       <c r="B153" s="5">
-        <f>IF(ISNA(VLOOKUP(H153,$A$2:$C$1040,3,1)),C153,VLOOKUP(H153,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H153,$A$2:$C$1041,3,1)),C153,VLOOKUP(H153,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C153" s="1">
@@ -11939,7 +11948,7 @@
         <v>477</v>
       </c>
       <c r="B154" s="5">
-        <f>IF(ISNA(VLOOKUP(H154,$A$2:$C$1040,3,1)),C154,VLOOKUP(H154,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H154,$A$2:$C$1041,3,1)),C154,VLOOKUP(H154,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C154" s="1">
@@ -11972,7 +11981,7 @@
         <v>480</v>
       </c>
       <c r="B155" s="5">
-        <f>IF(ISNA(VLOOKUP(H155,$A$2:$C$1040,3,1)),C155,VLOOKUP(H155,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H155,$A$2:$C$1041,3,1)),C155,VLOOKUP(H155,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C155" s="1">
@@ -12005,7 +12014,7 @@
         <v>483</v>
       </c>
       <c r="B156" s="5">
-        <f>IF(ISNA(VLOOKUP(H156,$A$2:$C$1040,3,1)),C156,VLOOKUP(H156,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H156,$A$2:$C$1041,3,1)),C156,VLOOKUP(H156,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C156" s="1">
@@ -12039,7 +12048,7 @@
         <v>486</v>
       </c>
       <c r="B157" s="5">
-        <f>IF(ISNA(VLOOKUP(H157,$A$2:$C$1040,3,1)),C157,VLOOKUP(H157,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H157,$A$2:$C$1041,3,1)),C157,VLOOKUP(H157,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C157" s="1">
@@ -12072,7 +12081,7 @@
         <v>489</v>
       </c>
       <c r="B158" s="5">
-        <f>IF(ISNA(VLOOKUP(H158,$A$2:$C$1040,3,1)),C158,VLOOKUP(H158,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H158,$A$2:$C$1041,3,1)),C158,VLOOKUP(H158,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C158" s="1">
@@ -12107,7 +12116,7 @@
         <v>492</v>
       </c>
       <c r="B159" s="5">
-        <f>IF(ISNA(VLOOKUP(H159,$A$2:$C$1040,3,1)),C159,VLOOKUP(H159,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H159,$A$2:$C$1041,3,1)),C159,VLOOKUP(H159,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C159" s="1">
@@ -12140,7 +12149,7 @@
         <v>495</v>
       </c>
       <c r="B160" s="5">
-        <f>IF(ISNA(VLOOKUP(H160,$A$2:$C$1040,3,1)),C160,VLOOKUP(H160,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H160,$A$2:$C$1041,3,1)),C160,VLOOKUP(H160,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C160" s="1">
@@ -12173,7 +12182,7 @@
         <v>498</v>
       </c>
       <c r="B161" s="5">
-        <f>IF(ISNA(VLOOKUP(H161,$A$2:$C$1040,3,1)),C161,VLOOKUP(H161,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H161,$A$2:$C$1041,3,1)),C161,VLOOKUP(H161,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C161" s="1">
@@ -12206,7 +12215,7 @@
         <v>501</v>
       </c>
       <c r="B162" s="5">
-        <f>IF(ISNA(VLOOKUP(H162,$A$2:$C$1040,3,1)),C162,VLOOKUP(H162,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H162,$A$2:$C$1041,3,1)),C162,VLOOKUP(H162,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C162" s="1">
@@ -12239,7 +12248,7 @@
         <v>504</v>
       </c>
       <c r="B163" s="5">
-        <f>IF(ISNA(VLOOKUP(H163,$A$2:$C$1040,3,1)),C163,VLOOKUP(H163,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H163,$A$2:$C$1041,3,1)),C163,VLOOKUP(H163,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C163" s="1">
@@ -12272,7 +12281,7 @@
         <v>507</v>
       </c>
       <c r="B164" s="5">
-        <f>IF(ISNA(VLOOKUP(H164,$A$2:$C$1040,3,1)),C164,VLOOKUP(H164,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H164,$A$2:$C$1041,3,1)),C164,VLOOKUP(H164,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C164" s="1">
@@ -12305,7 +12314,7 @@
         <v>510</v>
       </c>
       <c r="B165" s="5">
-        <f>IF(ISNA(VLOOKUP(H165,$A$2:$C$1040,3,1)),C165,VLOOKUP(H165,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H165,$A$2:$C$1041,3,1)),C165,VLOOKUP(H165,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C165" s="1">
@@ -12338,7 +12347,7 @@
         <v>513</v>
       </c>
       <c r="B166" s="5">
-        <f>IF(ISNA(VLOOKUP(H166,$A$2:$C$1040,3,1)),C166,VLOOKUP(H166,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H166,$A$2:$C$1041,3,1)),C166,VLOOKUP(H166,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C166" s="1">
@@ -12371,7 +12380,7 @@
         <v>516</v>
       </c>
       <c r="B167" s="5">
-        <f>IF(ISNA(VLOOKUP(H167,$A$2:$C$1040,3,1)),C167,VLOOKUP(H167,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H167,$A$2:$C$1041,3,1)),C167,VLOOKUP(H167,$A$2:$C$1041,3,1))</f>
         <v>551</v>
       </c>
       <c r="C167" s="1">
@@ -12404,7 +12413,7 @@
         <v>519</v>
       </c>
       <c r="B168" s="5">
-        <f>IF(ISNA(VLOOKUP(H168,$A$2:$C$1040,3,1)),C168,VLOOKUP(H168,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H168,$A$2:$C$1041,3,1)),C168,VLOOKUP(H168,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C168" s="1">
@@ -12437,7 +12446,7 @@
         <v>522</v>
       </c>
       <c r="B169" s="5">
-        <f>IF(ISNA(VLOOKUP(H169,$A$2:$C$1040,3,1)),C169,VLOOKUP(H169,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H169,$A$2:$C$1041,3,1)),C169,VLOOKUP(H169,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C169" s="1">
@@ -12470,7 +12479,7 @@
         <v>525</v>
       </c>
       <c r="B170" s="5">
-        <f>IF(ISNA(VLOOKUP(H170,$A$2:$C$1040,3,1)),C170,VLOOKUP(H170,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H170,$A$2:$C$1041,3,1)),C170,VLOOKUP(H170,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C170" s="1">
@@ -12503,7 +12512,7 @@
         <v>528</v>
       </c>
       <c r="B171" s="5">
-        <f>IF(ISNA(VLOOKUP(H171,$A$2:$C$1040,3,1)),C171,VLOOKUP(H171,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H171,$A$2:$C$1041,3,1)),C171,VLOOKUP(H171,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C171" s="1">
@@ -12536,7 +12545,7 @@
         <v>531</v>
       </c>
       <c r="B172" s="5">
-        <f>IF(ISNA(VLOOKUP(H172,$A$2:$C$1040,3,1)),C172,VLOOKUP(H172,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H172,$A$2:$C$1041,3,1)),C172,VLOOKUP(H172,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C172" s="1">
@@ -12569,7 +12578,7 @@
         <v>534</v>
       </c>
       <c r="B173" s="5">
-        <f>IF(ISNA(VLOOKUP(H173,$A$2:$C$1040,3,1)),C173,VLOOKUP(H173,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H173,$A$2:$C$1041,3,1)),C173,VLOOKUP(H173,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C173" s="1">
@@ -12602,7 +12611,7 @@
         <v>537</v>
       </c>
       <c r="B174" s="5">
-        <f>IF(ISNA(VLOOKUP(H174,$A$2:$C$1040,3,1)),C174,VLOOKUP(H174,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H174,$A$2:$C$1041,3,1)),C174,VLOOKUP(H174,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C174" s="1">
@@ -12635,7 +12644,7 @@
         <v>540</v>
       </c>
       <c r="B175" s="5">
-        <f>IF(ISNA(VLOOKUP(H175,$A$2:$C$1040,3,1)),C175,VLOOKUP(H175,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H175,$A$2:$C$1041,3,1)),C175,VLOOKUP(H175,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C175" s="1">
@@ -12668,7 +12677,7 @@
         <v>543</v>
       </c>
       <c r="B176" s="5">
-        <f>IF(ISNA(VLOOKUP(H176,$A$2:$C$1040,3,1)),C176,VLOOKUP(H176,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H176,$A$2:$C$1041,3,1)),C176,VLOOKUP(H176,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C176" s="1">
@@ -12701,7 +12710,7 @@
         <v>546</v>
       </c>
       <c r="B177" s="5">
-        <f>IF(ISNA(VLOOKUP(H177,$A$2:$C$1040,3,1)),C177,VLOOKUP(H177,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H177,$A$2:$C$1041,3,1)),C177,VLOOKUP(H177,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C177" s="1">
@@ -12734,7 +12743,7 @@
         <v>549</v>
       </c>
       <c r="B178" s="5">
-        <f>IF(ISNA(VLOOKUP(H178,$A$2:$C$1040,3,1)),C178,VLOOKUP(H178,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H178,$A$2:$C$1041,3,1)),C178,VLOOKUP(H178,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C178" s="1">
@@ -12767,7 +12776,7 @@
         <v>552</v>
       </c>
       <c r="B179" s="5">
-        <f>IF(ISNA(VLOOKUP(H179,$A$2:$C$1040,3,1)),C179,VLOOKUP(H179,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H179,$A$2:$C$1041,3,1)),C179,VLOOKUP(H179,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C179" s="1">
@@ -12800,7 +12809,7 @@
         <v>555</v>
       </c>
       <c r="B180" s="5">
-        <f>IF(ISNA(VLOOKUP(H180,$A$2:$C$1040,3,1)),C180,VLOOKUP(H180,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H180,$A$2:$C$1041,3,1)),C180,VLOOKUP(H180,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C180" s="1">
@@ -12833,7 +12842,7 @@
         <v>558</v>
       </c>
       <c r="B181" s="5">
-        <f>IF(ISNA(VLOOKUP(H181,$A$2:$C$1040,3,1)),C181,VLOOKUP(H181,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H181,$A$2:$C$1041,3,1)),C181,VLOOKUP(H181,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C181" s="1">
@@ -12866,7 +12875,7 @@
         <v>561</v>
       </c>
       <c r="B182" s="5">
-        <f>IF(ISNA(VLOOKUP(H182,$A$2:$C$1040,3,1)),C182,VLOOKUP(H182,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H182,$A$2:$C$1041,3,1)),C182,VLOOKUP(H182,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C182" s="1">
@@ -12899,7 +12908,7 @@
         <v>564</v>
       </c>
       <c r="B183" s="5">
-        <f>IF(ISNA(VLOOKUP(H183,$A$2:$C$1040,3,1)),C183,VLOOKUP(H183,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H183,$A$2:$C$1041,3,1)),C183,VLOOKUP(H183,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C183" s="1">
@@ -12932,7 +12941,7 @@
         <v>567</v>
       </c>
       <c r="B184" s="5">
-        <f>IF(ISNA(VLOOKUP(H184,$A$2:$C$1040,3,1)),C184,VLOOKUP(H184,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H184,$A$2:$C$1041,3,1)),C184,VLOOKUP(H184,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C184" s="1">
@@ -12965,7 +12974,7 @@
         <v>570</v>
       </c>
       <c r="B185" s="5">
-        <f>IF(ISNA(VLOOKUP(H185,$A$2:$C$1040,3,1)),C185,VLOOKUP(H185,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H185,$A$2:$C$1041,3,1)),C185,VLOOKUP(H185,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C185" s="1">
@@ -12998,7 +13007,7 @@
         <v>573</v>
       </c>
       <c r="B186" s="5">
-        <f>IF(ISNA(VLOOKUP(H186,$A$2:$C$1040,3,1)),C186,VLOOKUP(H186,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H186,$A$2:$C$1041,3,1)),C186,VLOOKUP(H186,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C186" s="1">
@@ -13031,7 +13040,7 @@
         <v>576</v>
       </c>
       <c r="B187" s="5">
-        <f>IF(ISNA(VLOOKUP(H187,$A$2:$C$1040,3,1)),C187,VLOOKUP(H187,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H187,$A$2:$C$1041,3,1)),C187,VLOOKUP(H187,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C187" s="1">
@@ -13064,7 +13073,7 @@
         <v>579</v>
       </c>
       <c r="B188" s="5">
-        <f>IF(ISNA(VLOOKUP(H188,$A$2:$C$1040,3,1)),C188,VLOOKUP(H188,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H188,$A$2:$C$1041,3,1)),C188,VLOOKUP(H188,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C188" s="1">
@@ -13097,7 +13106,7 @@
         <v>582</v>
       </c>
       <c r="B189" s="5">
-        <f>IF(ISNA(VLOOKUP(H189,$A$2:$C$1040,3,1)),C189,VLOOKUP(H189,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H189,$A$2:$C$1041,3,1)),C189,VLOOKUP(H189,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C189" s="1">
@@ -13130,7 +13139,7 @@
         <v>585</v>
       </c>
       <c r="B190" s="5">
-        <f>IF(ISNA(VLOOKUP(H190,$A$2:$C$1040,3,1)),C190,VLOOKUP(H190,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H190,$A$2:$C$1041,3,1)),C190,VLOOKUP(H190,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C190" s="1">
@@ -13163,7 +13172,7 @@
         <v>588</v>
       </c>
       <c r="B191" s="5">
-        <f>IF(ISNA(VLOOKUP(H191,$A$2:$C$1040,3,1)),C191,VLOOKUP(H191,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H191,$A$2:$C$1041,3,1)),C191,VLOOKUP(H191,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C191" s="1">
@@ -13196,7 +13205,7 @@
         <v>591</v>
       </c>
       <c r="B192" s="5">
-        <f>IF(ISNA(VLOOKUP(H192,$A$2:$C$1040,3,1)),C192,VLOOKUP(H192,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H192,$A$2:$C$1041,3,1)),C192,VLOOKUP(H192,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C192" s="1">
@@ -13229,7 +13238,7 @@
         <v>594</v>
       </c>
       <c r="B193" s="5">
-        <f>IF(ISNA(VLOOKUP(H193,$A$2:$C$1040,3,1)),C193,VLOOKUP(H193,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H193,$A$2:$C$1041,3,1)),C193,VLOOKUP(H193,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C193" s="1">
@@ -13262,7 +13271,7 @@
         <v>597</v>
       </c>
       <c r="B194" s="5">
-        <f>IF(ISNA(VLOOKUP(H194,$A$2:$C$1040,3,1)),C194,VLOOKUP(H194,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H194,$A$2:$C$1041,3,1)),C194,VLOOKUP(H194,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C194" s="1">
@@ -13295,7 +13304,7 @@
         <v>600</v>
       </c>
       <c r="B195" s="5">
-        <f>IF(ISNA(VLOOKUP(H195,$A$2:$C$1040,3,1)),C195,VLOOKUP(H195,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H195,$A$2:$C$1041,3,1)),C195,VLOOKUP(H195,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C195" s="1">
@@ -13328,7 +13337,7 @@
         <v>603</v>
       </c>
       <c r="B196" s="5">
-        <f>IF(ISNA(VLOOKUP(H196,$A$2:$C$1040,3,1)),C196,VLOOKUP(H196,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H196,$A$2:$C$1041,3,1)),C196,VLOOKUP(H196,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C196" s="1">
@@ -13361,7 +13370,7 @@
         <v>606</v>
       </c>
       <c r="B197" s="5">
-        <f>IF(ISNA(VLOOKUP(H197,$A$2:$C$1040,3,1)),C197,VLOOKUP(H197,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H197,$A$2:$C$1041,3,1)),C197,VLOOKUP(H197,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C197" s="1">
@@ -13394,7 +13403,7 @@
         <v>609</v>
       </c>
       <c r="B198" s="5">
-        <f>IF(ISNA(VLOOKUP(H198,$A$2:$C$1040,3,1)),C198,VLOOKUP(H198,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H198,$A$2:$C$1041,3,1)),C198,VLOOKUP(H198,$A$2:$C$1041,3,1))</f>
         <v>162</v>
       </c>
       <c r="C198" s="1">
@@ -13427,7 +13436,7 @@
         <v>612</v>
       </c>
       <c r="B199" s="5">
-        <f>IF(ISNA(VLOOKUP(H199,$A$2:$C$1040,3,1)),C199,VLOOKUP(H199,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H199,$A$2:$C$1041,3,1)),C199,VLOOKUP(H199,$A$2:$C$1041,3,1))</f>
         <v>162</v>
       </c>
       <c r="C199" s="1">
@@ -13460,7 +13469,7 @@
         <v>615</v>
       </c>
       <c r="B200" s="5">
-        <f>IF(ISNA(VLOOKUP(H200,$A$2:$C$1040,3,1)),C200,VLOOKUP(H200,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H200,$A$2:$C$1041,3,1)),C200,VLOOKUP(H200,$A$2:$C$1041,3,1))</f>
         <v>172</v>
       </c>
       <c r="C200" s="1">
@@ -13493,7 +13502,7 @@
         <v>618</v>
       </c>
       <c r="B201" s="5">
-        <f>IF(ISNA(VLOOKUP(H201,$A$2:$C$1040,3,1)),C201,VLOOKUP(H201,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H201,$A$2:$C$1041,3,1)),C201,VLOOKUP(H201,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C201" s="1">
@@ -13526,7 +13535,7 @@
         <v>621</v>
       </c>
       <c r="B202" s="5">
-        <f>IF(ISNA(VLOOKUP(H202,$A$2:$C$1040,3,1)),C202,VLOOKUP(H202,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H202,$A$2:$C$1041,3,1)),C202,VLOOKUP(H202,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C202" s="1">
@@ -13559,7 +13568,7 @@
         <v>624</v>
       </c>
       <c r="B203" s="5">
-        <f>IF(ISNA(VLOOKUP(H203,$A$2:$C$1040,3,1)),C203,VLOOKUP(H203,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H203,$A$2:$C$1041,3,1)),C203,VLOOKUP(H203,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C203" s="1">
@@ -13592,7 +13601,7 @@
         <v>627</v>
       </c>
       <c r="B204" s="5">
-        <f>IF(ISNA(VLOOKUP(H204,$A$2:$C$1040,3,1)),C204,VLOOKUP(H204,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H204,$A$2:$C$1041,3,1)),C204,VLOOKUP(H204,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C204" s="1">
@@ -13625,7 +13634,7 @@
         <v>630</v>
       </c>
       <c r="B205" s="5">
-        <f>IF(ISNA(VLOOKUP(H205,$A$2:$C$1040,3,1)),C205,VLOOKUP(H205,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H205,$A$2:$C$1041,3,1)),C205,VLOOKUP(H205,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C205" s="1">
@@ -13658,7 +13667,7 @@
         <v>633</v>
       </c>
       <c r="B206" s="5">
-        <f>IF(ISNA(VLOOKUP(H206,$A$2:$C$1040,3,1)),C206,VLOOKUP(H206,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H206,$A$2:$C$1041,3,1)),C206,VLOOKUP(H206,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C206" s="1">
@@ -13691,7 +13700,7 @@
         <v>636</v>
       </c>
       <c r="B207" s="5">
-        <f>IF(ISNA(VLOOKUP(H207,$A$2:$C$1040,3,1)),C207,VLOOKUP(H207,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H207,$A$2:$C$1041,3,1)),C207,VLOOKUP(H207,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C207" s="1">
@@ -13724,7 +13733,7 @@
         <v>639</v>
       </c>
       <c r="B208" s="5">
-        <f>IF(ISNA(VLOOKUP(H208,$A$2:$C$1040,3,1)),C208,VLOOKUP(H208,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H208,$A$2:$C$1041,3,1)),C208,VLOOKUP(H208,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C208" s="1">
@@ -13757,7 +13766,7 @@
         <v>1987</v>
       </c>
       <c r="B209" s="13">
-        <f>IF(ISNA(VLOOKUP(H209,$A$2:$C$1040,3,1)),C209,VLOOKUP(H209,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H209,$A$2:$C$1041,3,1)),C209,VLOOKUP(H209,$A$2:$C$1041,3,1))</f>
         <v>206</v>
       </c>
       <c r="C209" s="1">
@@ -13793,7 +13802,7 @@
         <v>1988</v>
       </c>
       <c r="B210" s="13">
-        <f>IF(ISNA(VLOOKUP(H210,$A$2:$C$1040,3,1)),C210,VLOOKUP(H210,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H210,$A$2:$C$1041,3,1)),C210,VLOOKUP(H210,$A$2:$C$1041,3,1))</f>
         <v>214</v>
       </c>
       <c r="C210" s="1">
@@ -13829,7 +13838,7 @@
         <v>642</v>
       </c>
       <c r="B211" s="5">
-        <f>IF(ISNA(VLOOKUP(H211,$A$2:$C$1040,3,1)),C211,VLOOKUP(H211,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H211,$A$2:$C$1041,3,1)),C211,VLOOKUP(H211,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C211" s="1">
@@ -13862,7 +13871,7 @@
         <v>645</v>
       </c>
       <c r="B212" s="5">
-        <f>IF(ISNA(VLOOKUP(H212,$A$2:$C$1040,3,1)),C212,VLOOKUP(H212,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H212,$A$2:$C$1041,3,1)),C212,VLOOKUP(H212,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C212" s="1">
@@ -13895,7 +13904,7 @@
         <v>648</v>
       </c>
       <c r="B213" s="5">
-        <f>IF(ISNA(VLOOKUP(H213,$A$2:$C$1040,3,1)),C213,VLOOKUP(H213,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H213,$A$2:$C$1041,3,1)),C213,VLOOKUP(H213,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C213" s="1">
@@ -13928,7 +13937,7 @@
         <v>651</v>
       </c>
       <c r="B214" s="5">
-        <f>IF(ISNA(VLOOKUP(H214,$A$2:$C$1040,3,1)),C214,VLOOKUP(H214,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H214,$A$2:$C$1041,3,1)),C214,VLOOKUP(H214,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C214" s="1">
@@ -13961,7 +13970,7 @@
         <v>654</v>
       </c>
       <c r="B215" s="5">
-        <f>IF(ISNA(VLOOKUP(H215,$A$2:$C$1040,3,1)),C215,VLOOKUP(H215,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H215,$A$2:$C$1041,3,1)),C215,VLOOKUP(H215,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C215" s="1">
@@ -13994,7 +14003,7 @@
         <v>657</v>
       </c>
       <c r="B216" s="5">
-        <f>IF(ISNA(VLOOKUP(H216,$A$2:$C$1040,3,1)),C216,VLOOKUP(H216,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H216,$A$2:$C$1041,3,1)),C216,VLOOKUP(H216,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C216" s="1">
@@ -14027,7 +14036,7 @@
         <v>660</v>
       </c>
       <c r="B217" s="5">
-        <f>IF(ISNA(VLOOKUP(H217,$A$2:$C$1040,3,1)),C217,VLOOKUP(H217,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H217,$A$2:$C$1041,3,1)),C217,VLOOKUP(H217,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C217" s="1">
@@ -14060,7 +14069,7 @@
         <v>663</v>
       </c>
       <c r="B218" s="5">
-        <f>IF(ISNA(VLOOKUP(H218,$A$2:$C$1040,3,1)),C218,VLOOKUP(H218,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H218,$A$2:$C$1041,3,1)),C218,VLOOKUP(H218,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C218" s="1">
@@ -14093,7 +14102,7 @@
         <v>666</v>
       </c>
       <c r="B219" s="5">
-        <f>IF(ISNA(VLOOKUP(H219,$A$2:$C$1040,3,1)),C219,VLOOKUP(H219,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H219,$A$2:$C$1041,3,1)),C219,VLOOKUP(H219,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C219" s="1">
@@ -14126,7 +14135,7 @@
         <v>669</v>
       </c>
       <c r="B220" s="5">
-        <f>IF(ISNA(VLOOKUP(H220,$A$2:$C$1040,3,1)),C220,VLOOKUP(H220,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H220,$A$2:$C$1041,3,1)),C220,VLOOKUP(H220,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C220" s="1">
@@ -14159,7 +14168,7 @@
         <v>672</v>
       </c>
       <c r="B221" s="5">
-        <f>IF(ISNA(VLOOKUP(H221,$A$2:$C$1040,3,1)),C221,VLOOKUP(H221,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H221,$A$2:$C$1041,3,1)),C221,VLOOKUP(H221,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C221" s="1">
@@ -14192,7 +14201,7 @@
         <v>675</v>
       </c>
       <c r="B222" s="5">
-        <f>IF(ISNA(VLOOKUP(H222,$A$2:$C$1040,3,1)),C222,VLOOKUP(H222,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H222,$A$2:$C$1041,3,1)),C222,VLOOKUP(H222,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C222" s="1">
@@ -14225,7 +14234,7 @@
         <v>678</v>
       </c>
       <c r="B223" s="5">
-        <f>IF(ISNA(VLOOKUP(H223,$A$2:$C$1040,3,1)),C223,VLOOKUP(H223,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H223,$A$2:$C$1041,3,1)),C223,VLOOKUP(H223,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C223" s="1">
@@ -14258,7 +14267,7 @@
         <v>681</v>
       </c>
       <c r="B224" s="5">
-        <f>IF(ISNA(VLOOKUP(H224,$A$2:$C$1040,3,1)),C224,VLOOKUP(H224,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H224,$A$2:$C$1041,3,1)),C224,VLOOKUP(H224,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C224" s="1">
@@ -14291,7 +14300,7 @@
         <v>684</v>
       </c>
       <c r="B225" s="5">
-        <f>IF(ISNA(VLOOKUP(H225,$A$2:$C$1040,3,1)),C225,VLOOKUP(H225,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H225,$A$2:$C$1041,3,1)),C225,VLOOKUP(H225,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C225" s="1">
@@ -14324,7 +14333,7 @@
         <v>687</v>
       </c>
       <c r="B226" s="5">
-        <f>IF(ISNA(VLOOKUP(H226,$A$2:$C$1040,3,1)),C226,VLOOKUP(H226,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H226,$A$2:$C$1041,3,1)),C226,VLOOKUP(H226,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C226" s="1">
@@ -14357,7 +14366,7 @@
         <v>690</v>
       </c>
       <c r="B227" s="5">
-        <f>IF(ISNA(VLOOKUP(H227,$A$2:$C$1040,3,1)),C227,VLOOKUP(H227,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H227,$A$2:$C$1041,3,1)),C227,VLOOKUP(H227,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C227" s="1">
@@ -14390,7 +14399,7 @@
         <v>693</v>
       </c>
       <c r="B228" s="5">
-        <f>IF(ISNA(VLOOKUP(H228,$A$2:$C$1040,3,1)),C228,VLOOKUP(H228,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H228,$A$2:$C$1041,3,1)),C228,VLOOKUP(H228,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C228" s="1">
@@ -14423,7 +14432,7 @@
         <v>696</v>
       </c>
       <c r="B229" s="5">
-        <f>IF(ISNA(VLOOKUP(H229,$A$2:$C$1040,3,1)),C229,VLOOKUP(H229,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H229,$A$2:$C$1041,3,1)),C229,VLOOKUP(H229,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C229" s="1">
@@ -14456,7 +14465,7 @@
         <v>699</v>
       </c>
       <c r="B230" s="5">
-        <f>IF(ISNA(VLOOKUP(H230,$A$2:$C$1040,3,1)),C230,VLOOKUP(H230,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H230,$A$2:$C$1041,3,1)),C230,VLOOKUP(H230,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C230" s="1">
@@ -14489,7 +14498,7 @@
         <v>702</v>
       </c>
       <c r="B231" s="5">
-        <f>IF(ISNA(VLOOKUP(H231,$A$2:$C$1040,3,1)),C231,VLOOKUP(H231,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H231,$A$2:$C$1041,3,1)),C231,VLOOKUP(H231,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C231" s="1">
@@ -14522,7 +14531,7 @@
         <v>705</v>
       </c>
       <c r="B232" s="5">
-        <f>IF(ISNA(VLOOKUP(H232,$A$2:$C$1040,3,1)),C232,VLOOKUP(H232,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H232,$A$2:$C$1041,3,1)),C232,VLOOKUP(H232,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C232" s="1">
@@ -14555,7 +14564,7 @@
         <v>708</v>
       </c>
       <c r="B233" s="5">
-        <f>IF(ISNA(VLOOKUP(H233,$A$2:$C$1040,3,1)),C233,VLOOKUP(H233,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H233,$A$2:$C$1041,3,1)),C233,VLOOKUP(H233,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C233" s="1">
@@ -14588,7 +14597,7 @@
         <v>711</v>
       </c>
       <c r="B234" s="5">
-        <f>IF(ISNA(VLOOKUP(H234,$A$2:$C$1040,3,1)),C234,VLOOKUP(H234,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H234,$A$2:$C$1041,3,1)),C234,VLOOKUP(H234,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C234" s="1">
@@ -14621,7 +14630,7 @@
         <v>714</v>
       </c>
       <c r="B235" s="5">
-        <f>IF(ISNA(VLOOKUP(H235,$A$2:$C$1040,3,1)),C235,VLOOKUP(H235,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H235,$A$2:$C$1041,3,1)),C235,VLOOKUP(H235,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C235" s="1">
@@ -14654,7 +14663,7 @@
         <v>717</v>
       </c>
       <c r="B236" s="5">
-        <f>IF(ISNA(VLOOKUP(H236,$A$2:$C$1040,3,1)),C236,VLOOKUP(H236,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H236,$A$2:$C$1041,3,1)),C236,VLOOKUP(H236,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C236" s="1">
@@ -14687,7 +14696,7 @@
         <v>720</v>
       </c>
       <c r="B237" s="5">
-        <f>IF(ISNA(VLOOKUP(H237,$A$2:$C$1040,3,1)),C237,VLOOKUP(H237,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H237,$A$2:$C$1041,3,1)),C237,VLOOKUP(H237,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C237" s="1">
@@ -14720,7 +14729,7 @@
         <v>723</v>
       </c>
       <c r="B238" s="5">
-        <f>IF(ISNA(VLOOKUP(H238,$A$2:$C$1040,3,1)),C238,VLOOKUP(H238,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H238,$A$2:$C$1041,3,1)),C238,VLOOKUP(H238,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C238" s="1">
@@ -14753,7 +14762,7 @@
         <v>726</v>
       </c>
       <c r="B239" s="5">
-        <f>IF(ISNA(VLOOKUP(H239,$A$2:$C$1040,3,1)),C239,VLOOKUP(H239,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H239,$A$2:$C$1041,3,1)),C239,VLOOKUP(H239,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C239" s="1">
@@ -14786,7 +14795,7 @@
         <v>729</v>
       </c>
       <c r="B240" s="5">
-        <f>IF(ISNA(VLOOKUP(H240,$A$2:$C$1040,3,1)),C240,VLOOKUP(H240,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H240,$A$2:$C$1041,3,1)),C240,VLOOKUP(H240,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C240" s="1">
@@ -14819,7 +14828,7 @@
         <v>732</v>
       </c>
       <c r="B241" s="5">
-        <f>IF(ISNA(VLOOKUP(H241,$A$2:$C$1040,3,1)),C241,VLOOKUP(H241,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H241,$A$2:$C$1041,3,1)),C241,VLOOKUP(H241,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C241" s="1">
@@ -14852,7 +14861,7 @@
         <v>735</v>
       </c>
       <c r="B242" s="5">
-        <f>IF(ISNA(VLOOKUP(H242,$A$2:$C$1040,3,1)),C242,VLOOKUP(H242,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H242,$A$2:$C$1041,3,1)),C242,VLOOKUP(H242,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C242" s="1">
@@ -14885,7 +14894,7 @@
         <v>738</v>
       </c>
       <c r="B243" s="5">
-        <f>IF(ISNA(VLOOKUP(H243,$A$2:$C$1040,3,1)),C243,VLOOKUP(H243,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H243,$A$2:$C$1041,3,1)),C243,VLOOKUP(H243,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C243" s="1">
@@ -14918,7 +14927,7 @@
         <v>741</v>
       </c>
       <c r="B244" s="5">
-        <f>IF(ISNA(VLOOKUP(H244,$A$2:$C$1040,3,1)),C244,VLOOKUP(H244,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H244,$A$2:$C$1041,3,1)),C244,VLOOKUP(H244,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C244" s="1">
@@ -14951,7 +14960,7 @@
         <v>744</v>
       </c>
       <c r="B245" s="5">
-        <f>IF(ISNA(VLOOKUP(H245,$A$2:$C$1040,3,1)),C245,VLOOKUP(H245,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H245,$A$2:$C$1041,3,1)),C245,VLOOKUP(H245,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C245" s="1">
@@ -14984,7 +14993,7 @@
         <v>747</v>
       </c>
       <c r="B246" s="5">
-        <f>IF(ISNA(VLOOKUP(H246,$A$2:$C$1040,3,1)),C246,VLOOKUP(H246,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H246,$A$2:$C$1041,3,1)),C246,VLOOKUP(H246,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C246" s="1">
@@ -15017,7 +15026,7 @@
         <v>750</v>
       </c>
       <c r="B247" s="5">
-        <f>IF(ISNA(VLOOKUP(H247,$A$2:$C$1040,3,1)),C247,VLOOKUP(H247,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H247,$A$2:$C$1041,3,1)),C247,VLOOKUP(H247,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C247" s="1">
@@ -15050,7 +15059,7 @@
         <v>753</v>
       </c>
       <c r="B248" s="5">
-        <f>IF(ISNA(VLOOKUP(H248,$A$2:$C$1040,3,1)),C248,VLOOKUP(H248,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H248,$A$2:$C$1041,3,1)),C248,VLOOKUP(H248,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C248" s="1">
@@ -15083,7 +15092,7 @@
         <v>756</v>
       </c>
       <c r="B249" s="5">
-        <f>IF(ISNA(VLOOKUP(H249,$A$2:$C$1040,3,1)),C249,VLOOKUP(H249,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H249,$A$2:$C$1041,3,1)),C249,VLOOKUP(H249,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C249" s="1">
@@ -15116,7 +15125,7 @@
         <v>759</v>
       </c>
       <c r="B250" s="5">
-        <f>IF(ISNA(VLOOKUP(H250,$A$2:$C$1040,3,1)),C250,VLOOKUP(H250,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H250,$A$2:$C$1041,3,1)),C250,VLOOKUP(H250,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C250" s="1">
@@ -15149,7 +15158,7 @@
         <v>762</v>
       </c>
       <c r="B251" s="5">
-        <f>IF(ISNA(VLOOKUP(H251,$A$2:$C$1040,3,1)),C251,VLOOKUP(H251,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H251,$A$2:$C$1041,3,1)),C251,VLOOKUP(H251,$A$2:$C$1041,3,1))</f>
         <v>367</v>
       </c>
       <c r="C251" s="1">
@@ -15182,7 +15191,7 @@
         <v>765</v>
       </c>
       <c r="B252" s="5">
-        <f>IF(ISNA(VLOOKUP(H252,$A$2:$C$1040,3,1)),C252,VLOOKUP(H252,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H252,$A$2:$C$1041,3,1)),C252,VLOOKUP(H252,$A$2:$C$1041,3,1))</f>
         <v>367</v>
       </c>
       <c r="C252" s="1">
@@ -15215,7 +15224,7 @@
         <v>768</v>
       </c>
       <c r="B253" s="5">
-        <f>IF(ISNA(VLOOKUP(H253,$A$2:$C$1040,3,1)),C253,VLOOKUP(H253,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H253,$A$2:$C$1041,3,1)),C253,VLOOKUP(H253,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C253" s="1">
@@ -15248,7 +15257,7 @@
         <v>771</v>
       </c>
       <c r="B254" s="5">
-        <f>IF(ISNA(VLOOKUP(H254,$A$2:$C$1040,3,1)),C254,VLOOKUP(H254,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H254,$A$2:$C$1041,3,1)),C254,VLOOKUP(H254,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C254" s="1">
@@ -15281,7 +15290,7 @@
         <v>774</v>
       </c>
       <c r="B255" s="5">
-        <f>IF(ISNA(VLOOKUP(H255,$A$2:$C$1040,3,1)),C255,VLOOKUP(H255,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H255,$A$2:$C$1041,3,1)),C255,VLOOKUP(H255,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C255" s="1">
@@ -15314,7 +15323,7 @@
         <v>777</v>
       </c>
       <c r="B256" s="5">
-        <f>IF(ISNA(VLOOKUP(H256,$A$2:$C$1040,3,1)),C256,VLOOKUP(H256,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H256,$A$2:$C$1041,3,1)),C256,VLOOKUP(H256,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C256" s="1">
@@ -15347,7 +15356,7 @@
         <v>780</v>
       </c>
       <c r="B257" s="5">
-        <f>IF(ISNA(VLOOKUP(H257,$A$2:$C$1040,3,1)),C257,VLOOKUP(H257,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H257,$A$2:$C$1041,3,1)),C257,VLOOKUP(H257,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C257" s="1">
@@ -15380,7 +15389,7 @@
         <v>783</v>
       </c>
       <c r="B258" s="5">
-        <f>IF(ISNA(VLOOKUP(H258,$A$2:$C$1040,3,1)),C258,VLOOKUP(H258,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H258,$A$2:$C$1041,3,1)),C258,VLOOKUP(H258,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C258" s="1">
@@ -15413,7 +15422,7 @@
         <v>786</v>
       </c>
       <c r="B259" s="5">
-        <f>IF(ISNA(VLOOKUP(H259,$A$2:$C$1040,3,1)),C259,VLOOKUP(H259,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H259,$A$2:$C$1041,3,1)),C259,VLOOKUP(H259,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C259" s="1">
@@ -15446,7 +15455,7 @@
         <v>789</v>
       </c>
       <c r="B260" s="5">
-        <f>IF(ISNA(VLOOKUP(H260,$A$2:$C$1040,3,1)),C260,VLOOKUP(H260,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H260,$A$2:$C$1041,3,1)),C260,VLOOKUP(H260,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C260" s="1">
@@ -15479,7 +15488,7 @@
         <v>792</v>
       </c>
       <c r="B261" s="5">
-        <f>IF(ISNA(VLOOKUP(H261,$A$2:$C$1040,3,1)),C261,VLOOKUP(H261,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H261,$A$2:$C$1041,3,1)),C261,VLOOKUP(H261,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C261" s="1">
@@ -15512,7 +15521,7 @@
         <v>795</v>
       </c>
       <c r="B262" s="5">
-        <f>IF(ISNA(VLOOKUP(H262,$A$2:$C$1040,3,1)),C262,VLOOKUP(H262,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H262,$A$2:$C$1041,3,1)),C262,VLOOKUP(H262,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C262" s="1">
@@ -15545,7 +15554,7 @@
         <v>798</v>
       </c>
       <c r="B263" s="5">
-        <f>IF(ISNA(VLOOKUP(H263,$A$2:$C$1040,3,1)),C263,VLOOKUP(H263,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H263,$A$2:$C$1041,3,1)),C263,VLOOKUP(H263,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C263" s="1">
@@ -15578,7 +15587,7 @@
         <v>801</v>
       </c>
       <c r="B264" s="5">
-        <f>IF(ISNA(VLOOKUP(H264,$A$2:$C$1040,3,1)),C264,VLOOKUP(H264,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H264,$A$2:$C$1041,3,1)),C264,VLOOKUP(H264,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C264" s="1">
@@ -15611,11 +15620,11 @@
         <v>2076</v>
       </c>
       <c r="B265" s="5">
-        <f>IF(ISNA(VLOOKUP(H265,$A$2:$C$1040,3,1)),C265,VLOOKUP(H265,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H265,$A$2:$C$1041,3,1)),C265,VLOOKUP(H265,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C265" s="1">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>2085</v>
@@ -15644,11 +15653,11 @@
         <v>2077</v>
       </c>
       <c r="B266" s="5">
-        <f>IF(ISNA(VLOOKUP(H266,$A$2:$C$1040,3,1)),C266,VLOOKUP(H266,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H266,$A$2:$C$1041,3,1)),C266,VLOOKUP(H266,$A$2:$C$1041,3,1))</f>
         <v>92</v>
       </c>
       <c r="C266" s="1">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>2086</v>
@@ -15677,11 +15686,11 @@
         <v>2078</v>
       </c>
       <c r="B267" s="5">
-        <f>IF(ISNA(VLOOKUP(H267,$A$2:$C$1040,3,1)),C267,VLOOKUP(H267,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H267,$A$2:$C$1041,3,1)),C267,VLOOKUP(H267,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C267" s="1">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D267" s="2" t="s">
         <v>2087</v>
@@ -15710,7 +15719,7 @@
         <v>804</v>
       </c>
       <c r="B268" s="5">
-        <f>IF(ISNA(VLOOKUP(H268,$A$2:$C$1040,3,1)),C268,VLOOKUP(H268,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H268,$A$2:$C$1041,3,1)),C268,VLOOKUP(H268,$A$2:$C$1041,3,1))</f>
         <v>172</v>
       </c>
       <c r="C268" s="1">
@@ -15743,7 +15752,7 @@
         <v>807</v>
       </c>
       <c r="B269" s="5">
-        <f>IF(ISNA(VLOOKUP(H269,$A$2:$C$1040,3,1)),C269,VLOOKUP(H269,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H269,$A$2:$C$1041,3,1)),C269,VLOOKUP(H269,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C269" s="1">
@@ -15776,7 +15785,7 @@
         <v>810</v>
       </c>
       <c r="B270" s="5">
-        <f>IF(ISNA(VLOOKUP(H270,$A$2:$C$1040,3,1)),C270,VLOOKUP(H270,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H270,$A$2:$C$1041,3,1)),C270,VLOOKUP(H270,$A$2:$C$1041,3,1))</f>
         <v>555</v>
       </c>
       <c r="C270" s="1">
@@ -15809,7 +15818,7 @@
         <v>813</v>
       </c>
       <c r="B271" s="5">
-        <f>IF(ISNA(VLOOKUP(H271,$A$2:$C$1040,3,1)),C271,VLOOKUP(H271,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H271,$A$2:$C$1041,3,1)),C271,VLOOKUP(H271,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C271" s="1">
@@ -15842,7 +15851,7 @@
         <v>816</v>
       </c>
       <c r="B272" s="5">
-        <f>IF(ISNA(VLOOKUP(H272,$A$2:$C$1040,3,1)),C272,VLOOKUP(H272,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H272,$A$2:$C$1041,3,1)),C272,VLOOKUP(H272,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C272" s="1">
@@ -15875,7 +15884,7 @@
         <v>818</v>
       </c>
       <c r="B273" s="5">
-        <f>IF(ISNA(VLOOKUP(H273,$A$2:$C$1040,3,1)),C273,VLOOKUP(H273,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H273,$A$2:$C$1041,3,1)),C273,VLOOKUP(H273,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C273" s="1">
@@ -15908,7 +15917,7 @@
         <v>820</v>
       </c>
       <c r="B274" s="5">
-        <f>IF(ISNA(VLOOKUP(H274,$A$2:$C$1040,3,1)),C274,VLOOKUP(H274,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H274,$A$2:$C$1041,3,1)),C274,VLOOKUP(H274,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C274" s="1">
@@ -15941,7 +15950,7 @@
         <v>823</v>
       </c>
       <c r="B275" s="5">
-        <f>IF(ISNA(VLOOKUP(H275,$A$2:$C$1040,3,1)),C275,VLOOKUP(H275,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H275,$A$2:$C$1041,3,1)),C275,VLOOKUP(H275,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C275" s="1">
@@ -15974,7 +15983,7 @@
         <v>824</v>
       </c>
       <c r="B276" s="5">
-        <f>IF(ISNA(VLOOKUP(H276,$A$2:$C$1040,3,1)),C276,VLOOKUP(H276,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H276,$A$2:$C$1041,3,1)),C276,VLOOKUP(H276,$A$2:$C$1041,3,1))</f>
         <v>359</v>
       </c>
       <c r="C276" s="1">
@@ -16007,7 +16016,7 @@
         <v>826</v>
       </c>
       <c r="B277" s="5">
-        <f>IF(ISNA(VLOOKUP(H277,$A$2:$C$1040,3,1)),C277,VLOOKUP(H277,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H277,$A$2:$C$1041,3,1)),C277,VLOOKUP(H277,$A$2:$C$1041,3,1))</f>
         <v>367</v>
       </c>
       <c r="C277" s="1">
@@ -16040,7 +16049,7 @@
         <v>828</v>
       </c>
       <c r="B278" s="5">
-        <f>IF(ISNA(VLOOKUP(H278,$A$2:$C$1040,3,1)),C278,VLOOKUP(H278,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H278,$A$2:$C$1041,3,1)),C278,VLOOKUP(H278,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C278" s="1">
@@ -16073,7 +16082,7 @@
         <v>830</v>
       </c>
       <c r="B279" s="5">
-        <f>IF(ISNA(VLOOKUP(H279,$A$2:$C$1040,3,1)),C279,VLOOKUP(H279,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H279,$A$2:$C$1041,3,1)),C279,VLOOKUP(H279,$A$2:$C$1041,3,1))</f>
         <v>359</v>
       </c>
       <c r="C279" s="1">
@@ -16106,7 +16115,7 @@
         <v>832</v>
       </c>
       <c r="B280" s="5">
-        <f>IF(ISNA(VLOOKUP(H280,$A$2:$C$1040,3,1)),C280,VLOOKUP(H280,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H280,$A$2:$C$1041,3,1)),C280,VLOOKUP(H280,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C280" s="1">
@@ -16139,7 +16148,7 @@
         <v>834</v>
       </c>
       <c r="B281" s="5">
-        <f>IF(ISNA(VLOOKUP(H281,$A$2:$C$1040,3,1)),C281,VLOOKUP(H281,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H281,$A$2:$C$1041,3,1)),C281,VLOOKUP(H281,$A$2:$C$1041,3,1))</f>
         <v>441</v>
       </c>
       <c r="C281" s="1">
@@ -16172,7 +16181,7 @@
         <v>838</v>
       </c>
       <c r="B282" s="5">
-        <f>IF(ISNA(VLOOKUP(H282,$A$2:$C$1040,3,1)),C282,VLOOKUP(H282,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H282,$A$2:$C$1041,3,1)),C282,VLOOKUP(H282,$A$2:$C$1041,3,1))</f>
         <v>418</v>
       </c>
       <c r="C282" s="1">
@@ -16205,7 +16214,7 @@
         <v>841</v>
       </c>
       <c r="B283" s="5">
-        <f>IF(ISNA(VLOOKUP(H283,$A$2:$C$1040,3,1)),C283,VLOOKUP(H283,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H283,$A$2:$C$1041,3,1)),C283,VLOOKUP(H283,$A$2:$C$1041,3,1))</f>
         <v>422</v>
       </c>
       <c r="C283" s="1">
@@ -16238,7 +16247,7 @@
         <v>844</v>
       </c>
       <c r="B284" s="5">
-        <f>IF(ISNA(VLOOKUP(H284,$A$2:$C$1040,3,1)),C284,VLOOKUP(H284,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H284,$A$2:$C$1041,3,1)),C284,VLOOKUP(H284,$A$2:$C$1041,3,1))</f>
         <v>424</v>
       </c>
       <c r="C284" s="1">
@@ -16271,7 +16280,7 @@
         <v>847</v>
       </c>
       <c r="B285" s="5">
-        <f>IF(ISNA(VLOOKUP(H285,$A$2:$C$1040,3,1)),C285,VLOOKUP(H285,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H285,$A$2:$C$1041,3,1)),C285,VLOOKUP(H285,$A$2:$C$1041,3,1))</f>
         <v>426</v>
       </c>
       <c r="C285" s="1">
@@ -16304,7 +16313,7 @@
         <v>850</v>
       </c>
       <c r="B286" s="5">
-        <f>IF(ISNA(VLOOKUP(H286,$A$2:$C$1040,3,1)),C286,VLOOKUP(H286,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H286,$A$2:$C$1041,3,1)),C286,VLOOKUP(H286,$A$2:$C$1041,3,1))</f>
         <v>429</v>
       </c>
       <c r="C286" s="1">
@@ -16337,7 +16346,7 @@
         <v>853</v>
       </c>
       <c r="B287" s="5">
-        <f>IF(ISNA(VLOOKUP(H287,$A$2:$C$1040,3,1)),C287,VLOOKUP(H287,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H287,$A$2:$C$1041,3,1)),C287,VLOOKUP(H287,$A$2:$C$1041,3,1))</f>
         <v>432</v>
       </c>
       <c r="C287" s="1">
@@ -16370,7 +16379,7 @@
         <v>856</v>
       </c>
       <c r="B288" s="5">
-        <f>IF(ISNA(VLOOKUP(H288,$A$2:$C$1040,3,1)),C288,VLOOKUP(H288,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H288,$A$2:$C$1041,3,1)),C288,VLOOKUP(H288,$A$2:$C$1041,3,1))</f>
         <v>434</v>
       </c>
       <c r="C288" s="1">
@@ -16403,7 +16412,7 @@
         <v>859</v>
       </c>
       <c r="B289" s="5">
-        <f>IF(ISNA(VLOOKUP(H289,$A$2:$C$1040,3,1)),C289,VLOOKUP(H289,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H289,$A$2:$C$1041,3,1)),C289,VLOOKUP(H289,$A$2:$C$1041,3,1))</f>
         <v>437</v>
       </c>
       <c r="C289" s="1">
@@ -16436,7 +16445,7 @@
         <v>837</v>
       </c>
       <c r="B290" s="5">
-        <f>IF(ISNA(VLOOKUP(H290,$A$2:$C$1040,3,1)),C290,VLOOKUP(H290,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H290,$A$2:$C$1041,3,1)),C290,VLOOKUP(H290,$A$2:$C$1041,3,1))</f>
         <v>441</v>
       </c>
       <c r="C290" s="1">
@@ -16469,7 +16478,7 @@
         <v>864</v>
       </c>
       <c r="B291" s="5">
-        <f>IF(ISNA(VLOOKUP(H291,$A$2:$C$1040,3,1)),C291,VLOOKUP(H291,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H291,$A$2:$C$1041,3,1)),C291,VLOOKUP(H291,$A$2:$C$1041,3,1))</f>
         <v>447</v>
       </c>
       <c r="C291" s="1">
@@ -16502,7 +16511,7 @@
         <v>867</v>
       </c>
       <c r="B292" s="5">
-        <f>IF(ISNA(VLOOKUP(H292,$A$2:$C$1040,3,1)),C292,VLOOKUP(H292,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H292,$A$2:$C$1041,3,1)),C292,VLOOKUP(H292,$A$2:$C$1041,3,1))</f>
         <v>449</v>
       </c>
       <c r="C292" s="1">
@@ -16535,7 +16544,7 @@
         <v>338</v>
       </c>
       <c r="B293" s="5">
-        <f>IF(ISNA(VLOOKUP(H293,$A$2:$C$1040,3,1)),C293,VLOOKUP(H293,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H293,$A$2:$C$1041,3,1)),C293,VLOOKUP(H293,$A$2:$C$1041,3,1))</f>
         <v>451</v>
       </c>
       <c r="C293" s="1">
@@ -16568,7 +16577,7 @@
         <v>872</v>
       </c>
       <c r="B294" s="5">
-        <f>IF(ISNA(VLOOKUP(H294,$A$2:$C$1040,3,1)),C294,VLOOKUP(H294,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H294,$A$2:$C$1041,3,1)),C294,VLOOKUP(H294,$A$2:$C$1041,3,1))</f>
         <v>455</v>
       </c>
       <c r="C294" s="1">
@@ -16601,7 +16610,7 @@
         <v>875</v>
       </c>
       <c r="B295" s="5">
-        <f>IF(ISNA(VLOOKUP(H295,$A$2:$C$1040,3,1)),C295,VLOOKUP(H295,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H295,$A$2:$C$1041,3,1)),C295,VLOOKUP(H295,$A$2:$C$1041,3,1))</f>
         <v>457</v>
       </c>
       <c r="C295" s="1">
@@ -16634,7 +16643,7 @@
         <v>878</v>
       </c>
       <c r="B296" s="5">
-        <f>IF(ISNA(VLOOKUP(H296,$A$2:$C$1040,3,1)),C296,VLOOKUP(H296,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H296,$A$2:$C$1041,3,1)),C296,VLOOKUP(H296,$A$2:$C$1041,3,1))</f>
         <v>459</v>
       </c>
       <c r="C296" s="1">
@@ -16667,7 +16676,7 @@
         <v>881</v>
       </c>
       <c r="B297" s="5">
-        <f>IF(ISNA(VLOOKUP(H297,$A$2:$C$1040,3,1)),C297,VLOOKUP(H297,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H297,$A$2:$C$1041,3,1)),C297,VLOOKUP(H297,$A$2:$C$1041,3,1))</f>
         <v>462</v>
       </c>
       <c r="C297" s="1">
@@ -16700,7 +16709,7 @@
         <v>884</v>
       </c>
       <c r="B298" s="5">
-        <f>IF(ISNA(VLOOKUP(H298,$A$2:$C$1040,3,1)),C298,VLOOKUP(H298,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H298,$A$2:$C$1041,3,1)),C298,VLOOKUP(H298,$A$2:$C$1041,3,1))</f>
         <v>468</v>
       </c>
       <c r="C298" s="1">
@@ -16733,7 +16742,7 @@
         <v>887</v>
       </c>
       <c r="B299" s="5">
-        <f>IF(ISNA(VLOOKUP(H299,$A$2:$C$1040,3,1)),C299,VLOOKUP(H299,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H299,$A$2:$C$1041,3,1)),C299,VLOOKUP(H299,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C299" s="1">
@@ -16766,7 +16775,7 @@
         <v>888</v>
       </c>
       <c r="B300" s="5">
-        <f>IF(ISNA(VLOOKUP(H300,$A$2:$C$1040,3,1)),C300,VLOOKUP(H300,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H300,$A$2:$C$1041,3,1)),C300,VLOOKUP(H300,$A$2:$C$1041,3,1))</f>
         <v>470</v>
       </c>
       <c r="C300" s="1">
@@ -16799,7 +16808,7 @@
         <v>891</v>
       </c>
       <c r="B301" s="5">
-        <f>IF(ISNA(VLOOKUP(H301,$A$2:$C$1040,3,1)),C301,VLOOKUP(H301,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H301,$A$2:$C$1041,3,1)),C301,VLOOKUP(H301,$A$2:$C$1041,3,1))</f>
         <v>474</v>
       </c>
       <c r="C301" s="1">
@@ -16832,7 +16841,7 @@
         <v>894</v>
       </c>
       <c r="B302" s="5">
-        <f>IF(ISNA(VLOOKUP(H302,$A$2:$C$1040,3,1)),C302,VLOOKUP(H302,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H302,$A$2:$C$1041,3,1)),C302,VLOOKUP(H302,$A$2:$C$1041,3,1))</f>
         <v>476</v>
       </c>
       <c r="C302" s="1">
@@ -16865,7 +16874,7 @@
         <v>897</v>
       </c>
       <c r="B303" s="5">
-        <f>IF(ISNA(VLOOKUP(H303,$A$2:$C$1040,3,1)),C303,VLOOKUP(H303,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H303,$A$2:$C$1041,3,1)),C303,VLOOKUP(H303,$A$2:$C$1041,3,1))</f>
         <v>482</v>
       </c>
       <c r="C303" s="1">
@@ -16898,7 +16907,7 @@
         <v>900</v>
       </c>
       <c r="B304" s="5">
-        <f>IF(ISNA(VLOOKUP(H304,$A$2:$C$1040,3,1)),C304,VLOOKUP(H304,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H304,$A$2:$C$1041,3,1)),C304,VLOOKUP(H304,$A$2:$C$1041,3,1))</f>
         <v>484</v>
       </c>
       <c r="C304" s="1">
@@ -16931,7 +16940,7 @@
         <v>903</v>
       </c>
       <c r="B305" s="5">
-        <f>IF(ISNA(VLOOKUP(H305,$A$2:$C$1040,3,1)),C305,VLOOKUP(H305,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H305,$A$2:$C$1041,3,1)),C305,VLOOKUP(H305,$A$2:$C$1041,3,1))</f>
         <v>486</v>
       </c>
       <c r="C305" s="1">
@@ -16964,7 +16973,7 @@
         <v>906</v>
       </c>
       <c r="B306" s="5">
-        <f>IF(ISNA(VLOOKUP(H306,$A$2:$C$1040,3,1)),C306,VLOOKUP(H306,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H306,$A$2:$C$1041,3,1)),C306,VLOOKUP(H306,$A$2:$C$1041,3,1))</f>
         <v>488</v>
       </c>
       <c r="C306" s="1">
@@ -16997,7 +17006,7 @@
         <v>909</v>
       </c>
       <c r="B307" s="5">
-        <f>IF(ISNA(VLOOKUP(H307,$A$2:$C$1040,3,1)),C307,VLOOKUP(H307,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H307,$A$2:$C$1041,3,1)),C307,VLOOKUP(H307,$A$2:$C$1041,3,1))</f>
         <v>441</v>
       </c>
       <c r="C307" s="1">
@@ -17030,7 +17039,7 @@
         <v>912</v>
       </c>
       <c r="B308" s="5">
-        <f>IF(ISNA(VLOOKUP(H308,$A$2:$C$1040,3,1)),C308,VLOOKUP(H308,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H308,$A$2:$C$1041,3,1)),C308,VLOOKUP(H308,$A$2:$C$1041,3,1))</f>
         <v>476</v>
       </c>
       <c r="C308" s="1">
@@ -17063,7 +17072,7 @@
         <v>915</v>
       </c>
       <c r="B309" s="5">
-        <f>IF(ISNA(VLOOKUP(H309,$A$2:$C$1040,3,1)),C309,VLOOKUP(H309,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H309,$A$2:$C$1041,3,1)),C309,VLOOKUP(H309,$A$2:$C$1041,3,1))</f>
         <v>418</v>
       </c>
       <c r="C309" s="1">
@@ -17096,7 +17105,7 @@
         <v>918</v>
       </c>
       <c r="B310" s="5">
-        <f>IF(ISNA(VLOOKUP(H310,$A$2:$C$1040,3,1)),C310,VLOOKUP(H310,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H310,$A$2:$C$1041,3,1)),C310,VLOOKUP(H310,$A$2:$C$1041,3,1))</f>
         <v>429</v>
       </c>
       <c r="C310" s="1">
@@ -17129,7 +17138,7 @@
         <v>921</v>
       </c>
       <c r="B311" s="5">
-        <f>IF(ISNA(VLOOKUP(H311,$A$2:$C$1040,3,1)),C311,VLOOKUP(H311,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H311,$A$2:$C$1041,3,1)),C311,VLOOKUP(H311,$A$2:$C$1041,3,1))</f>
         <v>434</v>
       </c>
       <c r="C311" s="1">
@@ -17162,7 +17171,7 @@
         <v>924</v>
       </c>
       <c r="B312" s="5">
-        <f>IF(ISNA(VLOOKUP(H312,$A$2:$C$1040,3,1)),C312,VLOOKUP(H312,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H312,$A$2:$C$1041,3,1)),C312,VLOOKUP(H312,$A$2:$C$1041,3,1))</f>
         <v>441</v>
       </c>
       <c r="C312" s="1">
@@ -17195,7 +17204,7 @@
         <v>927</v>
       </c>
       <c r="B313" s="5">
-        <f>IF(ISNA(VLOOKUP(H313,$A$2:$C$1040,3,1)),C313,VLOOKUP(H313,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H313,$A$2:$C$1041,3,1)),C313,VLOOKUP(H313,$A$2:$C$1041,3,1))</f>
         <v>476</v>
       </c>
       <c r="C313" s="1">
@@ -17228,7 +17237,7 @@
         <v>930</v>
       </c>
       <c r="B314" s="5">
-        <f>IF(ISNA(VLOOKUP(H314,$A$2:$C$1040,3,1)),C314,VLOOKUP(H314,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H314,$A$2:$C$1041,3,1)),C314,VLOOKUP(H314,$A$2:$C$1041,3,1))</f>
         <v>418</v>
       </c>
       <c r="C314" s="1">
@@ -17261,7 +17270,7 @@
         <v>933</v>
       </c>
       <c r="B315" s="5">
-        <f>IF(ISNA(VLOOKUP(H315,$A$2:$C$1040,3,1)),C315,VLOOKUP(H315,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H315,$A$2:$C$1041,3,1)),C315,VLOOKUP(H315,$A$2:$C$1041,3,1))</f>
         <v>422</v>
       </c>
       <c r="C315" s="1">
@@ -17294,7 +17303,7 @@
         <v>936</v>
       </c>
       <c r="B316" s="5">
-        <f>IF(ISNA(VLOOKUP(H316,$A$2:$C$1040,3,1)),C316,VLOOKUP(H316,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H316,$A$2:$C$1041,3,1)),C316,VLOOKUP(H316,$A$2:$C$1041,3,1))</f>
         <v>424</v>
       </c>
       <c r="C316" s="1">
@@ -17327,7 +17336,7 @@
         <v>939</v>
       </c>
       <c r="B317" s="5">
-        <f>IF(ISNA(VLOOKUP(H317,$A$2:$C$1040,3,1)),C317,VLOOKUP(H317,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H317,$A$2:$C$1041,3,1)),C317,VLOOKUP(H317,$A$2:$C$1041,3,1))</f>
         <v>426</v>
       </c>
       <c r="C317" s="1">
@@ -17360,7 +17369,7 @@
         <v>942</v>
       </c>
       <c r="B318" s="5">
-        <f>IF(ISNA(VLOOKUP(H318,$A$2:$C$1040,3,1)),C318,VLOOKUP(H318,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H318,$A$2:$C$1041,3,1)),C318,VLOOKUP(H318,$A$2:$C$1041,3,1))</f>
         <v>429</v>
       </c>
       <c r="C318" s="1">
@@ -17397,7 +17406,7 @@
         <v>945</v>
       </c>
       <c r="B319" s="5">
-        <f>IF(ISNA(VLOOKUP(H319,$A$2:$C$1040,3,1)),C319,VLOOKUP(H319,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H319,$A$2:$C$1041,3,1)),C319,VLOOKUP(H319,$A$2:$C$1041,3,1))</f>
         <v>432</v>
       </c>
       <c r="C319" s="1">
@@ -17430,7 +17439,7 @@
         <v>948</v>
       </c>
       <c r="B320" s="5">
-        <f>IF(ISNA(VLOOKUP(H320,$A$2:$C$1040,3,1)),C320,VLOOKUP(H320,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H320,$A$2:$C$1041,3,1)),C320,VLOOKUP(H320,$A$2:$C$1041,3,1))</f>
         <v>434</v>
       </c>
       <c r="C320" s="1">
@@ -17463,7 +17472,7 @@
         <v>951</v>
       </c>
       <c r="B321" s="13">
-        <f>IF(ISNA(VLOOKUP(H321,$A$2:$C$1040,3,1)),C321,VLOOKUP(H321,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H321,$A$2:$C$1041,3,1)),C321,VLOOKUP(H321,$A$2:$C$1041,3,1))</f>
         <v>437</v>
       </c>
       <c r="C321" s="1">
@@ -17496,7 +17505,7 @@
         <v>953</v>
       </c>
       <c r="B322" s="5">
-        <f>IF(ISNA(VLOOKUP(H322,$A$2:$C$1040,3,1)),C322,VLOOKUP(H322,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H322,$A$2:$C$1041,3,1)),C322,VLOOKUP(H322,$A$2:$C$1041,3,1))</f>
         <v>441</v>
       </c>
       <c r="C322" s="1">
@@ -17529,7 +17538,7 @@
         <v>956</v>
       </c>
       <c r="B323" s="5">
-        <f>IF(ISNA(VLOOKUP(H323,$A$2:$C$1040,3,1)),C323,VLOOKUP(H323,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H323,$A$2:$C$1041,3,1)),C323,VLOOKUP(H323,$A$2:$C$1041,3,1))</f>
         <v>447</v>
       </c>
       <c r="C323" s="1">
@@ -17562,7 +17571,7 @@
         <v>959</v>
       </c>
       <c r="B324" s="5">
-        <f>IF(ISNA(VLOOKUP(H324,$A$2:$C$1040,3,1)),C324,VLOOKUP(H324,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H324,$A$2:$C$1041,3,1)),C324,VLOOKUP(H324,$A$2:$C$1041,3,1))</f>
         <v>449</v>
       </c>
       <c r="C324" s="1">
@@ -17595,7 +17604,7 @@
         <v>962</v>
       </c>
       <c r="B325" s="5">
-        <f>IF(ISNA(VLOOKUP(H325,$A$2:$C$1040,3,1)),C325,VLOOKUP(H325,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H325,$A$2:$C$1041,3,1)),C325,VLOOKUP(H325,$A$2:$C$1041,3,1))</f>
         <v>451</v>
       </c>
       <c r="C325" s="1">
@@ -17628,7 +17637,7 @@
         <v>964</v>
       </c>
       <c r="B326" s="5">
-        <f>IF(ISNA(VLOOKUP(H326,$A$2:$C$1040,3,1)),C326,VLOOKUP(H326,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H326,$A$2:$C$1041,3,1)),C326,VLOOKUP(H326,$A$2:$C$1041,3,1))</f>
         <v>455</v>
       </c>
       <c r="C326" s="1">
@@ -17661,7 +17670,7 @@
         <v>967</v>
       </c>
       <c r="B327" s="5">
-        <f>IF(ISNA(VLOOKUP(H327,$A$2:$C$1040,3,1)),C327,VLOOKUP(H327,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H327,$A$2:$C$1041,3,1)),C327,VLOOKUP(H327,$A$2:$C$1041,3,1))</f>
         <v>457</v>
       </c>
       <c r="C327" s="1">
@@ -17694,7 +17703,7 @@
         <v>970</v>
       </c>
       <c r="B328" s="5">
-        <f>IF(ISNA(VLOOKUP(H328,$A$2:$C$1040,3,1)),C328,VLOOKUP(H328,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H328,$A$2:$C$1041,3,1)),C328,VLOOKUP(H328,$A$2:$C$1041,3,1))</f>
         <v>459</v>
       </c>
       <c r="C328" s="1">
@@ -17727,7 +17736,7 @@
         <v>973</v>
       </c>
       <c r="B329" s="5">
-        <f>IF(ISNA(VLOOKUP(H329,$A$2:$C$1040,3,1)),C329,VLOOKUP(H329,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H329,$A$2:$C$1041,3,1)),C329,VLOOKUP(H329,$A$2:$C$1041,3,1))</f>
         <v>462</v>
       </c>
       <c r="C329" s="1">
@@ -17760,7 +17769,7 @@
         <v>976</v>
       </c>
       <c r="B330" s="5">
-        <f>IF(ISNA(VLOOKUP(H330,$A$2:$C$1040,3,1)),C330,VLOOKUP(H330,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H330,$A$2:$C$1041,3,1)),C330,VLOOKUP(H330,$A$2:$C$1041,3,1))</f>
         <v>468</v>
       </c>
       <c r="C330" s="1">
@@ -17793,7 +17802,7 @@
         <v>979</v>
       </c>
       <c r="B331" s="5">
-        <f>IF(ISNA(VLOOKUP(H331,$A$2:$C$1040,3,1)),C331,VLOOKUP(H331,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H331,$A$2:$C$1041,3,1)),C331,VLOOKUP(H331,$A$2:$C$1041,3,1))</f>
         <v>470</v>
       </c>
       <c r="C331" s="1">
@@ -17826,7 +17835,7 @@
         <v>982</v>
       </c>
       <c r="B332" s="5">
-        <f>IF(ISNA(VLOOKUP(H332,$A$2:$C$1040,3,1)),C332,VLOOKUP(H332,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H332,$A$2:$C$1041,3,1)),C332,VLOOKUP(H332,$A$2:$C$1041,3,1))</f>
         <v>470</v>
       </c>
       <c r="C332" s="1">
@@ -17859,7 +17868,7 @@
         <v>985</v>
       </c>
       <c r="B333" s="5">
-        <f>IF(ISNA(VLOOKUP(H333,$A$2:$C$1040,3,1)),C333,VLOOKUP(H333,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H333,$A$2:$C$1041,3,1)),C333,VLOOKUP(H333,$A$2:$C$1041,3,1))</f>
         <v>474</v>
       </c>
       <c r="C333" s="1">
@@ -17892,7 +17901,7 @@
         <v>988</v>
       </c>
       <c r="B334" s="5">
-        <f>IF(ISNA(VLOOKUP(H334,$A$2:$C$1040,3,1)),C334,VLOOKUP(H334,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H334,$A$2:$C$1041,3,1)),C334,VLOOKUP(H334,$A$2:$C$1041,3,1))</f>
         <v>476</v>
       </c>
       <c r="C334" s="1">
@@ -17925,7 +17934,7 @@
         <v>991</v>
       </c>
       <c r="B335" s="5">
-        <f>IF(ISNA(VLOOKUP(H335,$A$2:$C$1040,3,1)),C335,VLOOKUP(H335,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H335,$A$2:$C$1041,3,1)),C335,VLOOKUP(H335,$A$2:$C$1041,3,1))</f>
         <v>482</v>
       </c>
       <c r="C335" s="1">
@@ -17958,7 +17967,7 @@
         <v>994</v>
       </c>
       <c r="B336" s="5">
-        <f>IF(ISNA(VLOOKUP(H336,$A$2:$C$1040,3,1)),C336,VLOOKUP(H336,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H336,$A$2:$C$1041,3,1)),C336,VLOOKUP(H336,$A$2:$C$1041,3,1))</f>
         <v>484</v>
       </c>
       <c r="C336" s="1">
@@ -17991,7 +18000,7 @@
         <v>997</v>
       </c>
       <c r="B337" s="5">
-        <f>IF(ISNA(VLOOKUP(H337,$A$2:$C$1040,3,1)),C337,VLOOKUP(H337,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H337,$A$2:$C$1041,3,1)),C337,VLOOKUP(H337,$A$2:$C$1041,3,1))</f>
         <v>486</v>
       </c>
       <c r="C337" s="1">
@@ -18024,7 +18033,7 @@
         <v>1000</v>
       </c>
       <c r="B338" s="5">
-        <f>IF(ISNA(VLOOKUP(H338,$A$2:$C$1040,3,1)),C338,VLOOKUP(H338,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H338,$A$2:$C$1041,3,1)),C338,VLOOKUP(H338,$A$2:$C$1041,3,1))</f>
         <v>488</v>
       </c>
       <c r="C338" s="1">
@@ -18057,7 +18066,7 @@
         <v>1003</v>
       </c>
       <c r="B339" s="5">
-        <f>IF(ISNA(VLOOKUP(H339,$A$2:$C$1040,3,1)),C339,VLOOKUP(H339,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H339,$A$2:$C$1041,3,1)),C339,VLOOKUP(H339,$A$2:$C$1041,3,1))</f>
         <v>441</v>
       </c>
       <c r="C339" s="1">
@@ -18090,7 +18099,7 @@
         <v>1006</v>
       </c>
       <c r="B340" s="5">
-        <f>IF(ISNA(VLOOKUP(H340,$A$2:$C$1040,3,1)),C340,VLOOKUP(H340,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H340,$A$2:$C$1041,3,1)),C340,VLOOKUP(H340,$A$2:$C$1041,3,1))</f>
         <v>476</v>
       </c>
       <c r="C340" s="1">
@@ -18123,7 +18132,7 @@
         <v>1009</v>
       </c>
       <c r="B341" s="5">
-        <f>IF(ISNA(VLOOKUP(H341,$A$2:$C$1040,3,1)),C341,VLOOKUP(H341,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H341,$A$2:$C$1041,3,1)),C341,VLOOKUP(H341,$A$2:$C$1041,3,1))</f>
         <v>459</v>
       </c>
       <c r="C341" s="1">
@@ -18160,7 +18169,7 @@
         <v>1012</v>
       </c>
       <c r="B342" s="5">
-        <f>IF(ISNA(VLOOKUP(H342,$A$2:$C$1040,3,1)),C342,VLOOKUP(H342,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H342,$A$2:$C$1041,3,1)),C342,VLOOKUP(H342,$A$2:$C$1041,3,1))</f>
         <v>476</v>
       </c>
       <c r="C342" s="1">
@@ -18197,7 +18206,7 @@
         <v>1015</v>
       </c>
       <c r="B343" s="5">
-        <f>IF(ISNA(VLOOKUP(H343,$A$2:$C$1040,3,1)),C343,VLOOKUP(H343,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H343,$A$2:$C$1041,3,1)),C343,VLOOKUP(H343,$A$2:$C$1041,3,1))</f>
         <v>488</v>
       </c>
       <c r="C343" s="1">
@@ -18230,7 +18239,7 @@
         <v>1993</v>
       </c>
       <c r="B344" s="13">
-        <f>IF(ISNA(VLOOKUP(H344,$A$2:$C$1040,3,1)),C344,VLOOKUP(H344,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H344,$A$2:$C$1041,3,1)),C344,VLOOKUP(H344,$A$2:$C$1041,3,1))</f>
         <v>437</v>
       </c>
       <c r="C344" s="1">
@@ -18263,7 +18272,7 @@
         <v>1998</v>
       </c>
       <c r="B345" s="13">
-        <f>IF(ISNA(VLOOKUP(H345,$A$2:$C$1040,3,1)),C345,VLOOKUP(H345,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H345,$A$2:$C$1041,3,1)),C345,VLOOKUP(H345,$A$2:$C$1041,3,1))</f>
         <v>482</v>
       </c>
       <c r="C345" s="1">
@@ -18296,7 +18305,7 @@
         <v>1018</v>
       </c>
       <c r="B346" s="5">
-        <f>IF(ISNA(VLOOKUP(H346,$A$2:$C$1040,3,1)),C346,VLOOKUP(H346,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H346,$A$2:$C$1041,3,1)),C346,VLOOKUP(H346,$A$2:$C$1041,3,1))</f>
         <v>491</v>
       </c>
       <c r="C346" s="1">
@@ -18329,7 +18338,7 @@
         <v>1021</v>
       </c>
       <c r="B347" s="5">
-        <f>IF(ISNA(VLOOKUP(H347,$A$2:$C$1040,3,1)),C347,VLOOKUP(H347,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H347,$A$2:$C$1041,3,1)),C347,VLOOKUP(H347,$A$2:$C$1041,3,1))</f>
         <v>491</v>
       </c>
       <c r="C347" s="1">
@@ -18362,7 +18371,7 @@
         <v>1024</v>
       </c>
       <c r="B348" s="5">
-        <f>IF(ISNA(VLOOKUP(H348,$A$2:$C$1040,3,1)),C348,VLOOKUP(H348,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H348,$A$2:$C$1041,3,1)),C348,VLOOKUP(H348,$A$2:$C$1041,3,1))</f>
         <v>493</v>
       </c>
       <c r="C348" s="1">
@@ -18395,7 +18404,7 @@
         <v>1027</v>
       </c>
       <c r="B349" s="5">
-        <f>IF(ISNA(VLOOKUP(H349,$A$2:$C$1040,3,1)),C349,VLOOKUP(H349,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H349,$A$2:$C$1041,3,1)),C349,VLOOKUP(H349,$A$2:$C$1041,3,1))</f>
         <v>493</v>
       </c>
       <c r="C349" s="1">
@@ -18428,7 +18437,7 @@
         <v>1030</v>
       </c>
       <c r="B350" s="5">
-        <f>IF(ISNA(VLOOKUP(H350,$A$2:$C$1040,3,1)),C350,VLOOKUP(H350,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H350,$A$2:$C$1041,3,1)),C350,VLOOKUP(H350,$A$2:$C$1041,3,1))</f>
         <v>495</v>
       </c>
       <c r="C350" s="1">
@@ -18461,7 +18470,7 @@
         <v>1033</v>
       </c>
       <c r="B351" s="5">
-        <f>IF(ISNA(VLOOKUP(H351,$A$2:$C$1040,3,1)),C351,VLOOKUP(H351,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H351,$A$2:$C$1041,3,1)),C351,VLOOKUP(H351,$A$2:$C$1041,3,1))</f>
         <v>495</v>
       </c>
       <c r="C351" s="1">
@@ -18494,7 +18503,7 @@
         <v>2024</v>
       </c>
       <c r="B352" s="5">
-        <f>IF(ISNA(VLOOKUP(H352,$A$2:$C$1040,3,1)),C352,VLOOKUP(H352,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H352,$A$2:$C$1041,3,1)),C352,VLOOKUP(H352,$A$2:$C$1041,3,1))</f>
         <v>234</v>
       </c>
       <c r="C352" s="1">
@@ -18527,7 +18536,7 @@
         <v>2027</v>
       </c>
       <c r="B353" s="5">
-        <f>IF(ISNA(VLOOKUP(H353,$A$2:$C$1040,3,1)),C353,VLOOKUP(H353,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H353,$A$2:$C$1041,3,1)),C353,VLOOKUP(H353,$A$2:$C$1041,3,1))</f>
         <v>526</v>
       </c>
       <c r="C353" s="1">
@@ -18560,7 +18569,7 @@
         <v>2038</v>
       </c>
       <c r="B354" s="5">
-        <f>IF(ISNA(VLOOKUP(H354,$A$2:$C$1040,3,1)),C354,VLOOKUP(H354,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H354,$A$2:$C$1041,3,1)),C354,VLOOKUP(H354,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C354" s="1">
@@ -18593,7 +18602,7 @@
         <v>2028</v>
       </c>
       <c r="B355" s="5">
-        <f>IF(ISNA(VLOOKUP(H355,$A$2:$C$1040,3,1)),C355,VLOOKUP(H355,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H355,$A$2:$C$1041,3,1)),C355,VLOOKUP(H355,$A$2:$C$1041,3,1))</f>
         <v>214</v>
       </c>
       <c r="C355" s="1">
@@ -18626,7 +18635,7 @@
         <v>2029</v>
       </c>
       <c r="B356" s="5">
-        <f>IF(ISNA(VLOOKUP(H356,$A$2:$C$1040,3,1)),C356,VLOOKUP(H356,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H356,$A$2:$C$1041,3,1)),C356,VLOOKUP(H356,$A$2:$C$1041,3,1))</f>
         <v>18</v>
       </c>
       <c r="C356" s="1">
@@ -18659,7 +18668,7 @@
         <v>2035</v>
       </c>
       <c r="B357" s="5">
-        <f>IF(ISNA(VLOOKUP(H357,$A$2:$C$1040,3,1)),C357,VLOOKUP(H357,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H357,$A$2:$C$1041,3,1)),C357,VLOOKUP(H357,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C357" s="1">
@@ -18692,7 +18701,7 @@
         <v>2052</v>
       </c>
       <c r="B358" s="5">
-        <f>IF(ISNA(VLOOKUP(H358,$A$2:$C$1040,3,1)),C358,VLOOKUP(H358,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H358,$A$2:$C$1041,3,1)),C358,VLOOKUP(H358,$A$2:$C$1041,3,1))</f>
         <v>280</v>
       </c>
       <c r="C358" s="1">
@@ -18725,7 +18734,7 @@
         <v>2040</v>
       </c>
       <c r="B359" s="5">
-        <f>IF(ISNA(VLOOKUP(H359,$A$2:$C$1040,3,1)),C359,VLOOKUP(H359,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H359,$A$2:$C$1041,3,1)),C359,VLOOKUP(H359,$A$2:$C$1041,3,1))</f>
         <v>509</v>
       </c>
       <c r="C359" s="1">
@@ -18758,7 +18767,7 @@
         <v>2041</v>
       </c>
       <c r="B360" s="5">
-        <f>IF(ISNA(VLOOKUP(H360,$A$2:$C$1040,3,1)),C360,VLOOKUP(H360,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H360,$A$2:$C$1041,3,1)),C360,VLOOKUP(H360,$A$2:$C$1041,3,1))</f>
         <v>509</v>
       </c>
       <c r="C360" s="1">
@@ -18791,11 +18800,11 @@
         <v>2075</v>
       </c>
       <c r="B361" s="5">
-        <f>IF(ISNA(VLOOKUP(H361,$A$2:$C$1040,3,1)),C361,VLOOKUP(H361,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H361,$A$2:$C$1041,3,1)),C361,VLOOKUP(H361,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C361" s="1">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>2084</v>
@@ -18824,11 +18833,11 @@
         <v>2106</v>
       </c>
       <c r="B362" s="5">
-        <f>IF(ISNA(VLOOKUP(H362,$A$2:$C$1040,3,1)),C362,VLOOKUP(H362,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H362,$A$2:$C$1041,3,1)),C362,VLOOKUP(H362,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C362" s="1">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>2088</v>
@@ -18857,11 +18866,11 @@
         <v>2079</v>
       </c>
       <c r="B363" s="5">
-        <f>IF(ISNA(VLOOKUP(H363,$A$2:$C$1040,3,1)),C363,VLOOKUP(H363,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H363,$A$2:$C$1041,3,1)),C363,VLOOKUP(H363,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C363" s="1">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>2089</v>
@@ -18890,11 +18899,11 @@
         <v>2080</v>
       </c>
       <c r="B364" s="5">
-        <f>IF(ISNA(VLOOKUP(H364,$A$2:$C$1040,3,1)),C364,VLOOKUP(H364,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H364,$A$2:$C$1041,3,1)),C364,VLOOKUP(H364,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C364" s="1">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>2090</v>
@@ -18923,11 +18932,11 @@
         <v>2081</v>
       </c>
       <c r="B365" s="5">
-        <f>IF(ISNA(VLOOKUP(H365,$A$2:$C$1040,3,1)),C365,VLOOKUP(H365,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H365,$A$2:$C$1041,3,1)),C365,VLOOKUP(H365,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C365" s="1">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>2091</v>
@@ -18956,11 +18965,11 @@
         <v>2082</v>
       </c>
       <c r="B366" s="5">
-        <f>IF(ISNA(VLOOKUP(H366,$A$2:$C$1040,3,1)),C366,VLOOKUP(H366,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H366,$A$2:$C$1041,3,1)),C366,VLOOKUP(H366,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C366" s="1">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>2092</v>
@@ -18989,7 +18998,7 @@
         <v>1036</v>
       </c>
       <c r="B367" s="5">
-        <f>IF(ISNA(VLOOKUP(H367,$A$2:$C$1040,3,1)),C367,VLOOKUP(H367,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H367,$A$2:$C$1041,3,1)),C367,VLOOKUP(H367,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C367" s="1">
@@ -19022,7 +19031,7 @@
         <v>1039</v>
       </c>
       <c r="B368" s="5">
-        <f>IF(ISNA(VLOOKUP(H368,$A$2:$C$1040,3,1)),C368,VLOOKUP(H368,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H368,$A$2:$C$1041,3,1)),C368,VLOOKUP(H368,$A$2:$C$1041,3,1))</f>
         <v>162</v>
       </c>
       <c r="C368" s="1">
@@ -19055,7 +19064,7 @@
         <v>1042</v>
       </c>
       <c r="B369" s="5">
-        <f>IF(ISNA(VLOOKUP(H369,$A$2:$C$1040,3,1)),C369,VLOOKUP(H369,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H369,$A$2:$C$1041,3,1)),C369,VLOOKUP(H369,$A$2:$C$1041,3,1))</f>
         <v>153</v>
       </c>
       <c r="C369" s="1">
@@ -19088,7 +19097,7 @@
         <v>1045</v>
       </c>
       <c r="B370" s="5">
-        <f>IF(ISNA(VLOOKUP(H370,$A$2:$C$1040,3,1)),C370,VLOOKUP(H370,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H370,$A$2:$C$1041,3,1)),C370,VLOOKUP(H370,$A$2:$C$1041,3,1))</f>
         <v>153</v>
       </c>
       <c r="C370" s="1">
@@ -19121,7 +19130,7 @@
         <v>1048</v>
       </c>
       <c r="B371" s="5">
-        <f>IF(ISNA(VLOOKUP(H371,$A$2:$C$1040,3,1)),C371,VLOOKUP(H371,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H371,$A$2:$C$1041,3,1)),C371,VLOOKUP(H371,$A$2:$C$1041,3,1))</f>
         <v>162</v>
       </c>
       <c r="C371" s="1">
@@ -19154,7 +19163,7 @@
         <v>1050</v>
       </c>
       <c r="B372" s="5">
-        <f>IF(ISNA(VLOOKUP(H372,$A$2:$C$1040,3,1)),C372,VLOOKUP(H372,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H372,$A$2:$C$1041,3,1)),C372,VLOOKUP(H372,$A$2:$C$1041,3,1))</f>
         <v>1</v>
       </c>
       <c r="C372" s="1">
@@ -19187,7 +19196,7 @@
         <v>1053</v>
       </c>
       <c r="B373" s="5">
-        <f>IF(ISNA(VLOOKUP(H373,$A$2:$C$1040,3,1)),C373,VLOOKUP(H373,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H373,$A$2:$C$1041,3,1)),C373,VLOOKUP(H373,$A$2:$C$1041,3,1))</f>
         <v>1</v>
       </c>
       <c r="C373" s="1">
@@ -19220,7 +19229,7 @@
         <v>1056</v>
       </c>
       <c r="B374" s="5">
-        <f>IF(ISNA(VLOOKUP(H374,$A$2:$C$1040,3,1)),C374,VLOOKUP(H374,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H374,$A$2:$C$1041,3,1)),C374,VLOOKUP(H374,$A$2:$C$1041,3,1))</f>
         <v>1</v>
       </c>
       <c r="C374" s="1">
@@ -19253,7 +19262,7 @@
         <v>1059</v>
       </c>
       <c r="B375" s="5">
-        <f>IF(ISNA(VLOOKUP(H375,$A$2:$C$1040,3,1)),C375,VLOOKUP(H375,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H375,$A$2:$C$1041,3,1)),C375,VLOOKUP(H375,$A$2:$C$1041,3,1))</f>
         <v>1</v>
       </c>
       <c r="C375" s="1">
@@ -19286,7 +19295,7 @@
         <v>1062</v>
       </c>
       <c r="B376" s="5">
-        <f>IF(ISNA(VLOOKUP(H376,$A$2:$C$1040,3,1)),C376,VLOOKUP(H376,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H376,$A$2:$C$1041,3,1)),C376,VLOOKUP(H376,$A$2:$C$1041,3,1))</f>
         <v>1</v>
       </c>
       <c r="C376" s="1">
@@ -19319,7 +19328,7 @@
         <v>1065</v>
       </c>
       <c r="B377" s="5">
-        <f>IF(ISNA(VLOOKUP(H377,$A$2:$C$1040,3,1)),C377,VLOOKUP(H377,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H377,$A$2:$C$1041,3,1)),C377,VLOOKUP(H377,$A$2:$C$1041,3,1))</f>
         <v>1</v>
       </c>
       <c r="C377" s="1">
@@ -19352,7 +19361,7 @@
         <v>1068</v>
       </c>
       <c r="B378" s="5">
-        <f>IF(ISNA(VLOOKUP(H378,$A$2:$C$1040,3,1)),C378,VLOOKUP(H378,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H378,$A$2:$C$1041,3,1)),C378,VLOOKUP(H378,$A$2:$C$1041,3,1))</f>
         <v>1</v>
       </c>
       <c r="C378" s="1">
@@ -19385,7 +19394,7 @@
         <v>1071</v>
       </c>
       <c r="B379" s="5">
-        <f>IF(ISNA(VLOOKUP(H379,$A$2:$C$1040,3,1)),C379,VLOOKUP(H379,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H379,$A$2:$C$1041,3,1)),C379,VLOOKUP(H379,$A$2:$C$1041,3,1))</f>
         <v>555</v>
       </c>
       <c r="C379" s="1">
@@ -19418,7 +19427,7 @@
         <v>1074</v>
       </c>
       <c r="B380" s="5">
-        <f>IF(ISNA(VLOOKUP(H380,$A$2:$C$1040,3,1)),C380,VLOOKUP(H380,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H380,$A$2:$C$1041,3,1)),C380,VLOOKUP(H380,$A$2:$C$1041,3,1))</f>
         <v>555</v>
       </c>
       <c r="C380" s="1">
@@ -19451,7 +19460,7 @@
         <v>1077</v>
       </c>
       <c r="B381" s="5">
-        <f>IF(ISNA(VLOOKUP(H381,$A$2:$C$1040,3,1)),C381,VLOOKUP(H381,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H381,$A$2:$C$1041,3,1)),C381,VLOOKUP(H381,$A$2:$C$1041,3,1))</f>
         <v>555</v>
       </c>
       <c r="C381" s="1">
@@ -19484,7 +19493,7 @@
         <v>1080</v>
       </c>
       <c r="B382" s="5">
-        <f>IF(ISNA(VLOOKUP(H382,$A$2:$C$1040,3,1)),C382,VLOOKUP(H382,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H382,$A$2:$C$1041,3,1)),C382,VLOOKUP(H382,$A$2:$C$1041,3,1))</f>
         <v>555</v>
       </c>
       <c r="C382" s="1">
@@ -19517,7 +19526,7 @@
         <v>1083</v>
       </c>
       <c r="B383" s="5">
-        <f>IF(ISNA(VLOOKUP(H383,$A$2:$C$1040,3,1)),C383,VLOOKUP(H383,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H383,$A$2:$C$1041,3,1)),C383,VLOOKUP(H383,$A$2:$C$1041,3,1))</f>
         <v>561</v>
       </c>
       <c r="C383" s="1">
@@ -19550,7 +19559,7 @@
         <v>1086</v>
       </c>
       <c r="B384" s="5">
-        <f>IF(ISNA(VLOOKUP(H384,$A$2:$C$1040,3,1)),C384,VLOOKUP(H384,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H384,$A$2:$C$1041,3,1)),C384,VLOOKUP(H384,$A$2:$C$1041,3,1))</f>
         <v>561</v>
       </c>
       <c r="C384" s="1">
@@ -19583,7 +19592,7 @@
         <v>1089</v>
       </c>
       <c r="B385" s="5">
-        <f>IF(ISNA(VLOOKUP(H385,$A$2:$C$1040,3,1)),C385,VLOOKUP(H385,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H385,$A$2:$C$1041,3,1)),C385,VLOOKUP(H385,$A$2:$C$1041,3,1))</f>
         <v>561</v>
       </c>
       <c r="C385" s="1">
@@ -19616,7 +19625,7 @@
         <v>1092</v>
       </c>
       <c r="B386" s="5">
-        <f>IF(ISNA(VLOOKUP(H386,$A$2:$C$1040,3,1)),C386,VLOOKUP(H386,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H386,$A$2:$C$1041,3,1)),C386,VLOOKUP(H386,$A$2:$C$1041,3,1))</f>
         <v>561</v>
       </c>
       <c r="C386" s="1">
@@ -19649,7 +19658,7 @@
         <v>2058</v>
       </c>
       <c r="B387" s="5">
-        <f>IF(ISNA(VLOOKUP(H387,$A$2:$C$1040,3,1)),C387,VLOOKUP(H387,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H387,$A$2:$C$1041,3,1)),C387,VLOOKUP(H387,$A$2:$C$1041,3,1))</f>
         <v>541</v>
       </c>
       <c r="C387" s="1">
@@ -19682,7 +19691,7 @@
         <v>1095</v>
       </c>
       <c r="B388" s="5">
-        <f>IF(ISNA(VLOOKUP(H388,$A$2:$C$1040,3,1)),C388,VLOOKUP(H388,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H388,$A$2:$C$1041,3,1)),C388,VLOOKUP(H388,$A$2:$C$1041,3,1))</f>
         <v>541</v>
       </c>
       <c r="C388" s="1">
@@ -19715,7 +19724,7 @@
         <v>1098</v>
       </c>
       <c r="B389" s="5">
-        <f>IF(ISNA(VLOOKUP(H389,$A$2:$C$1040,3,1)),C389,VLOOKUP(H389,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H389,$A$2:$C$1041,3,1)),C389,VLOOKUP(H389,$A$2:$C$1041,3,1))</f>
         <v>18</v>
       </c>
       <c r="C389" s="1">
@@ -19748,7 +19757,7 @@
         <v>1101</v>
       </c>
       <c r="B390" s="5">
-        <f>IF(ISNA(VLOOKUP(H390,$A$2:$C$1040,3,1)),C390,VLOOKUP(H390,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H390,$A$2:$C$1041,3,1)),C390,VLOOKUP(H390,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C390" s="1">
@@ -19781,7 +19790,7 @@
         <v>1103</v>
       </c>
       <c r="B391" s="5">
-        <f>IF(ISNA(VLOOKUP(H391,$A$2:$C$1040,3,1)),C391,VLOOKUP(H391,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H391,$A$2:$C$1041,3,1)),C391,VLOOKUP(H391,$A$2:$C$1041,3,1))</f>
         <v>11</v>
       </c>
       <c r="C391" s="1">
@@ -19814,7 +19823,7 @@
         <v>1106</v>
       </c>
       <c r="B392" s="5">
-        <f>IF(ISNA(VLOOKUP(H392,$A$2:$C$1040,3,1)),C392,VLOOKUP(H392,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H392,$A$2:$C$1041,3,1)),C392,VLOOKUP(H392,$A$2:$C$1041,3,1))</f>
         <v>18</v>
       </c>
       <c r="C392" s="1">
@@ -19847,7 +19856,7 @@
         <v>1109</v>
       </c>
       <c r="B393" s="5">
-        <f>IF(ISNA(VLOOKUP(H393,$A$2:$C$1040,3,1)),C393,VLOOKUP(H393,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H393,$A$2:$C$1041,3,1)),C393,VLOOKUP(H393,$A$2:$C$1041,3,1))</f>
         <v>25</v>
       </c>
       <c r="C393" s="1">
@@ -19880,7 +19889,7 @@
         <v>1112</v>
       </c>
       <c r="B394" s="5">
-        <f>IF(ISNA(VLOOKUP(H394,$A$2:$C$1040,3,1)),C394,VLOOKUP(H394,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H394,$A$2:$C$1041,3,1)),C394,VLOOKUP(H394,$A$2:$C$1041,3,1))</f>
         <v>29</v>
       </c>
       <c r="C394" s="1">
@@ -19913,7 +19922,7 @@
         <v>1115</v>
       </c>
       <c r="B395" s="5">
-        <f>IF(ISNA(VLOOKUP(H395,$A$2:$C$1040,3,1)),C395,VLOOKUP(H395,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H395,$A$2:$C$1041,3,1)),C395,VLOOKUP(H395,$A$2:$C$1041,3,1))</f>
         <v>34</v>
       </c>
       <c r="C395" s="1">
@@ -19946,7 +19955,7 @@
         <v>1118</v>
       </c>
       <c r="B396" s="5">
-        <f>IF(ISNA(VLOOKUP(H396,$A$2:$C$1040,3,1)),C396,VLOOKUP(H396,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H396,$A$2:$C$1041,3,1)),C396,VLOOKUP(H396,$A$2:$C$1041,3,1))</f>
         <v>38</v>
       </c>
       <c r="C396" s="1">
@@ -19979,7 +19988,7 @@
         <v>1121</v>
       </c>
       <c r="B397" s="5">
-        <f>IF(ISNA(VLOOKUP(H397,$A$2:$C$1040,3,1)),C397,VLOOKUP(H397,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H397,$A$2:$C$1041,3,1)),C397,VLOOKUP(H397,$A$2:$C$1041,3,1))</f>
         <v>42</v>
       </c>
       <c r="C397" s="1">
@@ -20012,7 +20021,7 @@
         <v>1124</v>
       </c>
       <c r="B398" s="5">
-        <f>IF(ISNA(VLOOKUP(H398,$A$2:$C$1040,3,1)),C398,VLOOKUP(H398,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H398,$A$2:$C$1041,3,1)),C398,VLOOKUP(H398,$A$2:$C$1041,3,1))</f>
         <v>46</v>
       </c>
       <c r="C398" s="1">
@@ -20045,7 +20054,7 @@
         <v>1127</v>
       </c>
       <c r="B399" s="5">
-        <f>IF(ISNA(VLOOKUP(H399,$A$2:$C$1040,3,1)),C399,VLOOKUP(H399,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H399,$A$2:$C$1041,3,1)),C399,VLOOKUP(H399,$A$2:$C$1041,3,1))</f>
         <v>50</v>
       </c>
       <c r="C399" s="1">
@@ -20078,7 +20087,7 @@
         <v>1130</v>
       </c>
       <c r="B400" s="5">
-        <f>IF(ISNA(VLOOKUP(H400,$A$2:$C$1040,3,1)),C400,VLOOKUP(H400,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H400,$A$2:$C$1041,3,1)),C400,VLOOKUP(H400,$A$2:$C$1041,3,1))</f>
         <v>54</v>
       </c>
       <c r="C400" s="1">
@@ -20111,7 +20120,7 @@
         <v>1133</v>
       </c>
       <c r="B401" s="5">
-        <f>IF(ISNA(VLOOKUP(H401,$A$2:$C$1040,3,1)),C401,VLOOKUP(H401,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H401,$A$2:$C$1041,3,1)),C401,VLOOKUP(H401,$A$2:$C$1041,3,1))</f>
         <v>517</v>
       </c>
       <c r="C401" s="1">
@@ -20144,7 +20153,7 @@
         <v>1136</v>
       </c>
       <c r="B402" s="5">
-        <f>IF(ISNA(VLOOKUP(H402,$A$2:$C$1040,3,1)),C402,VLOOKUP(H402,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H402,$A$2:$C$1041,3,1)),C402,VLOOKUP(H402,$A$2:$C$1041,3,1))</f>
         <v>521</v>
       </c>
       <c r="C402" s="1">
@@ -20177,7 +20186,7 @@
         <v>1139</v>
       </c>
       <c r="B403" s="5">
-        <f>IF(ISNA(VLOOKUP(H403,$A$2:$C$1040,3,1)),C403,VLOOKUP(H403,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H403,$A$2:$C$1041,3,1)),C403,VLOOKUP(H403,$A$2:$C$1041,3,1))</f>
         <v>526</v>
       </c>
       <c r="C403" s="1">
@@ -20210,7 +20219,7 @@
         <v>1141</v>
       </c>
       <c r="B404" s="5">
-        <f>IF(ISNA(VLOOKUP(H404,$A$2:$C$1040,3,1)),C404,VLOOKUP(H404,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H404,$A$2:$C$1041,3,1)),C404,VLOOKUP(H404,$A$2:$C$1041,3,1))</f>
         <v>635</v>
       </c>
       <c r="C404" s="1">
@@ -20243,7 +20252,7 @@
         <v>1144</v>
       </c>
       <c r="B405" s="5">
-        <f>IF(ISNA(VLOOKUP(H405,$A$2:$C$1040,3,1)),C405,VLOOKUP(H405,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H405,$A$2:$C$1041,3,1)),C405,VLOOKUP(H405,$A$2:$C$1041,3,1))</f>
         <v>635</v>
       </c>
       <c r="C405" s="1">
@@ -20276,7 +20285,7 @@
         <v>1146</v>
       </c>
       <c r="B406" s="5">
-        <f>IF(ISNA(VLOOKUP(H406,$A$2:$C$1040,3,1)),C406,VLOOKUP(H406,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H406,$A$2:$C$1041,3,1)),C406,VLOOKUP(H406,$A$2:$C$1041,3,1))</f>
         <v>626</v>
       </c>
       <c r="C406" s="1">
@@ -20309,7 +20318,7 @@
         <v>1149</v>
       </c>
       <c r="B407" s="5">
-        <f>IF(ISNA(VLOOKUP(H407,$A$2:$C$1040,3,1)),C407,VLOOKUP(H407,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H407,$A$2:$C$1041,3,1)),C407,VLOOKUP(H407,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C407" s="1">
@@ -20342,7 +20351,7 @@
         <v>1152</v>
       </c>
       <c r="B408" s="5">
-        <f>IF(ISNA(VLOOKUP(H408,$A$2:$C$1040,3,1)),C408,VLOOKUP(H408,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H408,$A$2:$C$1041,3,1)),C408,VLOOKUP(H408,$A$2:$C$1041,3,1))</f>
         <v>172</v>
       </c>
       <c r="C408" s="1">
@@ -20375,7 +20384,7 @@
         <v>1155</v>
       </c>
       <c r="B409" s="5">
-        <f>IF(ISNA(VLOOKUP(H409,$A$2:$C$1040,3,1)),C409,VLOOKUP(H409,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H409,$A$2:$C$1041,3,1)),C409,VLOOKUP(H409,$A$2:$C$1041,3,1))</f>
         <v>172</v>
       </c>
       <c r="C409" s="1">
@@ -20408,7 +20417,7 @@
         <v>1158</v>
       </c>
       <c r="B410" s="5">
-        <f>IF(ISNA(VLOOKUP(H410,$A$2:$C$1040,3,1)),C410,VLOOKUP(H410,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H410,$A$2:$C$1041,3,1)),C410,VLOOKUP(H410,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C410" s="1">
@@ -20441,7 +20450,7 @@
         <v>1161</v>
       </c>
       <c r="B411" s="5">
-        <f>IF(ISNA(VLOOKUP(H411,$A$2:$C$1040,3,1)),C411,VLOOKUP(H411,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H411,$A$2:$C$1041,3,1)),C411,VLOOKUP(H411,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C411" s="1">
@@ -20474,7 +20483,7 @@
         <v>1164</v>
       </c>
       <c r="B412" s="5">
-        <f>IF(ISNA(VLOOKUP(H412,$A$2:$C$1040,3,1)),C412,VLOOKUP(H412,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H412,$A$2:$C$1041,3,1)),C412,VLOOKUP(H412,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C412" s="1">
@@ -20507,7 +20516,7 @@
         <v>1167</v>
       </c>
       <c r="B413" s="5">
-        <f>IF(ISNA(VLOOKUP(H413,$A$2:$C$1040,3,1)),C413,VLOOKUP(H413,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H413,$A$2:$C$1041,3,1)),C413,VLOOKUP(H413,$A$2:$C$1041,3,1))</f>
         <v>287</v>
       </c>
       <c r="C413" s="1">
@@ -20540,7 +20549,7 @@
         <v>1170</v>
       </c>
       <c r="B414" s="5">
-        <f>IF(ISNA(VLOOKUP(H414,$A$2:$C$1040,3,1)),C414,VLOOKUP(H414,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H414,$A$2:$C$1041,3,1)),C414,VLOOKUP(H414,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C414" s="1">
@@ -20573,7 +20582,7 @@
         <v>1173</v>
       </c>
       <c r="B415" s="5">
-        <f>IF(ISNA(VLOOKUP(H415,$A$2:$C$1040,3,1)),C415,VLOOKUP(H415,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H415,$A$2:$C$1041,3,1)),C415,VLOOKUP(H415,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C415" s="1">
@@ -20606,7 +20615,7 @@
         <v>1176</v>
       </c>
       <c r="B416" s="5">
-        <f>IF(ISNA(VLOOKUP(H416,$A$2:$C$1040,3,1)),C416,VLOOKUP(H416,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H416,$A$2:$C$1041,3,1)),C416,VLOOKUP(H416,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C416" s="1">
@@ -20639,7 +20648,7 @@
         <v>1179</v>
       </c>
       <c r="B417" s="5">
-        <f>IF(ISNA(VLOOKUP(H417,$A$2:$C$1040,3,1)),C417,VLOOKUP(H417,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H417,$A$2:$C$1041,3,1)),C417,VLOOKUP(H417,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C417" s="1">
@@ -20672,7 +20681,7 @@
         <v>1181</v>
       </c>
       <c r="B418" s="5">
-        <f>IF(ISNA(VLOOKUP(H418,$A$2:$C$1040,3,1)),C418,VLOOKUP(H418,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H418,$A$2:$C$1041,3,1)),C418,VLOOKUP(H418,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C418" s="1">
@@ -20705,7 +20714,7 @@
         <v>1183</v>
       </c>
       <c r="B419" s="5">
-        <f>IF(ISNA(VLOOKUP(H419,$A$2:$C$1040,3,1)),C419,VLOOKUP(H419,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H419,$A$2:$C$1041,3,1)),C419,VLOOKUP(H419,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C419" s="1">
@@ -20738,7 +20747,7 @@
         <v>1186</v>
       </c>
       <c r="B420" s="5">
-        <f>IF(ISNA(VLOOKUP(H420,$A$2:$C$1040,3,1)),C420,VLOOKUP(H420,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H420,$A$2:$C$1041,3,1)),C420,VLOOKUP(H420,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C420" s="1">
@@ -20771,7 +20780,7 @@
         <v>1189</v>
       </c>
       <c r="B421" s="5">
-        <f>IF(ISNA(VLOOKUP(H421,$A$2:$C$1040,3,1)),C421,VLOOKUP(H421,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H421,$A$2:$C$1041,3,1)),C421,VLOOKUP(H421,$A$2:$C$1041,3,1))</f>
         <v>206</v>
       </c>
       <c r="C421" s="1">
@@ -20804,7 +20813,7 @@
         <v>1192</v>
       </c>
       <c r="B422" s="5">
-        <f>IF(ISNA(VLOOKUP(H422,$A$2:$C$1040,3,1)),C422,VLOOKUP(H422,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H422,$A$2:$C$1041,3,1)),C422,VLOOKUP(H422,$A$2:$C$1041,3,1))</f>
         <v>11</v>
       </c>
       <c r="C422" s="1">
@@ -20837,7 +20846,7 @@
         <v>1195</v>
       </c>
       <c r="B423" s="5">
-        <f>IF(ISNA(VLOOKUP(H423,$A$2:$C$1040,3,1)),C423,VLOOKUP(H423,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H423,$A$2:$C$1041,3,1)),C423,VLOOKUP(H423,$A$2:$C$1041,3,1))</f>
         <v>18</v>
       </c>
       <c r="C423" s="1">
@@ -20870,7 +20879,7 @@
         <v>1198</v>
       </c>
       <c r="B424" s="5">
-        <f>IF(ISNA(VLOOKUP(H424,$A$2:$C$1040,3,1)),C424,VLOOKUP(H424,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H424,$A$2:$C$1041,3,1)),C424,VLOOKUP(H424,$A$2:$C$1041,3,1))</f>
         <v>25</v>
       </c>
       <c r="C424" s="1">
@@ -20903,7 +20912,7 @@
         <v>1201</v>
       </c>
       <c r="B425" s="5">
-        <f>IF(ISNA(VLOOKUP(H425,$A$2:$C$1040,3,1)),C425,VLOOKUP(H425,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H425,$A$2:$C$1041,3,1)),C425,VLOOKUP(H425,$A$2:$C$1041,3,1))</f>
         <v>29</v>
       </c>
       <c r="C425" s="1">
@@ -20936,7 +20945,7 @@
         <v>1204</v>
       </c>
       <c r="B426" s="5">
-        <f>IF(ISNA(VLOOKUP(H426,$A$2:$C$1040,3,1)),C426,VLOOKUP(H426,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H426,$A$2:$C$1041,3,1)),C426,VLOOKUP(H426,$A$2:$C$1041,3,1))</f>
         <v>34</v>
       </c>
       <c r="C426" s="1">
@@ -20969,7 +20978,7 @@
         <v>1207</v>
       </c>
       <c r="B427" s="5">
-        <f>IF(ISNA(VLOOKUP(H427,$A$2:$C$1040,3,1)),C427,VLOOKUP(H427,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H427,$A$2:$C$1041,3,1)),C427,VLOOKUP(H427,$A$2:$C$1041,3,1))</f>
         <v>38</v>
       </c>
       <c r="C427" s="1">
@@ -21002,7 +21011,7 @@
         <v>1210</v>
       </c>
       <c r="B428" s="5">
-        <f>IF(ISNA(VLOOKUP(H428,$A$2:$C$1040,3,1)),C428,VLOOKUP(H428,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H428,$A$2:$C$1041,3,1)),C428,VLOOKUP(H428,$A$2:$C$1041,3,1))</f>
         <v>42</v>
       </c>
       <c r="C428" s="1">
@@ -21035,7 +21044,7 @@
         <v>1213</v>
       </c>
       <c r="B429" s="5">
-        <f>IF(ISNA(VLOOKUP(H429,$A$2:$C$1040,3,1)),C429,VLOOKUP(H429,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H429,$A$2:$C$1041,3,1)),C429,VLOOKUP(H429,$A$2:$C$1041,3,1))</f>
         <v>46</v>
       </c>
       <c r="C429" s="1">
@@ -21068,7 +21077,7 @@
         <v>1216</v>
       </c>
       <c r="B430" s="5">
-        <f>IF(ISNA(VLOOKUP(H430,$A$2:$C$1040,3,1)),C430,VLOOKUP(H430,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H430,$A$2:$C$1041,3,1)),C430,VLOOKUP(H430,$A$2:$C$1041,3,1))</f>
         <v>50</v>
       </c>
       <c r="C430" s="1">
@@ -21101,7 +21110,7 @@
         <v>1219</v>
       </c>
       <c r="B431" s="5">
-        <f>IF(ISNA(VLOOKUP(H431,$A$2:$C$1040,3,1)),C431,VLOOKUP(H431,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H431,$A$2:$C$1041,3,1)),C431,VLOOKUP(H431,$A$2:$C$1041,3,1))</f>
         <v>54</v>
       </c>
       <c r="C431" s="1">
@@ -21134,7 +21143,7 @@
         <v>1222</v>
       </c>
       <c r="B432" s="5">
-        <f>IF(ISNA(VLOOKUP(H432,$A$2:$C$1040,3,1)),C432,VLOOKUP(H432,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H432,$A$2:$C$1041,3,1)),C432,VLOOKUP(H432,$A$2:$C$1041,3,1))</f>
         <v>517</v>
       </c>
       <c r="C432" s="1">
@@ -21167,7 +21176,7 @@
         <v>1225</v>
       </c>
       <c r="B433" s="5">
-        <f>IF(ISNA(VLOOKUP(H433,$A$2:$C$1040,3,1)),C433,VLOOKUP(H433,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H433,$A$2:$C$1041,3,1)),C433,VLOOKUP(H433,$A$2:$C$1041,3,1))</f>
         <v>521</v>
       </c>
       <c r="C433" s="1">
@@ -21200,7 +21209,7 @@
         <v>1228</v>
       </c>
       <c r="B434" s="5">
-        <f>IF(ISNA(VLOOKUP(H434,$A$2:$C$1040,3,1)),C434,VLOOKUP(H434,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H434,$A$2:$C$1041,3,1)),C434,VLOOKUP(H434,$A$2:$C$1041,3,1))</f>
         <v>578</v>
       </c>
       <c r="C434" s="1">
@@ -21233,7 +21242,7 @@
         <v>1231</v>
       </c>
       <c r="B435" s="5">
-        <f>IF(ISNA(VLOOKUP(H435,$A$2:$C$1040,3,1)),C435,VLOOKUP(H435,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H435,$A$2:$C$1041,3,1)),C435,VLOOKUP(H435,$A$2:$C$1041,3,1))</f>
         <v>583</v>
       </c>
       <c r="C435" s="1">
@@ -21266,7 +21275,7 @@
         <v>1234</v>
       </c>
       <c r="B436" s="5">
-        <f>IF(ISNA(VLOOKUP(H436,$A$2:$C$1040,3,1)),C436,VLOOKUP(H436,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H436,$A$2:$C$1041,3,1)),C436,VLOOKUP(H436,$A$2:$C$1041,3,1))</f>
         <v>573</v>
       </c>
       <c r="C436" s="1">
@@ -21299,7 +21308,7 @@
         <v>1237</v>
       </c>
       <c r="B437" s="5">
-        <f>IF(ISNA(VLOOKUP(H437,$A$2:$C$1040,3,1)),C437,VLOOKUP(H437,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H437,$A$2:$C$1041,3,1)),C437,VLOOKUP(H437,$A$2:$C$1041,3,1))</f>
         <v>589</v>
       </c>
       <c r="C437" s="1">
@@ -21332,7 +21341,7 @@
         <v>1240</v>
       </c>
       <c r="B438" s="5">
-        <f>IF(ISNA(VLOOKUP(H438,$A$2:$C$1040,3,1)),C438,VLOOKUP(H438,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H438,$A$2:$C$1041,3,1)),C438,VLOOKUP(H438,$A$2:$C$1041,3,1))</f>
         <v>594</v>
       </c>
       <c r="C438" s="1">
@@ -21365,7 +21374,7 @@
         <v>1244</v>
       </c>
       <c r="B439" s="5">
-        <f>IF(ISNA(VLOOKUP(H439,$A$2:$C$1040,3,1)),C439,VLOOKUP(H439,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H439,$A$2:$C$1041,3,1)),C439,VLOOKUP(H439,$A$2:$C$1041,3,1))</f>
         <v>597</v>
       </c>
       <c r="C439" s="1">
@@ -21398,7 +21407,7 @@
         <v>1247</v>
       </c>
       <c r="B440" s="5">
-        <f>IF(ISNA(VLOOKUP(H440,$A$2:$C$1040,3,1)),C440,VLOOKUP(H440,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H440,$A$2:$C$1041,3,1)),C440,VLOOKUP(H440,$A$2:$C$1041,3,1))</f>
         <v>578</v>
       </c>
       <c r="C440" s="1">
@@ -21431,7 +21440,7 @@
         <v>1250</v>
       </c>
       <c r="B441" s="5">
-        <f>IF(ISNA(VLOOKUP(H441,$A$2:$C$1040,3,1)),C441,VLOOKUP(H441,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H441,$A$2:$C$1041,3,1)),C441,VLOOKUP(H441,$A$2:$C$1041,3,1))</f>
         <v>573</v>
       </c>
       <c r="C441" s="1">
@@ -21464,7 +21473,7 @@
         <v>1243</v>
       </c>
       <c r="B442" s="5">
-        <f>IF(ISNA(VLOOKUP(H442,$A$2:$C$1040,3,1)),C442,VLOOKUP(H442,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H442,$A$2:$C$1041,3,1)),C442,VLOOKUP(H442,$A$2:$C$1041,3,1))</f>
         <v>594</v>
       </c>
       <c r="C442" s="1">
@@ -21499,7 +21508,7 @@
         <v>1254</v>
       </c>
       <c r="B443" s="5">
-        <f>IF(ISNA(VLOOKUP(H443,$A$2:$C$1040,3,1)),C443,VLOOKUP(H443,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H443,$A$2:$C$1041,3,1)),C443,VLOOKUP(H443,$A$2:$C$1041,3,1))</f>
         <v>583</v>
       </c>
       <c r="C443" s="1">
@@ -21532,7 +21541,7 @@
         <v>1257</v>
       </c>
       <c r="B444" s="5">
-        <f>IF(ISNA(VLOOKUP(H444,$A$2:$C$1040,3,1)),C444,VLOOKUP(H444,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H444,$A$2:$C$1041,3,1)),C444,VLOOKUP(H444,$A$2:$C$1041,3,1))</f>
         <v>589</v>
       </c>
       <c r="C444" s="1">
@@ -21565,7 +21574,7 @@
         <v>1260</v>
       </c>
       <c r="B445" s="5">
-        <f>IF(ISNA(VLOOKUP(H445,$A$2:$C$1040,3,1)),C445,VLOOKUP(H445,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H445,$A$2:$C$1041,3,1)),C445,VLOOKUP(H445,$A$2:$C$1041,3,1))</f>
         <v>598</v>
       </c>
       <c r="C445" s="1">
@@ -21598,7 +21607,7 @@
         <v>1264</v>
       </c>
       <c r="B446" s="5">
-        <f>IF(ISNA(VLOOKUP(H446,$A$2:$C$1040,3,1)),C446,VLOOKUP(H446,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H446,$A$2:$C$1041,3,1)),C446,VLOOKUP(H446,$A$2:$C$1041,3,1))</f>
         <v>573</v>
       </c>
       <c r="C446" s="1">
@@ -21631,7 +21640,7 @@
         <v>1267</v>
       </c>
       <c r="B447" s="5">
-        <f>IF(ISNA(VLOOKUP(H447,$A$2:$C$1040,3,1)),C447,VLOOKUP(H447,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H447,$A$2:$C$1041,3,1)),C447,VLOOKUP(H447,$A$2:$C$1041,3,1))</f>
         <v>594</v>
       </c>
       <c r="C447" s="1">
@@ -21664,7 +21673,7 @@
         <v>1270</v>
       </c>
       <c r="B448" s="5">
-        <f>IF(ISNA(VLOOKUP(H448,$A$2:$C$1040,3,1)),C448,VLOOKUP(H448,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H448,$A$2:$C$1041,3,1)),C448,VLOOKUP(H448,$A$2:$C$1041,3,1))</f>
         <v>578</v>
       </c>
       <c r="C448" s="1">
@@ -21697,7 +21706,7 @@
         <v>1271</v>
       </c>
       <c r="B449" s="5">
-        <f>IF(ISNA(VLOOKUP(H449,$A$2:$C$1040,3,1)),C449,VLOOKUP(H449,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H449,$A$2:$C$1041,3,1)),C449,VLOOKUP(H449,$A$2:$C$1041,3,1))</f>
         <v>583</v>
       </c>
       <c r="C449" s="1">
@@ -21730,7 +21739,7 @@
         <v>1272</v>
       </c>
       <c r="B450" s="5">
-        <f>IF(ISNA(VLOOKUP(H450,$A$2:$C$1040,3,1)),C450,VLOOKUP(H450,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H450,$A$2:$C$1041,3,1)),C450,VLOOKUP(H450,$A$2:$C$1041,3,1))</f>
         <v>573</v>
       </c>
       <c r="C450" s="1">
@@ -21763,7 +21772,7 @@
         <v>1273</v>
       </c>
       <c r="B451" s="5">
-        <f>IF(ISNA(VLOOKUP(H451,$A$2:$C$1040,3,1)),C451,VLOOKUP(H451,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H451,$A$2:$C$1041,3,1)),C451,VLOOKUP(H451,$A$2:$C$1041,3,1))</f>
         <v>589</v>
       </c>
       <c r="C451" s="1">
@@ -21796,7 +21805,7 @@
         <v>1274</v>
       </c>
       <c r="B452" s="5">
-        <f>IF(ISNA(VLOOKUP(H452,$A$2:$C$1040,3,1)),C452,VLOOKUP(H452,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H452,$A$2:$C$1041,3,1)),C452,VLOOKUP(H452,$A$2:$C$1041,3,1))</f>
         <v>583</v>
       </c>
       <c r="C452" s="1">
@@ -21829,7 +21838,7 @@
         <v>1277</v>
       </c>
       <c r="B453" s="5">
-        <f>IF(ISNA(VLOOKUP(H453,$A$2:$C$1040,3,1)),C453,VLOOKUP(H453,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H453,$A$2:$C$1041,3,1)),C453,VLOOKUP(H453,$A$2:$C$1041,3,1))</f>
         <v>589</v>
       </c>
       <c r="C453" s="1">
@@ -21862,7 +21871,7 @@
         <v>1280</v>
       </c>
       <c r="B454" s="5">
-        <f>IF(ISNA(VLOOKUP(H454,$A$2:$C$1040,3,1)),C454,VLOOKUP(H454,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H454,$A$2:$C$1041,3,1)),C454,VLOOKUP(H454,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C454" s="1">
@@ -21895,7 +21904,7 @@
         <v>1283</v>
       </c>
       <c r="B455" s="5">
-        <f>IF(ISNA(VLOOKUP(H455,$A$2:$C$1040,3,1)),C455,VLOOKUP(H455,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H455,$A$2:$C$1041,3,1)),C455,VLOOKUP(H455,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C455" s="1">
@@ -21928,7 +21937,7 @@
         <v>1287</v>
       </c>
       <c r="B456" s="5">
-        <f>IF(ISNA(VLOOKUP(H456,$A$2:$C$1040,3,1)),C456,VLOOKUP(H456,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H456,$A$2:$C$1041,3,1)),C456,VLOOKUP(H456,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C456" s="1">
@@ -21961,7 +21970,7 @@
         <v>1290</v>
       </c>
       <c r="B457" s="5">
-        <f>IF(ISNA(VLOOKUP(H457,$A$2:$C$1040,3,1)),C457,VLOOKUP(H457,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H457,$A$2:$C$1041,3,1)),C457,VLOOKUP(H457,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C457" s="1">
@@ -21994,7 +22003,7 @@
         <v>1293</v>
       </c>
       <c r="B458" s="5">
-        <f>IF(ISNA(VLOOKUP(H458,$A$2:$C$1040,3,1)),C458,VLOOKUP(H458,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H458,$A$2:$C$1041,3,1)),C458,VLOOKUP(H458,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C458" s="1">
@@ -22027,7 +22036,7 @@
         <v>1296</v>
       </c>
       <c r="B459" s="5">
-        <f>IF(ISNA(VLOOKUP(H459,$A$2:$C$1040,3,1)),C459,VLOOKUP(H459,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H459,$A$2:$C$1041,3,1)),C459,VLOOKUP(H459,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C459" s="1">
@@ -22060,7 +22069,7 @@
         <v>1299</v>
       </c>
       <c r="B460" s="5">
-        <f>IF(ISNA(VLOOKUP(H460,$A$2:$C$1040,3,1)),C460,VLOOKUP(H460,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H460,$A$2:$C$1041,3,1)),C460,VLOOKUP(H460,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C460" s="1">
@@ -22093,7 +22102,7 @@
         <v>1302</v>
       </c>
       <c r="B461" s="5">
-        <f>IF(ISNA(VLOOKUP(H461,$A$2:$C$1040,3,1)),C461,VLOOKUP(H461,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H461,$A$2:$C$1041,3,1)),C461,VLOOKUP(H461,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C461" s="1">
@@ -22126,7 +22135,7 @@
         <v>1305</v>
       </c>
       <c r="B462" s="5">
-        <f>IF(ISNA(VLOOKUP(H462,$A$2:$C$1040,3,1)),C462,VLOOKUP(H462,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H462,$A$2:$C$1041,3,1)),C462,VLOOKUP(H462,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C462" s="1">
@@ -22159,7 +22168,7 @@
         <v>1308</v>
       </c>
       <c r="B463" s="5">
-        <f>IF(ISNA(VLOOKUP(H463,$A$2:$C$1040,3,1)),C463,VLOOKUP(H463,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H463,$A$2:$C$1041,3,1)),C463,VLOOKUP(H463,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C463" s="1">
@@ -22192,7 +22201,7 @@
         <v>1311</v>
       </c>
       <c r="B464" s="5">
-        <f>IF(ISNA(VLOOKUP(H464,$A$2:$C$1040,3,1)),C464,VLOOKUP(H464,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H464,$A$2:$C$1041,3,1)),C464,VLOOKUP(H464,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C464" s="1">
@@ -22225,7 +22234,7 @@
         <v>1314</v>
       </c>
       <c r="B465" s="5">
-        <f>IF(ISNA(VLOOKUP(H465,$A$2:$C$1040,3,1)),C465,VLOOKUP(H465,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H465,$A$2:$C$1041,3,1)),C465,VLOOKUP(H465,$A$2:$C$1041,3,1))</f>
         <v>11</v>
       </c>
       <c r="C465" s="1">
@@ -22258,7 +22267,7 @@
         <v>1317</v>
       </c>
       <c r="B466" s="5">
-        <f>IF(ISNA(VLOOKUP(H466,$A$2:$C$1040,3,1)),C466,VLOOKUP(H466,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H466,$A$2:$C$1041,3,1)),C466,VLOOKUP(H466,$A$2:$C$1041,3,1))</f>
         <v>462</v>
       </c>
       <c r="C466" s="1">
@@ -22291,7 +22300,7 @@
         <v>1320</v>
       </c>
       <c r="B467" s="5">
-        <f>IF(ISNA(VLOOKUP(H467,$A$2:$C$1040,3,1)),C467,VLOOKUP(H467,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H467,$A$2:$C$1041,3,1)),C467,VLOOKUP(H467,$A$2:$C$1041,3,1))</f>
         <v>470</v>
       </c>
       <c r="C467" s="1">
@@ -22324,7 +22333,7 @@
         <v>1323</v>
       </c>
       <c r="B468" s="5">
-        <f>IF(ISNA(VLOOKUP(H468,$A$2:$C$1040,3,1)),C468,VLOOKUP(H468,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H468,$A$2:$C$1041,3,1)),C468,VLOOKUP(H468,$A$2:$C$1041,3,1))</f>
         <v>521</v>
       </c>
       <c r="C468" s="1">
@@ -22357,7 +22366,7 @@
         <v>1326</v>
       </c>
       <c r="B469" s="5">
-        <f>IF(ISNA(VLOOKUP(H469,$A$2:$C$1040,3,1)),C469,VLOOKUP(H469,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H469,$A$2:$C$1041,3,1)),C469,VLOOKUP(H469,$A$2:$C$1041,3,1))</f>
         <v>526</v>
       </c>
       <c r="C469" s="1">
@@ -22390,7 +22399,7 @@
         <v>1329</v>
       </c>
       <c r="B470" s="5">
-        <f>IF(ISNA(VLOOKUP(H470,$A$2:$C$1040,3,1)),C470,VLOOKUP(H470,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H470,$A$2:$C$1041,3,1)),C470,VLOOKUP(H470,$A$2:$C$1041,3,1))</f>
         <v>526</v>
       </c>
       <c r="C470" s="1">
@@ -22423,7 +22432,7 @@
         <v>1332</v>
       </c>
       <c r="B471" s="5">
-        <f>IF(ISNA(VLOOKUP(H471,$A$2:$C$1040,3,1)),C471,VLOOKUP(H471,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H471,$A$2:$C$1041,3,1)),C471,VLOOKUP(H471,$A$2:$C$1041,3,1))</f>
         <v>633</v>
       </c>
       <c r="C471" s="1">
@@ -22456,7 +22465,7 @@
         <v>1335</v>
       </c>
       <c r="B472" s="5">
-        <f>IF(ISNA(VLOOKUP(H472,$A$2:$C$1040,3,1)),C472,VLOOKUP(H472,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H472,$A$2:$C$1041,3,1)),C472,VLOOKUP(H472,$A$2:$C$1041,3,1))</f>
         <v>29</v>
       </c>
       <c r="C472" s="1">
@@ -22489,7 +22498,7 @@
         <v>1338</v>
       </c>
       <c r="B473" s="5">
-        <f>IF(ISNA(VLOOKUP(H473,$A$2:$C$1040,3,1)),C473,VLOOKUP(H473,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H473,$A$2:$C$1041,3,1)),C473,VLOOKUP(H473,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C473" s="1">
@@ -22522,7 +22531,7 @@
         <v>1341</v>
       </c>
       <c r="B474" s="5">
-        <f>IF(ISNA(VLOOKUP(H474,$A$2:$C$1040,3,1)),C474,VLOOKUP(H474,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H474,$A$2:$C$1041,3,1)),C474,VLOOKUP(H474,$A$2:$C$1041,3,1))</f>
         <v>633</v>
       </c>
       <c r="C474" s="1">
@@ -22555,7 +22564,7 @@
         <v>1143</v>
       </c>
       <c r="B475" s="5">
-        <f>IF(ISNA(VLOOKUP(H475,$A$2:$C$1040,3,1)),C475,VLOOKUP(H475,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H475,$A$2:$C$1041,3,1)),C475,VLOOKUP(H475,$A$2:$C$1041,3,1))</f>
         <v>635</v>
       </c>
       <c r="C475" s="1">
@@ -22588,7 +22597,7 @@
         <v>1346</v>
       </c>
       <c r="B476" s="5">
-        <f>IF(ISNA(VLOOKUP(H476,$A$2:$C$1040,3,1)),C476,VLOOKUP(H476,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H476,$A$2:$C$1041,3,1)),C476,VLOOKUP(H476,$A$2:$C$1041,3,1))</f>
         <v>647</v>
       </c>
       <c r="C476" s="1">
@@ -22621,7 +22630,7 @@
         <v>1349</v>
       </c>
       <c r="B477" s="5">
-        <f>IF(ISNA(VLOOKUP(H477,$A$2:$C$1040,3,1)),C477,VLOOKUP(H477,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H477,$A$2:$C$1041,3,1)),C477,VLOOKUP(H477,$A$2:$C$1041,3,1))</f>
         <v>649</v>
       </c>
       <c r="C477" s="1">
@@ -22654,7 +22663,7 @@
         <v>1352</v>
       </c>
       <c r="B478" s="5">
-        <f>IF(ISNA(VLOOKUP(H478,$A$2:$C$1040,3,1)),C478,VLOOKUP(H478,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H478,$A$2:$C$1041,3,1)),C478,VLOOKUP(H478,$A$2:$C$1041,3,1))</f>
         <v>649</v>
       </c>
       <c r="C478" s="1">
@@ -22687,7 +22696,7 @@
         <v>1355</v>
       </c>
       <c r="B479" s="5">
-        <f>IF(ISNA(VLOOKUP(H479,$A$2:$C$1040,3,1)),C479,VLOOKUP(H479,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H479,$A$2:$C$1041,3,1)),C479,VLOOKUP(H479,$A$2:$C$1041,3,1))</f>
         <v>649</v>
       </c>
       <c r="C479" s="1">
@@ -22720,7 +22729,7 @@
         <v>1358</v>
       </c>
       <c r="B480" s="5">
-        <f>IF(ISNA(VLOOKUP(H480,$A$2:$C$1040,3,1)),C480,VLOOKUP(H480,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H480,$A$2:$C$1041,3,1)),C480,VLOOKUP(H480,$A$2:$C$1041,3,1))</f>
         <v>606</v>
       </c>
       <c r="C480" s="1">
@@ -22753,7 +22762,7 @@
         <v>1361</v>
       </c>
       <c r="B481" s="5">
-        <f>IF(ISNA(VLOOKUP(H481,$A$2:$C$1040,3,1)),C481,VLOOKUP(H481,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H481,$A$2:$C$1041,3,1)),C481,VLOOKUP(H481,$A$2:$C$1041,3,1))</f>
         <v>606</v>
       </c>
       <c r="C481" s="1">
@@ -22786,7 +22795,7 @@
         <v>1364</v>
       </c>
       <c r="B482" s="5">
-        <f>IF(ISNA(VLOOKUP(H482,$A$2:$C$1040,3,1)),C482,VLOOKUP(H482,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H482,$A$2:$C$1041,3,1)),C482,VLOOKUP(H482,$A$2:$C$1041,3,1))</f>
         <v>606</v>
       </c>
       <c r="C482" s="1">
@@ -22819,7 +22828,7 @@
         <v>1367</v>
       </c>
       <c r="B483" s="5">
-        <f>IF(ISNA(VLOOKUP(H483,$A$2:$C$1040,3,1)),C483,VLOOKUP(H483,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H483,$A$2:$C$1041,3,1)),C483,VLOOKUP(H483,$A$2:$C$1041,3,1))</f>
         <v>606</v>
       </c>
       <c r="C483" s="1">
@@ -22852,7 +22861,7 @@
         <v>1370</v>
       </c>
       <c r="B484" s="5">
-        <f>IF(ISNA(VLOOKUP(H484,$A$2:$C$1040,3,1)),C484,VLOOKUP(H484,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H484,$A$2:$C$1041,3,1)),C484,VLOOKUP(H484,$A$2:$C$1041,3,1))</f>
         <v>599</v>
       </c>
       <c r="C484" s="1">
@@ -22885,7 +22894,7 @@
         <v>1373</v>
       </c>
       <c r="B485" s="5">
-        <f>IF(ISNA(VLOOKUP(H485,$A$2:$C$1040,3,1)),C485,VLOOKUP(H485,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H485,$A$2:$C$1041,3,1)),C485,VLOOKUP(H485,$A$2:$C$1041,3,1))</f>
         <v>599</v>
       </c>
       <c r="C485" s="1">
@@ -22918,7 +22927,7 @@
         <v>1376</v>
       </c>
       <c r="B486" s="5">
-        <f>IF(ISNA(VLOOKUP(H486,$A$2:$C$1040,3,1)),C486,VLOOKUP(H486,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H486,$A$2:$C$1041,3,1)),C486,VLOOKUP(H486,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C486" s="1">
@@ -22951,7 +22960,7 @@
         <v>1379</v>
       </c>
       <c r="B487" s="5">
-        <f>IF(ISNA(VLOOKUP(H487,$A$2:$C$1040,3,1)),C487,VLOOKUP(H487,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H487,$A$2:$C$1041,3,1)),C487,VLOOKUP(H487,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C487" s="1">
@@ -22984,7 +22993,7 @@
         <v>1382</v>
       </c>
       <c r="B488" s="5">
-        <f>IF(ISNA(VLOOKUP(H488,$A$2:$C$1040,3,1)),C488,VLOOKUP(H488,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H488,$A$2:$C$1041,3,1)),C488,VLOOKUP(H488,$A$2:$C$1041,3,1))</f>
         <v>638</v>
       </c>
       <c r="C488" s="1">
@@ -23017,7 +23026,7 @@
         <v>1385</v>
       </c>
       <c r="B489" s="5">
-        <f>IF(ISNA(VLOOKUP(H489,$A$2:$C$1040,3,1)),C489,VLOOKUP(H489,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H489,$A$2:$C$1041,3,1)),C489,VLOOKUP(H489,$A$2:$C$1041,3,1))</f>
         <v>638</v>
       </c>
       <c r="C489" s="1">
@@ -23050,7 +23059,7 @@
         <v>1388</v>
       </c>
       <c r="B490" s="5">
-        <f>IF(ISNA(VLOOKUP(H490,$A$2:$C$1040,3,1)),C490,VLOOKUP(H490,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H490,$A$2:$C$1041,3,1)),C490,VLOOKUP(H490,$A$2:$C$1041,3,1))</f>
         <v>638</v>
       </c>
       <c r="C490" s="1">
@@ -23083,7 +23092,7 @@
         <v>1391</v>
       </c>
       <c r="B491" s="5">
-        <f>IF(ISNA(VLOOKUP(H491,$A$2:$C$1040,3,1)),C491,VLOOKUP(H491,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H491,$A$2:$C$1041,3,1)),C491,VLOOKUP(H491,$A$2:$C$1041,3,1))</f>
         <v>638</v>
       </c>
       <c r="C491" s="1">
@@ -23116,7 +23125,7 @@
         <v>1394</v>
       </c>
       <c r="B492" s="5">
-        <f>IF(ISNA(VLOOKUP(H492,$A$2:$C$1040,3,1)),C492,VLOOKUP(H492,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H492,$A$2:$C$1041,3,1)),C492,VLOOKUP(H492,$A$2:$C$1041,3,1))</f>
         <v>638</v>
       </c>
       <c r="C492" s="1">
@@ -23149,7 +23158,7 @@
         <v>1397</v>
       </c>
       <c r="B493" s="5">
-        <f>IF(ISNA(VLOOKUP(H493,$A$2:$C$1040,3,1)),C493,VLOOKUP(H493,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H493,$A$2:$C$1041,3,1)),C493,VLOOKUP(H493,$A$2:$C$1041,3,1))</f>
         <v>638</v>
       </c>
       <c r="C493" s="1">
@@ -23182,7 +23191,7 @@
         <v>1400</v>
       </c>
       <c r="B494" s="5">
-        <f>IF(ISNA(VLOOKUP(H494,$A$2:$C$1040,3,1)),C494,VLOOKUP(H494,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H494,$A$2:$C$1041,3,1)),C494,VLOOKUP(H494,$A$2:$C$1041,3,1))</f>
         <v>551</v>
       </c>
       <c r="C494" s="1">
@@ -23215,7 +23224,7 @@
         <v>1403</v>
       </c>
       <c r="B495" s="5">
-        <f>IF(ISNA(VLOOKUP(H495,$A$2:$C$1040,3,1)),C495,VLOOKUP(H495,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H495,$A$2:$C$1041,3,1)),C495,VLOOKUP(H495,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C495" s="1">
@@ -23248,7 +23257,7 @@
         <v>1406</v>
       </c>
       <c r="B496" s="5">
-        <f>IF(ISNA(VLOOKUP(H496,$A$2:$C$1040,3,1)),C496,VLOOKUP(H496,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H496,$A$2:$C$1041,3,1)),C496,VLOOKUP(H496,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C496" s="1">
@@ -23281,7 +23290,7 @@
         <v>1409</v>
       </c>
       <c r="B497" s="5">
-        <f>IF(ISNA(VLOOKUP(H497,$A$2:$C$1040,3,1)),C497,VLOOKUP(H497,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H497,$A$2:$C$1041,3,1)),C497,VLOOKUP(H497,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C497" s="1">
@@ -23314,7 +23323,7 @@
         <v>1412</v>
       </c>
       <c r="B498" s="5">
-        <f>IF(ISNA(VLOOKUP(H498,$A$2:$C$1040,3,1)),C498,VLOOKUP(H498,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H498,$A$2:$C$1041,3,1)),C498,VLOOKUP(H498,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C498" s="1">
@@ -23347,7 +23356,7 @@
         <v>1415</v>
       </c>
       <c r="B499" s="5">
-        <f>IF(ISNA(VLOOKUP(H499,$A$2:$C$1040,3,1)),C499,VLOOKUP(H499,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H499,$A$2:$C$1041,3,1)),C499,VLOOKUP(H499,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C499" s="1">
@@ -23380,7 +23389,7 @@
         <v>1418</v>
       </c>
       <c r="B500" s="5">
-        <f>IF(ISNA(VLOOKUP(H500,$A$2:$C$1040,3,1)),C500,VLOOKUP(H500,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H500,$A$2:$C$1041,3,1)),C500,VLOOKUP(H500,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C500" s="1">
@@ -23413,7 +23422,7 @@
         <v>1421</v>
       </c>
       <c r="B501" s="5">
-        <f>IF(ISNA(VLOOKUP(H501,$A$2:$C$1040,3,1)),C501,VLOOKUP(H501,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H501,$A$2:$C$1041,3,1)),C501,VLOOKUP(H501,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C501" s="1">
@@ -23446,7 +23455,7 @@
         <v>1424</v>
       </c>
       <c r="B502" s="5">
-        <f>IF(ISNA(VLOOKUP(H502,$A$2:$C$1040,3,1)),C502,VLOOKUP(H502,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H502,$A$2:$C$1041,3,1)),C502,VLOOKUP(H502,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C502" s="1">
@@ -23479,7 +23488,7 @@
         <v>1427</v>
       </c>
       <c r="B503" s="5">
-        <f>IF(ISNA(VLOOKUP(H503,$A$2:$C$1040,3,1)),C503,VLOOKUP(H503,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H503,$A$2:$C$1041,3,1)),C503,VLOOKUP(H503,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C503" s="1">
@@ -23512,7 +23521,7 @@
         <v>107</v>
       </c>
       <c r="B504" s="5">
-        <f>IF(ISNA(VLOOKUP(H504,$A$2:$C$1040,3,1)),C504,VLOOKUP(H504,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H504,$A$2:$C$1041,3,1)),C504,VLOOKUP(H504,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C504" s="1">
@@ -23545,7 +23554,7 @@
         <v>1432</v>
       </c>
       <c r="B505" s="5">
-        <f>IF(ISNA(VLOOKUP(H505,$A$2:$C$1040,3,1)),C505,VLOOKUP(H505,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H505,$A$2:$C$1041,3,1)),C505,VLOOKUP(H505,$A$2:$C$1041,3,1))</f>
         <v>611</v>
       </c>
       <c r="C505" s="1">
@@ -23578,7 +23587,7 @@
         <v>1435</v>
       </c>
       <c r="B506" s="5">
-        <f>IF(ISNA(VLOOKUP(H506,$A$2:$C$1040,3,1)),C506,VLOOKUP(H506,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H506,$A$2:$C$1041,3,1)),C506,VLOOKUP(H506,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C506" s="1">
@@ -23611,7 +23620,7 @@
         <v>1438</v>
       </c>
       <c r="B507" s="5">
-        <f>IF(ISNA(VLOOKUP(H507,$A$2:$C$1040,3,1)),C507,VLOOKUP(H507,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H507,$A$2:$C$1041,3,1)),C507,VLOOKUP(H507,$A$2:$C$1041,3,1))</f>
         <v>675</v>
       </c>
       <c r="C507" s="1">
@@ -23644,7 +23653,7 @@
         <v>1441</v>
       </c>
       <c r="B508" s="5">
-        <f>IF(ISNA(VLOOKUP(H508,$A$2:$C$1040,3,1)),C508,VLOOKUP(H508,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H508,$A$2:$C$1041,3,1)),C508,VLOOKUP(H508,$A$2:$C$1041,3,1))</f>
         <v>646</v>
       </c>
       <c r="C508" s="1">
@@ -23677,7 +23686,7 @@
         <v>1444</v>
       </c>
       <c r="B509" s="5">
-        <f>IF(ISNA(VLOOKUP(H509,$A$2:$C$1040,3,1)),C509,VLOOKUP(H509,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H509,$A$2:$C$1041,3,1)),C509,VLOOKUP(H509,$A$2:$C$1041,3,1))</f>
         <v>418</v>
       </c>
       <c r="C509" s="1">
@@ -23710,7 +23719,7 @@
         <v>1447</v>
       </c>
       <c r="B510" s="5">
-        <f>IF(ISNA(VLOOKUP(H510,$A$2:$C$1040,3,1)),C510,VLOOKUP(H510,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H510,$A$2:$C$1041,3,1)),C510,VLOOKUP(H510,$A$2:$C$1041,3,1))</f>
         <v>426</v>
       </c>
       <c r="C510" s="1">
@@ -23743,7 +23752,7 @@
         <v>1450</v>
       </c>
       <c r="B511" s="5">
-        <f>IF(ISNA(VLOOKUP(H511,$A$2:$C$1040,3,1)),C511,VLOOKUP(H511,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H511,$A$2:$C$1041,3,1)),C511,VLOOKUP(H511,$A$2:$C$1041,3,1))</f>
         <v>451</v>
       </c>
       <c r="C511" s="1">
@@ -23776,7 +23785,7 @@
         <v>1453</v>
       </c>
       <c r="B512" s="5">
-        <f>IF(ISNA(VLOOKUP(H512,$A$2:$C$1040,3,1)),C512,VLOOKUP(H512,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H512,$A$2:$C$1041,3,1)),C512,VLOOKUP(H512,$A$2:$C$1041,3,1))</f>
         <v>644</v>
       </c>
       <c r="C512" s="1">
@@ -23809,7 +23818,7 @@
         <v>1456</v>
       </c>
       <c r="B513" s="5">
-        <f>IF(ISNA(VLOOKUP(H513,$A$2:$C$1040,3,1)),C513,VLOOKUP(H513,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H513,$A$2:$C$1041,3,1)),C513,VLOOKUP(H513,$A$2:$C$1041,3,1))</f>
         <v>644</v>
       </c>
       <c r="C513" s="1">
@@ -23842,7 +23851,7 @@
         <v>1459</v>
       </c>
       <c r="B514" s="5">
-        <f>IF(ISNA(VLOOKUP(H514,$A$2:$C$1040,3,1)),C514,VLOOKUP(H514,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H514,$A$2:$C$1041,3,1)),C514,VLOOKUP(H514,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C514" s="1">
@@ -23875,7 +23884,7 @@
         <v>1462</v>
       </c>
       <c r="B515" s="5">
-        <f>IF(ISNA(VLOOKUP(H515,$A$2:$C$1040,3,1)),C515,VLOOKUP(H515,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H515,$A$2:$C$1041,3,1)),C515,VLOOKUP(H515,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C515" s="1">
@@ -23908,7 +23917,7 @@
         <v>1465</v>
       </c>
       <c r="B516" s="5">
-        <f>IF(ISNA(VLOOKUP(H516,$A$2:$C$1040,3,1)),C516,VLOOKUP(H516,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H516,$A$2:$C$1041,3,1)),C516,VLOOKUP(H516,$A$2:$C$1041,3,1))</f>
         <v>647</v>
       </c>
       <c r="C516" s="1">
@@ -23941,7 +23950,7 @@
         <v>1468</v>
       </c>
       <c r="B517" s="5">
-        <f>IF(ISNA(VLOOKUP(H517,$A$2:$C$1040,3,1)),C517,VLOOKUP(H517,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H517,$A$2:$C$1041,3,1)),C517,VLOOKUP(H517,$A$2:$C$1041,3,1))</f>
         <v>599</v>
       </c>
       <c r="C517" s="1">
@@ -23974,7 +23983,7 @@
         <v>1471</v>
       </c>
       <c r="B518" s="5">
-        <f>IF(ISNA(VLOOKUP(H518,$A$2:$C$1040,3,1)),C518,VLOOKUP(H518,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H518,$A$2:$C$1041,3,1)),C518,VLOOKUP(H518,$A$2:$C$1041,3,1))</f>
         <v>599</v>
       </c>
       <c r="C518" s="1">
@@ -24007,7 +24016,7 @@
         <v>1474</v>
       </c>
       <c r="B519" s="5">
-        <f>IF(ISNA(VLOOKUP(H519,$A$2:$C$1040,3,1)),C519,VLOOKUP(H519,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H519,$A$2:$C$1041,3,1)),C519,VLOOKUP(H519,$A$2:$C$1041,3,1))</f>
         <v>599</v>
       </c>
       <c r="C519" s="1">
@@ -24040,7 +24049,7 @@
         <v>1477</v>
       </c>
       <c r="B520" s="5">
-        <f>IF(ISNA(VLOOKUP(H520,$A$2:$C$1040,3,1)),C520,VLOOKUP(H520,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H520,$A$2:$C$1041,3,1)),C520,VLOOKUP(H520,$A$2:$C$1041,3,1))</f>
         <v>541</v>
       </c>
       <c r="C520" s="1">
@@ -24073,7 +24082,7 @@
         <v>1480</v>
       </c>
       <c r="B521" s="5">
-        <f>IF(ISNA(VLOOKUP(H521,$A$2:$C$1040,3,1)),C521,VLOOKUP(H521,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H521,$A$2:$C$1041,3,1)),C521,VLOOKUP(H521,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C521" s="1">
@@ -24106,7 +24115,7 @@
         <v>1484</v>
       </c>
       <c r="B522" s="5">
-        <f>IF(ISNA(VLOOKUP(H522,$A$2:$C$1040,3,1)),C522,VLOOKUP(H522,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H522,$A$2:$C$1041,3,1)),C522,VLOOKUP(H522,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C522" s="1">
@@ -24139,7 +24148,7 @@
         <v>2022</v>
       </c>
       <c r="B523" s="5">
-        <f>IF(ISNA(VLOOKUP(H523,$A$2:$C$1040,3,1)),C523,VLOOKUP(H523,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H523,$A$2:$C$1041,3,1)),C523,VLOOKUP(H523,$A$2:$C$1041,3,1))</f>
         <v>578</v>
       </c>
       <c r="C523" s="1">
@@ -24172,7 +24181,7 @@
         <v>1487</v>
       </c>
       <c r="B524" s="5">
-        <f>IF(ISNA(VLOOKUP(H524,$A$2:$C$1040,3,1)),C524,VLOOKUP(H524,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H524,$A$2:$C$1041,3,1)),C524,VLOOKUP(H524,$A$2:$C$1041,3,1))</f>
         <v>521</v>
       </c>
       <c r="C524" s="1">
@@ -24205,7 +24214,7 @@
         <v>1483</v>
       </c>
       <c r="B525" s="5">
-        <f>IF(ISNA(VLOOKUP(H525,$A$2:$C$1040,3,1)),C525,VLOOKUP(H525,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H525,$A$2:$C$1041,3,1)),C525,VLOOKUP(H525,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C525" s="1">
@@ -24238,7 +24247,7 @@
         <v>1492</v>
       </c>
       <c r="B526" s="5">
-        <f>IF(ISNA(VLOOKUP(H526,$A$2:$C$1040,3,1)),C526,VLOOKUP(H526,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H526,$A$2:$C$1041,3,1)),C526,VLOOKUP(H526,$A$2:$C$1041,3,1))</f>
         <v>499</v>
       </c>
       <c r="C526" s="1">
@@ -24271,7 +24280,7 @@
         <v>1495</v>
       </c>
       <c r="B527" s="5">
-        <f>IF(ISNA(VLOOKUP(H527,$A$2:$C$1040,3,1)),C527,VLOOKUP(H527,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H527,$A$2:$C$1041,3,1)),C527,VLOOKUP(H527,$A$2:$C$1041,3,1))</f>
         <v>499</v>
       </c>
       <c r="C527" s="1">
@@ -24304,7 +24313,7 @@
         <v>1498</v>
       </c>
       <c r="B528" s="5">
-        <f>IF(ISNA(VLOOKUP(H528,$A$2:$C$1040,3,1)),C528,VLOOKUP(H528,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H528,$A$2:$C$1041,3,1)),C528,VLOOKUP(H528,$A$2:$C$1041,3,1))</f>
         <v>499</v>
       </c>
       <c r="C528" s="1">
@@ -24337,7 +24346,7 @@
         <v>1501</v>
       </c>
       <c r="B529" s="5">
-        <f>IF(ISNA(VLOOKUP(H529,$A$2:$C$1040,3,1)),C529,VLOOKUP(H529,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H529,$A$2:$C$1041,3,1)),C529,VLOOKUP(H529,$A$2:$C$1041,3,1))</f>
         <v>499</v>
       </c>
       <c r="C529" s="1">
@@ -24370,7 +24379,7 @@
         <v>1504</v>
       </c>
       <c r="B530" s="5">
-        <f>IF(ISNA(VLOOKUP(H530,$A$2:$C$1040,3,1)),C530,VLOOKUP(H530,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H530,$A$2:$C$1041,3,1)),C530,VLOOKUP(H530,$A$2:$C$1041,3,1))</f>
         <v>499</v>
       </c>
       <c r="C530" s="1">
@@ -24403,7 +24412,7 @@
         <v>1507</v>
       </c>
       <c r="B531" s="5">
-        <f>IF(ISNA(VLOOKUP(H531,$A$2:$C$1040,3,1)),C531,VLOOKUP(H531,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H531,$A$2:$C$1041,3,1)),C531,VLOOKUP(H531,$A$2:$C$1041,3,1))</f>
         <v>499</v>
       </c>
       <c r="C531" s="1">
@@ -24436,7 +24445,7 @@
         <v>1510</v>
       </c>
       <c r="B532" s="5">
-        <f>IF(ISNA(VLOOKUP(H532,$A$2:$C$1040,3,1)),C532,VLOOKUP(H532,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H532,$A$2:$C$1041,3,1)),C532,VLOOKUP(H532,$A$2:$C$1041,3,1))</f>
         <v>1</v>
       </c>
       <c r="C532" s="1">
@@ -24469,7 +24478,7 @@
         <v>1513</v>
       </c>
       <c r="B533" s="5">
-        <f>IF(ISNA(VLOOKUP(H533,$A$2:$C$1040,3,1)),C533,VLOOKUP(H533,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H533,$A$2:$C$1041,3,1)),C533,VLOOKUP(H533,$A$2:$C$1041,3,1))</f>
         <v>571</v>
       </c>
       <c r="C533" s="1">
@@ -24502,7 +24511,7 @@
         <v>1516</v>
       </c>
       <c r="B534" s="5">
-        <f>IF(ISNA(VLOOKUP(H534,$A$2:$C$1040,3,1)),C534,VLOOKUP(H534,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H534,$A$2:$C$1041,3,1)),C534,VLOOKUP(H534,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C534" s="1">
@@ -24535,7 +24544,7 @@
         <v>1519</v>
       </c>
       <c r="B535" s="5">
-        <f>IF(ISNA(VLOOKUP(H535,$A$2:$C$1040,3,1)),C535,VLOOKUP(H535,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H535,$A$2:$C$1041,3,1)),C535,VLOOKUP(H535,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C535" s="1">
@@ -24568,7 +24577,7 @@
         <v>2073</v>
       </c>
       <c r="B536" s="5">
-        <f>IF(ISNA(VLOOKUP(H536,$A$2:$C$1040,3,1)),C536,VLOOKUP(H536,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H536,$A$2:$C$1041,3,1)),C536,VLOOKUP(H536,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C536" s="1">
@@ -24578,7 +24587,7 @@
         <v>2074</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>2065</v>
+        <v>2116</v>
       </c>
       <c r="F536" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A536,3,4)))</f>
@@ -24601,11 +24610,11 @@
         <v>2062</v>
       </c>
       <c r="B537" s="5">
-        <f>IF(ISNA(VLOOKUP(H537,$A$2:$C$1040,3,1)),C537,VLOOKUP(H537,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H537,$A$2:$C$1041,3,1)),C537,VLOOKUP(H537,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C537" s="1">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D537" s="2" t="s">
         <v>2070</v>
@@ -24634,11 +24643,11 @@
         <v>2063</v>
       </c>
       <c r="B538" s="5">
-        <f>IF(ISNA(VLOOKUP(H538,$A$2:$C$1040,3,1)),C538,VLOOKUP(H538,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H538,$A$2:$C$1041,3,1)),C538,VLOOKUP(H538,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C538" s="1">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D538" s="2" t="s">
         <v>2071</v>
@@ -24667,7 +24676,7 @@
         <v>1522</v>
       </c>
       <c r="B539" s="5">
-        <f>IF(ISNA(VLOOKUP(H539,$A$2:$C$1040,3,1)),C539,VLOOKUP(H539,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H539,$A$2:$C$1041,3,1)),C539,VLOOKUP(H539,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C539" s="1">
@@ -24700,7 +24709,7 @@
         <v>1525</v>
       </c>
       <c r="B540" s="5">
-        <f>IF(ISNA(VLOOKUP(H540,$A$2:$C$1040,3,1)),C540,VLOOKUP(H540,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H540,$A$2:$C$1041,3,1)),C540,VLOOKUP(H540,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C540" s="1">
@@ -24733,7 +24742,7 @@
         <v>1528</v>
       </c>
       <c r="B541" s="5">
-        <f>IF(ISNA(VLOOKUP(H541,$A$2:$C$1040,3,1)),C541,VLOOKUP(H541,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H541,$A$2:$C$1041,3,1)),C541,VLOOKUP(H541,$A$2:$C$1041,3,1))</f>
         <v>1</v>
       </c>
       <c r="C541" s="1">
@@ -24766,7 +24775,7 @@
         <v>1531</v>
       </c>
       <c r="B542" s="5">
-        <f>IF(ISNA(VLOOKUP(H542,$A$2:$C$1040,3,1)),C542,VLOOKUP(H542,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H542,$A$2:$C$1041,3,1)),C542,VLOOKUP(H542,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C542" s="1">
@@ -24799,7 +24808,7 @@
         <v>1534</v>
       </c>
       <c r="B543" s="5">
-        <f>IF(ISNA(VLOOKUP(H543,$A$2:$C$1040,3,1)),C543,VLOOKUP(H543,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H543,$A$2:$C$1041,3,1)),C543,VLOOKUP(H543,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C543" s="1">
@@ -24832,7 +24841,7 @@
         <v>1537</v>
       </c>
       <c r="B544" s="5">
-        <f>IF(ISNA(VLOOKUP(H544,$A$2:$C$1040,3,1)),C544,VLOOKUP(H544,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H544,$A$2:$C$1041,3,1)),C544,VLOOKUP(H544,$A$2:$C$1041,3,1))</f>
         <v>569</v>
       </c>
       <c r="C544" s="1">
@@ -24865,7 +24874,7 @@
         <v>1539</v>
       </c>
       <c r="B545" s="5">
-        <f>IF(ISNA(VLOOKUP(H545,$A$2:$C$1040,3,1)),C545,VLOOKUP(H545,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H545,$A$2:$C$1041,3,1)),C545,VLOOKUP(H545,$A$2:$C$1041,3,1))</f>
         <v>541</v>
       </c>
       <c r="C545" s="1">
@@ -24898,7 +24907,7 @@
         <v>1541</v>
       </c>
       <c r="B546" s="5">
-        <f>IF(ISNA(VLOOKUP(H546,$A$2:$C$1040,3,1)),C546,VLOOKUP(H546,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H546,$A$2:$C$1041,3,1)),C546,VLOOKUP(H546,$A$2:$C$1041,3,1))</f>
         <v>538</v>
       </c>
       <c r="C546" s="1">
@@ -24931,7 +24940,7 @@
         <v>1542</v>
       </c>
       <c r="B547" s="5">
-        <f>IF(ISNA(VLOOKUP(H547,$A$2:$C$1040,3,1)),C547,VLOOKUP(H547,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H547,$A$2:$C$1041,3,1)),C547,VLOOKUP(H547,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C547" s="1">
@@ -24964,7 +24973,7 @@
         <v>1544</v>
       </c>
       <c r="B548" s="5">
-        <f>IF(ISNA(VLOOKUP(H548,$A$2:$C$1040,3,1)),C548,VLOOKUP(H548,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H548,$A$2:$C$1041,3,1)),C548,VLOOKUP(H548,$A$2:$C$1041,3,1))</f>
         <v>583</v>
       </c>
       <c r="C548" s="1">
@@ -24997,7 +25006,7 @@
         <v>1546</v>
       </c>
       <c r="B549" s="5">
-        <f>IF(ISNA(VLOOKUP(H549,$A$2:$C$1040,3,1)),C549,VLOOKUP(H549,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H549,$A$2:$C$1041,3,1)),C549,VLOOKUP(H549,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C549" s="1">
@@ -25030,7 +25039,7 @@
         <v>1548</v>
       </c>
       <c r="B550" s="5">
-        <f>IF(ISNA(VLOOKUP(H550,$A$2:$C$1040,3,1)),C550,VLOOKUP(H550,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H550,$A$2:$C$1041,3,1)),C550,VLOOKUP(H550,$A$2:$C$1041,3,1))</f>
         <v>673</v>
       </c>
       <c r="C550" s="1">
@@ -25063,7 +25072,7 @@
         <v>1550</v>
       </c>
       <c r="B551" s="5">
-        <f>IF(ISNA(VLOOKUP(H551,$A$2:$C$1040,3,1)),C551,VLOOKUP(H551,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H551,$A$2:$C$1041,3,1)),C551,VLOOKUP(H551,$A$2:$C$1041,3,1))</f>
         <v>673</v>
       </c>
       <c r="C551" s="1">
@@ -25096,7 +25105,7 @@
         <v>1552</v>
       </c>
       <c r="B552" s="5">
-        <f>IF(ISNA(VLOOKUP(H552,$A$2:$C$1040,3,1)),C552,VLOOKUP(H552,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H552,$A$2:$C$1041,3,1)),C552,VLOOKUP(H552,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C552" s="1">
@@ -25129,7 +25138,7 @@
         <v>1554</v>
       </c>
       <c r="B553" s="5">
-        <f>IF(ISNA(VLOOKUP(H553,$A$2:$C$1040,3,1)),C553,VLOOKUP(H553,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H553,$A$2:$C$1041,3,1)),C553,VLOOKUP(H553,$A$2:$C$1041,3,1))</f>
         <v>509</v>
       </c>
       <c r="C553" s="1">
@@ -25162,7 +25171,7 @@
         <v>1556</v>
       </c>
       <c r="B554" s="5">
-        <f>IF(ISNA(VLOOKUP(H554,$A$2:$C$1040,3,1)),C554,VLOOKUP(H554,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H554,$A$2:$C$1041,3,1)),C554,VLOOKUP(H554,$A$2:$C$1041,3,1))</f>
         <v>509</v>
       </c>
       <c r="C554" s="1">
@@ -25195,7 +25204,7 @@
         <v>1558</v>
       </c>
       <c r="B555" s="5">
-        <f>IF(ISNA(VLOOKUP(H555,$A$2:$C$1040,3,1)),C555,VLOOKUP(H555,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H555,$A$2:$C$1041,3,1)),C555,VLOOKUP(H555,$A$2:$C$1041,3,1))</f>
         <v>509</v>
       </c>
       <c r="C555" s="1">
@@ -25228,7 +25237,7 @@
         <v>1560</v>
       </c>
       <c r="B556" s="5">
-        <f>IF(ISNA(VLOOKUP(H556,$A$2:$C$1040,3,1)),C556,VLOOKUP(H556,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H556,$A$2:$C$1041,3,1)),C556,VLOOKUP(H556,$A$2:$C$1041,3,1))</f>
         <v>509</v>
       </c>
       <c r="C556" s="1">
@@ -25261,7 +25270,7 @@
         <v>1562</v>
       </c>
       <c r="B557" s="5">
-        <f>IF(ISNA(VLOOKUP(H557,$A$2:$C$1040,3,1)),C557,VLOOKUP(H557,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H557,$A$2:$C$1041,3,1)),C557,VLOOKUP(H557,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C557" s="1">
@@ -25294,7 +25303,7 @@
         <v>1564</v>
       </c>
       <c r="B558" s="5">
-        <f>IF(ISNA(VLOOKUP(H558,$A$2:$C$1040,3,1)),C558,VLOOKUP(H558,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H558,$A$2:$C$1041,3,1)),C558,VLOOKUP(H558,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C558" s="1">
@@ -25327,7 +25336,7 @@
         <v>1566</v>
       </c>
       <c r="B559" s="5">
-        <f>IF(ISNA(VLOOKUP(H559,$A$2:$C$1040,3,1)),C559,VLOOKUP(H559,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H559,$A$2:$C$1041,3,1)),C559,VLOOKUP(H559,$A$2:$C$1041,3,1))</f>
         <v>18</v>
       </c>
       <c r="C559" s="1">
@@ -25360,7 +25369,7 @@
         <v>1569</v>
       </c>
       <c r="B560" s="5">
-        <f>IF(ISNA(VLOOKUP(H560,$A$2:$C$1040,3,1)),C560,VLOOKUP(H560,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H560,$A$2:$C$1041,3,1)),C560,VLOOKUP(H560,$A$2:$C$1041,3,1))</f>
         <v>25</v>
       </c>
       <c r="C560" s="1">
@@ -25393,7 +25402,7 @@
         <v>1572</v>
       </c>
       <c r="B561" s="5">
-        <f>IF(ISNA(VLOOKUP(H561,$A$2:$C$1040,3,1)),C561,VLOOKUP(H561,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H561,$A$2:$C$1041,3,1)),C561,VLOOKUP(H561,$A$2:$C$1041,3,1))</f>
         <v>29</v>
       </c>
       <c r="C561" s="1">
@@ -25426,7 +25435,7 @@
         <v>1575</v>
       </c>
       <c r="B562" s="5">
-        <f>IF(ISNA(VLOOKUP(H562,$A$2:$C$1040,3,1)),C562,VLOOKUP(H562,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H562,$A$2:$C$1041,3,1)),C562,VLOOKUP(H562,$A$2:$C$1041,3,1))</f>
         <v>34</v>
       </c>
       <c r="C562" s="1">
@@ -25459,7 +25468,7 @@
         <v>1578</v>
       </c>
       <c r="B563" s="5">
-        <f>IF(ISNA(VLOOKUP(H563,$A$2:$C$1040,3,1)),C563,VLOOKUP(H563,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H563,$A$2:$C$1041,3,1)),C563,VLOOKUP(H563,$A$2:$C$1041,3,1))</f>
         <v>38</v>
       </c>
       <c r="C563" s="1">
@@ -25492,7 +25501,7 @@
         <v>1581</v>
       </c>
       <c r="B564" s="5">
-        <f>IF(ISNA(VLOOKUP(H564,$A$2:$C$1040,3,1)),C564,VLOOKUP(H564,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H564,$A$2:$C$1041,3,1)),C564,VLOOKUP(H564,$A$2:$C$1041,3,1))</f>
         <v>42</v>
       </c>
       <c r="C564" s="1">
@@ -25525,7 +25534,7 @@
         <v>1584</v>
       </c>
       <c r="B565" s="5">
-        <f>IF(ISNA(VLOOKUP(H565,$A$2:$C$1040,3,1)),C565,VLOOKUP(H565,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H565,$A$2:$C$1041,3,1)),C565,VLOOKUP(H565,$A$2:$C$1041,3,1))</f>
         <v>46</v>
       </c>
       <c r="C565" s="1">
@@ -25558,7 +25567,7 @@
         <v>1587</v>
       </c>
       <c r="B566" s="5">
-        <f>IF(ISNA(VLOOKUP(H566,$A$2:$C$1040,3,1)),C566,VLOOKUP(H566,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H566,$A$2:$C$1041,3,1)),C566,VLOOKUP(H566,$A$2:$C$1041,3,1))</f>
         <v>50</v>
       </c>
       <c r="C566" s="1">
@@ -25591,7 +25600,7 @@
         <v>1590</v>
       </c>
       <c r="B567" s="5">
-        <f>IF(ISNA(VLOOKUP(H567,$A$2:$C$1040,3,1)),C567,VLOOKUP(H567,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H567,$A$2:$C$1041,3,1)),C567,VLOOKUP(H567,$A$2:$C$1041,3,1))</f>
         <v>54</v>
       </c>
       <c r="C567" s="1">
@@ -25624,7 +25633,7 @@
         <v>1593</v>
       </c>
       <c r="B568" s="5">
-        <f>IF(ISNA(VLOOKUP(H568,$A$2:$C$1040,3,1)),C568,VLOOKUP(H568,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H568,$A$2:$C$1041,3,1)),C568,VLOOKUP(H568,$A$2:$C$1041,3,1))</f>
         <v>58</v>
       </c>
       <c r="C568" s="1">
@@ -25657,7 +25666,7 @@
         <v>1597</v>
       </c>
       <c r="B569" s="5">
-        <f>IF(ISNA(VLOOKUP(H569,$A$2:$C$1040,3,1)),C569,VLOOKUP(H569,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H569,$A$2:$C$1041,3,1)),C569,VLOOKUP(H569,$A$2:$C$1041,3,1))</f>
         <v>60</v>
       </c>
       <c r="C569" s="1">
@@ -25690,7 +25699,7 @@
         <v>1600</v>
       </c>
       <c r="B570" s="5">
-        <f>IF(ISNA(VLOOKUP(H570,$A$2:$C$1040,3,1)),C570,VLOOKUP(H570,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H570,$A$2:$C$1041,3,1)),C570,VLOOKUP(H570,$A$2:$C$1041,3,1))</f>
         <v>61</v>
       </c>
       <c r="C570" s="1">
@@ -25723,7 +25732,7 @@
         <v>1603</v>
       </c>
       <c r="B571" s="5">
-        <f>IF(ISNA(VLOOKUP(H571,$A$2:$C$1040,3,1)),C571,VLOOKUP(H571,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H571,$A$2:$C$1041,3,1)),C571,VLOOKUP(H571,$A$2:$C$1041,3,1))</f>
         <v>62</v>
       </c>
       <c r="C571" s="1">
@@ -25756,7 +25765,7 @@
         <v>1606</v>
       </c>
       <c r="B572" s="5">
-        <f>IF(ISNA(VLOOKUP(H572,$A$2:$C$1040,3,1)),C572,VLOOKUP(H572,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H572,$A$2:$C$1041,3,1)),C572,VLOOKUP(H572,$A$2:$C$1041,3,1))</f>
         <v>63</v>
       </c>
       <c r="C572" s="1">
@@ -25789,7 +25798,7 @@
         <v>1609</v>
       </c>
       <c r="B573" s="5">
-        <f>IF(ISNA(VLOOKUP(H573,$A$2:$C$1040,3,1)),C573,VLOOKUP(H573,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H573,$A$2:$C$1041,3,1)),C573,VLOOKUP(H573,$A$2:$C$1041,3,1))</f>
         <v>64</v>
       </c>
       <c r="C573" s="1">
@@ -25822,7 +25831,7 @@
         <v>1612</v>
       </c>
       <c r="B574" s="5">
-        <f>IF(ISNA(VLOOKUP(H574,$A$2:$C$1040,3,1)),C574,VLOOKUP(H574,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H574,$A$2:$C$1041,3,1)),C574,VLOOKUP(H574,$A$2:$C$1041,3,1))</f>
         <v>65</v>
       </c>
       <c r="C574" s="1">
@@ -25855,7 +25864,7 @@
         <v>1596</v>
       </c>
       <c r="B575" s="5">
-        <f>IF(ISNA(VLOOKUP(H575,$A$2:$C$1040,3,1)),C575,VLOOKUP(H575,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H575,$A$2:$C$1041,3,1)),C575,VLOOKUP(H575,$A$2:$C$1041,3,1))</f>
         <v>58</v>
       </c>
       <c r="C575" s="1">
@@ -25888,7 +25897,7 @@
         <v>1617</v>
       </c>
       <c r="B576" s="5">
-        <f>IF(ISNA(VLOOKUP(H576,$A$2:$C$1040,3,1)),C576,VLOOKUP(H576,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H576,$A$2:$C$1041,3,1)),C576,VLOOKUP(H576,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C576" s="1">
@@ -25921,7 +25930,7 @@
         <v>1620</v>
       </c>
       <c r="B577" s="5">
-        <f>IF(ISNA(VLOOKUP(H577,$A$2:$C$1040,3,1)),C577,VLOOKUP(H577,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H577,$A$2:$C$1041,3,1)),C577,VLOOKUP(H577,$A$2:$C$1041,3,1))</f>
         <v>92</v>
       </c>
       <c r="C577" s="1">
@@ -25954,7 +25963,7 @@
         <v>1623</v>
       </c>
       <c r="B578" s="5">
-        <f>IF(ISNA(VLOOKUP(H578,$A$2:$C$1040,3,1)),C578,VLOOKUP(H578,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H578,$A$2:$C$1041,3,1)),C578,VLOOKUP(H578,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C578" s="1">
@@ -25987,7 +25996,7 @@
         <v>1626</v>
       </c>
       <c r="B579" s="5">
-        <f>IF(ISNA(VLOOKUP(H579,$A$2:$C$1040,3,1)),C579,VLOOKUP(H579,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H579,$A$2:$C$1041,3,1)),C579,VLOOKUP(H579,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C579" s="1">
@@ -26020,7 +26029,7 @@
         <v>1629</v>
       </c>
       <c r="B580" s="5">
-        <f>IF(ISNA(VLOOKUP(H580,$A$2:$C$1040,3,1)),C580,VLOOKUP(H580,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H580,$A$2:$C$1041,3,1)),C580,VLOOKUP(H580,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C580" s="1">
@@ -26053,7 +26062,7 @@
         <v>1632</v>
       </c>
       <c r="B581" s="5">
-        <f>IF(ISNA(VLOOKUP(H581,$A$2:$C$1040,3,1)),C581,VLOOKUP(H581,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H581,$A$2:$C$1041,3,1)),C581,VLOOKUP(H581,$A$2:$C$1041,3,1))</f>
         <v>153</v>
       </c>
       <c r="C581" s="1">
@@ -26086,7 +26095,7 @@
         <v>1634</v>
       </c>
       <c r="B582" s="5">
-        <f>IF(ISNA(VLOOKUP(H582,$A$2:$C$1040,3,1)),C582,VLOOKUP(H582,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H582,$A$2:$C$1041,3,1)),C582,VLOOKUP(H582,$A$2:$C$1041,3,1))</f>
         <v>162</v>
       </c>
       <c r="C582" s="1">
@@ -26119,7 +26128,7 @@
         <v>1636</v>
       </c>
       <c r="B583" s="5">
-        <f>IF(ISNA(VLOOKUP(H583,$A$2:$C$1040,3,1)),C583,VLOOKUP(H583,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H583,$A$2:$C$1041,3,1)),C583,VLOOKUP(H583,$A$2:$C$1041,3,1))</f>
         <v>172</v>
       </c>
       <c r="C583" s="1">
@@ -26152,7 +26161,7 @@
         <v>1638</v>
       </c>
       <c r="B584" s="5">
-        <f>IF(ISNA(VLOOKUP(H584,$A$2:$C$1040,3,1)),C584,VLOOKUP(H584,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H584,$A$2:$C$1041,3,1)),C584,VLOOKUP(H584,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C584" s="1">
@@ -26185,7 +26194,7 @@
         <v>1641</v>
       </c>
       <c r="B585" s="5">
-        <f>IF(ISNA(VLOOKUP(H585,$A$2:$C$1040,3,1)),C585,VLOOKUP(H585,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H585,$A$2:$C$1041,3,1)),C585,VLOOKUP(H585,$A$2:$C$1041,3,1))</f>
         <v>206</v>
       </c>
       <c r="C585" s="1">
@@ -26218,7 +26227,7 @@
         <v>1644</v>
       </c>
       <c r="B586" s="5">
-        <f>IF(ISNA(VLOOKUP(H586,$A$2:$C$1040,3,1)),C586,VLOOKUP(H586,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H586,$A$2:$C$1041,3,1)),C586,VLOOKUP(H586,$A$2:$C$1041,3,1))</f>
         <v>214</v>
       </c>
       <c r="C586" s="1">
@@ -26251,7 +26260,7 @@
         <v>1647</v>
       </c>
       <c r="B587" s="5">
-        <f>IF(ISNA(VLOOKUP(H587,$A$2:$C$1040,3,1)),C587,VLOOKUP(H587,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H587,$A$2:$C$1041,3,1)),C587,VLOOKUP(H587,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C587" s="1">
@@ -26284,7 +26293,7 @@
         <v>1650</v>
       </c>
       <c r="B588" s="5">
-        <f>IF(ISNA(VLOOKUP(H588,$A$2:$C$1040,3,1)),C588,VLOOKUP(H588,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H588,$A$2:$C$1041,3,1)),C588,VLOOKUP(H588,$A$2:$C$1041,3,1))</f>
         <v>234</v>
       </c>
       <c r="C588" s="1">
@@ -26317,7 +26326,7 @@
         <v>1653</v>
       </c>
       <c r="B589" s="5">
-        <f>IF(ISNA(VLOOKUP(H589,$A$2:$C$1040,3,1)),C589,VLOOKUP(H589,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H589,$A$2:$C$1041,3,1)),C589,VLOOKUP(H589,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C589" s="1">
@@ -26350,7 +26359,7 @@
         <v>1656</v>
       </c>
       <c r="B590" s="5">
-        <f>IF(ISNA(VLOOKUP(H590,$A$2:$C$1040,3,1)),C590,VLOOKUP(H590,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H590,$A$2:$C$1041,3,1)),C590,VLOOKUP(H590,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C590" s="1">
@@ -26383,7 +26392,7 @@
         <v>1659</v>
       </c>
       <c r="B591" s="5">
-        <f>IF(ISNA(VLOOKUP(H591,$A$2:$C$1040,3,1)),C591,VLOOKUP(H591,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H591,$A$2:$C$1041,3,1)),C591,VLOOKUP(H591,$A$2:$C$1041,3,1))</f>
         <v>280</v>
       </c>
       <c r="C591" s="1">
@@ -26416,7 +26425,7 @@
         <v>1662</v>
       </c>
       <c r="B592" s="5">
-        <f>IF(ISNA(VLOOKUP(H592,$A$2:$C$1040,3,1)),C592,VLOOKUP(H592,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H592,$A$2:$C$1041,3,1)),C592,VLOOKUP(H592,$A$2:$C$1041,3,1))</f>
         <v>287</v>
       </c>
       <c r="C592" s="1">
@@ -26449,7 +26458,7 @@
         <v>1665</v>
       </c>
       <c r="B593" s="5">
-        <f>IF(ISNA(VLOOKUP(H593,$A$2:$C$1040,3,1)),C593,VLOOKUP(H593,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H593,$A$2:$C$1041,3,1)),C593,VLOOKUP(H593,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C593" s="1">
@@ -26482,7 +26491,7 @@
         <v>1667</v>
       </c>
       <c r="B594" s="5">
-        <f>IF(ISNA(VLOOKUP(H594,$A$2:$C$1040,3,1)),C594,VLOOKUP(H594,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H594,$A$2:$C$1041,3,1)),C594,VLOOKUP(H594,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C594" s="1">
@@ -26515,7 +26524,7 @@
         <v>1670</v>
       </c>
       <c r="B595" s="5">
-        <f>IF(ISNA(VLOOKUP(H595,$A$2:$C$1040,3,1)),C595,VLOOKUP(H595,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H595,$A$2:$C$1041,3,1)),C595,VLOOKUP(H595,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C595" s="1">
@@ -26548,7 +26557,7 @@
         <v>1673</v>
       </c>
       <c r="B596" s="5">
-        <f>IF(ISNA(VLOOKUP(H596,$A$2:$C$1040,3,1)),C596,VLOOKUP(H596,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H596,$A$2:$C$1041,3,1)),C596,VLOOKUP(H596,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C596" s="1">
@@ -26581,7 +26590,7 @@
         <v>1676</v>
       </c>
       <c r="B597" s="5">
-        <f>IF(ISNA(VLOOKUP(H597,$A$2:$C$1040,3,1)),C597,VLOOKUP(H597,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H597,$A$2:$C$1041,3,1)),C597,VLOOKUP(H597,$A$2:$C$1041,3,1))</f>
         <v>359</v>
       </c>
       <c r="C597" s="1">
@@ -26615,7 +26624,7 @@
         <v>1679</v>
       </c>
       <c r="B598" s="5">
-        <f>IF(ISNA(VLOOKUP(H598,$A$2:$C$1040,3,1)),C598,VLOOKUP(H598,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H598,$A$2:$C$1041,3,1)),C598,VLOOKUP(H598,$A$2:$C$1041,3,1))</f>
         <v>367</v>
       </c>
       <c r="C598" s="1">
@@ -26648,7 +26657,7 @@
         <v>1682</v>
       </c>
       <c r="B599" s="5">
-        <f>IF(ISNA(VLOOKUP(H599,$A$2:$C$1040,3,1)),C599,VLOOKUP(H599,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H599,$A$2:$C$1041,3,1)),C599,VLOOKUP(H599,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C599" s="1">
@@ -26683,7 +26692,7 @@
         <v>1684</v>
       </c>
       <c r="B600" s="5">
-        <f>IF(ISNA(VLOOKUP(H600,$A$2:$C$1040,3,1)),C600,VLOOKUP(H600,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H600,$A$2:$C$1041,3,1)),C600,VLOOKUP(H600,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C600" s="1">
@@ -26716,7 +26725,7 @@
         <v>1687</v>
       </c>
       <c r="B601" s="5">
-        <f>IF(ISNA(VLOOKUP(H601,$A$2:$C$1040,3,1)),C601,VLOOKUP(H601,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H601,$A$2:$C$1041,3,1)),C601,VLOOKUP(H601,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C601" s="1">
@@ -26749,7 +26758,7 @@
         <v>1690</v>
       </c>
       <c r="B602" s="5">
-        <f>IF(ISNA(VLOOKUP(H602,$A$2:$C$1040,3,1)),C602,VLOOKUP(H602,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H602,$A$2:$C$1041,3,1)),C602,VLOOKUP(H602,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C602" s="1">
@@ -26782,7 +26791,7 @@
         <v>1693</v>
       </c>
       <c r="B603" s="5">
-        <f>IF(ISNA(VLOOKUP(H603,$A$2:$C$1040,3,1)),C603,VLOOKUP(H603,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H603,$A$2:$C$1041,3,1)),C603,VLOOKUP(H603,$A$2:$C$1041,3,1))</f>
         <v>92</v>
       </c>
       <c r="C603" s="1">
@@ -26815,7 +26824,7 @@
         <v>1696</v>
       </c>
       <c r="B604" s="5">
-        <f>IF(ISNA(VLOOKUP(H604,$A$2:$C$1040,3,1)),C604,VLOOKUP(H604,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H604,$A$2:$C$1041,3,1)),C604,VLOOKUP(H604,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C604" s="1">
@@ -26848,7 +26857,7 @@
         <v>1699</v>
       </c>
       <c r="B605" s="5">
-        <f>IF(ISNA(VLOOKUP(H605,$A$2:$C$1040,3,1)),C605,VLOOKUP(H605,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H605,$A$2:$C$1041,3,1)),C605,VLOOKUP(H605,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C605" s="1">
@@ -26881,7 +26890,7 @@
         <v>1702</v>
       </c>
       <c r="B606" s="5">
-        <f>IF(ISNA(VLOOKUP(H606,$A$2:$C$1040,3,1)),C606,VLOOKUP(H606,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H606,$A$2:$C$1041,3,1)),C606,VLOOKUP(H606,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C606" s="1">
@@ -26914,7 +26923,7 @@
         <v>1705</v>
       </c>
       <c r="B607" s="5">
-        <f>IF(ISNA(VLOOKUP(H607,$A$2:$C$1040,3,1)),C607,VLOOKUP(H607,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H607,$A$2:$C$1041,3,1)),C607,VLOOKUP(H607,$A$2:$C$1041,3,1))</f>
         <v>153</v>
       </c>
       <c r="C607" s="1">
@@ -26947,7 +26956,7 @@
         <v>1708</v>
       </c>
       <c r="B608" s="5">
-        <f>IF(ISNA(VLOOKUP(H608,$A$2:$C$1040,3,1)),C608,VLOOKUP(H608,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H608,$A$2:$C$1041,3,1)),C608,VLOOKUP(H608,$A$2:$C$1041,3,1))</f>
         <v>162</v>
       </c>
       <c r="C608" s="1">
@@ -26980,7 +26989,7 @@
         <v>1711</v>
       </c>
       <c r="B609" s="5">
-        <f>IF(ISNA(VLOOKUP(H609,$A$2:$C$1040,3,1)),C609,VLOOKUP(H609,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H609,$A$2:$C$1041,3,1)),C609,VLOOKUP(H609,$A$2:$C$1041,3,1))</f>
         <v>172</v>
       </c>
       <c r="C609" s="1">
@@ -27013,7 +27022,7 @@
         <v>1714</v>
       </c>
       <c r="B610" s="5">
-        <f>IF(ISNA(VLOOKUP(H610,$A$2:$C$1040,3,1)),C610,VLOOKUP(H610,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H610,$A$2:$C$1041,3,1)),C610,VLOOKUP(H610,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C610" s="1">
@@ -27046,7 +27055,7 @@
         <v>1717</v>
       </c>
       <c r="B611" s="5">
-        <f>IF(ISNA(VLOOKUP(H611,$A$2:$C$1040,3,1)),C611,VLOOKUP(H611,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H611,$A$2:$C$1041,3,1)),C611,VLOOKUP(H611,$A$2:$C$1041,3,1))</f>
         <v>206</v>
       </c>
       <c r="C611" s="1">
@@ -27079,7 +27088,7 @@
         <v>1720</v>
       </c>
       <c r="B612" s="5">
-        <f>IF(ISNA(VLOOKUP(H612,$A$2:$C$1040,3,1)),C612,VLOOKUP(H612,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H612,$A$2:$C$1041,3,1)),C612,VLOOKUP(H612,$A$2:$C$1041,3,1))</f>
         <v>214</v>
       </c>
       <c r="C612" s="1">
@@ -27112,7 +27121,7 @@
         <v>1723</v>
       </c>
       <c r="B613" s="5">
-        <f>IF(ISNA(VLOOKUP(H613,$A$2:$C$1040,3,1)),C613,VLOOKUP(H613,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H613,$A$2:$C$1041,3,1)),C613,VLOOKUP(H613,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C613" s="1">
@@ -27145,7 +27154,7 @@
         <v>1726</v>
       </c>
       <c r="B614" s="5">
-        <f>IF(ISNA(VLOOKUP(H614,$A$2:$C$1040,3,1)),C614,VLOOKUP(H614,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H614,$A$2:$C$1041,3,1)),C614,VLOOKUP(H614,$A$2:$C$1041,3,1))</f>
         <v>234</v>
       </c>
       <c r="C614" s="1">
@@ -27178,7 +27187,7 @@
         <v>1729</v>
       </c>
       <c r="B615" s="5">
-        <f>IF(ISNA(VLOOKUP(H615,$A$2:$C$1040,3,1)),C615,VLOOKUP(H615,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H615,$A$2:$C$1041,3,1)),C615,VLOOKUP(H615,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C615" s="1">
@@ -27211,7 +27220,7 @@
         <v>1732</v>
       </c>
       <c r="B616" s="5">
-        <f>IF(ISNA(VLOOKUP(H616,$A$2:$C$1040,3,1)),C616,VLOOKUP(H616,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H616,$A$2:$C$1041,3,1)),C616,VLOOKUP(H616,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C616" s="1">
@@ -27244,7 +27253,7 @@
         <v>1735</v>
       </c>
       <c r="B617" s="5">
-        <f>IF(ISNA(VLOOKUP(H617,$A$2:$C$1040,3,1)),C617,VLOOKUP(H617,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H617,$A$2:$C$1041,3,1)),C617,VLOOKUP(H617,$A$2:$C$1041,3,1))</f>
         <v>280</v>
       </c>
       <c r="C617" s="1">
@@ -27277,7 +27286,7 @@
         <v>1738</v>
       </c>
       <c r="B618" s="5">
-        <f>IF(ISNA(VLOOKUP(H618,$A$2:$C$1040,3,1)),C618,VLOOKUP(H618,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H618,$A$2:$C$1041,3,1)),C618,VLOOKUP(H618,$A$2:$C$1041,3,1))</f>
         <v>287</v>
       </c>
       <c r="C618" s="1">
@@ -27310,7 +27319,7 @@
         <v>1741</v>
       </c>
       <c r="B619" s="5">
-        <f>IF(ISNA(VLOOKUP(H619,$A$2:$C$1040,3,1)),C619,VLOOKUP(H619,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H619,$A$2:$C$1041,3,1)),C619,VLOOKUP(H619,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C619" s="1">
@@ -27343,7 +27352,7 @@
         <v>1744</v>
       </c>
       <c r="B620" s="5">
-        <f>IF(ISNA(VLOOKUP(H620,$A$2:$C$1040,3,1)),C620,VLOOKUP(H620,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H620,$A$2:$C$1041,3,1)),C620,VLOOKUP(H620,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C620" s="1">
@@ -27376,7 +27385,7 @@
         <v>1747</v>
       </c>
       <c r="B621" s="5">
-        <f>IF(ISNA(VLOOKUP(H621,$A$2:$C$1040,3,1)),C621,VLOOKUP(H621,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H621,$A$2:$C$1041,3,1)),C621,VLOOKUP(H621,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C621" s="1">
@@ -27409,7 +27418,7 @@
         <v>1750</v>
       </c>
       <c r="B622" s="5">
-        <f>IF(ISNA(VLOOKUP(H622,$A$2:$C$1040,3,1)),C622,VLOOKUP(H622,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H622,$A$2:$C$1041,3,1)),C622,VLOOKUP(H622,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C622" s="1">
@@ -27442,7 +27451,7 @@
         <v>1753</v>
       </c>
       <c r="B623" s="5">
-        <f>IF(ISNA(VLOOKUP(H623,$A$2:$C$1040,3,1)),C623,VLOOKUP(H623,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H623,$A$2:$C$1041,3,1)),C623,VLOOKUP(H623,$A$2:$C$1041,3,1))</f>
         <v>359</v>
       </c>
       <c r="C623" s="1">
@@ -27475,7 +27484,7 @@
         <v>1756</v>
       </c>
       <c r="B624" s="5">
-        <f>IF(ISNA(VLOOKUP(H624,$A$2:$C$1040,3,1)),C624,VLOOKUP(H624,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H624,$A$2:$C$1041,3,1)),C624,VLOOKUP(H624,$A$2:$C$1041,3,1))</f>
         <v>367</v>
       </c>
       <c r="C624" s="1">
@@ -27508,7 +27517,7 @@
         <v>1759</v>
       </c>
       <c r="B625" s="5">
-        <f>IF(ISNA(VLOOKUP(H625,$A$2:$C$1040,3,1)),C625,VLOOKUP(H625,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H625,$A$2:$C$1041,3,1)),C625,VLOOKUP(H625,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C625" s="1">
@@ -27541,7 +27550,7 @@
         <v>1762</v>
       </c>
       <c r="B626" s="5">
-        <f>IF(ISNA(VLOOKUP(H626,$A$2:$C$1040,3,1)),C626,VLOOKUP(H626,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H626,$A$2:$C$1041,3,1)),C626,VLOOKUP(H626,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C626" s="1">
@@ -27574,7 +27583,7 @@
         <v>1765</v>
       </c>
       <c r="B627" s="5">
-        <f>IF(ISNA(VLOOKUP(H627,$A$2:$C$1040,3,1)),C627,VLOOKUP(H627,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H627,$A$2:$C$1041,3,1)),C627,VLOOKUP(H627,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C627" s="1">
@@ -27607,7 +27616,7 @@
         <v>1768</v>
       </c>
       <c r="B628" s="5">
-        <f>IF(ISNA(VLOOKUP(H628,$A$2:$C$1040,3,1)),C628,VLOOKUP(H628,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H628,$A$2:$C$1041,3,1)),C628,VLOOKUP(H628,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C628" s="1">
@@ -27640,7 +27649,7 @@
         <v>1771</v>
       </c>
       <c r="B629" s="5">
-        <f>IF(ISNA(VLOOKUP(H629,$A$2:$C$1040,3,1)),C629,VLOOKUP(H629,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H629,$A$2:$C$1041,3,1)),C629,VLOOKUP(H629,$A$2:$C$1041,3,1))</f>
         <v>92</v>
       </c>
       <c r="C629" s="1">
@@ -27673,7 +27682,7 @@
         <v>1774</v>
       </c>
       <c r="B630" s="5">
-        <f>IF(ISNA(VLOOKUP(H630,$A$2:$C$1040,3,1)),C630,VLOOKUP(H630,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H630,$A$2:$C$1041,3,1)),C630,VLOOKUP(H630,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C630" s="1">
@@ -27706,7 +27715,7 @@
         <v>1777</v>
       </c>
       <c r="B631" s="5">
-        <f>IF(ISNA(VLOOKUP(H631,$A$2:$C$1040,3,1)),C631,VLOOKUP(H631,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H631,$A$2:$C$1041,3,1)),C631,VLOOKUP(H631,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C631" s="1">
@@ -27739,7 +27748,7 @@
         <v>1780</v>
       </c>
       <c r="B632" s="5">
-        <f>IF(ISNA(VLOOKUP(H632,$A$2:$C$1040,3,1)),C632,VLOOKUP(H632,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H632,$A$2:$C$1041,3,1)),C632,VLOOKUP(H632,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C632" s="1">
@@ -27772,7 +27781,7 @@
         <v>1783</v>
       </c>
       <c r="B633" s="5">
-        <f>IF(ISNA(VLOOKUP(H633,$A$2:$C$1040,3,1)),C633,VLOOKUP(H633,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H633,$A$2:$C$1041,3,1)),C633,VLOOKUP(H633,$A$2:$C$1041,3,1))</f>
         <v>153</v>
       </c>
       <c r="C633" s="1">
@@ -27805,7 +27814,7 @@
         <v>1786</v>
       </c>
       <c r="B634" s="5">
-        <f>IF(ISNA(VLOOKUP(H634,$A$2:$C$1040,3,1)),C634,VLOOKUP(H634,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H634,$A$2:$C$1041,3,1)),C634,VLOOKUP(H634,$A$2:$C$1041,3,1))</f>
         <v>162</v>
       </c>
       <c r="C634" s="1">
@@ -27838,7 +27847,7 @@
         <v>1789</v>
       </c>
       <c r="B635" s="5">
-        <f>IF(ISNA(VLOOKUP(H635,$A$2:$C$1040,3,1)),C635,VLOOKUP(H635,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H635,$A$2:$C$1041,3,1)),C635,VLOOKUP(H635,$A$2:$C$1041,3,1))</f>
         <v>172</v>
       </c>
       <c r="C635" s="1">
@@ -27871,7 +27880,7 @@
         <v>1792</v>
       </c>
       <c r="B636" s="5">
-        <f>IF(ISNA(VLOOKUP(H636,$A$2:$C$1040,3,1)),C636,VLOOKUP(H636,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H636,$A$2:$C$1041,3,1)),C636,VLOOKUP(H636,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C636" s="1">
@@ -27904,7 +27913,7 @@
         <v>1795</v>
       </c>
       <c r="B637" s="5">
-        <f>IF(ISNA(VLOOKUP(H637,$A$2:$C$1040,3,1)),C637,VLOOKUP(H637,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H637,$A$2:$C$1041,3,1)),C637,VLOOKUP(H637,$A$2:$C$1041,3,1))</f>
         <v>206</v>
       </c>
       <c r="C637" s="1">
@@ -27937,7 +27946,7 @@
         <v>1798</v>
       </c>
       <c r="B638" s="5">
-        <f>IF(ISNA(VLOOKUP(H638,$A$2:$C$1040,3,1)),C638,VLOOKUP(H638,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H638,$A$2:$C$1041,3,1)),C638,VLOOKUP(H638,$A$2:$C$1041,3,1))</f>
         <v>214</v>
       </c>
       <c r="C638" s="1">
@@ -27970,7 +27979,7 @@
         <v>1801</v>
       </c>
       <c r="B639" s="5">
-        <f>IF(ISNA(VLOOKUP(H639,$A$2:$C$1040,3,1)),C639,VLOOKUP(H639,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H639,$A$2:$C$1041,3,1)),C639,VLOOKUP(H639,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C639" s="1">
@@ -28003,7 +28012,7 @@
         <v>1804</v>
       </c>
       <c r="B640" s="5">
-        <f>IF(ISNA(VLOOKUP(H640,$A$2:$C$1040,3,1)),C640,VLOOKUP(H640,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H640,$A$2:$C$1041,3,1)),C640,VLOOKUP(H640,$A$2:$C$1041,3,1))</f>
         <v>234</v>
       </c>
       <c r="C640" s="1">
@@ -28036,7 +28045,7 @@
         <v>1807</v>
       </c>
       <c r="B641" s="5">
-        <f>IF(ISNA(VLOOKUP(H641,$A$2:$C$1040,3,1)),C641,VLOOKUP(H641,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H641,$A$2:$C$1041,3,1)),C641,VLOOKUP(H641,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C641" s="1">
@@ -28069,7 +28078,7 @@
         <v>1810</v>
       </c>
       <c r="B642" s="5">
-        <f>IF(ISNA(VLOOKUP(H642,$A$2:$C$1040,3,1)),C642,VLOOKUP(H642,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H642,$A$2:$C$1041,3,1)),C642,VLOOKUP(H642,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C642" s="1">
@@ -28102,7 +28111,7 @@
         <v>1813</v>
       </c>
       <c r="B643" s="5">
-        <f>IF(ISNA(VLOOKUP(H643,$A$2:$C$1040,3,1)),C643,VLOOKUP(H643,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H643,$A$2:$C$1041,3,1)),C643,VLOOKUP(H643,$A$2:$C$1041,3,1))</f>
         <v>280</v>
       </c>
       <c r="C643" s="1">
@@ -28135,7 +28144,7 @@
         <v>1816</v>
       </c>
       <c r="B644" s="5">
-        <f>IF(ISNA(VLOOKUP(H644,$A$2:$C$1040,3,1)),C644,VLOOKUP(H644,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H644,$A$2:$C$1041,3,1)),C644,VLOOKUP(H644,$A$2:$C$1041,3,1))</f>
         <v>287</v>
       </c>
       <c r="C644" s="1">
@@ -28168,7 +28177,7 @@
         <v>1819</v>
       </c>
       <c r="B645" s="5">
-        <f>IF(ISNA(VLOOKUP(H645,$A$2:$C$1040,3,1)),C645,VLOOKUP(H645,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H645,$A$2:$C$1041,3,1)),C645,VLOOKUP(H645,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C645" s="1">
@@ -28201,7 +28210,7 @@
         <v>1822</v>
       </c>
       <c r="B646" s="5">
-        <f>IF(ISNA(VLOOKUP(H646,$A$2:$C$1040,3,1)),C646,VLOOKUP(H646,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H646,$A$2:$C$1041,3,1)),C646,VLOOKUP(H646,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C646" s="1">
@@ -28234,7 +28243,7 @@
         <v>1825</v>
       </c>
       <c r="B647" s="5">
-        <f>IF(ISNA(VLOOKUP(H647,$A$2:$C$1040,3,1)),C647,VLOOKUP(H647,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H647,$A$2:$C$1041,3,1)),C647,VLOOKUP(H647,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C647" s="1">
@@ -28267,7 +28276,7 @@
         <v>1827</v>
       </c>
       <c r="B648" s="5">
-        <f>IF(ISNA(VLOOKUP(H648,$A$2:$C$1040,3,1)),C648,VLOOKUP(H648,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H648,$A$2:$C$1041,3,1)),C648,VLOOKUP(H648,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C648" s="1">
@@ -28300,7 +28309,7 @@
         <v>1830</v>
       </c>
       <c r="B649" s="5">
-        <f>IF(ISNA(VLOOKUP(H649,$A$2:$C$1040,3,1)),C649,VLOOKUP(H649,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H649,$A$2:$C$1041,3,1)),C649,VLOOKUP(H649,$A$2:$C$1041,3,1))</f>
         <v>359</v>
       </c>
       <c r="C649" s="1">
@@ -28333,7 +28342,7 @@
         <v>1833</v>
       </c>
       <c r="B650" s="5">
-        <f>IF(ISNA(VLOOKUP(H650,$A$2:$C$1040,3,1)),C650,VLOOKUP(H650,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H650,$A$2:$C$1041,3,1)),C650,VLOOKUP(H650,$A$2:$C$1041,3,1))</f>
         <v>367</v>
       </c>
       <c r="C650" s="1">
@@ -28366,7 +28375,7 @@
         <v>1836</v>
       </c>
       <c r="B651" s="5">
-        <f>IF(ISNA(VLOOKUP(H651,$A$2:$C$1040,3,1)),C651,VLOOKUP(H651,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H651,$A$2:$C$1041,3,1)),C651,VLOOKUP(H651,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C651" s="1">
@@ -28399,7 +28408,7 @@
         <v>1839</v>
       </c>
       <c r="B652" s="5">
-        <f>IF(ISNA(VLOOKUP(H652,$A$2:$C$1040,3,1)),C652,VLOOKUP(H652,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H652,$A$2:$C$1041,3,1)),C652,VLOOKUP(H652,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C652" s="1">
@@ -28432,7 +28441,7 @@
         <v>1842</v>
       </c>
       <c r="B653" s="5">
-        <f>IF(ISNA(VLOOKUP(H653,$A$2:$C$1040,3,1)),C653,VLOOKUP(H653,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H653,$A$2:$C$1041,3,1)),C653,VLOOKUP(H653,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C653" s="1">
@@ -28465,7 +28474,7 @@
         <v>1845</v>
       </c>
       <c r="B654" s="5">
-        <f>IF(ISNA(VLOOKUP(H654,$A$2:$C$1040,3,1)),C654,VLOOKUP(H654,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H654,$A$2:$C$1041,3,1)),C654,VLOOKUP(H654,$A$2:$C$1041,3,1))</f>
         <v>66</v>
       </c>
       <c r="C654" s="1">
@@ -28498,7 +28507,7 @@
         <v>1848</v>
       </c>
       <c r="B655" s="5">
-        <f>IF(ISNA(VLOOKUP(H655,$A$2:$C$1040,3,1)),C655,VLOOKUP(H655,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H655,$A$2:$C$1041,3,1)),C655,VLOOKUP(H655,$A$2:$C$1041,3,1))</f>
         <v>92</v>
       </c>
       <c r="C655" s="1">
@@ -28531,7 +28540,7 @@
         <v>1851</v>
       </c>
       <c r="B656" s="5">
-        <f>IF(ISNA(VLOOKUP(H656,$A$2:$C$1040,3,1)),C656,VLOOKUP(H656,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H656,$A$2:$C$1041,3,1)),C656,VLOOKUP(H656,$A$2:$C$1041,3,1))</f>
         <v>98</v>
       </c>
       <c r="C656" s="1">
@@ -28564,7 +28573,7 @@
         <v>1854</v>
       </c>
       <c r="B657" s="5">
-        <f>IF(ISNA(VLOOKUP(H657,$A$2:$C$1040,3,1)),C657,VLOOKUP(H657,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H657,$A$2:$C$1041,3,1)),C657,VLOOKUP(H657,$A$2:$C$1041,3,1))</f>
         <v>113</v>
       </c>
       <c r="C657" s="1">
@@ -28597,7 +28606,7 @@
         <v>1857</v>
       </c>
       <c r="B658" s="5">
-        <f>IF(ISNA(VLOOKUP(H658,$A$2:$C$1040,3,1)),C658,VLOOKUP(H658,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H658,$A$2:$C$1041,3,1)),C658,VLOOKUP(H658,$A$2:$C$1041,3,1))</f>
         <v>127</v>
       </c>
       <c r="C658" s="1">
@@ -28630,7 +28639,7 @@
         <v>1859</v>
       </c>
       <c r="B659" s="5">
-        <f>IF(ISNA(VLOOKUP(H659,$A$2:$C$1040,3,1)),C659,VLOOKUP(H659,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H659,$A$2:$C$1041,3,1)),C659,VLOOKUP(H659,$A$2:$C$1041,3,1))</f>
         <v>153</v>
       </c>
       <c r="C659" s="1">
@@ -28663,7 +28672,7 @@
         <v>1862</v>
       </c>
       <c r="B660" s="5">
-        <f>IF(ISNA(VLOOKUP(H660,$A$2:$C$1040,3,1)),C660,VLOOKUP(H660,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H660,$A$2:$C$1041,3,1)),C660,VLOOKUP(H660,$A$2:$C$1041,3,1))</f>
         <v>162</v>
       </c>
       <c r="C660" s="1">
@@ -28696,7 +28705,7 @@
         <v>1865</v>
       </c>
       <c r="B661" s="5">
-        <f>IF(ISNA(VLOOKUP(H661,$A$2:$C$1040,3,1)),C661,VLOOKUP(H661,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H661,$A$2:$C$1041,3,1)),C661,VLOOKUP(H661,$A$2:$C$1041,3,1))</f>
         <v>172</v>
       </c>
       <c r="C661" s="1">
@@ -28729,7 +28738,7 @@
         <v>1868</v>
       </c>
       <c r="B662" s="5">
-        <f>IF(ISNA(VLOOKUP(H662,$A$2:$C$1040,3,1)),C662,VLOOKUP(H662,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H662,$A$2:$C$1041,3,1)),C662,VLOOKUP(H662,$A$2:$C$1041,3,1))</f>
         <v>182</v>
       </c>
       <c r="C662" s="1">
@@ -28762,7 +28771,7 @@
         <v>1871</v>
       </c>
       <c r="B663" s="5">
-        <f>IF(ISNA(VLOOKUP(H663,$A$2:$C$1040,3,1)),C663,VLOOKUP(H663,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H663,$A$2:$C$1041,3,1)),C663,VLOOKUP(H663,$A$2:$C$1041,3,1))</f>
         <v>206</v>
       </c>
       <c r="C663" s="1">
@@ -28795,7 +28804,7 @@
         <v>1874</v>
       </c>
       <c r="B664" s="5">
-        <f>IF(ISNA(VLOOKUP(H664,$A$2:$C$1040,3,1)),C664,VLOOKUP(H664,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H664,$A$2:$C$1041,3,1)),C664,VLOOKUP(H664,$A$2:$C$1041,3,1))</f>
         <v>214</v>
       </c>
       <c r="C664" s="1">
@@ -28828,7 +28837,7 @@
         <v>1877</v>
       </c>
       <c r="B665" s="5">
-        <f>IF(ISNA(VLOOKUP(H665,$A$2:$C$1040,3,1)),C665,VLOOKUP(H665,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H665,$A$2:$C$1041,3,1)),C665,VLOOKUP(H665,$A$2:$C$1041,3,1))</f>
         <v>221</v>
       </c>
       <c r="C665" s="1">
@@ -28861,7 +28870,7 @@
         <v>1880</v>
       </c>
       <c r="B666" s="5">
-        <f>IF(ISNA(VLOOKUP(H666,$A$2:$C$1040,3,1)),C666,VLOOKUP(H666,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H666,$A$2:$C$1041,3,1)),C666,VLOOKUP(H666,$A$2:$C$1041,3,1))</f>
         <v>234</v>
       </c>
       <c r="C666" s="1">
@@ -28894,7 +28903,7 @@
         <v>1883</v>
       </c>
       <c r="B667" s="5">
-        <f>IF(ISNA(VLOOKUP(H667,$A$2:$C$1040,3,1)),C667,VLOOKUP(H667,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H667,$A$2:$C$1041,3,1)),C667,VLOOKUP(H667,$A$2:$C$1041,3,1))</f>
         <v>241</v>
       </c>
       <c r="C667" s="1">
@@ -28927,7 +28936,7 @@
         <v>1886</v>
       </c>
       <c r="B668" s="5">
-        <f>IF(ISNA(VLOOKUP(H668,$A$2:$C$1040,3,1)),C668,VLOOKUP(H668,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H668,$A$2:$C$1041,3,1)),C668,VLOOKUP(H668,$A$2:$C$1041,3,1))</f>
         <v>255</v>
       </c>
       <c r="C668" s="1">
@@ -28960,7 +28969,7 @@
         <v>1889</v>
       </c>
       <c r="B669" s="5">
-        <f>IF(ISNA(VLOOKUP(H669,$A$2:$C$1040,3,1)),C669,VLOOKUP(H669,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H669,$A$2:$C$1041,3,1)),C669,VLOOKUP(H669,$A$2:$C$1041,3,1))</f>
         <v>280</v>
       </c>
       <c r="C669" s="1">
@@ -28993,7 +29002,7 @@
         <v>1892</v>
       </c>
       <c r="B670" s="5">
-        <f>IF(ISNA(VLOOKUP(H670,$A$2:$C$1040,3,1)),C670,VLOOKUP(H670,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H670,$A$2:$C$1041,3,1)),C670,VLOOKUP(H670,$A$2:$C$1041,3,1))</f>
         <v>287</v>
       </c>
       <c r="C670" s="1">
@@ -29026,7 +29035,7 @@
         <v>1895</v>
       </c>
       <c r="B671" s="5">
-        <f>IF(ISNA(VLOOKUP(H671,$A$2:$C$1040,3,1)),C671,VLOOKUP(H671,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H671,$A$2:$C$1041,3,1)),C671,VLOOKUP(H671,$A$2:$C$1041,3,1))</f>
         <v>294</v>
       </c>
       <c r="C671" s="1">
@@ -29059,7 +29068,7 @@
         <v>1898</v>
       </c>
       <c r="B672" s="5">
-        <f>IF(ISNA(VLOOKUP(H672,$A$2:$C$1040,3,1)),C672,VLOOKUP(H672,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H672,$A$2:$C$1041,3,1)),C672,VLOOKUP(H672,$A$2:$C$1041,3,1))</f>
         <v>306</v>
       </c>
       <c r="C672" s="1">
@@ -29092,7 +29101,7 @@
         <v>1901</v>
       </c>
       <c r="B673" s="5">
-        <f>IF(ISNA(VLOOKUP(H673,$A$2:$C$1040,3,1)),C673,VLOOKUP(H673,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H673,$A$2:$C$1041,3,1)),C673,VLOOKUP(H673,$A$2:$C$1041,3,1))</f>
         <v>319</v>
       </c>
       <c r="C673" s="1">
@@ -29125,7 +29134,7 @@
         <v>1904</v>
       </c>
       <c r="B674" s="5">
-        <f>IF(ISNA(VLOOKUP(H674,$A$2:$C$1040,3,1)),C674,VLOOKUP(H674,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H674,$A$2:$C$1041,3,1)),C674,VLOOKUP(H674,$A$2:$C$1041,3,1))</f>
         <v>333</v>
       </c>
       <c r="C674" s="1">
@@ -29158,7 +29167,7 @@
         <v>1907</v>
       </c>
       <c r="B675" s="5">
-        <f>IF(ISNA(VLOOKUP(H675,$A$2:$C$1040,3,1)),C675,VLOOKUP(H675,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H675,$A$2:$C$1041,3,1)),C675,VLOOKUP(H675,$A$2:$C$1041,3,1))</f>
         <v>359</v>
       </c>
       <c r="C675" s="1">
@@ -29191,7 +29200,7 @@
         <v>1910</v>
       </c>
       <c r="B676" s="5">
-        <f>IF(ISNA(VLOOKUP(H676,$A$2:$C$1040,3,1)),C676,VLOOKUP(H676,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H676,$A$2:$C$1041,3,1)),C676,VLOOKUP(H676,$A$2:$C$1041,3,1))</f>
         <v>367</v>
       </c>
       <c r="C676" s="1">
@@ -29224,7 +29233,7 @@
         <v>1913</v>
       </c>
       <c r="B677" s="5">
-        <f>IF(ISNA(VLOOKUP(H677,$A$2:$C$1040,3,1)),C677,VLOOKUP(H677,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H677,$A$2:$C$1041,3,1)),C677,VLOOKUP(H677,$A$2:$C$1041,3,1))</f>
         <v>376</v>
       </c>
       <c r="C677" s="1">
@@ -29257,7 +29266,7 @@
         <v>1916</v>
       </c>
       <c r="B678" s="5">
-        <f>IF(ISNA(VLOOKUP(H678,$A$2:$C$1040,3,1)),C678,VLOOKUP(H678,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H678,$A$2:$C$1041,3,1)),C678,VLOOKUP(H678,$A$2:$C$1041,3,1))</f>
         <v>387</v>
       </c>
       <c r="C678" s="1">
@@ -29290,7 +29299,7 @@
         <v>1919</v>
       </c>
       <c r="B679" s="5">
-        <f>IF(ISNA(VLOOKUP(H679,$A$2:$C$1040,3,1)),C679,VLOOKUP(H679,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H679,$A$2:$C$1041,3,1)),C679,VLOOKUP(H679,$A$2:$C$1041,3,1))</f>
         <v>402</v>
       </c>
       <c r="C679" s="1">
@@ -29323,7 +29332,7 @@
         <v>2003</v>
       </c>
       <c r="B680" s="5">
-        <f>IF(ISNA(VLOOKUP(H680,$A$2:$C$1040,3,1)),C680,VLOOKUP(H680,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H680,$A$2:$C$1041,3,1)),C680,VLOOKUP(H680,$A$2:$C$1041,3,1))</f>
         <v>11</v>
       </c>
       <c r="C680" s="1">
@@ -29353,61 +29362,61 @@
     </row>
     <row r="681" spans="1:9" ht="17" customHeight="1">
       <c r="A681" s="1" t="s">
-        <v>1922</v>
+        <v>2114</v>
       </c>
       <c r="B681" s="5">
-        <f>IF(ISNA(VLOOKUP(H681,$A$2:$C$1040,3,1)),C681,VLOOKUP(H681,$A$2:$C$1040,3,1))</f>
-        <v>652</v>
+        <f>IF(ISNA(VLOOKUP(H681,$A$2:$C$1041,3,1)),C681,VLOOKUP(H681,$A$2:$C$1041,3,1))</f>
+        <v>690</v>
       </c>
       <c r="C681" s="1">
-        <v>664</v>
+        <v>696</v>
       </c>
       <c r="D681" s="2" t="s">
-        <v>1923</v>
+        <v>2115</v>
       </c>
       <c r="E681" s="2" t="s">
-        <v>1924</v>
+        <v>2065</v>
       </c>
       <c r="F681" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A681,3,4)))</f>
-        <v>▢</v>
+        <v>▒</v>
       </c>
       <c r="G681" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A681,3,4)))</f>
-        <v>▢</v>
-      </c>
-      <c r="H681" s="17" t="s">
-        <v>1483</v>
+        <v>▒</v>
+      </c>
+      <c r="H681" s="21" t="s">
+        <v>1522</v>
       </c>
       <c r="I681" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H681,3,4)))</f>
-        <v>⎙</v>
+        <v>␡</v>
       </c>
     </row>
     <row r="682" spans="1:9" ht="17" customHeight="1">
       <c r="A682" s="1" t="s">
-        <v>1925</v>
+        <v>1922</v>
       </c>
       <c r="B682" s="5">
-        <f>IF(ISNA(VLOOKUP(H682,$A$2:$C$1040,3,1)),C682,VLOOKUP(H682,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H682,$A$2:$C$1041,3,1)),C682,VLOOKUP(H682,$A$2:$C$1041,3,1))</f>
         <v>652</v>
       </c>
       <c r="C682" s="1">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D682" s="2" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
       <c r="E682" s="2" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
       <c r="F682" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A682,3,4)))</f>
-        <v>▦</v>
+        <v>▢</v>
       </c>
       <c r="G682" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A682,3,4)))</f>
-        <v>▦</v>
+        <v>▢</v>
       </c>
       <c r="H682" s="17" t="s">
         <v>1483</v>
@@ -29419,61 +29428,61 @@
     </row>
     <row r="683" spans="1:9" ht="17" customHeight="1">
       <c r="A683" s="1" t="s">
-        <v>2064</v>
+        <v>1925</v>
       </c>
       <c r="B683" s="5">
-        <f>IF(ISNA(VLOOKUP(H683,$A$2:$C$1040,3,1)),C683,VLOOKUP(H683,$A$2:$C$1040,3,1))</f>
-        <v>690</v>
+        <f>IF(ISNA(VLOOKUP(H683,$A$2:$C$1041,3,1)),C683,VLOOKUP(H683,$A$2:$C$1041,3,1))</f>
+        <v>652</v>
       </c>
       <c r="C683" s="1">
-        <v>699</v>
+        <v>665</v>
       </c>
       <c r="D683" s="2" t="s">
-        <v>2072</v>
+        <v>1926</v>
       </c>
       <c r="E683" s="2" t="s">
-        <v>2069</v>
+        <v>1927</v>
       </c>
       <c r="F683" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A683,3,4)))</f>
-        <v>▪</v>
+        <v>▦</v>
       </c>
       <c r="G683" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A683,3,4)))</f>
-        <v>▪</v>
-      </c>
-      <c r="H683" s="21" t="s">
-        <v>1522</v>
+        <v>▦</v>
+      </c>
+      <c r="H683" s="17" t="s">
+        <v>1483</v>
       </c>
       <c r="I683" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H683,3,4)))</f>
-        <v>␡</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="684" spans="1:9" ht="17" customHeight="1">
-      <c r="A684" s="22" t="s">
-        <v>2061</v>
+      <c r="A684" s="1" t="s">
+        <v>2064</v>
       </c>
       <c r="B684" s="5">
-        <f>IF(ISNA(VLOOKUP(H684,$A$2:$C$1040,3,1)),C684,VLOOKUP(H684,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H684,$A$2:$C$1041,3,1)),C684,VLOOKUP(H684,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C684" s="1">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D684" s="2" t="s">
-        <v>2109</v>
+        <v>2072</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="F684" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A684,3,4)))</f>
-        <v>▶</v>
+        <v>▪</v>
       </c>
       <c r="G684" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A684,3,4)))</f>
-        <v>▶</v>
+        <v>▪</v>
       </c>
       <c r="H684" s="21" t="s">
         <v>1522</v>
@@ -29485,28 +29494,28 @@
     </row>
     <row r="685" spans="1:9" ht="17" customHeight="1">
       <c r="A685" s="22" t="s">
-        <v>2083</v>
+        <v>2061</v>
       </c>
       <c r="B685" s="5">
-        <f>IF(ISNA(VLOOKUP(H685,$A$2:$C$1040,3,1)),C685,VLOOKUP(H685,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H685,$A$2:$C$1041,3,1)),C685,VLOOKUP(H685,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C685" s="1">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="D685" s="2" t="s">
-        <v>2093</v>
+        <v>2109</v>
       </c>
       <c r="E685" s="2" t="s">
-        <v>2103</v>
+        <v>2066</v>
       </c>
       <c r="F685" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A685,3,4)))</f>
-        <v>▷</v>
+        <v>▶</v>
       </c>
       <c r="G685" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A685,3,4)))</f>
-        <v>▷</v>
+        <v>▶</v>
       </c>
       <c r="H685" s="21" t="s">
         <v>1522</v>
@@ -29518,28 +29527,28 @@
     </row>
     <row r="686" spans="1:9" ht="17" customHeight="1">
       <c r="A686" s="22" t="s">
-        <v>2107</v>
+        <v>2083</v>
       </c>
       <c r="B686" s="5">
-        <f>IF(ISNA(VLOOKUP(H686,$A$2:$C$1040,3,1)),C686,VLOOKUP(H686,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H686,$A$2:$C$1041,3,1)),C686,VLOOKUP(H686,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C686" s="1">
         <v>710</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>2110</v>
+        <v>2093</v>
       </c>
       <c r="E686" s="2" t="s">
-        <v>2112</v>
+        <v>2103</v>
       </c>
       <c r="F686" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A686,3,4)))</f>
-        <v>▸</v>
+        <v>▷</v>
       </c>
       <c r="G686" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A686,3,4)))</f>
-        <v>▸</v>
+        <v>▷</v>
       </c>
       <c r="H686" s="21" t="s">
         <v>1522</v>
@@ -29551,28 +29560,28 @@
     </row>
     <row r="687" spans="1:9" ht="17" customHeight="1">
       <c r="A687" s="22" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="B687" s="5">
-        <f>IF(ISNA(VLOOKUP(H687,$A$2:$C$1040,3,1)),C687,VLOOKUP(H687,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H687,$A$2:$C$1041,3,1)),C687,VLOOKUP(H687,$A$2:$C$1041,3,1))</f>
         <v>690</v>
       </c>
       <c r="C687" s="1">
         <v>711</v>
       </c>
       <c r="D687" s="2" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="E687" s="2" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="F687" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A687,3,4)))</f>
-        <v>▹</v>
+        <v>▸</v>
       </c>
       <c r="G687" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A687,3,4)))</f>
-        <v>▹</v>
+        <v>▸</v>
       </c>
       <c r="H687" s="21" t="s">
         <v>1522</v>
@@ -29583,62 +29592,62 @@
       </c>
     </row>
     <row r="688" spans="1:9" ht="17" customHeight="1">
-      <c r="A688" s="1" t="s">
-        <v>2008</v>
+      <c r="A688" s="22" t="s">
+        <v>2108</v>
       </c>
       <c r="B688" s="5">
-        <f>IF(ISNA(VLOOKUP(H688,$A$2:$C$1040,3,1)),C688,VLOOKUP(H688,$A$2:$C$1040,3,1))</f>
-        <v>668</v>
+        <f>IF(ISNA(VLOOKUP(H688,$A$2:$C$1041,3,1)),C688,VLOOKUP(H688,$A$2:$C$1041,3,1))</f>
+        <v>690</v>
       </c>
       <c r="C688" s="1">
-        <v>670</v>
+        <v>712</v>
       </c>
       <c r="D688" s="2" t="s">
-        <v>2014</v>
+        <v>2111</v>
       </c>
       <c r="E688" s="2" t="s">
-        <v>2020</v>
+        <v>2113</v>
       </c>
       <c r="F688" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A688,3,4)))</f>
-        <v>◇</v>
+        <v>▹</v>
       </c>
       <c r="G688" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A688,3,4)))</f>
-        <v>◇</v>
-      </c>
-      <c r="H688" s="18" t="s">
-        <v>2006</v>
+        <v>▹</v>
+      </c>
+      <c r="H688" s="21" t="s">
+        <v>1522</v>
       </c>
       <c r="I688" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H688,3,4)))</f>
-        <v>◯</v>
+        <v>␡</v>
       </c>
     </row>
     <row r="689" spans="1:9" ht="17" customHeight="1">
       <c r="A689" s="1" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B689" s="5">
-        <f>IF(ISNA(VLOOKUP(H689,$A$2:$C$1040,3,1)),C689,VLOOKUP(H689,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H689,$A$2:$C$1041,3,1)),C689,VLOOKUP(H689,$A$2:$C$1041,3,1))</f>
         <v>668</v>
       </c>
       <c r="C689" s="1">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D689" s="2" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E689" s="2" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F689" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A689,3,4)))</f>
-        <v>◈</v>
+        <v>◇</v>
       </c>
       <c r="G689" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A689,3,4)))</f>
-        <v>◈</v>
+        <v>◇</v>
       </c>
       <c r="H689" s="18" t="s">
         <v>2006</v>
@@ -29649,62 +29658,62 @@
       </c>
     </row>
     <row r="690" spans="1:9" ht="17" customHeight="1">
-      <c r="A690" s="22" t="s">
-        <v>2042</v>
+      <c r="A690" s="1" t="s">
+        <v>2009</v>
       </c>
       <c r="B690" s="5">
-        <f>IF(ISNA(VLOOKUP(H690,$A$2:$C$1040,3,1)),C690,VLOOKUP(H690,$A$2:$C$1040,3,1))</f>
-        <v>509</v>
+        <f>IF(ISNA(VLOOKUP(H690,$A$2:$C$1041,3,1)),C690,VLOOKUP(H690,$A$2:$C$1041,3,1))</f>
+        <v>668</v>
       </c>
       <c r="C690" s="1">
-        <v>515</v>
+        <v>671</v>
       </c>
       <c r="D690" s="2" t="s">
-        <v>2046</v>
+        <v>2015</v>
       </c>
       <c r="E690" s="2" t="s">
-        <v>2048</v>
+        <v>2021</v>
       </c>
       <c r="F690" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A690,3,4)))</f>
-        <v>◭</v>
+        <v>◈</v>
       </c>
       <c r="G690" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A690,3,4)))</f>
-        <v>◭</v>
-      </c>
-      <c r="H690" s="1" t="s">
-        <v>1554</v>
+        <v>◈</v>
+      </c>
+      <c r="H690" s="18" t="s">
+        <v>2006</v>
       </c>
       <c r="I690" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H690,3,4)))</f>
-        <v>␰</v>
+        <v>◯</v>
       </c>
     </row>
     <row r="691" spans="1:9" ht="17" customHeight="1">
       <c r="A691" s="22" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B691" s="5">
-        <f>IF(ISNA(VLOOKUP(H691,$A$2:$C$1040,3,1)),C691,VLOOKUP(H691,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H691,$A$2:$C$1041,3,1)),C691,VLOOKUP(H691,$A$2:$C$1041,3,1))</f>
         <v>509</v>
       </c>
       <c r="C691" s="1">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D691" s="2" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="E691" s="2" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="F691" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A691,3,4)))</f>
-        <v>◮</v>
+        <v>◭</v>
       </c>
       <c r="G691" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A691,3,4)))</f>
-        <v>◮</v>
+        <v>◭</v>
       </c>
       <c r="H691" s="1" t="s">
         <v>1554</v>
@@ -29715,62 +29724,62 @@
       </c>
     </row>
     <row r="692" spans="1:9" ht="17" customHeight="1">
-      <c r="A692" s="1" t="s">
-        <v>2006</v>
+      <c r="A692" s="22" t="s">
+        <v>2043</v>
       </c>
       <c r="B692" s="5">
-        <f>IF(ISNA(VLOOKUP(H692,$A$2:$C$1040,3,1)),C692,VLOOKUP(H692,$A$2:$C$1040,3,1))</f>
-        <v>668</v>
+        <f>IF(ISNA(VLOOKUP(H692,$A$2:$C$1041,3,1)),C692,VLOOKUP(H692,$A$2:$C$1041,3,1))</f>
+        <v>509</v>
       </c>
       <c r="C692" s="1">
-        <v>668</v>
+        <v>516</v>
       </c>
       <c r="D692" s="2" t="s">
-        <v>2012</v>
+        <v>2047</v>
       </c>
       <c r="E692" s="2" t="s">
-        <v>2018</v>
+        <v>2049</v>
       </c>
       <c r="F692" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A692,3,4)))</f>
-        <v>◯</v>
+        <v>◮</v>
       </c>
       <c r="G692" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A692,3,4)))</f>
-        <v>◯</v>
-      </c>
-      <c r="H692" s="18" t="s">
-        <v>2006</v>
+        <v>◮</v>
+      </c>
+      <c r="H692" s="1" t="s">
+        <v>1554</v>
       </c>
       <c r="I692" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H692,3,4)))</f>
-        <v>◯</v>
+        <v>␰</v>
       </c>
     </row>
     <row r="693" spans="1:9" ht="17" customHeight="1">
       <c r="A693" s="1" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B693" s="5">
-        <f>IF(ISNA(VLOOKUP(H693,$A$2:$C$1040,3,1)),C693,VLOOKUP(H693,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H693,$A$2:$C$1041,3,1)),C693,VLOOKUP(H693,$A$2:$C$1041,3,1))</f>
         <v>668</v>
       </c>
       <c r="C693" s="1">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D693" s="2" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E693" s="2" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F693" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A693,3,4)))</f>
-        <v>☐</v>
+        <v>◯</v>
       </c>
       <c r="G693" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A693,3,4)))</f>
-        <v>☐</v>
+        <v>◯</v>
       </c>
       <c r="H693" s="18" t="s">
         <v>2006</v>
@@ -29782,28 +29791,28 @@
     </row>
     <row r="694" spans="1:9" ht="17" customHeight="1">
       <c r="A694" s="1" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B694" s="5">
-        <f>IF(ISNA(VLOOKUP(H694,$A$2:$C$1040,3,1)),C694,VLOOKUP(H694,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H694,$A$2:$C$1041,3,1)),C694,VLOOKUP(H694,$A$2:$C$1041,3,1))</f>
         <v>668</v>
       </c>
       <c r="C694" s="1">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D694" s="2" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E694" s="2" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F694" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A694,3,4)))</f>
-        <v>☒</v>
+        <v>☐</v>
       </c>
       <c r="G694" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A694,3,4)))</f>
-        <v>☒</v>
+        <v>☐</v>
       </c>
       <c r="H694" s="18" t="s">
         <v>2006</v>
@@ -29815,523 +29824,523 @@
     </row>
     <row r="695" spans="1:9" ht="17" customHeight="1">
       <c r="A695" s="1" t="s">
-        <v>1928</v>
+        <v>2005</v>
       </c>
       <c r="B695" s="5">
-        <f>IF(ISNA(VLOOKUP(H695,$A$2:$C$1040,3,1)),C695,VLOOKUP(H695,$A$2:$C$1040,3,1))</f>
-        <v>652</v>
+        <f>IF(ISNA(VLOOKUP(H695,$A$2:$C$1041,3,1)),C695,VLOOKUP(H695,$A$2:$C$1041,3,1))</f>
+        <v>668</v>
       </c>
       <c r="C695" s="1">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="D695" s="2" t="s">
-        <v>1929</v>
+        <v>2011</v>
       </c>
       <c r="E695" s="2" t="s">
-        <v>1930</v>
+        <v>2017</v>
       </c>
       <c r="F695" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A695,3,4)))</f>
-        <v>♺</v>
+        <v>☒</v>
       </c>
       <c r="G695" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A695,3,4)))</f>
-        <v>♺</v>
-      </c>
-      <c r="H695" s="17" t="s">
-        <v>1483</v>
+        <v>☒</v>
+      </c>
+      <c r="H695" s="18" t="s">
+        <v>2006</v>
       </c>
       <c r="I695" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H695,3,4)))</f>
-        <v>⎙</v>
+        <v>◯</v>
       </c>
     </row>
     <row r="696" spans="1:9" ht="17" customHeight="1">
       <c r="A696" s="1" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
       <c r="B696" s="5">
-        <f>IF(ISNA(VLOOKUP(H696,$A$2:$C$1040,3,1)),C696,VLOOKUP(H696,$A$2:$C$1040,3,1))</f>
-        <v>98</v>
+        <f>IF(ISNA(VLOOKUP(H696,$A$2:$C$1041,3,1)),C696,VLOOKUP(H696,$A$2:$C$1041,3,1))</f>
+        <v>652</v>
       </c>
       <c r="C696" s="1">
-        <v>112</v>
+        <v>662</v>
       </c>
       <c r="D696" s="2" t="s">
-        <v>1932</v>
+        <v>1929</v>
       </c>
       <c r="E696" s="2" t="s">
-        <v>1933</v>
+        <v>1930</v>
       </c>
       <c r="F696" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A696,3,4)))</f>
-        <v>♻</v>
+        <v>♺</v>
       </c>
       <c r="G696" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A696,3,4)))</f>
-        <v>♻</v>
-      </c>
-      <c r="H696" s="1" t="s">
-        <v>126</v>
+        <v>♺</v>
+      </c>
+      <c r="H696" s="17" t="s">
+        <v>1483</v>
       </c>
       <c r="I696" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H696,3,4)))</f>
-        <v>C</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="697" spans="1:9" ht="17" customHeight="1">
       <c r="A697" s="1" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
       <c r="B697" s="5">
-        <f>IF(ISNA(VLOOKUP(H697,$A$2:$C$1040,3,1)),C697,VLOOKUP(H697,$A$2:$C$1040,3,1))</f>
-        <v>241</v>
+        <f>IF(ISNA(VLOOKUP(H697,$A$2:$C$1041,3,1)),C697,VLOOKUP(H697,$A$2:$C$1041,3,1))</f>
+        <v>98</v>
       </c>
       <c r="C697" s="1">
-        <v>254</v>
+        <v>112</v>
       </c>
       <c r="D697" s="2" t="s">
-        <v>1935</v>
+        <v>1932</v>
       </c>
       <c r="E697" s="2" t="s">
-        <v>1936</v>
+        <v>1933</v>
       </c>
       <c r="F697" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A697,3,4)))</f>
-        <v>♾</v>
+        <v>♻</v>
       </c>
       <c r="G697" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A697,3,4)))</f>
-        <v>♾</v>
+        <v>♻</v>
       </c>
       <c r="H697" s="1" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="I697" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H697,3,4)))</f>
-        <v>N</v>
+        <v>C</v>
       </c>
     </row>
     <row r="698" spans="1:9" ht="17" customHeight="1">
       <c r="A698" s="1" t="s">
-        <v>1937</v>
+        <v>1934</v>
       </c>
       <c r="B698" s="5">
-        <f>IF(ISNA(VLOOKUP(H698,$A$2:$C$1040,3,1)),C698,VLOOKUP(H698,$A$2:$C$1040,3,1))</f>
-        <v>694</v>
+        <f>IF(ISNA(VLOOKUP(H698,$A$2:$C$1041,3,1)),C698,VLOOKUP(H698,$A$2:$C$1041,3,1))</f>
+        <v>241</v>
       </c>
       <c r="C698" s="1">
-        <v>694</v>
+        <v>254</v>
       </c>
       <c r="D698" s="2" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
       <c r="E698" s="2" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
       <c r="F698" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A698,3,4)))</f>
-        <v>✓</v>
+        <v>♾</v>
       </c>
       <c r="G698" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A698,3,4)))</f>
-        <v>✓</v>
+        <v>♾</v>
       </c>
       <c r="H698" s="1" t="s">
-        <v>1937</v>
+        <v>159</v>
       </c>
       <c r="I698" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H698,3,4)))</f>
-        <v>✓</v>
+        <v>N</v>
       </c>
     </row>
     <row r="699" spans="1:9" ht="17" customHeight="1">
       <c r="A699" s="1" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
       <c r="B699" s="5">
-        <f>IF(ISNA(VLOOKUP(H699,$A$2:$C$1040,3,1)),C699,VLOOKUP(H699,$A$2:$C$1040,3,1))</f>
-        <v>538</v>
+        <f>IF(ISNA(VLOOKUP(H699,$A$2:$C$1041,3,1)),C699,VLOOKUP(H699,$A$2:$C$1041,3,1))</f>
+        <v>694</v>
       </c>
       <c r="C699" s="1">
-        <v>540</v>
+        <v>694</v>
       </c>
       <c r="D699" s="2" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="E699" s="2" t="s">
-        <v>1942</v>
+        <v>1939</v>
       </c>
       <c r="F699" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A699,3,4)))</f>
-        <v>➈</v>
+        <v>✓</v>
       </c>
       <c r="G699" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A699,3,4)))</f>
-        <v>➈</v>
+        <v>✓</v>
       </c>
       <c r="H699" s="1" t="s">
-        <v>51</v>
+        <v>1937</v>
       </c>
       <c r="I699" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H699,3,4)))</f>
-        <v>,</v>
+        <v>✓</v>
       </c>
     </row>
     <row r="700" spans="1:9" ht="17" customHeight="1">
       <c r="A700" s="1" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
       <c r="B700" s="5">
-        <f>IF(ISNA(VLOOKUP(H700,$A$2:$C$1040,3,1)),C700,VLOOKUP(H700,$A$2:$C$1040,3,1))</f>
-        <v>541</v>
+        <f>IF(ISNA(VLOOKUP(H700,$A$2:$C$1041,3,1)),C700,VLOOKUP(H700,$A$2:$C$1041,3,1))</f>
+        <v>538</v>
       </c>
       <c r="C700" s="1">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D700" s="2" t="s">
-        <v>1944</v>
+        <v>1941</v>
       </c>
       <c r="E700" s="2" t="s">
-        <v>1945</v>
+        <v>1942</v>
       </c>
       <c r="F700" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A700,3,4)))</f>
-        <v>➉</v>
+        <v>➈</v>
       </c>
       <c r="G700" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A700,3,4)))</f>
-        <v>➉</v>
+        <v>➈</v>
       </c>
       <c r="H700" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I700" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H700,3,4)))</f>
-        <v>.</v>
+        <v>,</v>
       </c>
     </row>
     <row r="701" spans="1:9" ht="17" customHeight="1">
       <c r="A701" s="1" t="s">
-        <v>2007</v>
+        <v>1943</v>
       </c>
       <c r="B701" s="5">
-        <f>IF(ISNA(VLOOKUP(H701,$A$2:$C$1040,3,1)),C701,VLOOKUP(H701,$A$2:$C$1040,3,1))</f>
-        <v>668</v>
+        <f>IF(ISNA(VLOOKUP(H701,$A$2:$C$1041,3,1)),C701,VLOOKUP(H701,$A$2:$C$1041,3,1))</f>
+        <v>541</v>
       </c>
       <c r="C701" s="1">
-        <v>669</v>
+        <v>544</v>
       </c>
       <c r="D701" s="2" t="s">
-        <v>2013</v>
+        <v>1944</v>
       </c>
       <c r="E701" s="2" t="s">
-        <v>2019</v>
+        <v>1945</v>
       </c>
       <c r="F701" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A701,3,4)))</f>
-        <v>⦿</v>
+        <v>➉</v>
       </c>
       <c r="G701" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A701,3,4)))</f>
-        <v>⦿</v>
-      </c>
-      <c r="H701" s="18" t="s">
-        <v>2006</v>
+        <v>➉</v>
+      </c>
+      <c r="H701" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="I701" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H701,3,4)))</f>
-        <v>◯</v>
+        <v>.</v>
       </c>
     </row>
     <row r="702" spans="1:9" ht="17" customHeight="1">
       <c r="A702" s="1" t="s">
-        <v>1946</v>
+        <v>2007</v>
       </c>
       <c r="B702" s="5">
-        <f>IF(ISNA(VLOOKUP(H702,$A$2:$C$1040,3,1)),C702,VLOOKUP(H702,$A$2:$C$1040,3,1))</f>
-        <v>652</v>
+        <f>IF(ISNA(VLOOKUP(H702,$A$2:$C$1041,3,1)),C702,VLOOKUP(H702,$A$2:$C$1041,3,1))</f>
+        <v>668</v>
       </c>
       <c r="C702" s="1">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="D702" s="2" t="s">
-        <v>1947</v>
+        <v>2013</v>
       </c>
       <c r="E702" s="2" t="s">
-        <v>1486</v>
+        <v>2019</v>
       </c>
       <c r="F702" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A702,3,4)))</f>
-        <v>⧖</v>
+        <v>⦿</v>
       </c>
       <c r="G702" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A702,3,4)))</f>
-        <v>⧖</v>
-      </c>
-      <c r="H702" s="17" t="s">
-        <v>1483</v>
+        <v>⦿</v>
+      </c>
+      <c r="H702" s="18" t="s">
+        <v>2006</v>
       </c>
       <c r="I702" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H702,3,4)))</f>
-        <v>⎙</v>
+        <v>◯</v>
       </c>
     </row>
     <row r="703" spans="1:9" ht="17" customHeight="1">
       <c r="A703" s="1" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="B703" s="5">
-        <f>IF(ISNA(VLOOKUP(H703,$A$2:$C$1040,3,1)),C703,VLOOKUP(H703,$A$2:$C$1040,3,1))</f>
-        <v>387</v>
+        <f>IF(ISNA(VLOOKUP(H703,$A$2:$C$1041,3,1)),C703,VLOOKUP(H703,$A$2:$C$1041,3,1))</f>
+        <v>652</v>
       </c>
       <c r="C703" s="1">
-        <v>401</v>
+        <v>654</v>
       </c>
       <c r="D703" s="2" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="E703" s="2" t="s">
-        <v>1950</v>
+        <v>1486</v>
       </c>
       <c r="F703" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A703,3,4)))</f>
-        <v>⧰</v>
+        <v>⧖</v>
       </c>
       <c r="G703" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A703,3,4)))</f>
-        <v>⧰</v>
-      </c>
-      <c r="H703" s="1" t="s">
-        <v>192</v>
+        <v>⧖</v>
+      </c>
+      <c r="H703" s="17" t="s">
+        <v>1483</v>
       </c>
       <c r="I703" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H703,3,4)))</f>
-        <v>Y</v>
+        <v>⎙</v>
       </c>
     </row>
     <row r="704" spans="1:9" ht="17" customHeight="1">
       <c r="A704" s="1" t="s">
-        <v>1951</v>
+        <v>1948</v>
       </c>
       <c r="B704" s="5">
-        <f>IF(ISNA(VLOOKUP(H704,$A$2:$C$1040,3,1)),C704,VLOOKUP(H704,$A$2:$C$1040,3,1))</f>
-        <v>153</v>
+        <f>IF(ISNA(VLOOKUP(H704,$A$2:$C$1041,3,1)),C704,VLOOKUP(H704,$A$2:$C$1041,3,1))</f>
+        <v>387</v>
       </c>
       <c r="C704" s="1">
-        <v>161</v>
+        <v>401</v>
       </c>
       <c r="D704" s="2" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="E704" s="2" t="s">
-        <v>1953</v>
+        <v>1950</v>
       </c>
       <c r="F704" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A704,3,4)))</f>
-        <v>⧱</v>
+        <v>⧰</v>
       </c>
       <c r="G704" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A704,3,4)))</f>
-        <v>⧱</v>
+        <v>⧰</v>
       </c>
       <c r="H704" s="1" t="s">
-        <v>135</v>
+        <v>192</v>
       </c>
       <c r="I704" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H704,3,4)))</f>
-        <v>F</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="705" spans="1:11" ht="17" customHeight="1">
       <c r="A705" s="1" t="s">
-        <v>1954</v>
+        <v>1951</v>
       </c>
       <c r="B705" s="5">
-        <f>IF(ISNA(VLOOKUP(H705,$A$2:$C$1040,3,1)),C705,VLOOKUP(H705,$A$2:$C$1040,3,1))</f>
-        <v>578</v>
+        <f>IF(ISNA(VLOOKUP(H705,$A$2:$C$1041,3,1)),C705,VLOOKUP(H705,$A$2:$C$1041,3,1))</f>
+        <v>153</v>
       </c>
       <c r="C705" s="1">
-        <v>580</v>
+        <v>161</v>
       </c>
       <c r="D705" s="2" t="s">
-        <v>1955</v>
+        <v>1952</v>
       </c>
       <c r="E705" s="2" t="s">
-        <v>1956</v>
+        <v>1953</v>
       </c>
       <c r="F705" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A705,3,4)))</f>
-        <v>⭠</v>
+        <v>⧱</v>
       </c>
       <c r="G705" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A705,3,4)))</f>
-        <v>⭠</v>
+        <v>⧱</v>
       </c>
       <c r="H705" s="1" t="s">
-        <v>1228</v>
+        <v>135</v>
       </c>
       <c r="I705" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H705,3,4)))</f>
-        <v>←</v>
+        <v>F</v>
       </c>
     </row>
     <row r="706" spans="1:11" ht="17" customHeight="1">
       <c r="A706" s="1" t="s">
-        <v>1957</v>
+        <v>1954</v>
       </c>
       <c r="B706" s="5">
-        <f>IF(ISNA(VLOOKUP(H706,$A$2:$C$1040,3,1)),C706,VLOOKUP(H706,$A$2:$C$1040,3,1))</f>
-        <v>583</v>
+        <f>IF(ISNA(VLOOKUP(H706,$A$2:$C$1041,3,1)),C706,VLOOKUP(H706,$A$2:$C$1041,3,1))</f>
+        <v>578</v>
       </c>
       <c r="C706" s="1">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D706" s="2" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
       <c r="E706" s="2" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="F706" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A706,3,4)))</f>
-        <v>⭡</v>
+        <v>⭠</v>
       </c>
       <c r="G706" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A706,3,4)))</f>
-        <v>⭡</v>
+        <v>⭠</v>
       </c>
       <c r="H706" s="1" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="I706" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H706,3,4)))</f>
-        <v>↑</v>
+        <v>←</v>
       </c>
     </row>
     <row r="707" spans="1:11" ht="17" customHeight="1">
       <c r="A707" s="1" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
       <c r="B707" s="5">
-        <f>IF(ISNA(VLOOKUP(H707,$A$2:$C$1040,3,1)),C707,VLOOKUP(H707,$A$2:$C$1040,3,1))</f>
-        <v>573</v>
+        <f>IF(ISNA(VLOOKUP(H707,$A$2:$C$1041,3,1)),C707,VLOOKUP(H707,$A$2:$C$1041,3,1))</f>
+        <v>583</v>
       </c>
       <c r="C707" s="1">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="D707" s="2" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
       <c r="E707" s="2" t="s">
-        <v>1962</v>
+        <v>1959</v>
       </c>
       <c r="F707" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A707,3,4)))</f>
-        <v>⭢</v>
+        <v>⭡</v>
       </c>
       <c r="G707" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A707,3,4)))</f>
-        <v>⭢</v>
+        <v>⭡</v>
       </c>
       <c r="H707" s="1" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="I707" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H707,3,4)))</f>
-        <v>→</v>
+        <v>↑</v>
       </c>
     </row>
     <row r="708" spans="1:11" ht="17" customHeight="1">
       <c r="A708" s="1" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="B708" s="5">
-        <f>IF(ISNA(VLOOKUP(H708,$A$2:$C$1040,3,1)),C708,VLOOKUP(H708,$A$2:$C$1040,3,1))</f>
-        <v>589</v>
+        <f>IF(ISNA(VLOOKUP(H708,$A$2:$C$1041,3,1)),C708,VLOOKUP(H708,$A$2:$C$1041,3,1))</f>
+        <v>573</v>
       </c>
       <c r="C708" s="1">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="D708" s="2" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="E708" s="2" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="F708" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A708,3,4)))</f>
-        <v>⭣</v>
+        <v>⭢</v>
       </c>
       <c r="G708" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A708,3,4)))</f>
-        <v>⭣</v>
+        <v>⭢</v>
       </c>
       <c r="H708" s="1" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="I708" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H708,3,4)))</f>
-        <v>↓</v>
+        <v>→</v>
       </c>
     </row>
     <row r="709" spans="1:11" ht="17" customHeight="1">
       <c r="A709" s="1" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="B709" s="5">
-        <f>IF(ISNA(VLOOKUP(H709,$A$2:$C$1040,3,1)),C709,VLOOKUP(H709,$A$2:$C$1040,3,1))</f>
-        <v>462</v>
+        <f>IF(ISNA(VLOOKUP(H709,$A$2:$C$1041,3,1)),C709,VLOOKUP(H709,$A$2:$C$1041,3,1))</f>
+        <v>589</v>
       </c>
       <c r="C709" s="1">
-        <v>465</v>
+        <v>591</v>
       </c>
       <c r="D709" s="2" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="E709" s="2" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="F709" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A709,3,4)))</f>
-        <v>Ɽ</v>
+        <v>⭣</v>
       </c>
       <c r="G709" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A709,3,4)))</f>
-        <v>Ɽ</v>
+        <v>⭣</v>
       </c>
       <c r="H709" s="1" t="s">
-        <v>881</v>
+        <v>1237</v>
       </c>
       <c r="I709" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H709,3,4)))</f>
-        <v>Π</v>
+        <v>↓</v>
       </c>
     </row>
     <row r="710" spans="1:11" ht="17" customHeight="1">
       <c r="A710" s="1" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="B710" s="5">
-        <f>IF(ISNA(VLOOKUP(H710,$A$2:$C$1040,3,1)),C710,VLOOKUP(H710,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H710,$A$2:$C$1041,3,1)),C710,VLOOKUP(H710,$A$2:$C$1041,3,1))</f>
         <v>462</v>
       </c>
       <c r="C710" s="1">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D710" s="2" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="E710" s="2" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="F710" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A710,3,4)))</f>
-        <v>ⱥ</v>
+        <v>Ɽ</v>
       </c>
       <c r="G710" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A710,3,4)))</f>
-        <v>ⱥ</v>
+        <v>Ɽ</v>
       </c>
       <c r="H710" s="1" t="s">
         <v>881</v>
@@ -30343,28 +30352,28 @@
     </row>
     <row r="711" spans="1:11" ht="17" customHeight="1">
       <c r="A711" s="1" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="B711" s="5">
-        <f>IF(ISNA(VLOOKUP(H711,$A$2:$C$1040,3,1)),C711,VLOOKUP(H711,$A$2:$C$1040,3,1))</f>
+        <f>IF(ISNA(VLOOKUP(H711,$A$2:$C$1041,3,1)),C711,VLOOKUP(H711,$A$2:$C$1041,3,1))</f>
         <v>462</v>
       </c>
       <c r="C711" s="1">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="E711" s="2" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="F711" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A711,3,4)))</f>
-        <v>ⱦ</v>
+        <v>ⱥ</v>
       </c>
       <c r="G711" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A711,3,4)))</f>
-        <v>ⱦ</v>
+        <v>ⱥ</v>
       </c>
       <c r="H711" s="1" t="s">
         <v>881</v>
@@ -30376,63 +30385,93 @@
     </row>
     <row r="712" spans="1:11" ht="17" customHeight="1">
       <c r="A712" s="1" t="s">
-        <v>1286</v>
+        <v>1972</v>
       </c>
       <c r="B712" s="5">
-        <f>IF(ISNA(VLOOKUP(H712,$A$2:$C$1040,3,1)),C712,VLOOKUP(H712,$A$2:$C$1040,3,1))</f>
-        <v>675</v>
+        <f>IF(ISNA(VLOOKUP(H712,$A$2:$C$1041,3,1)),C712,VLOOKUP(H712,$A$2:$C$1041,3,1))</f>
+        <v>462</v>
       </c>
       <c r="C712" s="1">
-        <v>675</v>
+        <v>467</v>
       </c>
       <c r="D712" s="2" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="E712" s="2" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="F712" s="5" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A712,3,4)))</f>
-        <v>Ɐ</v>
+        <v>ⱦ</v>
       </c>
       <c r="G712" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(A712,3,4)))</f>
-        <v>Ɐ</v>
-      </c>
-      <c r="H712" s="20" t="s">
-        <v>1286</v>
+        <v>ⱦ</v>
+      </c>
+      <c r="H712" s="1" t="s">
+        <v>881</v>
       </c>
       <c r="I712" s="6" t="str">
         <f>_xlfn.UNICHAR(HEX2DEC(MID(H712,3,4)))</f>
-        <v>Ɐ</v>
+        <v>Π</v>
       </c>
     </row>
     <row r="713" spans="1:11" ht="17" customHeight="1">
       <c r="A713" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B713" s="5">
+        <f>IF(ISNA(VLOOKUP(H713,$A$2:$C$1041,3,1)),C713,VLOOKUP(H713,$A$2:$C$1041,3,1))</f>
+        <v>675</v>
+      </c>
+      <c r="C713" s="1">
+        <v>675</v>
+      </c>
+      <c r="D713" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="E713" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F713" s="5" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A713,3,4)))</f>
+        <v>Ɐ</v>
+      </c>
+      <c r="G713" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(A713,3,4)))</f>
+        <v>Ɐ</v>
+      </c>
+      <c r="H713" s="20" t="s">
+        <v>1286</v>
+      </c>
+      <c r="I713" s="6" t="str">
+        <f>_xlfn.UNICHAR(HEX2DEC(MID(H713,3,4)))</f>
+        <v>Ɐ</v>
+      </c>
+    </row>
+    <row r="714" spans="1:11" ht="17" customHeight="1">
+      <c r="A714" s="1" t="s">
         <v>1977</v>
       </c>
-      <c r="B713" s="5">
-        <f>IF(ISNA(VLOOKUP(H713,$A$2:$C$1040,3,1)),C713,VLOOKUP(H713,$A$2:$C$1040,3,1))</f>
+      <c r="B714" s="5">
+        <f>IF(ISNA(VLOOKUP(H714,$A$2:$C$1041,3,1)),C714,VLOOKUP(H714,$A$2:$C$1041,3,1))</f>
         <v>9999</v>
       </c>
-      <c r="C713" s="1">
+      <c r="C714" s="1">
         <v>9999</v>
       </c>
-      <c r="D713" s="2" t="s">
+      <c r="D714" s="2" t="s">
         <v>1978</v>
       </c>
-      <c r="E713" s="2" t="s">
+      <c r="E714" s="2" t="s">
         <v>1979</v>
       </c>
-    </row>
-    <row r="717" spans="1:11" customFormat="1" ht="17" customHeight="1">
-      <c r="K717" s="2"/>
     </row>
     <row r="718" spans="1:11" customFormat="1" ht="17" customHeight="1">
       <c r="K718" s="2"/>
     </row>
-    <row r="723" spans="11:11" customFormat="1" ht="17" customHeight="1">
-      <c r="K723" s="2"/>
+    <row r="719" spans="1:11" customFormat="1" ht="17" customHeight="1">
+      <c r="K719" s="2"/>
     </row>
     <row r="724" spans="11:11" customFormat="1" ht="17" customHeight="1">
       <c r="K724" s="2"/>
@@ -30494,9 +30533,12 @@
     <row r="743" spans="11:11" customFormat="1" ht="17" customHeight="1">
       <c r="K743" s="2"/>
     </row>
+    <row r="744" spans="11:11" customFormat="1" ht="17" customHeight="1">
+      <c r="K744" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I713">
-    <sortCondition ref="A2:A713"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I745">
+    <sortCondition ref="A2:A745"/>
   </sortState>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
